--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -219,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -319,6 +319,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -708,7 +714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AT96"/>
+  <dimension ref="A1:AT101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2847,7 +2853,7 @@
       <c r="C64" s="5" t="n"/>
       <c r="D64" s="26" t="inlineStr">
         <is>
-          <t>TRAÇO</t>
+          <t>TRAÇO · até 9</t>
         </is>
       </c>
       <c r="V64" s="5" t="n"/>
@@ -2856,7 +2862,7 @@
       <c r="Y64" s="5" t="n"/>
       <c r="Z64" s="26" t="inlineStr">
         <is>
-          <t>COMANDO</t>
+          <t>COMANDO · até 6</t>
         </is>
       </c>
       <c r="AR64" s="5" t="n"/>
@@ -2987,46 +2993,28 @@
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="5" t="n"/>
-      <c r="D69" s="5" t="n"/>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="n"/>
-      <c r="I69" s="5" t="n"/>
-      <c r="J69" s="5" t="n"/>
-      <c r="K69" s="5" t="n"/>
-      <c r="L69" s="5" t="n"/>
-      <c r="M69" s="5" t="n"/>
-      <c r="N69" s="5" t="n"/>
-      <c r="O69" s="5" t="n"/>
-      <c r="P69" s="5" t="n"/>
-      <c r="Q69" s="5" t="n"/>
-      <c r="R69" s="5" t="n"/>
-      <c r="S69" s="5" t="n"/>
-      <c r="T69" s="5" t="n"/>
-      <c r="U69" s="5" t="n"/>
+      <c r="D69" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q69" s="28">
+        <f>IFERROR(VLOOKUP($D$69,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+        <v/>
+      </c>
       <c r="V69" s="5" t="n"/>
       <c r="W69" s="5" t="n"/>
       <c r="X69" s="5" t="n"/>
       <c r="Y69" s="5" t="n"/>
-      <c r="Z69" s="5" t="n"/>
-      <c r="AA69" s="5" t="n"/>
-      <c r="AB69" s="5" t="n"/>
-      <c r="AC69" s="5" t="n"/>
-      <c r="AD69" s="5" t="n"/>
-      <c r="AE69" s="5" t="n"/>
-      <c r="AF69" s="5" t="n"/>
-      <c r="AG69" s="5" t="n"/>
-      <c r="AH69" s="5" t="n"/>
-      <c r="AI69" s="5" t="n"/>
-      <c r="AJ69" s="5" t="n"/>
-      <c r="AK69" s="5" t="n"/>
-      <c r="AL69" s="5" t="n"/>
-      <c r="AM69" s="5" t="n"/>
-      <c r="AN69" s="5" t="n"/>
-      <c r="AO69" s="5" t="n"/>
-      <c r="AP69" s="5" t="n"/>
-      <c r="AQ69" s="5" t="n"/>
+      <c r="Z69" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM69" s="28">
+        <f>IFERROR(VLOOKUP($Z$69,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+        <v/>
+      </c>
       <c r="AR69" s="5" t="n"/>
       <c r="AS69" s="5" t="n"/>
       <c r="AT69" s="5" t="n"/>
@@ -3035,87 +3023,123 @@
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="5" t="n"/>
-      <c r="D70" s="8" t="inlineStr">
-        <is>
-          <t>GASTO</t>
-        </is>
-      </c>
-      <c r="K70" s="5" t="n"/>
-      <c r="L70" s="8" t="inlineStr">
-        <is>
-          <t>SOBRA</t>
-        </is>
-      </c>
-      <c r="S70" s="5" t="n"/>
-      <c r="T70" s="8" t="inlineStr">
-        <is>
-          <t>O QUE ELE NÃO COMPRA A PREÇO NENHUM</t>
-        </is>
-      </c>
+      <c r="D70" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q70" s="30">
+        <f>IFERROR(VLOOKUP($D$70,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="V70" s="5" t="n"/>
+      <c r="W70" s="5" t="n"/>
+      <c r="X70" s="5" t="n"/>
+      <c r="Y70" s="5" t="n"/>
+      <c r="Z70" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AM70" s="30">
+        <f>IFERROR(VLOOKUP($Z$70,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="AR70" s="5" t="n"/>
+      <c r="AS70" s="5" t="n"/>
+      <c r="AT70" s="5" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="5" t="n"/>
-      <c r="D71" s="24">
-        <f>$Q$65+$Q$66+$Q$67+$Q$68+$AM$65+$AM$66+$AM$67+$AM$68</f>
+      <c r="D71" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q71" s="28">
+        <f>IFERROR(VLOOKUP($D$71,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="31">
-        <f>IF($D$61-($Q$65+$Q$66+$Q$67+$Q$68+$AM$65+$AM$66+$AM$67+$AM$68)&lt;0,"estourou "&amp;(($Q$65+$Q$66+$Q$67+$Q$68+$AM$65+$AM$66+$AM$67+$AM$68)-$D$61),$D$61-($Q$65+$Q$66+$Q$67+$Q$68+$AM$65+$AM$66+$AM$67+$AM$68))</f>
-        <v/>
-      </c>
-      <c r="S71" s="5" t="n"/>
-      <c r="T71" s="25" t="inlineStr">
-        <is>
-          <t>dado de dano · qualquer coisa que cresça com refino · atributo · Defesa, acerto ou vida direto</t>
-        </is>
-      </c>
+      <c r="V71" s="5" t="n"/>
+      <c r="W71" s="5" t="n"/>
+      <c r="X71" s="5" t="n"/>
+      <c r="Y71" s="5" t="n"/>
+      <c r="Z71" s="5" t="n"/>
+      <c r="AA71" s="5" t="n"/>
+      <c r="AB71" s="5" t="n"/>
+      <c r="AC71" s="5" t="n"/>
+      <c r="AD71" s="5" t="n"/>
+      <c r="AE71" s="5" t="n"/>
+      <c r="AF71" s="5" t="n"/>
+      <c r="AG71" s="5" t="n"/>
+      <c r="AH71" s="5" t="n"/>
+      <c r="AI71" s="5" t="n"/>
+      <c r="AJ71" s="5" t="n"/>
+      <c r="AK71" s="5" t="n"/>
+      <c r="AL71" s="5" t="n"/>
+      <c r="AM71" s="5" t="n"/>
+      <c r="AN71" s="5" t="n"/>
+      <c r="AO71" s="5" t="n"/>
+      <c r="AP71" s="5" t="n"/>
+      <c r="AQ71" s="5" t="n"/>
+      <c r="AR71" s="5" t="n"/>
+      <c r="AS71" s="5" t="n"/>
+      <c r="AT71" s="5" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="5" t="n"/>
-      <c r="D72" s="13" t="n"/>
-      <c r="E72" s="13" t="n"/>
-      <c r="F72" s="13" t="n"/>
-      <c r="G72" s="13" t="n"/>
-      <c r="H72" s="13" t="n"/>
-      <c r="I72" s="13" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="5" t="n"/>
-      <c r="L72" s="13" t="n"/>
-      <c r="M72" s="13" t="n"/>
-      <c r="N72" s="13" t="n"/>
-      <c r="O72" s="13" t="n"/>
-      <c r="P72" s="13" t="n"/>
-      <c r="Q72" s="13" t="n"/>
-      <c r="R72" s="13" t="n"/>
-      <c r="S72" s="5" t="n"/>
+      <c r="D72" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="30">
+        <f>IFERROR(VLOOKUP($D$72,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+        <v/>
+      </c>
+      <c r="V72" s="5" t="n"/>
+      <c r="W72" s="5" t="n"/>
+      <c r="X72" s="5" t="n"/>
+      <c r="Y72" s="5" t="n"/>
+      <c r="Z72" s="5" t="n"/>
+      <c r="AA72" s="5" t="n"/>
+      <c r="AB72" s="5" t="n"/>
+      <c r="AC72" s="5" t="n"/>
+      <c r="AD72" s="5" t="n"/>
+      <c r="AE72" s="5" t="n"/>
+      <c r="AF72" s="5" t="n"/>
+      <c r="AG72" s="5" t="n"/>
+      <c r="AH72" s="5" t="n"/>
+      <c r="AI72" s="5" t="n"/>
+      <c r="AJ72" s="5" t="n"/>
+      <c r="AK72" s="5" t="n"/>
+      <c r="AL72" s="5" t="n"/>
+      <c r="AM72" s="5" t="n"/>
+      <c r="AN72" s="5" t="n"/>
+      <c r="AO72" s="5" t="n"/>
+      <c r="AP72" s="5" t="n"/>
+      <c r="AQ72" s="5" t="n"/>
+      <c r="AR72" s="5" t="n"/>
+      <c r="AS72" s="5" t="n"/>
+      <c r="AT72" s="5" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="5" t="n"/>
-      <c r="D73" s="5" t="n"/>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
-      <c r="N73" s="5" t="n"/>
-      <c r="O73" s="5" t="n"/>
-      <c r="P73" s="5" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
-      <c r="S73" s="5" t="n"/>
-      <c r="T73" s="5" t="n"/>
-      <c r="U73" s="5" t="n"/>
+      <c r="D73" s="27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q73" s="28">
+        <f>IFERROR(VLOOKUP($D$73,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+        <v/>
+      </c>
       <c r="V73" s="5" t="n"/>
       <c r="W73" s="5" t="n"/>
       <c r="X73" s="5" t="n"/>
@@ -3146,150 +3170,138 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="5" t="n"/>
-      <c r="D74" s="14" t="inlineStr">
-        <is>
-          <t>o Servo monta com o orçamento da ficha mais metade, porque é um corpo só e não cinco. Todo orçamento é múltiplo de 4, então fecha redondo.</t>
-        </is>
-      </c>
+      <c r="D74" s="5" t="n"/>
+      <c r="E74" s="5" t="n"/>
+      <c r="F74" s="5" t="n"/>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
+      <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="5" t="n"/>
+      <c r="S74" s="5" t="n"/>
+      <c r="T74" s="5" t="n"/>
+      <c r="U74" s="5" t="n"/>
+      <c r="V74" s="5" t="n"/>
+      <c r="W74" s="5" t="n"/>
+      <c r="X74" s="5" t="n"/>
+      <c r="Y74" s="5" t="n"/>
+      <c r="Z74" s="5" t="n"/>
+      <c r="AA74" s="5" t="n"/>
+      <c r="AB74" s="5" t="n"/>
+      <c r="AC74" s="5" t="n"/>
+      <c r="AD74" s="5" t="n"/>
+      <c r="AE74" s="5" t="n"/>
+      <c r="AF74" s="5" t="n"/>
+      <c r="AG74" s="5" t="n"/>
+      <c r="AH74" s="5" t="n"/>
+      <c r="AI74" s="5" t="n"/>
+      <c r="AJ74" s="5" t="n"/>
+      <c r="AK74" s="5" t="n"/>
+      <c r="AL74" s="5" t="n"/>
+      <c r="AM74" s="5" t="n"/>
+      <c r="AN74" s="5" t="n"/>
+      <c r="AO74" s="5" t="n"/>
+      <c r="AP74" s="5" t="n"/>
+      <c r="AQ74" s="5" t="n"/>
+      <c r="AR74" s="5" t="n"/>
+      <c r="AS74" s="5" t="n"/>
+      <c r="AT74" s="5" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>GASTO</t>
+        </is>
+      </c>
       <c r="K75" s="5" t="n"/>
-      <c r="L75" s="5" t="n"/>
-      <c r="M75" s="5" t="n"/>
-      <c r="N75" s="5" t="n"/>
-      <c r="O75" s="5" t="n"/>
-      <c r="P75" s="5" t="n"/>
-      <c r="Q75" s="5" t="n"/>
-      <c r="R75" s="5" t="n"/>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>SOBRA</t>
+        </is>
+      </c>
       <c r="S75" s="5" t="n"/>
-      <c r="T75" s="5" t="n"/>
-      <c r="U75" s="5" t="n"/>
-      <c r="V75" s="5" t="n"/>
-      <c r="W75" s="5" t="n"/>
-      <c r="X75" s="5" t="n"/>
-      <c r="Y75" s="5" t="n"/>
-      <c r="Z75" s="5" t="n"/>
-      <c r="AA75" s="5" t="n"/>
-      <c r="AB75" s="5" t="n"/>
-      <c r="AC75" s="5" t="n"/>
-      <c r="AD75" s="5" t="n"/>
-      <c r="AE75" s="5" t="n"/>
-      <c r="AF75" s="5" t="n"/>
-      <c r="AG75" s="5" t="n"/>
-      <c r="AH75" s="5" t="n"/>
-      <c r="AI75" s="5" t="n"/>
-      <c r="AJ75" s="5" t="n"/>
-      <c r="AK75" s="5" t="n"/>
-      <c r="AL75" s="5" t="n"/>
-      <c r="AM75" s="5" t="n"/>
-      <c r="AN75" s="5" t="n"/>
-      <c r="AO75" s="5" t="n"/>
-      <c r="AP75" s="5" t="n"/>
-      <c r="AQ75" s="5" t="n"/>
-      <c r="AR75" s="5" t="n"/>
-      <c r="AS75" s="5" t="n"/>
-      <c r="AT75" s="5" t="n"/>
+      <c r="T75" s="8" t="inlineStr">
+        <is>
+          <t>O QUE ELE NÃO COMPRA A PREÇO NENHUM</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="5" t="n"/>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>INVESTIR — o ataque, e toda invocação tem</t>
-        </is>
-      </c>
-      <c r="AG76" s="5" t="n"/>
-      <c r="AH76" s="5" t="n"/>
-      <c r="AI76" s="5" t="n"/>
-      <c r="AJ76" s="5" t="n"/>
-      <c r="AK76" s="5" t="n"/>
-      <c r="AL76" s="5" t="n"/>
-      <c r="AM76" s="5" t="n"/>
-      <c r="AN76" s="5" t="n"/>
-      <c r="AO76" s="5" t="n"/>
-      <c r="AP76" s="5" t="n"/>
-      <c r="AQ76" s="5" t="n"/>
-      <c r="AR76" s="5" t="n"/>
-      <c r="AS76" s="5" t="n"/>
-      <c r="AT76" s="5" t="n"/>
+      <c r="D76" s="24">
+        <f>$Q$65+$Q$66+$Q$67+$Q$68+$Q$69+$Q$70+$Q$71+$Q$72+$Q$73+$AM$65+$AM$66+$AM$67+$AM$68+$AM$69+$AM$70</f>
+        <v/>
+      </c>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="31">
+        <f>IF($D$61-($Q$65+$Q$66+$Q$67+$Q$68+$Q$69+$Q$70+$Q$71+$Q$72+$Q$73+$AM$65+$AM$66+$AM$67+$AM$68+$AM$69+$AM$70)&lt;0,"estourou "&amp;(($Q$65+$Q$66+$Q$67+$Q$68+$Q$69+$Q$70+$Q$71+$Q$72+$Q$73+$AM$65+$AM$66+$AM$67+$AM$68+$AM$69+$AM$70)-$D$61),$D$61-($Q$65+$Q$66+$Q$67+$Q$68+$Q$69+$Q$70+$Q$71+$Q$72+$Q$73+$AM$65+$AM$66+$AM$67+$AM$68+$AM$69+$AM$70))</f>
+        <v/>
+      </c>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="25" t="inlineStr">
+        <is>
+          <t>dado de dano · qualquer coisa que cresça com refino · atributo · Defesa, acerto ou vida direto</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+      <c r="F77" s="13" t="n"/>
+      <c r="G77" s="13" t="n"/>
+      <c r="H77" s="13" t="n"/>
+      <c r="I77" s="13" t="n"/>
+      <c r="J77" s="13" t="n"/>
       <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
-      <c r="N77" s="5" t="n"/>
-      <c r="O77" s="5" t="n"/>
-      <c r="P77" s="5" t="n"/>
-      <c r="Q77" s="5" t="n"/>
-      <c r="R77" s="5" t="n"/>
+      <c r="L77" s="13" t="n"/>
+      <c r="M77" s="13" t="n"/>
+      <c r="N77" s="13" t="n"/>
+      <c r="O77" s="13" t="n"/>
+      <c r="P77" s="13" t="n"/>
+      <c r="Q77" s="13" t="n"/>
+      <c r="R77" s="13" t="n"/>
       <c r="S77" s="5" t="n"/>
-      <c r="T77" s="5" t="n"/>
-      <c r="U77" s="5" t="n"/>
-      <c r="V77" s="5" t="n"/>
-      <c r="W77" s="5" t="n"/>
-      <c r="X77" s="5" t="n"/>
-      <c r="Y77" s="5" t="n"/>
-      <c r="Z77" s="5" t="n"/>
-      <c r="AA77" s="5" t="n"/>
-      <c r="AB77" s="5" t="n"/>
-      <c r="AC77" s="5" t="n"/>
-      <c r="AD77" s="5" t="n"/>
-      <c r="AE77" s="5" t="n"/>
-      <c r="AF77" s="5" t="n"/>
-      <c r="AG77" s="5" t="n"/>
-      <c r="AH77" s="5" t="n"/>
-      <c r="AI77" s="5" t="n"/>
-      <c r="AJ77" s="5" t="n"/>
-      <c r="AK77" s="5" t="n"/>
-      <c r="AL77" s="5" t="n"/>
-      <c r="AM77" s="5" t="n"/>
-      <c r="AN77" s="5" t="n"/>
-      <c r="AO77" s="5" t="n"/>
-      <c r="AP77" s="5" t="n"/>
-      <c r="AQ77" s="5" t="n"/>
-      <c r="AR77" s="5" t="n"/>
-      <c r="AS77" s="5" t="n"/>
-      <c r="AT77" s="5" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="8" t="inlineStr">
-        <is>
-          <t>DANO DO INVESTIR</t>
-        </is>
-      </c>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
       <c r="L78" s="5" t="n"/>
       <c r="M78" s="5" t="n"/>
-      <c r="N78" s="8" t="inlineStr">
-        <is>
-          <t>POR CORPO</t>
-        </is>
-      </c>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="5" t="n"/>
+      <c r="U78" s="5" t="n"/>
+      <c r="V78" s="5" t="n"/>
+      <c r="W78" s="5" t="n"/>
+      <c r="X78" s="5" t="n"/>
       <c r="Y78" s="5" t="n"/>
       <c r="Z78" s="5" t="n"/>
       <c r="AA78" s="5" t="n"/>
@@ -3317,45 +3329,24 @@
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="5" t="n"/>
-      <c r="D79" s="22">
-        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AA$14="Matilha",3,2),TRUE))</f>
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n"/>
-      <c r="M79" s="5" t="n"/>
-      <c r="N79" s="32">
-        <f>IF($AA$14="Matilha","cada um dos cinco rola isto",IF($AA$14="","","o corpo em campo rola isto"))</f>
-        <v/>
-      </c>
-      <c r="AE79" s="5" t="n"/>
-      <c r="AF79" s="5" t="n"/>
-      <c r="AG79" s="5" t="n"/>
-      <c r="AH79" s="5" t="n"/>
-      <c r="AI79" s="5" t="n"/>
-      <c r="AJ79" s="5" t="n"/>
-      <c r="AK79" s="5" t="n"/>
-      <c r="AL79" s="5" t="n"/>
-      <c r="AM79" s="5" t="n"/>
-      <c r="AN79" s="5" t="n"/>
-      <c r="AO79" s="5" t="n"/>
-      <c r="AP79" s="5" t="n"/>
-      <c r="AQ79" s="5" t="n"/>
-      <c r="AR79" s="5" t="n"/>
-      <c r="AS79" s="5" t="n"/>
-      <c r="AT79" s="5" t="n"/>
+      <c r="D79" s="14" t="inlineStr">
+        <is>
+          <t>o Servo monta com o orçamento da ficha mais metade, porque é um corpo só e não cinco. Todo orçamento é múltiplo de 4, então fecha redondo.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="5" t="n"/>
-      <c r="D80" s="13" t="n"/>
-      <c r="E80" s="13" t="n"/>
-      <c r="F80" s="13" t="n"/>
-      <c r="G80" s="13" t="n"/>
-      <c r="H80" s="13" t="n"/>
-      <c r="I80" s="13" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="13" t="n"/>
+      <c r="D80" s="5" t="n"/>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="n"/>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="n"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="n"/>
+      <c r="K80" s="5" t="n"/>
       <c r="L80" s="5" t="n"/>
       <c r="M80" s="5" t="n"/>
       <c r="N80" s="5" t="n"/>
@@ -3396,19 +3387,35 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="5" t="n"/>
-      <c r="D81" s="14" t="inlineStr">
-        <is>
-          <t>você e todas as suas invocações somados entregam uma Rotina. O número de dados sempre desce — a soma nunca passa do que você faria sozinho.</t>
-        </is>
-      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIR — o ataque, e toda invocação tem</t>
+        </is>
+      </c>
+      <c r="AG81" s="5" t="n"/>
+      <c r="AH81" s="5" t="n"/>
+      <c r="AI81" s="5" t="n"/>
+      <c r="AJ81" s="5" t="n"/>
+      <c r="AK81" s="5" t="n"/>
+      <c r="AL81" s="5" t="n"/>
+      <c r="AM81" s="5" t="n"/>
+      <c r="AN81" s="5" t="n"/>
+      <c r="AO81" s="5" t="n"/>
+      <c r="AP81" s="5" t="n"/>
+      <c r="AQ81" s="5" t="n"/>
+      <c r="AR81" s="5" t="n"/>
+      <c r="AS81" s="5" t="n"/>
+      <c r="AT81" s="5" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="5" t="n"/>
-      <c r="D82" s="5" t="n"/>
-      <c r="E82" s="5" t="n"/>
-      <c r="F82" s="5" t="n"/>
       <c r="G82" s="5" t="n"/>
       <c r="H82" s="5" t="n"/>
       <c r="I82" s="5" t="n"/>
@@ -3454,16 +3461,24 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="5" t="n"/>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>NA MESA — o que não muda</t>
-        </is>
-      </c>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>DANO DO INVESTIR</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="8" t="inlineStr">
+        <is>
+          <t>POR CORPO</t>
+        </is>
+      </c>
+      <c r="Y83" s="5" t="n"/>
+      <c r="Z83" s="5" t="n"/>
+      <c r="AA83" s="5" t="n"/>
+      <c r="AB83" s="5" t="n"/>
+      <c r="AC83" s="5" t="n"/>
+      <c r="AD83" s="5" t="n"/>
       <c r="AE83" s="5" t="n"/>
       <c r="AF83" s="5" t="n"/>
       <c r="AG83" s="5" t="n"/>
@@ -3485,30 +3500,16 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
-      <c r="K84" s="5" t="n"/>
+      <c r="D84" s="22">
+        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AA$14="Matilha",3,2),TRUE))</f>
+        <v/>
+      </c>
       <c r="L84" s="5" t="n"/>
       <c r="M84" s="5" t="n"/>
-      <c r="N84" s="5" t="n"/>
-      <c r="O84" s="5" t="n"/>
-      <c r="P84" s="5" t="n"/>
-      <c r="Q84" s="5" t="n"/>
-      <c r="R84" s="5" t="n"/>
-      <c r="S84" s="5" t="n"/>
-      <c r="T84" s="5" t="n"/>
-      <c r="U84" s="5" t="n"/>
-      <c r="V84" s="5" t="n"/>
-      <c r="W84" s="5" t="n"/>
-      <c r="X84" s="5" t="n"/>
-      <c r="Y84" s="5" t="n"/>
-      <c r="Z84" s="5" t="n"/>
-      <c r="AA84" s="5" t="n"/>
-      <c r="AB84" s="5" t="n"/>
-      <c r="AC84" s="5" t="n"/>
-      <c r="AD84" s="5" t="n"/>
+      <c r="N84" s="32">
+        <f>IF($AA$14="Matilha","cada um dos cinco rola isto",IF($AA$14="","","o corpo em campo rola isto"))</f>
+        <v/>
+      </c>
       <c r="AE84" s="5" t="n"/>
       <c r="AF84" s="5" t="n"/>
       <c r="AG84" s="5" t="n"/>
@@ -3530,246 +3531,315 @@
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="5" t="n"/>
-      <c r="D85" s="33" t="inlineStr">
-        <is>
-          <t>invocar</t>
-        </is>
-      </c>
-      <c r="M85" s="34">
-        <f>("custa "&amp;$AM$7&amp;" PE e a Ação Padrão")</f>
-        <v/>
-      </c>
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="13" t="n"/>
+      <c r="G85" s="13" t="n"/>
+      <c r="H85" s="13" t="n"/>
+      <c r="I85" s="13" t="n"/>
+      <c r="J85" s="13" t="n"/>
+      <c r="K85" s="13" t="n"/>
+      <c r="L85" s="5" t="n"/>
+      <c r="M85" s="5" t="n"/>
+      <c r="N85" s="5" t="n"/>
+      <c r="O85" s="5" t="n"/>
+      <c r="P85" s="5" t="n"/>
+      <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="5" t="n"/>
+      <c r="S85" s="5" t="n"/>
+      <c r="T85" s="5" t="n"/>
+      <c r="U85" s="5" t="n"/>
+      <c r="V85" s="5" t="n"/>
+      <c r="W85" s="5" t="n"/>
+      <c r="X85" s="5" t="n"/>
+      <c r="Y85" s="5" t="n"/>
+      <c r="Z85" s="5" t="n"/>
+      <c r="AA85" s="5" t="n"/>
+      <c r="AB85" s="5" t="n"/>
+      <c r="AC85" s="5" t="n"/>
+      <c r="AD85" s="5" t="n"/>
+      <c r="AE85" s="5" t="n"/>
+      <c r="AF85" s="5" t="n"/>
+      <c r="AG85" s="5" t="n"/>
+      <c r="AH85" s="5" t="n"/>
+      <c r="AI85" s="5" t="n"/>
+      <c r="AJ85" s="5" t="n"/>
+      <c r="AK85" s="5" t="n"/>
+      <c r="AL85" s="5" t="n"/>
+      <c r="AM85" s="5" t="n"/>
+      <c r="AN85" s="5" t="n"/>
+      <c r="AO85" s="5" t="n"/>
+      <c r="AP85" s="5" t="n"/>
+      <c r="AQ85" s="5" t="n"/>
+      <c r="AR85" s="5" t="n"/>
+      <c r="AS85" s="5" t="n"/>
+      <c r="AT85" s="5" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="5" t="n"/>
-      <c r="D86" s="35" t="inlineStr">
-        <is>
-          <t>comandar</t>
-        </is>
-      </c>
-      <c r="M86" s="36">
-        <f>"a Ação Padrão, toda rodada"</f>
-        <v/>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>você e todas as suas invocações somados entregam uma Rotina. O número de dados sempre desce — a soma nunca passa do que você faria sozinho.</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="5" t="n"/>
-      <c r="D87" s="33" t="inlineStr">
-        <is>
-          <t>iniciativa</t>
-        </is>
-      </c>
-      <c r="M87" s="34">
-        <f>"a sua, e ela age logo depois de você"</f>
-        <v/>
-      </c>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="n"/>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="5" t="n"/>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
+      <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="5" t="n"/>
+      <c r="S87" s="5" t="n"/>
+      <c r="T87" s="5" t="n"/>
+      <c r="U87" s="5" t="n"/>
+      <c r="V87" s="5" t="n"/>
+      <c r="W87" s="5" t="n"/>
+      <c r="X87" s="5" t="n"/>
+      <c r="Y87" s="5" t="n"/>
+      <c r="Z87" s="5" t="n"/>
+      <c r="AA87" s="5" t="n"/>
+      <c r="AB87" s="5" t="n"/>
+      <c r="AC87" s="5" t="n"/>
+      <c r="AD87" s="5" t="n"/>
+      <c r="AE87" s="5" t="n"/>
+      <c r="AF87" s="5" t="n"/>
+      <c r="AG87" s="5" t="n"/>
+      <c r="AH87" s="5" t="n"/>
+      <c r="AI87" s="5" t="n"/>
+      <c r="AJ87" s="5" t="n"/>
+      <c r="AK87" s="5" t="n"/>
+      <c r="AL87" s="5" t="n"/>
+      <c r="AM87" s="5" t="n"/>
+      <c r="AN87" s="5" t="n"/>
+      <c r="AO87" s="5" t="n"/>
+      <c r="AP87" s="5" t="n"/>
+      <c r="AQ87" s="5" t="n"/>
+      <c r="AR87" s="5" t="n"/>
+      <c r="AS87" s="5" t="n"/>
+      <c r="AT87" s="5" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="35" t="inlineStr">
-        <is>
-          <t>deslocamento</t>
-        </is>
-      </c>
-      <c r="M88" s="36">
-        <f>(9&amp;" metros")</f>
-        <v/>
-      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>NA MESA — o que não muda</t>
+        </is>
+      </c>
+      <c r="AE88" s="5" t="n"/>
+      <c r="AF88" s="5" t="n"/>
+      <c r="AG88" s="5" t="n"/>
+      <c r="AH88" s="5" t="n"/>
+      <c r="AI88" s="5" t="n"/>
+      <c r="AJ88" s="5" t="n"/>
+      <c r="AK88" s="5" t="n"/>
+      <c r="AL88" s="5" t="n"/>
+      <c r="AM88" s="5" t="n"/>
+      <c r="AN88" s="5" t="n"/>
+      <c r="AO88" s="5" t="n"/>
+      <c r="AP88" s="5" t="n"/>
+      <c r="AQ88" s="5" t="n"/>
+      <c r="AR88" s="5" t="n"/>
+      <c r="AS88" s="5" t="n"/>
+      <c r="AT88" s="5" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="5" t="n"/>
-      <c r="D89" s="33" t="inlineStr">
-        <is>
-          <t>amarra</t>
-        </is>
-      </c>
-      <c r="M89" s="34">
-        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
-        <v/>
-      </c>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+      <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="5" t="n"/>
+      <c r="U89" s="5" t="n"/>
+      <c r="V89" s="5" t="n"/>
+      <c r="W89" s="5" t="n"/>
+      <c r="X89" s="5" t="n"/>
+      <c r="Y89" s="5" t="n"/>
+      <c r="Z89" s="5" t="n"/>
+      <c r="AA89" s="5" t="n"/>
+      <c r="AB89" s="5" t="n"/>
+      <c r="AC89" s="5" t="n"/>
+      <c r="AD89" s="5" t="n"/>
+      <c r="AE89" s="5" t="n"/>
+      <c r="AF89" s="5" t="n"/>
+      <c r="AG89" s="5" t="n"/>
+      <c r="AH89" s="5" t="n"/>
+      <c r="AI89" s="5" t="n"/>
+      <c r="AJ89" s="5" t="n"/>
+      <c r="AK89" s="5" t="n"/>
+      <c r="AL89" s="5" t="n"/>
+      <c r="AM89" s="5" t="n"/>
+      <c r="AN89" s="5" t="n"/>
+      <c r="AO89" s="5" t="n"/>
+      <c r="AP89" s="5" t="n"/>
+      <c r="AQ89" s="5" t="n"/>
+      <c r="AR89" s="5" t="n"/>
+      <c r="AS89" s="5" t="n"/>
+      <c r="AT89" s="5" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
-      <c r="E90" s="5" t="n"/>
-      <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
-      <c r="H90" s="5" t="n"/>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="5" t="n"/>
-      <c r="K90" s="5" t="n"/>
-      <c r="L90" s="5" t="n"/>
-      <c r="M90" s="5" t="n"/>
-      <c r="N90" s="5" t="n"/>
-      <c r="O90" s="5" t="n"/>
-      <c r="P90" s="5" t="n"/>
-      <c r="Q90" s="5" t="n"/>
-      <c r="R90" s="5" t="n"/>
-      <c r="S90" s="5" t="n"/>
-      <c r="T90" s="5" t="n"/>
-      <c r="U90" s="5" t="n"/>
-      <c r="V90" s="5" t="n"/>
-      <c r="W90" s="5" t="n"/>
-      <c r="X90" s="5" t="n"/>
-      <c r="Y90" s="5" t="n"/>
-      <c r="Z90" s="5" t="n"/>
-      <c r="AA90" s="5" t="n"/>
-      <c r="AB90" s="5" t="n"/>
-      <c r="AC90" s="5" t="n"/>
-      <c r="AD90" s="5" t="n"/>
-      <c r="AE90" s="5" t="n"/>
-      <c r="AF90" s="5" t="n"/>
-      <c r="AG90" s="5" t="n"/>
-      <c r="AH90" s="5" t="n"/>
-      <c r="AI90" s="5" t="n"/>
-      <c r="AJ90" s="5" t="n"/>
-      <c r="AK90" s="5" t="n"/>
-      <c r="AL90" s="5" t="n"/>
-      <c r="AM90" s="5" t="n"/>
-      <c r="AN90" s="5" t="n"/>
-      <c r="AO90" s="5" t="n"/>
-      <c r="AP90" s="5" t="n"/>
-      <c r="AQ90" s="5" t="n"/>
-      <c r="AR90" s="5" t="n"/>
-      <c r="AS90" s="5" t="n"/>
-      <c r="AT90" s="5" t="n"/>
+      <c r="D90" s="33" t="inlineStr">
+        <is>
+          <t>invocar</t>
+        </is>
+      </c>
+      <c r="M90" s="34">
+        <f>("custa "&amp;$AM$7&amp;" PE e a Ação Padrão")</f>
+        <v/>
+      </c>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="5" t="n"/>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>O QUE ESTA FICHA NÃO CALCULA, E POR QUÊ</t>
-        </is>
-      </c>
-      <c r="AK91" s="5" t="n"/>
-      <c r="AL91" s="5" t="n"/>
-      <c r="AM91" s="5" t="n"/>
-      <c r="AN91" s="5" t="n"/>
-      <c r="AO91" s="5" t="n"/>
-      <c r="AP91" s="5" t="n"/>
-      <c r="AQ91" s="5" t="n"/>
-      <c r="AR91" s="5" t="n"/>
-      <c r="AS91" s="5" t="n"/>
-      <c r="AT91" s="5" t="n"/>
+      <c r="D91" s="35" t="inlineStr">
+        <is>
+          <t>comandar</t>
+        </is>
+      </c>
+      <c r="M91" s="36">
+        <f>"a Ação Padrão, toda rodada"</f>
+        <v/>
+      </c>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
-      <c r="N92" s="5" t="n"/>
-      <c r="O92" s="5" t="n"/>
-      <c r="P92" s="5" t="n"/>
-      <c r="Q92" s="5" t="n"/>
-      <c r="R92" s="5" t="n"/>
-      <c r="S92" s="5" t="n"/>
-      <c r="T92" s="5" t="n"/>
-      <c r="U92" s="5" t="n"/>
-      <c r="V92" s="5" t="n"/>
-      <c r="W92" s="5" t="n"/>
-      <c r="X92" s="5" t="n"/>
-      <c r="Y92" s="5" t="n"/>
-      <c r="Z92" s="5" t="n"/>
-      <c r="AA92" s="5" t="n"/>
-      <c r="AB92" s="5" t="n"/>
-      <c r="AC92" s="5" t="n"/>
-      <c r="AD92" s="5" t="n"/>
-      <c r="AE92" s="5" t="n"/>
-      <c r="AF92" s="5" t="n"/>
-      <c r="AG92" s="5" t="n"/>
-      <c r="AH92" s="5" t="n"/>
-      <c r="AI92" s="5" t="n"/>
-      <c r="AJ92" s="5" t="n"/>
-      <c r="AK92" s="5" t="n"/>
-      <c r="AL92" s="5" t="n"/>
-      <c r="AM92" s="5" t="n"/>
-      <c r="AN92" s="5" t="n"/>
-      <c r="AO92" s="5" t="n"/>
-      <c r="AP92" s="5" t="n"/>
-      <c r="AQ92" s="5" t="n"/>
-      <c r="AR92" s="5" t="n"/>
-      <c r="AS92" s="5" t="n"/>
-      <c r="AT92" s="5" t="n"/>
+      <c r="D92" s="33" t="inlineStr">
+        <is>
+          <t>iniciativa</t>
+        </is>
+      </c>
+      <c r="M92" s="34">
+        <f>"a sua, e ela age logo depois de você"</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
-      <c r="D93" s="37" t="inlineStr">
+      <c r="D93" s="35" t="inlineStr">
+        <is>
+          <t>deslocamento</t>
+        </is>
+      </c>
+      <c r="M93" s="36">
+        <f>(9&amp;" metros")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="D94" s="33" t="inlineStr">
+        <is>
+          <t>amarra</t>
+        </is>
+      </c>
+      <c r="M94" s="34">
+        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="D96" s="37" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="G96" s="38" t="inlineStr">
+        <is>
+          <t>O QUE ESTA FICHA NÃO CALCULA, E POR QUÊ</t>
+        </is>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="D98" s="39" t="inlineStr">
         <is>
           <t>a CD dos efeitos dela</t>
         </is>
       </c>
-      <c r="U93" s="38" t="n"/>
-      <c r="V93" s="38" t="n"/>
-      <c r="W93" s="38" t="n"/>
-      <c r="X93" s="38" t="n"/>
-      <c r="Y93" s="38" t="n"/>
-      <c r="Z93" s="38" t="n"/>
-      <c r="AA93" s="38" t="n"/>
-      <c r="AB93" s="38" t="n"/>
-      <c r="AC93" s="38" t="n"/>
-      <c r="AD93" s="38" t="n"/>
-      <c r="AE93" s="38" t="n"/>
-      <c r="AF93" s="38" t="n"/>
-      <c r="AG93" s="38" t="n"/>
-      <c r="AH93" s="38" t="n"/>
-      <c r="AI93" s="38" t="n"/>
-      <c r="AJ93" s="38" t="n"/>
-      <c r="AK93" s="38" t="n"/>
-      <c r="AL93" s="38" t="n"/>
-      <c r="AM93" s="38" t="n"/>
-      <c r="AN93" s="38" t="n"/>
-      <c r="AO93" s="38" t="n"/>
-      <c r="AP93" s="38" t="n"/>
-      <c r="AQ93" s="38" t="n"/>
-      <c r="AR93" s="38" t="n"/>
-      <c r="AS93" s="38" t="n"/>
-      <c r="AT93" s="38" t="n"/>
-    </row>
-    <row r="94">
-      <c r="D94" s="39">
+      <c r="U98" s="40" t="n"/>
+      <c r="V98" s="40" t="n"/>
+      <c r="W98" s="40" t="n"/>
+      <c r="X98" s="40" t="n"/>
+      <c r="Y98" s="40" t="n"/>
+      <c r="Z98" s="40" t="n"/>
+      <c r="AA98" s="40" t="n"/>
+      <c r="AB98" s="40" t="n"/>
+      <c r="AC98" s="40" t="n"/>
+      <c r="AD98" s="40" t="n"/>
+      <c r="AE98" s="40" t="n"/>
+      <c r="AF98" s="40" t="n"/>
+      <c r="AG98" s="40" t="n"/>
+      <c r="AH98" s="40" t="n"/>
+      <c r="AI98" s="40" t="n"/>
+      <c r="AJ98" s="40" t="n"/>
+      <c r="AK98" s="40" t="n"/>
+      <c r="AL98" s="40" t="n"/>
+      <c r="AM98" s="40" t="n"/>
+      <c r="AN98" s="40" t="n"/>
+      <c r="AO98" s="40" t="n"/>
+      <c r="AP98" s="40" t="n"/>
+      <c r="AQ98" s="40" t="n"/>
+      <c r="AR98" s="40" t="n"/>
+      <c r="AS98" s="40" t="n"/>
+      <c r="AT98" s="40" t="n"/>
+    </row>
+    <row r="99">
+      <c r="D99" s="41">
         <f>IF($AI$14="Voz","a Voz manda subir a CD dela, e a invocação não tem fórmula de CD em documento nenhum — combine com o mestre","")</f>
         <v/>
       </c>
     </row>
-    <row r="95">
-      <c r="D95" s="40" t="inlineStr">
+    <row r="100">
+      <c r="D100" s="42" t="inlineStr">
         <is>
           <t>A invocação não tem fórmula de CD em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Esta rota soma num número que o sistema ainda não produz, então combine com o mestre em vez de chutar.</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
+    <row r="101"/>
   </sheetData>
-  <mergeCells count="148">
+  <mergeCells count="162">
     <mergeCell ref="AI39:AM39"/>
-    <mergeCell ref="D86:L86"/>
     <mergeCell ref="D58:F59"/>
     <mergeCell ref="AI13:AS13"/>
     <mergeCell ref="D19:F20"/>
     <mergeCell ref="Q68:U68"/>
-    <mergeCell ref="M85:AT85"/>
     <mergeCell ref="D68:P68"/>
     <mergeCell ref="AN47:AS47"/>
     <mergeCell ref="M52:T52"/>
@@ -3777,142 +3847,158 @@
     <mergeCell ref="AM33:AS33"/>
     <mergeCell ref="D67:P67"/>
     <mergeCell ref="Y6:AD6"/>
+    <mergeCell ref="Q72:U72"/>
     <mergeCell ref="D1:AD2"/>
-    <mergeCell ref="T70:AT70"/>
+    <mergeCell ref="D69:P69"/>
     <mergeCell ref="A8:B26"/>
     <mergeCell ref="K7:P7"/>
     <mergeCell ref="G4:AD4"/>
-    <mergeCell ref="M87:AT87"/>
     <mergeCell ref="D33:L33"/>
     <mergeCell ref="D64:U64"/>
     <mergeCell ref="D45:F46"/>
     <mergeCell ref="Z66:AL66"/>
-    <mergeCell ref="D88:L88"/>
     <mergeCell ref="D26:L26"/>
     <mergeCell ref="N26:V26"/>
+    <mergeCell ref="D76:J76"/>
     <mergeCell ref="Q65:U65"/>
-    <mergeCell ref="D93:T93"/>
-    <mergeCell ref="T71:AT72"/>
-    <mergeCell ref="M88:AT88"/>
+    <mergeCell ref="Q70:U70"/>
     <mergeCell ref="AM65:AQ65"/>
+    <mergeCell ref="D70:P70"/>
+    <mergeCell ref="D83:K83"/>
+    <mergeCell ref="D90:L90"/>
     <mergeCell ref="N25:V25"/>
+    <mergeCell ref="D75:J75"/>
     <mergeCell ref="D47:J47"/>
+    <mergeCell ref="D86:AT86"/>
     <mergeCell ref="D6:I6"/>
     <mergeCell ref="Q66:U66"/>
     <mergeCell ref="D36:L36"/>
+    <mergeCell ref="D72:P72"/>
     <mergeCell ref="AF22:AK23"/>
     <mergeCell ref="D21:I21"/>
     <mergeCell ref="N36:U36"/>
+    <mergeCell ref="L76:R76"/>
+    <mergeCell ref="M90:AT90"/>
     <mergeCell ref="R6:W6"/>
+    <mergeCell ref="D71:P71"/>
     <mergeCell ref="AM7:AS7"/>
+    <mergeCell ref="D84:K84"/>
     <mergeCell ref="V52:AC52"/>
     <mergeCell ref="R21:W21"/>
     <mergeCell ref="D7:I7"/>
+    <mergeCell ref="D73:P73"/>
     <mergeCell ref="O39:S39"/>
     <mergeCell ref="N37:U37"/>
+    <mergeCell ref="M91:AT91"/>
     <mergeCell ref="D37:L37"/>
-    <mergeCell ref="G83:AD83"/>
-    <mergeCell ref="L70:R70"/>
     <mergeCell ref="Q67:U67"/>
     <mergeCell ref="L48:R48"/>
     <mergeCell ref="Z65:AL65"/>
     <mergeCell ref="AF32:AK32"/>
     <mergeCell ref="AM67:AQ67"/>
+    <mergeCell ref="M93:AT93"/>
     <mergeCell ref="AE51:AT51"/>
     <mergeCell ref="G45:AD45"/>
+    <mergeCell ref="D79:AT79"/>
     <mergeCell ref="D11:F12"/>
-    <mergeCell ref="D95:AT96"/>
+    <mergeCell ref="T75:AT75"/>
+    <mergeCell ref="Q69:U69"/>
     <mergeCell ref="AF7:AK7"/>
     <mergeCell ref="D35:AT35"/>
     <mergeCell ref="L47:R47"/>
-    <mergeCell ref="D78:K78"/>
-    <mergeCell ref="D89:L89"/>
+    <mergeCell ref="M92:AT92"/>
+    <mergeCell ref="AM69:AQ69"/>
     <mergeCell ref="V51:AC51"/>
     <mergeCell ref="D14:O14"/>
-    <mergeCell ref="D81:AT81"/>
+    <mergeCell ref="D99:AT99"/>
     <mergeCell ref="T48:AE48"/>
-    <mergeCell ref="N78:X78"/>
     <mergeCell ref="AF33:AK33"/>
     <mergeCell ref="G19:AH19"/>
     <mergeCell ref="D51:K51"/>
     <mergeCell ref="K21:P21"/>
     <mergeCell ref="R22:W23"/>
+    <mergeCell ref="T76:AT77"/>
     <mergeCell ref="Y21:AD21"/>
     <mergeCell ref="Z67:AL67"/>
     <mergeCell ref="Q14:Y14"/>
     <mergeCell ref="X39:AH39"/>
     <mergeCell ref="D30:F31"/>
+    <mergeCell ref="D100:AT101"/>
+    <mergeCell ref="Q71:U71"/>
+    <mergeCell ref="D88:F89"/>
     <mergeCell ref="D28:AT28"/>
+    <mergeCell ref="Z69:AL69"/>
+    <mergeCell ref="G81:AF81"/>
+    <mergeCell ref="D91:L91"/>
     <mergeCell ref="AM66:AQ66"/>
     <mergeCell ref="Y7:AD7"/>
     <mergeCell ref="AA14:AG14"/>
     <mergeCell ref="D9:AT9"/>
+    <mergeCell ref="D81:F82"/>
+    <mergeCell ref="Q73:U73"/>
     <mergeCell ref="M51:T51"/>
     <mergeCell ref="AM32:AS32"/>
+    <mergeCell ref="D93:L93"/>
     <mergeCell ref="G30:AJ30"/>
     <mergeCell ref="AM68:AQ68"/>
     <mergeCell ref="D25:L25"/>
-    <mergeCell ref="D94:AT94"/>
     <mergeCell ref="AN48:AS48"/>
+    <mergeCell ref="D92:L92"/>
     <mergeCell ref="X26:AR26"/>
-    <mergeCell ref="D76:F77"/>
     <mergeCell ref="D65:P65"/>
     <mergeCell ref="K6:P6"/>
-    <mergeCell ref="D85:L85"/>
     <mergeCell ref="D16:AT17"/>
     <mergeCell ref="X25:AR25"/>
     <mergeCell ref="K22:P23"/>
+    <mergeCell ref="D94:L94"/>
     <mergeCell ref="Y22:AD23"/>
-    <mergeCell ref="L71:R71"/>
+    <mergeCell ref="N84:AD84"/>
     <mergeCell ref="N32:S32"/>
     <mergeCell ref="D39:N39"/>
+    <mergeCell ref="G96:AJ96"/>
+    <mergeCell ref="M94:AT94"/>
     <mergeCell ref="D66:P66"/>
+    <mergeCell ref="D98:T98"/>
     <mergeCell ref="A30:B48"/>
     <mergeCell ref="Z68:AL68"/>
-    <mergeCell ref="D79:K79"/>
     <mergeCell ref="R7:W7"/>
-    <mergeCell ref="D71:J71"/>
     <mergeCell ref="U33:AD33"/>
-    <mergeCell ref="N79:AD79"/>
     <mergeCell ref="D13:O13"/>
     <mergeCell ref="N33:S33"/>
-    <mergeCell ref="M86:AT86"/>
     <mergeCell ref="D32:L32"/>
     <mergeCell ref="D43:AT43"/>
     <mergeCell ref="AF6:AK6"/>
-    <mergeCell ref="M89:AT89"/>
     <mergeCell ref="AM6:AS6"/>
     <mergeCell ref="AG48:AL48"/>
     <mergeCell ref="AE52:AT53"/>
-    <mergeCell ref="D87:L87"/>
     <mergeCell ref="D52:K52"/>
-    <mergeCell ref="D74:AT74"/>
     <mergeCell ref="Z64:AQ64"/>
     <mergeCell ref="D22:I23"/>
     <mergeCell ref="AG47:AL47"/>
     <mergeCell ref="D60:J60"/>
+    <mergeCell ref="D96:F97"/>
     <mergeCell ref="G58:AJ58"/>
     <mergeCell ref="O41:S41"/>
     <mergeCell ref="D41:N41"/>
     <mergeCell ref="AI41:AM41"/>
     <mergeCell ref="AA13:AG13"/>
-    <mergeCell ref="G91:AJ91"/>
+    <mergeCell ref="G88:AD88"/>
+    <mergeCell ref="AM70:AQ70"/>
+    <mergeCell ref="L75:R75"/>
+    <mergeCell ref="Z70:AL70"/>
     <mergeCell ref="D4:F5"/>
     <mergeCell ref="Q13:Y13"/>
-    <mergeCell ref="D91:F92"/>
     <mergeCell ref="X41:AH41"/>
     <mergeCell ref="D61:J61"/>
     <mergeCell ref="U32:AD32"/>
-    <mergeCell ref="D70:J70"/>
     <mergeCell ref="D48:J48"/>
-    <mergeCell ref="D83:F84"/>
     <mergeCell ref="D55:AT56"/>
     <mergeCell ref="G11:AD11"/>
     <mergeCell ref="AF1:AT2"/>
     <mergeCell ref="AI14:AS14"/>
-    <mergeCell ref="G76:AF76"/>
+    <mergeCell ref="N83:X83"/>
   </mergeCells>
-  <dataValidations count="15">
+  <dataValidations count="22">
     <dataValidation sqref="Q14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$A$2:$A$5</formula1>
     </dataValidation>
@@ -3946,6 +4032,21 @@
     <dataValidation sqref="D68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
+    <dataValidation sqref="D69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="D70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="D71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="D72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
+    </dataValidation>
+    <dataValidation sqref="D73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
+    </dataValidation>
     <dataValidation sqref="Z65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
@@ -3956,6 +4057,12 @@
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
     <dataValidation sqref="Z68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$I$2:$I$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$I$2:$I$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -3970,7 +4077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN55"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4007,60 +4114,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="41" t="inlineStr">
+      <c r="A1" s="43" t="inlineStr">
         <is>
           <t>tipos</t>
         </is>
       </c>
-      <c r="B1" s="41" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>trilhas</t>
         </is>
       </c>
-      <c r="C1" s="41" t="inlineStr">
+      <c r="C1" s="43" t="inlineStr">
         <is>
           <t>atributos</t>
         </is>
       </c>
-      <c r="D1" s="41" t="inlineStr">
+      <c r="D1" s="43" t="inlineStr">
         <is>
           <t>trs</t>
         </is>
       </c>
-      <c r="E1" s="41" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="F1" s="41" t="inlineStr">
+      <c r="F1" s="43" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="G1" s="41" t="inlineStr">
+      <c r="G1" s="43" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="H1" s="41" t="inlineStr">
+      <c r="H1" s="43" t="inlineStr">
         <is>
           <t>traco</t>
         </is>
       </c>
-      <c r="I1" s="41" t="inlineStr">
+      <c r="I1" s="43" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
       <c r="J1" s="5" t="n"/>
-      <c r="K1" s="41" t="inlineStr">
+      <c r="K1" s="43" t="inlineStr">
         <is>
           <t>tab_tipos</t>
         </is>
       </c>
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
-      <c r="N1" s="41" t="inlineStr">
+      <c r="N1" s="43" t="inlineStr">
         <is>
           <t>tab_trilhas</t>
         </is>
@@ -4070,21 +4177,21 @@
       <c r="Q1" s="5" t="n"/>
       <c r="R1" s="5" t="n"/>
       <c r="S1" s="5" t="n"/>
-      <c r="T1" s="41" t="inlineStr">
+      <c r="T1" s="43" t="inlineStr">
         <is>
           <t>tab_traco</t>
         </is>
       </c>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
-      <c r="W1" s="41" t="inlineStr">
+      <c r="W1" s="43" t="inlineStr">
         <is>
           <t>tab_comando</t>
         </is>
       </c>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
-      <c r="Z1" s="41" t="inlineStr">
+      <c r="Z1" s="43" t="inlineStr">
         <is>
           <t>tab_investir</t>
         </is>
@@ -4092,7 +4199,7 @@
       <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="5" t="n"/>
       <c r="AC1" s="5" t="n"/>
-      <c r="AD1" s="41" t="inlineStr">
+      <c r="AD1" s="43" t="inlineStr">
         <is>
           <t>tab_trs</t>
         </is>
@@ -4154,120 +4261,120 @@
         </is>
       </c>
       <c r="J2" s="5" t="n"/>
-      <c r="K2" s="42" t="inlineStr">
+      <c r="K2" s="44" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="L2" s="42" t="inlineStr">
+      <c r="L2" s="44" t="inlineStr">
         <is>
           <t>base</t>
         </is>
       </c>
       <c r="M2" s="5" t="n"/>
-      <c r="N2" s="42" t="inlineStr">
+      <c r="N2" s="44" t="inlineStr">
         <is>
           <t>trilha</t>
         </is>
       </c>
-      <c r="O2" s="42" t="inlineStr">
+      <c r="O2" s="44" t="inlineStr">
         <is>
           <t>corpos</t>
         </is>
       </c>
-      <c r="P2" s="42" t="inlineStr">
+      <c r="P2" s="44" t="inlineStr">
         <is>
           <t>mult</t>
         </is>
       </c>
-      <c r="Q2" s="42" t="inlineStr">
+      <c r="Q2" s="44" t="inlineStr">
         <is>
           <t>corpo</t>
         </is>
       </c>
-      <c r="R2" s="42" t="inlineStr">
+      <c r="R2" s="44" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
       <c r="S2" s="5" t="n"/>
-      <c r="T2" s="42" t="inlineStr">
+      <c r="T2" s="44" t="inlineStr">
         <is>
           <t>traço</t>
         </is>
       </c>
-      <c r="U2" s="42" t="inlineStr">
+      <c r="U2" s="44" t="inlineStr">
         <is>
           <t>pontos</t>
         </is>
       </c>
       <c r="V2" s="5" t="n"/>
-      <c r="W2" s="42" t="inlineStr">
+      <c r="W2" s="44" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
-      <c r="X2" s="42" t="inlineStr">
+      <c r="X2" s="44" t="inlineStr">
         <is>
           <t>pontos</t>
         </is>
       </c>
       <c r="Y2" s="5" t="n"/>
-      <c r="Z2" s="42" t="inlineStr">
+      <c r="Z2" s="44" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="AA2" s="42" t="inlineStr">
+      <c r="AA2" s="44" t="inlineStr">
         <is>
           <t>uma</t>
         </is>
       </c>
-      <c r="AB2" s="42" t="inlineStr">
+      <c r="AB2" s="44" t="inlineStr">
         <is>
           <t>matilha</t>
         </is>
       </c>
       <c r="AC2" s="5" t="n"/>
-      <c r="AD2" s="42" t="inlineStr">
+      <c r="AD2" s="44" t="inlineStr">
         <is>
           <t>tr</t>
         </is>
       </c>
-      <c r="AE2" s="42" t="inlineStr">
+      <c r="AE2" s="44" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
       <c r="AF2" s="5" t="n"/>
-      <c r="AG2" s="42" t="inlineStr">
+      <c r="AG2" s="44" t="inlineStr">
         <is>
           <t>e_marcos</t>
         </is>
       </c>
-      <c r="AH2" s="42" t="inlineStr">
+      <c r="AH2" s="44" t="inlineStr">
         <is>
           <t>e_maestria</t>
         </is>
       </c>
-      <c r="AI2" s="42" t="inlineStr">
+      <c r="AI2" s="44" t="inlineStr">
         <is>
           <t>e_classe</t>
         </is>
       </c>
       <c r="AJ2" s="5" t="n"/>
-      <c r="AK2" s="42" t="inlineStr">
+      <c r="AK2" s="44" t="inlineStr">
         <is>
           <t>espelho</t>
         </is>
       </c>
       <c r="AL2" s="5" t="n"/>
-      <c r="AM2" s="42" t="inlineStr">
+      <c r="AM2" s="44" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="AN2" s="43" t="inlineStr">
+      <c r="AN2" s="45" t="inlineStr">
         <is>
           <t>célula</t>
         </is>
@@ -4412,7 +4519,7 @@
           <t>nivel</t>
         </is>
       </c>
-      <c r="AN3" s="44" t="inlineStr">
+      <c r="AN3" s="46" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
@@ -4549,7 +4656,7 @@
           <t>ess_dono</t>
         </is>
       </c>
-      <c r="AN4" s="44" t="inlineStr">
+      <c r="AN4" s="46" t="inlineStr">
         <is>
           <t>K7</t>
         </is>
@@ -4682,7 +4789,7 @@
           <t>int_dono</t>
         </is>
       </c>
-      <c r="AN5" s="44" t="inlineStr">
+      <c r="AN5" s="46" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
@@ -4787,7 +4894,7 @@
           <t>maestria</t>
         </is>
       </c>
-      <c r="AN6" s="44" t="inlineStr">
+      <c r="AN6" s="46" t="inlineStr">
         <is>
           <t>Y7</t>
         </is>
@@ -4874,7 +4981,7 @@
           <t>marcos</t>
         </is>
       </c>
-      <c r="AN7" s="44" t="inlineStr">
+      <c r="AN7" s="46" t="inlineStr">
         <is>
           <t>AF7</t>
         </is>
@@ -4958,7 +5065,7 @@
           <t>classe</t>
         </is>
       </c>
-      <c r="AN8" s="44" t="inlineStr">
+      <c r="AN8" s="46" t="inlineStr">
         <is>
           <t>AM7</t>
         </is>
@@ -5042,7 +5149,7 @@
           <t>nome</t>
         </is>
       </c>
-      <c r="AN9" s="44" t="inlineStr">
+      <c r="AN9" s="46" t="inlineStr">
         <is>
           <t>D14</t>
         </is>
@@ -5108,7 +5215,7 @@
           <t>tipo</t>
         </is>
       </c>
-      <c r="AN10" s="44" t="inlineStr">
+      <c r="AN10" s="46" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
@@ -5168,7 +5275,7 @@
           <t>trilha</t>
         </is>
       </c>
-      <c r="AN11" s="44" t="inlineStr">
+      <c r="AN11" s="46" t="inlineStr">
         <is>
           <t>AA14</t>
         </is>
@@ -5228,7 +5335,7 @@
           <t>sintonia</t>
         </is>
       </c>
-      <c r="AN12" s="44" t="inlineStr">
+      <c r="AN12" s="46" t="inlineStr">
         <is>
           <t>AI14</t>
         </is>
@@ -5288,7 +5395,7 @@
           <t>pontos_atributo</t>
         </is>
       </c>
-      <c r="AN13" s="44" t="inlineStr">
+      <c r="AN13" s="46" t="inlineStr">
         <is>
           <t>D26</t>
         </is>
@@ -5348,7 +5455,7 @@
           <t>pontos_disp</t>
         </is>
       </c>
-      <c r="AN14" s="44" t="inlineStr">
+      <c r="AN14" s="46" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
@@ -5408,7 +5515,7 @@
           <t>aviso_atributo</t>
         </is>
       </c>
-      <c r="AN15" s="44" t="inlineStr">
+      <c r="AN15" s="46" t="inlineStr">
         <is>
           <t>X26</t>
         </is>
@@ -5464,7 +5571,7 @@
           <t>atr_acerto</t>
         </is>
       </c>
-      <c r="AN16" s="44" t="inlineStr">
+      <c r="AN16" s="46" t="inlineStr">
         <is>
           <t>D33</t>
         </is>
@@ -5514,7 +5621,7 @@
           <t>acerto</t>
         </is>
       </c>
-      <c r="AN17" s="44" t="inlineStr">
+      <c r="AN17" s="46" t="inlineStr">
         <is>
           <t>N33</t>
         </is>
@@ -5564,7 +5671,7 @@
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="AN18" s="44" t="inlineStr">
+      <c r="AN18" s="46" t="inlineStr">
         <is>
           <t>U33</t>
         </is>
@@ -5614,7 +5721,7 @@
           <t>defesa</t>
         </is>
       </c>
-      <c r="AN19" s="44" t="inlineStr">
+      <c r="AN19" s="46" t="inlineStr">
         <is>
           <t>AF33</t>
         </is>
@@ -5664,7 +5771,7 @@
           <t>critico</t>
         </is>
       </c>
-      <c r="AN20" s="44" t="inlineStr">
+      <c r="AN20" s="46" t="inlineStr">
         <is>
           <t>AM33</t>
         </is>
@@ -5714,7 +5821,7 @@
           <t>tr_treinado</t>
         </is>
       </c>
-      <c r="AN21" s="44" t="inlineStr">
+      <c r="AN21" s="46" t="inlineStr">
         <is>
           <t>D37</t>
         </is>
@@ -5764,7 +5871,7 @@
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="AN22" s="44" t="inlineStr">
+      <c r="AN22" s="46" t="inlineStr">
         <is>
           <t>N37</t>
         </is>
@@ -5814,7 +5921,7 @@
           <t>vida_max</t>
         </is>
       </c>
-      <c r="AN23" s="44" t="inlineStr">
+      <c r="AN23" s="46" t="inlineStr">
         <is>
           <t>D48</t>
         </is>
@@ -5864,7 +5971,7 @@
           <t>vida</t>
         </is>
       </c>
-      <c r="AN24" s="44" t="inlineStr">
+      <c r="AN24" s="46" t="inlineStr">
         <is>
           <t>L48</t>
         </is>
@@ -5914,7 +6021,7 @@
           <t>corpos</t>
         </is>
       </c>
-      <c r="AN25" s="44" t="inlineStr">
+      <c r="AN25" s="46" t="inlineStr">
         <is>
           <t>AG48</t>
         </is>
@@ -5964,7 +6071,7 @@
           <t>area</t>
         </is>
       </c>
-      <c r="AN26" s="44" t="inlineStr">
+      <c r="AN26" s="46" t="inlineStr">
         <is>
           <t>AN48</t>
         </is>
@@ -6014,7 +6121,7 @@
           <t>regua</t>
         </is>
       </c>
-      <c r="AN27" s="44" t="inlineStr">
+      <c r="AN27" s="46" t="inlineStr">
         <is>
           <t>D52</t>
         </is>
@@ -6064,7 +6171,7 @@
           <t>meia_regua</t>
         </is>
       </c>
-      <c r="AN28" s="44" t="inlineStr">
+      <c r="AN28" s="46" t="inlineStr">
         <is>
           <t>M52</t>
         </is>
@@ -6114,7 +6221,7 @@
           <t>volta_com</t>
         </is>
       </c>
-      <c r="AN29" s="44" t="inlineStr">
+      <c r="AN29" s="46" t="inlineStr">
         <is>
           <t>V52</t>
         </is>
@@ -6164,309 +6271,477 @@
           <t>orcamento</t>
         </is>
       </c>
-      <c r="AN30" s="44" t="inlineStr">
+      <c r="AN30" s="46" t="inlineStr">
         <is>
           <t>D61</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="AM31" s="44" t="inlineStr">
+      <c r="AM31" s="46" t="inlineStr">
         <is>
           <t>gasto</t>
         </is>
       </c>
-      <c r="AN31" s="44" t="inlineStr">
+      <c r="AN31" s="46" t="inlineStr">
+        <is>
+          <t>D76</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AM32" s="46" t="inlineStr">
+        <is>
+          <t>sobra</t>
+        </is>
+      </c>
+      <c r="AN32" s="46" t="inlineStr">
+        <is>
+          <t>L76</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="AM33" s="46" t="inlineStr">
+        <is>
+          <t>investir</t>
+        </is>
+      </c>
+      <c r="AN33" s="46" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="AM34" s="46" t="inlineStr">
+        <is>
+          <t>cd_pendente</t>
+        </is>
+      </c>
+      <c r="AN34" s="46" t="inlineStr">
+        <is>
+          <t>D99</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="AM35" s="46" t="inlineStr">
+        <is>
+          <t>atr_Força</t>
+        </is>
+      </c>
+      <c r="AN35" s="46" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="AM36" s="46" t="inlineStr">
+        <is>
+          <t>atr_Destreza</t>
+        </is>
+      </c>
+      <c r="AN36" s="46" t="inlineStr">
+        <is>
+          <t>K22</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="AM37" s="46" t="inlineStr">
+        <is>
+          <t>atr_Constituição</t>
+        </is>
+      </c>
+      <c r="AN37" s="46" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="AM38" s="46" t="inlineStr">
+        <is>
+          <t>atr_Inteligência</t>
+        </is>
+      </c>
+      <c r="AN38" s="46" t="inlineStr">
+        <is>
+          <t>Y22</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="AM39" s="46" t="inlineStr">
+        <is>
+          <t>atr_Essência</t>
+        </is>
+      </c>
+      <c r="AN39" s="46" t="inlineStr">
+        <is>
+          <t>AF22</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="AM40" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_1</t>
+        </is>
+      </c>
+      <c r="AN40" s="46" t="inlineStr">
+        <is>
+          <t>Q65</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="AM41" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_2</t>
+        </is>
+      </c>
+      <c r="AN41" s="46" t="inlineStr">
+        <is>
+          <t>Q66</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="AM42" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_3</t>
+        </is>
+      </c>
+      <c r="AN42" s="46" t="inlineStr">
+        <is>
+          <t>Q67</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="AM43" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_4</t>
+        </is>
+      </c>
+      <c r="AN43" s="46" t="inlineStr">
+        <is>
+          <t>Q68</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="AM44" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_5</t>
+        </is>
+      </c>
+      <c r="AN44" s="46" t="inlineStr">
+        <is>
+          <t>Q69</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="AM45" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_6</t>
+        </is>
+      </c>
+      <c r="AN45" s="46" t="inlineStr">
+        <is>
+          <t>Q70</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="AM46" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_7</t>
+        </is>
+      </c>
+      <c r="AN46" s="46" t="inlineStr">
+        <is>
+          <t>Q71</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="AM47" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_8</t>
+        </is>
+      </c>
+      <c r="AN47" s="46" t="inlineStr">
+        <is>
+          <t>Q72</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="AM48" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_9</t>
+        </is>
+      </c>
+      <c r="AN48" s="46" t="inlineStr">
+        <is>
+          <t>Q73</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="AM49" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_10</t>
+        </is>
+      </c>
+      <c r="AN49" s="46" t="inlineStr">
+        <is>
+          <t>AM65</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="AM50" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_11</t>
+        </is>
+      </c>
+      <c r="AN50" s="46" t="inlineStr">
+        <is>
+          <t>AM66</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="AM51" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_12</t>
+        </is>
+      </c>
+      <c r="AN51" s="46" t="inlineStr">
+        <is>
+          <t>AM67</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="AM52" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_13</t>
+        </is>
+      </c>
+      <c r="AN52" s="46" t="inlineStr">
+        <is>
+          <t>AM68</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="AM53" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_14</t>
+        </is>
+      </c>
+      <c r="AN53" s="46" t="inlineStr">
+        <is>
+          <t>AM69</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="AM54" s="46" t="inlineStr">
+        <is>
+          <t>slot_pontos_15</t>
+        </is>
+      </c>
+      <c r="AN54" s="46" t="inlineStr">
+        <is>
+          <t>AM70</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="AM55" s="46" t="inlineStr">
+        <is>
+          <t>traco_1</t>
+        </is>
+      </c>
+      <c r="AN55" s="46" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="AM56" s="46" t="inlineStr">
+        <is>
+          <t>traco_2</t>
+        </is>
+      </c>
+      <c r="AN56" s="46" t="inlineStr">
+        <is>
+          <t>D66</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="AM57" s="46" t="inlineStr">
+        <is>
+          <t>traco_3</t>
+        </is>
+      </c>
+      <c r="AN57" s="46" t="inlineStr">
+        <is>
+          <t>D67</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="AM58" s="46" t="inlineStr">
+        <is>
+          <t>traco_4</t>
+        </is>
+      </c>
+      <c r="AN58" s="46" t="inlineStr">
+        <is>
+          <t>D68</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="AM59" s="46" t="inlineStr">
+        <is>
+          <t>traco_5</t>
+        </is>
+      </c>
+      <c r="AN59" s="46" t="inlineStr">
+        <is>
+          <t>D69</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="AM60" s="46" t="inlineStr">
+        <is>
+          <t>traco_6</t>
+        </is>
+      </c>
+      <c r="AN60" s="46" t="inlineStr">
+        <is>
+          <t>D70</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="AM61" s="46" t="inlineStr">
+        <is>
+          <t>traco_7</t>
+        </is>
+      </c>
+      <c r="AN61" s="46" t="inlineStr">
         <is>
           <t>D71</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="AM32" s="44" t="inlineStr">
-        <is>
-          <t>sobra</t>
-        </is>
-      </c>
-      <c r="AN32" s="44" t="inlineStr">
-        <is>
-          <t>L71</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="AM33" s="44" t="inlineStr">
-        <is>
-          <t>investir</t>
-        </is>
-      </c>
-      <c r="AN33" s="44" t="inlineStr">
-        <is>
-          <t>D79</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="AM34" s="44" t="inlineStr">
-        <is>
-          <t>cd_pendente</t>
-        </is>
-      </c>
-      <c r="AN34" s="44" t="inlineStr">
-        <is>
-          <t>D94</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="AM35" s="44" t="inlineStr">
-        <is>
-          <t>atr_Força</t>
-        </is>
-      </c>
-      <c r="AN35" s="44" t="inlineStr">
-        <is>
-          <t>D22</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="AM36" s="44" t="inlineStr">
-        <is>
-          <t>atr_Destreza</t>
-        </is>
-      </c>
-      <c r="AN36" s="44" t="inlineStr">
-        <is>
-          <t>K22</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="AM37" s="44" t="inlineStr">
-        <is>
-          <t>atr_Constituição</t>
-        </is>
-      </c>
-      <c r="AN37" s="44" t="inlineStr">
-        <is>
-          <t>R22</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="AM38" s="44" t="inlineStr">
-        <is>
-          <t>atr_Inteligência</t>
-        </is>
-      </c>
-      <c r="AN38" s="44" t="inlineStr">
-        <is>
-          <t>Y22</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="AM39" s="44" t="inlineStr">
-        <is>
-          <t>atr_Essência</t>
-        </is>
-      </c>
-      <c r="AN39" s="44" t="inlineStr">
-        <is>
-          <t>AF22</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="AM40" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_1</t>
-        </is>
-      </c>
-      <c r="AN40" s="44" t="inlineStr">
-        <is>
-          <t>Q65</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="AM41" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_2</t>
-        </is>
-      </c>
-      <c r="AN41" s="44" t="inlineStr">
-        <is>
-          <t>Q66</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="AM42" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_3</t>
-        </is>
-      </c>
-      <c r="AN42" s="44" t="inlineStr">
-        <is>
-          <t>Q67</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="AM43" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_4</t>
-        </is>
-      </c>
-      <c r="AN43" s="44" t="inlineStr">
-        <is>
-          <t>Q68</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="AM44" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_5</t>
-        </is>
-      </c>
-      <c r="AN44" s="44" t="inlineStr">
-        <is>
-          <t>AM65</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="AM45" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_6</t>
-        </is>
-      </c>
-      <c r="AN45" s="44" t="inlineStr">
-        <is>
-          <t>AM66</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="AM46" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_7</t>
-        </is>
-      </c>
-      <c r="AN46" s="44" t="inlineStr">
-        <is>
-          <t>AM67</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="AM47" s="44" t="inlineStr">
-        <is>
-          <t>slot_pontos_8</t>
-        </is>
-      </c>
-      <c r="AN47" s="44" t="inlineStr">
-        <is>
-          <t>AM68</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="AM48" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_1</t>
-        </is>
-      </c>
-      <c r="AN48" s="44" t="inlineStr">
-        <is>
-          <t>D65</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="AM49" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_2</t>
-        </is>
-      </c>
-      <c r="AN49" s="44" t="inlineStr">
-        <is>
-          <t>D66</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="AM50" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_3</t>
-        </is>
-      </c>
-      <c r="AN50" s="44" t="inlineStr">
-        <is>
-          <t>D67</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="AM51" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_4</t>
-        </is>
-      </c>
-      <c r="AN51" s="44" t="inlineStr">
-        <is>
-          <t>D68</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="AM52" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_5</t>
-        </is>
-      </c>
-      <c r="AN52" s="44" t="inlineStr">
+    <row r="62">
+      <c r="AM62" s="46" t="inlineStr">
+        <is>
+          <t>traco_8</t>
+        </is>
+      </c>
+      <c r="AN62" s="46" t="inlineStr">
+        <is>
+          <t>D72</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="AM63" s="46" t="inlineStr">
+        <is>
+          <t>traco_9</t>
+        </is>
+      </c>
+      <c r="AN63" s="46" t="inlineStr">
+        <is>
+          <t>D73</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="AM64" s="46" t="inlineStr">
+        <is>
+          <t>comando_1</t>
+        </is>
+      </c>
+      <c r="AN64" s="46" t="inlineStr">
         <is>
           <t>Z65</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="AM53" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_6</t>
-        </is>
-      </c>
-      <c r="AN53" s="44" t="inlineStr">
+    <row r="65">
+      <c r="AM65" s="46" t="inlineStr">
+        <is>
+          <t>comando_2</t>
+        </is>
+      </c>
+      <c r="AN65" s="46" t="inlineStr">
         <is>
           <t>Z66</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="AM54" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_7</t>
-        </is>
-      </c>
-      <c r="AN54" s="44" t="inlineStr">
+    <row r="66">
+      <c r="AM66" s="46" t="inlineStr">
+        <is>
+          <t>comando_3</t>
+        </is>
+      </c>
+      <c r="AN66" s="46" t="inlineStr">
         <is>
           <t>Z67</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="AM55" s="44" t="inlineStr">
-        <is>
-          <t>slot_nome_8</t>
-        </is>
-      </c>
-      <c r="AN55" s="44" t="inlineStr">
+    <row r="67">
+      <c r="AM67" s="46" t="inlineStr">
+        <is>
+          <t>comando_4</t>
+        </is>
+      </c>
+      <c r="AN67" s="46" t="inlineStr">
         <is>
           <t>Z68</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="AM68" s="46" t="inlineStr">
+        <is>
+          <t>comando_5</t>
+        </is>
+      </c>
+      <c r="AN68" s="46" t="inlineStr">
+        <is>
+          <t>Z69</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="AM69" s="46" t="inlineStr">
+        <is>
+          <t>comando_6</t>
+        </is>
+      </c>
+      <c r="AN69" s="46" t="inlineStr">
+        <is>
+          <t>Z70</t>
         </is>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INVOCAÇÃO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DADOS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATÁLOGO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DADOS" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="34">
     <font>
       <name val="Roboto"/>
       <color rgb="00F4F1F7"/>
@@ -169,6 +170,26 @@
       <color rgb="00D89B3A"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Oswald"/>
+      <color rgb="00E8DCD4"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Oswald"/>
+      <color rgb="00E8DCD4"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Castoro"/>
+      <color rgb="00E8DCD4"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Oswald"/>
+      <color rgb="00D89B3A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -202,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -215,11 +236,20 @@
         <color rgb="00493F54"/>
       </top>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00493F54"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -337,10 +367,50 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -777,7 +847,7 @@
       <c r="AE1" s="2" t="n"/>
       <c r="AF1" s="4" t="inlineStr">
         <is>
-          <t>capítulo 16 · sistema v0.200</t>
+          <t>capítulo 16 · sistema v0.200, e os dois capitulos conferidos IDENTICOS na 0.205</t>
         </is>
       </c>
     </row>
@@ -4075,6 +4145,2050 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AT64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="9" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="4" customWidth="1" min="11" max="11"/>
+    <col width="4" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="18" max="18"/>
+    <col width="4" customWidth="1" min="19" max="19"/>
+    <col width="4" customWidth="1" min="20" max="20"/>
+    <col width="4" customWidth="1" min="21" max="21"/>
+    <col width="4" customWidth="1" min="22" max="22"/>
+    <col width="4" customWidth="1" min="23" max="23"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="27" max="27"/>
+    <col width="4" customWidth="1" min="28" max="28"/>
+    <col width="4" customWidth="1" min="29" max="29"/>
+    <col width="4" customWidth="1" min="30" max="30"/>
+    <col width="4" customWidth="1" min="31" max="31"/>
+    <col width="4" customWidth="1" min="32" max="32"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="36" max="36"/>
+    <col width="4" customWidth="1" min="37" max="37"/>
+    <col width="4" customWidth="1" min="38" max="38"/>
+    <col width="4" customWidth="1" min="39" max="39"/>
+    <col width="4" customWidth="1" min="40" max="40"/>
+    <col width="4" customWidth="1" min="41" max="41"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="45" max="45"/>
+    <col width="4" customWidth="1" min="46" max="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="5" t="n"/>
+      <c r="B1" s="5" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="43" t="inlineStr">
+        <is>
+          <t>O CATÁLOGO — o que dá para comprar</t>
+        </is>
+      </c>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="4" t="inlineStr">
+        <is>
+          <t>capítulo 16</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="AE2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="5" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="5" t="n"/>
+      <c r="U3" s="5" t="n"/>
+      <c r="V3" s="5" t="n"/>
+      <c r="W3" s="5" t="n"/>
+      <c r="X3" s="5" t="n"/>
+      <c r="Y3" s="5" t="n"/>
+      <c r="Z3" s="5" t="n"/>
+      <c r="AA3" s="5" t="n"/>
+      <c r="AB3" s="5" t="n"/>
+      <c r="AC3" s="5" t="n"/>
+      <c r="AD3" s="5" t="n"/>
+      <c r="AE3" s="5" t="n"/>
+      <c r="AF3" s="5" t="n"/>
+      <c r="AG3" s="5" t="n"/>
+      <c r="AH3" s="5" t="n"/>
+      <c r="AI3" s="5" t="n"/>
+      <c r="AJ3" s="5" t="n"/>
+      <c r="AK3" s="5" t="n"/>
+      <c r="AL3" s="5" t="n"/>
+      <c r="AM3" s="5" t="n"/>
+      <c r="AN3" s="5" t="n"/>
+      <c r="AO3" s="5" t="n"/>
+      <c r="AP3" s="5" t="n"/>
+      <c r="AQ3" s="5" t="n"/>
+      <c r="AR3" s="5" t="n"/>
+      <c r="AS3" s="5" t="n"/>
+      <c r="AT3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>TRAÇO</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n"/>
+      <c r="W4" s="5" t="n"/>
+      <c r="X4" s="5" t="n"/>
+      <c r="Y4" s="5" t="n"/>
+      <c r="Z4" s="5" t="n"/>
+      <c r="AA4" s="5" t="n"/>
+      <c r="AB4" s="5" t="n"/>
+      <c r="AC4" s="5" t="n"/>
+      <c r="AD4" s="5" t="n"/>
+      <c r="AE4" s="5" t="n"/>
+      <c r="AF4" s="5" t="n"/>
+      <c r="AG4" s="5" t="n"/>
+      <c r="AH4" s="5" t="n"/>
+      <c r="AI4" s="5" t="n"/>
+      <c r="AJ4" s="5" t="n"/>
+      <c r="AK4" s="5" t="n"/>
+      <c r="AL4" s="5" t="n"/>
+      <c r="AM4" s="5" t="n"/>
+      <c r="AN4" s="5" t="n"/>
+      <c r="AO4" s="5" t="n"/>
+      <c r="AP4" s="5" t="n"/>
+      <c r="AQ4" s="5" t="n"/>
+      <c r="AR4" s="5" t="n"/>
+      <c r="AS4" s="5" t="n"/>
+      <c r="AT4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="5" t="n"/>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>o que ela É. Sempre ligado, sem gastar ação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>PONTOS</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t>O QUE FAZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="46" t="n"/>
+      <c r="F7" s="46" t="n"/>
+      <c r="G7" s="46" t="n"/>
+      <c r="H7" s="47" t="inlineStr">
+        <is>
+          <t>Escalada</t>
+        </is>
+      </c>
+      <c r="I7" s="46" t="n"/>
+      <c r="J7" s="46" t="n"/>
+      <c r="K7" s="46" t="n"/>
+      <c r="L7" s="46" t="n"/>
+      <c r="M7" s="46" t="n"/>
+      <c r="N7" s="46" t="n"/>
+      <c r="O7" s="46" t="n"/>
+      <c r="P7" s="48" t="inlineStr">
+        <is>
+          <t>sobe parede e teto sem teste</t>
+        </is>
+      </c>
+      <c r="Q7" s="46" t="n"/>
+      <c r="R7" s="46" t="n"/>
+      <c r="S7" s="46" t="n"/>
+      <c r="T7" s="46" t="n"/>
+      <c r="U7" s="46" t="n"/>
+      <c r="V7" s="46" t="n"/>
+      <c r="W7" s="46" t="n"/>
+      <c r="X7" s="46" t="n"/>
+      <c r="Y7" s="46" t="n"/>
+      <c r="Z7" s="46" t="n"/>
+      <c r="AA7" s="46" t="n"/>
+      <c r="AB7" s="46" t="n"/>
+      <c r="AC7" s="46" t="n"/>
+      <c r="AD7" s="46" t="n"/>
+      <c r="AE7" s="46" t="n"/>
+      <c r="AF7" s="46" t="n"/>
+      <c r="AG7" s="46" t="n"/>
+      <c r="AH7" s="46" t="n"/>
+      <c r="AI7" s="46" t="n"/>
+      <c r="AJ7" s="46" t="n"/>
+      <c r="AK7" s="46" t="n"/>
+      <c r="AL7" s="46" t="n"/>
+      <c r="AM7" s="46" t="n"/>
+      <c r="AN7" s="46" t="n"/>
+      <c r="AO7" s="46" t="n"/>
+      <c r="AP7" s="46" t="n"/>
+      <c r="AQ7" s="46" t="n"/>
+      <c r="AR7" s="46" t="n"/>
+      <c r="AS7" s="46" t="n"/>
+      <c r="AT7" s="46" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="49" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="50" t="inlineStr">
+        <is>
+          <t>Nado</t>
+        </is>
+      </c>
+      <c r="P8" s="51" t="inlineStr">
+        <is>
+          <t>move na água sem penalidade. Rio, cisterna, tanque alagado de estação</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="5" t="n"/>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="53" t="inlineStr">
+        <is>
+          <t>Fala</t>
+        </is>
+      </c>
+      <c r="P9" s="41" t="inlineStr">
+        <is>
+          <t>ela fala, e dá para conversar com ela</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="50" t="inlineStr">
+        <is>
+          <t>Faro</t>
+        </is>
+      </c>
+      <c r="P10" s="51" t="inlineStr">
+        <is>
+          <t>rastreia por cheiro e por energia. Pega rastro velho de horas</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="5" t="n"/>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="53" t="inlineStr">
+        <is>
+          <t>Vigia</t>
+        </is>
+      </c>
+      <c r="P11" s="41" t="inlineStr">
+        <is>
+          <t>o que ela vê e ouve, você vê e ouve também</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="50" t="inlineStr">
+        <is>
+          <t>Miúdo</t>
+        </is>
+      </c>
+      <c r="P12" s="51" t="inlineStr">
+        <is>
+          <t>ocupa espaço menor e passa por vão. Duto, grade de bueiro, folga embaixo da porta</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H13" s="53" t="inlineStr">
+        <is>
+          <t>Voo</t>
+        </is>
+      </c>
+      <c r="P13" s="41" t="inlineStr">
+        <is>
+          <t>o deslocamento dela passa a ser de voo também</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" s="50" t="inlineStr">
+        <is>
+          <t>Montaria</t>
+        </is>
+      </c>
+      <c r="P14" s="51" t="inlineStr">
+        <is>
+          <t>carrega uma pessoa ou mais, dependendo do tamanho</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="53" t="inlineStr">
+        <is>
+          <t>Fisgada</t>
+        </is>
+      </c>
+      <c r="P15" s="41" t="inlineStr">
+        <is>
+          <t>prende à distância. Ela alcança, engancha, e quem ia fugir para de conseguir</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="50" t="inlineStr">
+        <is>
+          <t>Emboscada</t>
+        </is>
+      </c>
+      <c r="P16" s="51" t="inlineStr">
+        <is>
+          <t>surge do chão, fora do alcance de visão</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" s="53" t="inlineStr">
+        <is>
+          <t>Jorro</t>
+        </is>
+      </c>
+      <c r="P17" s="41" t="inlineStr">
+        <is>
+          <t>ataca em linha ou em área</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="50" t="inlineStr">
+        <is>
+          <t>Graúdo</t>
+        </is>
+      </c>
+      <c r="P18" s="51" t="inlineStr">
+        <is>
+          <t>ocupa espaço maior e barra passagem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="53" t="inlineStr">
+        <is>
+          <t>Remoto</t>
+        </is>
+      </c>
+      <c r="P19" s="41" t="inlineStr">
+        <is>
+          <t>funciona além dos 18 metros da amarra. Dentro da cena, para qualquer um; fora da cena, com requisito</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="5" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="5" t="n"/>
+      <c r="AD20" s="5" t="n"/>
+      <c r="AE20" s="5" t="n"/>
+      <c r="AF20" s="5" t="n"/>
+      <c r="AG20" s="5" t="n"/>
+      <c r="AH20" s="5" t="n"/>
+      <c r="AI20" s="5" t="n"/>
+      <c r="AJ20" s="5" t="n"/>
+      <c r="AK20" s="5" t="n"/>
+      <c r="AL20" s="5" t="n"/>
+      <c r="AM20" s="5" t="n"/>
+      <c r="AN20" s="5" t="n"/>
+      <c r="AO20" s="5" t="n"/>
+      <c r="AP20" s="5" t="n"/>
+      <c r="AQ20" s="5" t="n"/>
+      <c r="AR20" s="5" t="n"/>
+      <c r="AS20" s="5" t="n"/>
+      <c r="AT20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="5" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="5" t="n"/>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="5" t="n"/>
+      <c r="AF21" s="5" t="n"/>
+      <c r="AG21" s="5" t="n"/>
+      <c r="AH21" s="5" t="n"/>
+      <c r="AI21" s="5" t="n"/>
+      <c r="AJ21" s="5" t="n"/>
+      <c r="AK21" s="5" t="n"/>
+      <c r="AL21" s="5" t="n"/>
+      <c r="AM21" s="5" t="n"/>
+      <c r="AN21" s="5" t="n"/>
+      <c r="AO21" s="5" t="n"/>
+      <c r="AP21" s="5" t="n"/>
+      <c r="AQ21" s="5" t="n"/>
+      <c r="AR21" s="5" t="n"/>
+      <c r="AS21" s="5" t="n"/>
+      <c r="AT21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>COMANDO</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="n"/>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
+      <c r="AE22" s="5" t="n"/>
+      <c r="AF22" s="5" t="n"/>
+      <c r="AG22" s="5" t="n"/>
+      <c r="AH22" s="5" t="n"/>
+      <c r="AI22" s="5" t="n"/>
+      <c r="AJ22" s="5" t="n"/>
+      <c r="AK22" s="5" t="n"/>
+      <c r="AL22" s="5" t="n"/>
+      <c r="AM22" s="5" t="n"/>
+      <c r="AN22" s="5" t="n"/>
+      <c r="AO22" s="5" t="n"/>
+      <c r="AP22" s="5" t="n"/>
+      <c r="AQ22" s="5" t="n"/>
+      <c r="AR22" s="5" t="n"/>
+      <c r="AS22" s="5" t="n"/>
+      <c r="AT22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="44" t="inlineStr">
+        <is>
+          <t>o que ela FAZ quando o dono gasta a Ação Padrão nela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>PONTOS</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>NOME</t>
+        </is>
+      </c>
+      <c r="P24" s="8" t="inlineStr">
+        <is>
+          <t>O QUE FAZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="46" t="n"/>
+      <c r="F25" s="46" t="n"/>
+      <c r="G25" s="46" t="n"/>
+      <c r="H25" s="47" t="inlineStr">
+        <is>
+          <t>Investir</t>
+        </is>
+      </c>
+      <c r="I25" s="46" t="n"/>
+      <c r="J25" s="46" t="n"/>
+      <c r="K25" s="46" t="n"/>
+      <c r="L25" s="46" t="n"/>
+      <c r="M25" s="46" t="n"/>
+      <c r="N25" s="46" t="n"/>
+      <c r="O25" s="46" t="n"/>
+      <c r="P25" s="48" t="inlineStr">
+        <is>
+          <t>o ataque. Toda invocação tem</t>
+        </is>
+      </c>
+      <c r="Q25" s="46" t="n"/>
+      <c r="R25" s="46" t="n"/>
+      <c r="S25" s="46" t="n"/>
+      <c r="T25" s="46" t="n"/>
+      <c r="U25" s="46" t="n"/>
+      <c r="V25" s="46" t="n"/>
+      <c r="W25" s="46" t="n"/>
+      <c r="X25" s="46" t="n"/>
+      <c r="Y25" s="46" t="n"/>
+      <c r="Z25" s="46" t="n"/>
+      <c r="AA25" s="46" t="n"/>
+      <c r="AB25" s="46" t="n"/>
+      <c r="AC25" s="46" t="n"/>
+      <c r="AD25" s="46" t="n"/>
+      <c r="AE25" s="46" t="n"/>
+      <c r="AF25" s="46" t="n"/>
+      <c r="AG25" s="46" t="n"/>
+      <c r="AH25" s="46" t="n"/>
+      <c r="AI25" s="46" t="n"/>
+      <c r="AJ25" s="46" t="n"/>
+      <c r="AK25" s="46" t="n"/>
+      <c r="AL25" s="46" t="n"/>
+      <c r="AM25" s="46" t="n"/>
+      <c r="AN25" s="46" t="n"/>
+      <c r="AO25" s="46" t="n"/>
+      <c r="AP25" s="46" t="n"/>
+      <c r="AQ25" s="46" t="n"/>
+      <c r="AR25" s="46" t="n"/>
+      <c r="AS25" s="46" t="n"/>
+      <c r="AT25" s="46" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="50" t="inlineStr">
+        <is>
+          <t>Agarrar</t>
+        </is>
+      </c>
+      <c r="P26" s="51" t="inlineStr">
+        <is>
+          <t>prende o alvo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" s="53" t="inlineStr">
+        <is>
+          <t>Arrastar</t>
+        </is>
+      </c>
+      <c r="P27" s="41" t="inlineStr">
+        <is>
+          <t>move o alvo, ou se move levando ele. Tira alguém de cima de uma beirada, ou põe</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="50" t="inlineStr">
+        <is>
+          <t>Buscar</t>
+        </is>
+      </c>
+      <c r="P28" s="51" t="inlineStr">
+        <is>
+          <t>pega um objeto, ou rastreia de forma ativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="53" t="inlineStr">
+        <is>
+          <t>Cavar</t>
+        </is>
+      </c>
+      <c r="P29" s="41" t="inlineStr">
+        <is>
+          <t>abre buraco, desenterra, revira o terreno. Faz rota onde não havia rota</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="49" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="50" t="inlineStr">
+        <is>
+          <t>Interpor</t>
+        </is>
+      </c>
+      <c r="P30" s="51" t="inlineStr">
+        <is>
+          <t>se põe entre você e o golpe. O corpo dela recebe o que ia em você</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H31" s="53" t="inlineStr">
+        <is>
+          <t>Chamariz</t>
+        </is>
+      </c>
+      <c r="P31" s="41" t="inlineStr">
+        <is>
+          <t>o alvo tem de vir para cima dela. Você escolhe em quem a coisa está prestando atenção</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="5" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="5" t="n"/>
+      <c r="U32" s="5" t="n"/>
+      <c r="V32" s="5" t="n"/>
+      <c r="W32" s="5" t="n"/>
+      <c r="X32" s="5" t="n"/>
+      <c r="Y32" s="5" t="n"/>
+      <c r="Z32" s="5" t="n"/>
+      <c r="AA32" s="5" t="n"/>
+      <c r="AB32" s="5" t="n"/>
+      <c r="AC32" s="5" t="n"/>
+      <c r="AD32" s="5" t="n"/>
+      <c r="AE32" s="5" t="n"/>
+      <c r="AF32" s="5" t="n"/>
+      <c r="AG32" s="5" t="n"/>
+      <c r="AH32" s="5" t="n"/>
+      <c r="AI32" s="5" t="n"/>
+      <c r="AJ32" s="5" t="n"/>
+      <c r="AK32" s="5" t="n"/>
+      <c r="AL32" s="5" t="n"/>
+      <c r="AM32" s="5" t="n"/>
+      <c r="AN32" s="5" t="n"/>
+      <c r="AO32" s="5" t="n"/>
+      <c r="AP32" s="5" t="n"/>
+      <c r="AQ32" s="5" t="n"/>
+      <c r="AR32" s="5" t="n"/>
+      <c r="AS32" s="5" t="n"/>
+      <c r="AT32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="5" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="5" t="n"/>
+      <c r="U33" s="5" t="n"/>
+      <c r="V33" s="5" t="n"/>
+      <c r="W33" s="5" t="n"/>
+      <c r="X33" s="5" t="n"/>
+      <c r="Y33" s="5" t="n"/>
+      <c r="Z33" s="5" t="n"/>
+      <c r="AA33" s="5" t="n"/>
+      <c r="AB33" s="5" t="n"/>
+      <c r="AC33" s="5" t="n"/>
+      <c r="AD33" s="5" t="n"/>
+      <c r="AE33" s="5" t="n"/>
+      <c r="AF33" s="5" t="n"/>
+      <c r="AG33" s="5" t="n"/>
+      <c r="AH33" s="5" t="n"/>
+      <c r="AI33" s="5" t="n"/>
+      <c r="AJ33" s="5" t="n"/>
+      <c r="AK33" s="5" t="n"/>
+      <c r="AL33" s="5" t="n"/>
+      <c r="AM33" s="5" t="n"/>
+      <c r="AN33" s="5" t="n"/>
+      <c r="AO33" s="5" t="n"/>
+      <c r="AP33" s="5" t="n"/>
+      <c r="AQ33" s="5" t="n"/>
+      <c r="AR33" s="5" t="n"/>
+      <c r="AS33" s="5" t="n"/>
+      <c r="AT33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>INVENTAR O SEU</t>
+        </is>
+      </c>
+      <c r="U34" s="5" t="n"/>
+      <c r="V34" s="5" t="n"/>
+      <c r="W34" s="5" t="n"/>
+      <c r="X34" s="5" t="n"/>
+      <c r="Y34" s="5" t="n"/>
+      <c r="Z34" s="5" t="n"/>
+      <c r="AA34" s="5" t="n"/>
+      <c r="AB34" s="5" t="n"/>
+      <c r="AC34" s="5" t="n"/>
+      <c r="AD34" s="5" t="n"/>
+      <c r="AE34" s="5" t="n"/>
+      <c r="AF34" s="5" t="n"/>
+      <c r="AG34" s="5" t="n"/>
+      <c r="AH34" s="5" t="n"/>
+      <c r="AI34" s="5" t="n"/>
+      <c r="AJ34" s="5" t="n"/>
+      <c r="AK34" s="5" t="n"/>
+      <c r="AL34" s="5" t="n"/>
+      <c r="AM34" s="5" t="n"/>
+      <c r="AN34" s="5" t="n"/>
+      <c r="AO34" s="5" t="n"/>
+      <c r="AP34" s="5" t="n"/>
+      <c r="AQ34" s="5" t="n"/>
+      <c r="AR34" s="5" t="n"/>
+      <c r="AS34" s="5" t="n"/>
+      <c r="AT34" s="5" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="44" t="inlineStr">
+        <is>
+          <t>escreva o efeito, ache na régua o degrau em que ele cai, e leve para o mestre. A palavra final é dele, sempre em cima de uma entrada escrita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="54" t="inlineStr">
+        <is>
+          <t>régua de TRAÇO</t>
+        </is>
+      </c>
+      <c r="U37" s="5" t="n"/>
+      <c r="V37" s="5" t="n"/>
+      <c r="W37" s="5" t="n"/>
+      <c r="X37" s="5" t="n"/>
+      <c r="Y37" s="5" t="n"/>
+      <c r="Z37" s="5" t="n"/>
+      <c r="AA37" s="5" t="n"/>
+      <c r="AB37" s="5" t="n"/>
+      <c r="AC37" s="5" t="n"/>
+      <c r="AD37" s="5" t="n"/>
+      <c r="AE37" s="5" t="n"/>
+      <c r="AF37" s="5" t="n"/>
+      <c r="AG37" s="5" t="n"/>
+      <c r="AH37" s="5" t="n"/>
+      <c r="AI37" s="5" t="n"/>
+      <c r="AJ37" s="5" t="n"/>
+      <c r="AK37" s="5" t="n"/>
+      <c r="AL37" s="5" t="n"/>
+      <c r="AM37" s="5" t="n"/>
+      <c r="AN37" s="5" t="n"/>
+      <c r="AO37" s="5" t="n"/>
+      <c r="AP37" s="5" t="n"/>
+      <c r="AQ37" s="5" t="n"/>
+      <c r="AR37" s="5" t="n"/>
+      <c r="AS37" s="5" t="n"/>
+      <c r="AT37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="41" t="inlineStr">
+        <is>
+          <t>muda como ela anda, e só ela</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="49" t="n">
+        <v>3</v>
+      </c>
+      <c r="H39" s="51" t="inlineStr">
+        <is>
+          <t>muda o que ela comunica</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="H40" s="41" t="inlineStr">
+        <is>
+          <t>muda o que ela percebe</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="H41" s="51" t="inlineStr">
+        <is>
+          <t>muda que espaço ela ocupa, a um passo de mexer no tabuleiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H42" s="41" t="inlineStr">
+        <is>
+          <t>encosta em outra criatura ou no ambiente: carrega, prende, empurra, barra, alcança além do alcance, aparece onde não dava</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="5" t="n"/>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+      <c r="H43" s="5" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="5" t="n"/>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="5" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="5" t="n"/>
+      <c r="U43" s="5" t="n"/>
+      <c r="V43" s="5" t="n"/>
+      <c r="W43" s="5" t="n"/>
+      <c r="X43" s="5" t="n"/>
+      <c r="Y43" s="5" t="n"/>
+      <c r="Z43" s="5" t="n"/>
+      <c r="AA43" s="5" t="n"/>
+      <c r="AB43" s="5" t="n"/>
+      <c r="AC43" s="5" t="n"/>
+      <c r="AD43" s="5" t="n"/>
+      <c r="AE43" s="5" t="n"/>
+      <c r="AF43" s="5" t="n"/>
+      <c r="AG43" s="5" t="n"/>
+      <c r="AH43" s="5" t="n"/>
+      <c r="AI43" s="5" t="n"/>
+      <c r="AJ43" s="5" t="n"/>
+      <c r="AK43" s="5" t="n"/>
+      <c r="AL43" s="5" t="n"/>
+      <c r="AM43" s="5" t="n"/>
+      <c r="AN43" s="5" t="n"/>
+      <c r="AO43" s="5" t="n"/>
+      <c r="AP43" s="5" t="n"/>
+      <c r="AQ43" s="5" t="n"/>
+      <c r="AR43" s="5" t="n"/>
+      <c r="AS43" s="5" t="n"/>
+      <c r="AT43" s="5" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="5" t="n"/>
+      <c r="B44" s="5" t="n"/>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="54" t="inlineStr">
+        <is>
+          <t>régua de COMANDO</t>
+        </is>
+      </c>
+      <c r="U44" s="5" t="n"/>
+      <c r="V44" s="5" t="n"/>
+      <c r="W44" s="5" t="n"/>
+      <c r="X44" s="5" t="n"/>
+      <c r="Y44" s="5" t="n"/>
+      <c r="Z44" s="5" t="n"/>
+      <c r="AA44" s="5" t="n"/>
+      <c r="AB44" s="5" t="n"/>
+      <c r="AC44" s="5" t="n"/>
+      <c r="AD44" s="5" t="n"/>
+      <c r="AE44" s="5" t="n"/>
+      <c r="AF44" s="5" t="n"/>
+      <c r="AG44" s="5" t="n"/>
+      <c r="AH44" s="5" t="n"/>
+      <c r="AI44" s="5" t="n"/>
+      <c r="AJ44" s="5" t="n"/>
+      <c r="AK44" s="5" t="n"/>
+      <c r="AL44" s="5" t="n"/>
+      <c r="AM44" s="5" t="n"/>
+      <c r="AN44" s="5" t="n"/>
+      <c r="AO44" s="5" t="n"/>
+      <c r="AP44" s="5" t="n"/>
+      <c r="AQ44" s="5" t="n"/>
+      <c r="AR44" s="5" t="n"/>
+      <c r="AS44" s="5" t="n"/>
+      <c r="AT44" s="5" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="5" t="n"/>
+      <c r="B45" s="5" t="n"/>
+      <c r="C45" s="5" t="n"/>
+      <c r="D45" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="41" t="inlineStr">
+        <is>
+          <t>é o ataque</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H46" s="51" t="inlineStr">
+        <is>
+          <t>faz uma coisa com um alvo ou um objeto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="5" t="n"/>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="H47" s="41" t="inlineStr">
+        <is>
+          <t>protege você, ou nega a ação de outro</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="5" t="n"/>
+      <c r="B48" s="5" t="n"/>
+      <c r="C48" s="5" t="n"/>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+      <c r="H48" s="5" t="n"/>
+      <c r="I48" s="5" t="n"/>
+      <c r="J48" s="5" t="n"/>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="5" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="5" t="n"/>
+      <c r="U48" s="5" t="n"/>
+      <c r="V48" s="5" t="n"/>
+      <c r="W48" s="5" t="n"/>
+      <c r="X48" s="5" t="n"/>
+      <c r="Y48" s="5" t="n"/>
+      <c r="Z48" s="5" t="n"/>
+      <c r="AA48" s="5" t="n"/>
+      <c r="AB48" s="5" t="n"/>
+      <c r="AC48" s="5" t="n"/>
+      <c r="AD48" s="5" t="n"/>
+      <c r="AE48" s="5" t="n"/>
+      <c r="AF48" s="5" t="n"/>
+      <c r="AG48" s="5" t="n"/>
+      <c r="AH48" s="5" t="n"/>
+      <c r="AI48" s="5" t="n"/>
+      <c r="AJ48" s="5" t="n"/>
+      <c r="AK48" s="5" t="n"/>
+      <c r="AL48" s="5" t="n"/>
+      <c r="AM48" s="5" t="n"/>
+      <c r="AN48" s="5" t="n"/>
+      <c r="AO48" s="5" t="n"/>
+      <c r="AP48" s="5" t="n"/>
+      <c r="AQ48" s="5" t="n"/>
+      <c r="AR48" s="5" t="n"/>
+      <c r="AS48" s="5" t="n"/>
+      <c r="AT48" s="5" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="55" t="inlineStr">
+        <is>
+          <t>E O QUE NÃO SE COMPRA A PREÇO NENHUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="56" t="inlineStr">
+        <is>
+          <t>dado de dano</t>
+        </is>
+      </c>
+      <c r="P50" s="44" t="inlineStr">
+        <is>
+          <t>o teto de uma Rotina já governa a saída. Um Traço que dê +1d6 não existe</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="57" t="inlineStr">
+        <is>
+          <t>qualquer coisa que cresça com refino</t>
+        </is>
+      </c>
+      <c r="E51" s="46" t="n"/>
+      <c r="F51" s="46" t="n"/>
+      <c r="G51" s="46" t="n"/>
+      <c r="H51" s="46" t="n"/>
+      <c r="I51" s="46" t="n"/>
+      <c r="J51" s="46" t="n"/>
+      <c r="K51" s="46" t="n"/>
+      <c r="L51" s="46" t="n"/>
+      <c r="M51" s="46" t="n"/>
+      <c r="N51" s="46" t="n"/>
+      <c r="O51" s="46" t="n"/>
+      <c r="P51" s="58" t="inlineStr">
+        <is>
+          <t>refino cresce muito mais rápido que a ficha dela, e ela passaria de você</t>
+        </is>
+      </c>
+      <c r="Q51" s="46" t="n"/>
+      <c r="R51" s="46" t="n"/>
+      <c r="S51" s="46" t="n"/>
+      <c r="T51" s="46" t="n"/>
+      <c r="U51" s="46" t="n"/>
+      <c r="V51" s="46" t="n"/>
+      <c r="W51" s="46" t="n"/>
+      <c r="X51" s="46" t="n"/>
+      <c r="Y51" s="46" t="n"/>
+      <c r="Z51" s="46" t="n"/>
+      <c r="AA51" s="46" t="n"/>
+      <c r="AB51" s="46" t="n"/>
+      <c r="AC51" s="46" t="n"/>
+      <c r="AD51" s="46" t="n"/>
+      <c r="AE51" s="46" t="n"/>
+      <c r="AF51" s="46" t="n"/>
+      <c r="AG51" s="46" t="n"/>
+      <c r="AH51" s="46" t="n"/>
+      <c r="AI51" s="46" t="n"/>
+      <c r="AJ51" s="46" t="n"/>
+      <c r="AK51" s="46" t="n"/>
+      <c r="AL51" s="46" t="n"/>
+      <c r="AM51" s="46" t="n"/>
+      <c r="AN51" s="46" t="n"/>
+      <c r="AO51" s="46" t="n"/>
+      <c r="AP51" s="46" t="n"/>
+      <c r="AQ51" s="46" t="n"/>
+      <c r="AR51" s="46" t="n"/>
+      <c r="AS51" s="46" t="n"/>
+      <c r="AT51" s="46" t="n"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="57" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="E52" s="46" t="n"/>
+      <c r="F52" s="46" t="n"/>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="46" t="n"/>
+      <c r="I52" s="46" t="n"/>
+      <c r="J52" s="46" t="n"/>
+      <c r="K52" s="46" t="n"/>
+      <c r="L52" s="46" t="n"/>
+      <c r="M52" s="46" t="n"/>
+      <c r="N52" s="46" t="n"/>
+      <c r="O52" s="46" t="n"/>
+      <c r="P52" s="58" t="inlineStr">
+        <is>
+          <t>os cinco já saem do arranjo dela, e comprar de novo é pagar duas vezes</t>
+        </is>
+      </c>
+      <c r="Q52" s="46" t="n"/>
+      <c r="R52" s="46" t="n"/>
+      <c r="S52" s="46" t="n"/>
+      <c r="T52" s="46" t="n"/>
+      <c r="U52" s="46" t="n"/>
+      <c r="V52" s="46" t="n"/>
+      <c r="W52" s="46" t="n"/>
+      <c r="X52" s="46" t="n"/>
+      <c r="Y52" s="46" t="n"/>
+      <c r="Z52" s="46" t="n"/>
+      <c r="AA52" s="46" t="n"/>
+      <c r="AB52" s="46" t="n"/>
+      <c r="AC52" s="46" t="n"/>
+      <c r="AD52" s="46" t="n"/>
+      <c r="AE52" s="46" t="n"/>
+      <c r="AF52" s="46" t="n"/>
+      <c r="AG52" s="46" t="n"/>
+      <c r="AH52" s="46" t="n"/>
+      <c r="AI52" s="46" t="n"/>
+      <c r="AJ52" s="46" t="n"/>
+      <c r="AK52" s="46" t="n"/>
+      <c r="AL52" s="46" t="n"/>
+      <c r="AM52" s="46" t="n"/>
+      <c r="AN52" s="46" t="n"/>
+      <c r="AO52" s="46" t="n"/>
+      <c r="AP52" s="46" t="n"/>
+      <c r="AQ52" s="46" t="n"/>
+      <c r="AR52" s="46" t="n"/>
+      <c r="AS52" s="46" t="n"/>
+      <c r="AT52" s="46" t="n"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="57" t="inlineStr">
+        <is>
+          <t>Defesa, acerto ou vida direto</t>
+        </is>
+      </c>
+      <c r="E53" s="46" t="n"/>
+      <c r="F53" s="46" t="n"/>
+      <c r="G53" s="46" t="n"/>
+      <c r="H53" s="46" t="n"/>
+      <c r="I53" s="46" t="n"/>
+      <c r="J53" s="46" t="n"/>
+      <c r="K53" s="46" t="n"/>
+      <c r="L53" s="46" t="n"/>
+      <c r="M53" s="46" t="n"/>
+      <c r="N53" s="46" t="n"/>
+      <c r="O53" s="46" t="n"/>
+      <c r="P53" s="58" t="inlineStr">
+        <is>
+          <t>os três saem dos atributos dela</t>
+        </is>
+      </c>
+      <c r="Q53" s="46" t="n"/>
+      <c r="R53" s="46" t="n"/>
+      <c r="S53" s="46" t="n"/>
+      <c r="T53" s="46" t="n"/>
+      <c r="U53" s="46" t="n"/>
+      <c r="V53" s="46" t="n"/>
+      <c r="W53" s="46" t="n"/>
+      <c r="X53" s="46" t="n"/>
+      <c r="Y53" s="46" t="n"/>
+      <c r="Z53" s="46" t="n"/>
+      <c r="AA53" s="46" t="n"/>
+      <c r="AB53" s="46" t="n"/>
+      <c r="AC53" s="46" t="n"/>
+      <c r="AD53" s="46" t="n"/>
+      <c r="AE53" s="46" t="n"/>
+      <c r="AF53" s="46" t="n"/>
+      <c r="AG53" s="46" t="n"/>
+      <c r="AH53" s="46" t="n"/>
+      <c r="AI53" s="46" t="n"/>
+      <c r="AJ53" s="46" t="n"/>
+      <c r="AK53" s="46" t="n"/>
+      <c r="AL53" s="46" t="n"/>
+      <c r="AM53" s="46" t="n"/>
+      <c r="AN53" s="46" t="n"/>
+      <c r="AO53" s="46" t="n"/>
+      <c r="AP53" s="46" t="n"/>
+      <c r="AQ53" s="46" t="n"/>
+      <c r="AR53" s="46" t="n"/>
+      <c r="AS53" s="46" t="n"/>
+      <c r="AT53" s="46" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="13" t="n"/>
+      <c r="I54" s="13" t="n"/>
+      <c r="J54" s="13" t="n"/>
+      <c r="K54" s="13" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
+      <c r="N54" s="13" t="n"/>
+      <c r="O54" s="13" t="n"/>
+      <c r="P54" s="13" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="13" t="n"/>
+      <c r="U54" s="13" t="n"/>
+      <c r="V54" s="13" t="n"/>
+      <c r="W54" s="13" t="n"/>
+      <c r="X54" s="13" t="n"/>
+      <c r="Y54" s="13" t="n"/>
+      <c r="Z54" s="13" t="n"/>
+      <c r="AA54" s="13" t="n"/>
+      <c r="AB54" s="13" t="n"/>
+      <c r="AC54" s="13" t="n"/>
+      <c r="AD54" s="13" t="n"/>
+      <c r="AE54" s="13" t="n"/>
+      <c r="AF54" s="13" t="n"/>
+      <c r="AG54" s="13" t="n"/>
+      <c r="AH54" s="13" t="n"/>
+      <c r="AI54" s="13" t="n"/>
+      <c r="AJ54" s="13" t="n"/>
+      <c r="AK54" s="13" t="n"/>
+      <c r="AL54" s="13" t="n"/>
+      <c r="AM54" s="13" t="n"/>
+      <c r="AN54" s="13" t="n"/>
+      <c r="AO54" s="13" t="n"/>
+      <c r="AP54" s="13" t="n"/>
+      <c r="AQ54" s="13" t="n"/>
+      <c r="AR54" s="13" t="n"/>
+      <c r="AS54" s="13" t="n"/>
+      <c r="AT54" s="13" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="5" t="n"/>
+      <c r="B55" s="5" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+      <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
+      <c r="U55" s="5" t="n"/>
+      <c r="V55" s="5" t="n"/>
+      <c r="W55" s="5" t="n"/>
+      <c r="X55" s="5" t="n"/>
+      <c r="Y55" s="5" t="n"/>
+      <c r="Z55" s="5" t="n"/>
+      <c r="AA55" s="5" t="n"/>
+      <c r="AB55" s="5" t="n"/>
+      <c r="AC55" s="5" t="n"/>
+      <c r="AD55" s="5" t="n"/>
+      <c r="AE55" s="5" t="n"/>
+      <c r="AF55" s="5" t="n"/>
+      <c r="AG55" s="5" t="n"/>
+      <c r="AH55" s="5" t="n"/>
+      <c r="AI55" s="5" t="n"/>
+      <c r="AJ55" s="5" t="n"/>
+      <c r="AK55" s="5" t="n"/>
+      <c r="AL55" s="5" t="n"/>
+      <c r="AM55" s="5" t="n"/>
+      <c r="AN55" s="5" t="n"/>
+      <c r="AO55" s="5" t="n"/>
+      <c r="AP55" s="5" t="n"/>
+      <c r="AQ55" s="5" t="n"/>
+      <c r="AR55" s="5" t="n"/>
+      <c r="AS55" s="5" t="n"/>
+      <c r="AT55" s="5" t="n"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="5" t="n"/>
+      <c r="B56" s="5" t="n"/>
+      <c r="C56" s="5" t="n"/>
+      <c r="D56" s="5" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="5" t="n"/>
+      <c r="H56" s="5" t="n"/>
+      <c r="I56" s="5" t="n"/>
+      <c r="J56" s="5" t="n"/>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="5" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="5" t="n"/>
+      <c r="U56" s="5" t="n"/>
+      <c r="V56" s="5" t="n"/>
+      <c r="W56" s="5" t="n"/>
+      <c r="X56" s="5" t="n"/>
+      <c r="Y56" s="5" t="n"/>
+      <c r="Z56" s="5" t="n"/>
+      <c r="AA56" s="5" t="n"/>
+      <c r="AB56" s="5" t="n"/>
+      <c r="AC56" s="5" t="n"/>
+      <c r="AD56" s="5" t="n"/>
+      <c r="AE56" s="5" t="n"/>
+      <c r="AF56" s="5" t="n"/>
+      <c r="AG56" s="5" t="n"/>
+      <c r="AH56" s="5" t="n"/>
+      <c r="AI56" s="5" t="n"/>
+      <c r="AJ56" s="5" t="n"/>
+      <c r="AK56" s="5" t="n"/>
+      <c r="AL56" s="5" t="n"/>
+      <c r="AM56" s="5" t="n"/>
+      <c r="AN56" s="5" t="n"/>
+      <c r="AO56" s="5" t="n"/>
+      <c r="AP56" s="5" t="n"/>
+      <c r="AQ56" s="5" t="n"/>
+      <c r="AR56" s="5" t="n"/>
+      <c r="AS56" s="5" t="n"/>
+      <c r="AT56" s="5" t="n"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="5" t="n"/>
+      <c r="B57" s="5" t="n"/>
+      <c r="C57" s="5" t="n"/>
+      <c r="D57" s="5" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
+      <c r="Y57" s="5" t="n"/>
+      <c r="Z57" s="5" t="n"/>
+      <c r="AA57" s="5" t="n"/>
+      <c r="AB57" s="5" t="n"/>
+      <c r="AC57" s="5" t="n"/>
+      <c r="AD57" s="5" t="n"/>
+      <c r="AE57" s="5" t="n"/>
+      <c r="AF57" s="5" t="n"/>
+      <c r="AG57" s="5" t="n"/>
+      <c r="AH57" s="5" t="n"/>
+      <c r="AI57" s="5" t="n"/>
+      <c r="AJ57" s="5" t="n"/>
+      <c r="AK57" s="5" t="n"/>
+      <c r="AL57" s="5" t="n"/>
+      <c r="AM57" s="5" t="n"/>
+      <c r="AN57" s="5" t="n"/>
+      <c r="AO57" s="5" t="n"/>
+      <c r="AP57" s="5" t="n"/>
+      <c r="AQ57" s="5" t="n"/>
+      <c r="AR57" s="5" t="n"/>
+      <c r="AS57" s="5" t="n"/>
+      <c r="AT57" s="5" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="n"/>
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="5" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="5" t="n"/>
+      <c r="U58" s="5" t="n"/>
+      <c r="V58" s="5" t="n"/>
+      <c r="W58" s="5" t="n"/>
+      <c r="X58" s="5" t="n"/>
+      <c r="Y58" s="5" t="n"/>
+      <c r="Z58" s="5" t="n"/>
+      <c r="AA58" s="5" t="n"/>
+      <c r="AB58" s="5" t="n"/>
+      <c r="AC58" s="5" t="n"/>
+      <c r="AD58" s="5" t="n"/>
+      <c r="AE58" s="5" t="n"/>
+      <c r="AF58" s="5" t="n"/>
+      <c r="AG58" s="5" t="n"/>
+      <c r="AH58" s="5" t="n"/>
+      <c r="AI58" s="5" t="n"/>
+      <c r="AJ58" s="5" t="n"/>
+      <c r="AK58" s="5" t="n"/>
+      <c r="AL58" s="5" t="n"/>
+      <c r="AM58" s="5" t="n"/>
+      <c r="AN58" s="5" t="n"/>
+      <c r="AO58" s="5" t="n"/>
+      <c r="AP58" s="5" t="n"/>
+      <c r="AQ58" s="5" t="n"/>
+      <c r="AR58" s="5" t="n"/>
+      <c r="AS58" s="5" t="n"/>
+      <c r="AT58" s="5" t="n"/>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="5" t="n"/>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n"/>
+      <c r="D59" s="5" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="5" t="n"/>
+      <c r="H59" s="5" t="n"/>
+      <c r="I59" s="5" t="n"/>
+      <c r="J59" s="5" t="n"/>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="5" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="5" t="n"/>
+      <c r="U59" s="5" t="n"/>
+      <c r="V59" s="5" t="n"/>
+      <c r="W59" s="5" t="n"/>
+      <c r="X59" s="5" t="n"/>
+      <c r="Y59" s="5" t="n"/>
+      <c r="Z59" s="5" t="n"/>
+      <c r="AA59" s="5" t="n"/>
+      <c r="AB59" s="5" t="n"/>
+      <c r="AC59" s="5" t="n"/>
+      <c r="AD59" s="5" t="n"/>
+      <c r="AE59" s="5" t="n"/>
+      <c r="AF59" s="5" t="n"/>
+      <c r="AG59" s="5" t="n"/>
+      <c r="AH59" s="5" t="n"/>
+      <c r="AI59" s="5" t="n"/>
+      <c r="AJ59" s="5" t="n"/>
+      <c r="AK59" s="5" t="n"/>
+      <c r="AL59" s="5" t="n"/>
+      <c r="AM59" s="5" t="n"/>
+      <c r="AN59" s="5" t="n"/>
+      <c r="AO59" s="5" t="n"/>
+      <c r="AP59" s="5" t="n"/>
+      <c r="AQ59" s="5" t="n"/>
+      <c r="AR59" s="5" t="n"/>
+      <c r="AS59" s="5" t="n"/>
+      <c r="AT59" s="5" t="n"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="5" t="n"/>
+      <c r="B60" s="5" t="n"/>
+      <c r="C60" s="5" t="n"/>
+      <c r="D60" s="5" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="5" t="n"/>
+      <c r="H60" s="5" t="n"/>
+      <c r="I60" s="5" t="n"/>
+      <c r="J60" s="5" t="n"/>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="5" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="5" t="n"/>
+      <c r="U60" s="5" t="n"/>
+      <c r="V60" s="5" t="n"/>
+      <c r="W60" s="5" t="n"/>
+      <c r="X60" s="5" t="n"/>
+      <c r="Y60" s="5" t="n"/>
+      <c r="Z60" s="5" t="n"/>
+      <c r="AA60" s="5" t="n"/>
+      <c r="AB60" s="5" t="n"/>
+      <c r="AC60" s="5" t="n"/>
+      <c r="AD60" s="5" t="n"/>
+      <c r="AE60" s="5" t="n"/>
+      <c r="AF60" s="5" t="n"/>
+      <c r="AG60" s="5" t="n"/>
+      <c r="AH60" s="5" t="n"/>
+      <c r="AI60" s="5" t="n"/>
+      <c r="AJ60" s="5" t="n"/>
+      <c r="AK60" s="5" t="n"/>
+      <c r="AL60" s="5" t="n"/>
+      <c r="AM60" s="5" t="n"/>
+      <c r="AN60" s="5" t="n"/>
+      <c r="AO60" s="5" t="n"/>
+      <c r="AP60" s="5" t="n"/>
+      <c r="AQ60" s="5" t="n"/>
+      <c r="AR60" s="5" t="n"/>
+      <c r="AS60" s="5" t="n"/>
+      <c r="AT60" s="5" t="n"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="5" t="n"/>
+      <c r="B61" s="5" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="5" t="n"/>
+      <c r="Y61" s="5" t="n"/>
+      <c r="Z61" s="5" t="n"/>
+      <c r="AA61" s="5" t="n"/>
+      <c r="AB61" s="5" t="n"/>
+      <c r="AC61" s="5" t="n"/>
+      <c r="AD61" s="5" t="n"/>
+      <c r="AE61" s="5" t="n"/>
+      <c r="AF61" s="5" t="n"/>
+      <c r="AG61" s="5" t="n"/>
+      <c r="AH61" s="5" t="n"/>
+      <c r="AI61" s="5" t="n"/>
+      <c r="AJ61" s="5" t="n"/>
+      <c r="AK61" s="5" t="n"/>
+      <c r="AL61" s="5" t="n"/>
+      <c r="AM61" s="5" t="n"/>
+      <c r="AN61" s="5" t="n"/>
+      <c r="AO61" s="5" t="n"/>
+      <c r="AP61" s="5" t="n"/>
+      <c r="AQ61" s="5" t="n"/>
+      <c r="AR61" s="5" t="n"/>
+      <c r="AS61" s="5" t="n"/>
+      <c r="AT61" s="5" t="n"/>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="5" t="n"/>
+      <c r="B62" s="5" t="n"/>
+      <c r="C62" s="5" t="n"/>
+      <c r="D62" s="5" t="n"/>
+      <c r="E62" s="5" t="n"/>
+      <c r="F62" s="5" t="n"/>
+      <c r="G62" s="5" t="n"/>
+      <c r="H62" s="5" t="n"/>
+      <c r="I62" s="5" t="n"/>
+      <c r="J62" s="5" t="n"/>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
+      <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="5" t="n"/>
+      <c r="S62" s="5" t="n"/>
+      <c r="T62" s="5" t="n"/>
+      <c r="U62" s="5" t="n"/>
+      <c r="V62" s="5" t="n"/>
+      <c r="W62" s="5" t="n"/>
+      <c r="X62" s="5" t="n"/>
+      <c r="Y62" s="5" t="n"/>
+      <c r="Z62" s="5" t="n"/>
+      <c r="AA62" s="5" t="n"/>
+      <c r="AB62" s="5" t="n"/>
+      <c r="AC62" s="5" t="n"/>
+      <c r="AD62" s="5" t="n"/>
+      <c r="AE62" s="5" t="n"/>
+      <c r="AF62" s="5" t="n"/>
+      <c r="AG62" s="5" t="n"/>
+      <c r="AH62" s="5" t="n"/>
+      <c r="AI62" s="5" t="n"/>
+      <c r="AJ62" s="5" t="n"/>
+      <c r="AK62" s="5" t="n"/>
+      <c r="AL62" s="5" t="n"/>
+      <c r="AM62" s="5" t="n"/>
+      <c r="AN62" s="5" t="n"/>
+      <c r="AO62" s="5" t="n"/>
+      <c r="AP62" s="5" t="n"/>
+      <c r="AQ62" s="5" t="n"/>
+      <c r="AR62" s="5" t="n"/>
+      <c r="AS62" s="5" t="n"/>
+      <c r="AT62" s="5" t="n"/>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="5" t="n"/>
+      <c r="B63" s="5" t="n"/>
+      <c r="C63" s="5" t="n"/>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="5" t="n"/>
+      <c r="U63" s="5" t="n"/>
+      <c r="V63" s="5" t="n"/>
+      <c r="W63" s="5" t="n"/>
+      <c r="X63" s="5" t="n"/>
+      <c r="Y63" s="5" t="n"/>
+      <c r="Z63" s="5" t="n"/>
+      <c r="AA63" s="5" t="n"/>
+      <c r="AB63" s="5" t="n"/>
+      <c r="AC63" s="5" t="n"/>
+      <c r="AD63" s="5" t="n"/>
+      <c r="AE63" s="5" t="n"/>
+      <c r="AF63" s="5" t="n"/>
+      <c r="AG63" s="5" t="n"/>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
+      <c r="AJ63" s="5" t="n"/>
+      <c r="AK63" s="5" t="n"/>
+      <c r="AL63" s="5" t="n"/>
+      <c r="AM63" s="5" t="n"/>
+      <c r="AN63" s="5" t="n"/>
+      <c r="AO63" s="5" t="n"/>
+      <c r="AP63" s="5" t="n"/>
+      <c r="AQ63" s="5" t="n"/>
+      <c r="AR63" s="5" t="n"/>
+      <c r="AS63" s="5" t="n"/>
+      <c r="AT63" s="5" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="5" t="n"/>
+      <c r="B64" s="5" t="n"/>
+      <c r="C64" s="5" t="n"/>
+      <c r="D64" s="5" t="n"/>
+      <c r="E64" s="5" t="n"/>
+      <c r="F64" s="5" t="n"/>
+      <c r="G64" s="5" t="n"/>
+      <c r="H64" s="5" t="n"/>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="5" t="n"/>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
+      <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="5" t="n"/>
+      <c r="S64" s="5" t="n"/>
+      <c r="T64" s="5" t="n"/>
+      <c r="U64" s="5" t="n"/>
+      <c r="V64" s="5" t="n"/>
+      <c r="W64" s="5" t="n"/>
+      <c r="X64" s="5" t="n"/>
+      <c r="Y64" s="5" t="n"/>
+      <c r="Z64" s="5" t="n"/>
+      <c r="AA64" s="5" t="n"/>
+      <c r="AB64" s="5" t="n"/>
+      <c r="AC64" s="5" t="n"/>
+      <c r="AD64" s="5" t="n"/>
+      <c r="AE64" s="5" t="n"/>
+      <c r="AF64" s="5" t="n"/>
+      <c r="AG64" s="5" t="n"/>
+      <c r="AH64" s="5" t="n"/>
+      <c r="AI64" s="5" t="n"/>
+      <c r="AJ64" s="5" t="n"/>
+      <c r="AK64" s="5" t="n"/>
+      <c r="AL64" s="5" t="n"/>
+      <c r="AM64" s="5" t="n"/>
+      <c r="AN64" s="5" t="n"/>
+      <c r="AO64" s="5" t="n"/>
+      <c r="AP64" s="5" t="n"/>
+      <c r="AQ64" s="5" t="n"/>
+      <c r="AR64" s="5" t="n"/>
+      <c r="AS64" s="5" t="n"/>
+      <c r="AT64" s="5" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="101">
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="P17:AT17"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H29:O29"/>
+    <mergeCell ref="H39:AT39"/>
+    <mergeCell ref="P19:AT19"/>
+    <mergeCell ref="P53:AT53"/>
+    <mergeCell ref="D53:O53"/>
+    <mergeCell ref="H31:O31"/>
+    <mergeCell ref="D1:AD2"/>
+    <mergeCell ref="D31:G31"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="P29:AT29"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="H16:O16"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="P31:AT31"/>
+    <mergeCell ref="H27:O27"/>
+    <mergeCell ref="P8:AT8"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="H38:AT38"/>
+    <mergeCell ref="H40:AT40"/>
+    <mergeCell ref="P7:AT7"/>
+    <mergeCell ref="P16:AT16"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="D42:G42"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="P18:AT18"/>
+    <mergeCell ref="D26:G26"/>
+    <mergeCell ref="H6:O6"/>
+    <mergeCell ref="D19:G19"/>
+    <mergeCell ref="P25:AT25"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="P9:AT9"/>
+    <mergeCell ref="H13:O13"/>
+    <mergeCell ref="P6:AT6"/>
+    <mergeCell ref="D47:G47"/>
+    <mergeCell ref="P11:AT11"/>
+    <mergeCell ref="H15:O15"/>
+    <mergeCell ref="H24:O24"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="H8:O8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H26:O26"/>
+    <mergeCell ref="D44:T44"/>
+    <mergeCell ref="D39:G39"/>
+    <mergeCell ref="D34:T34"/>
+    <mergeCell ref="H10:O10"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D29:G29"/>
+    <mergeCell ref="P13:AT13"/>
+    <mergeCell ref="D38:G38"/>
+    <mergeCell ref="D22:T22"/>
+    <mergeCell ref="P15:AT15"/>
+    <mergeCell ref="P24:AT24"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D23:AT23"/>
+    <mergeCell ref="P26:AT26"/>
+    <mergeCell ref="P10:AT10"/>
+    <mergeCell ref="P50:AT50"/>
+    <mergeCell ref="D50:O50"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="H28:O28"/>
+    <mergeCell ref="H42:AT42"/>
+    <mergeCell ref="D4:T4"/>
+    <mergeCell ref="H12:O12"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="P52:AT52"/>
+    <mergeCell ref="D49:AT49"/>
+    <mergeCell ref="H14:O14"/>
+    <mergeCell ref="D28:G28"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D25:G25"/>
+    <mergeCell ref="D30:G30"/>
+    <mergeCell ref="P28:AT28"/>
+    <mergeCell ref="D35:AT36"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="H46:AT46"/>
+    <mergeCell ref="P12:AT12"/>
+    <mergeCell ref="P30:AT30"/>
+    <mergeCell ref="H25:O25"/>
+    <mergeCell ref="P14:AT14"/>
+    <mergeCell ref="D5:AT5"/>
+    <mergeCell ref="H45:AT45"/>
+    <mergeCell ref="D46:G46"/>
+    <mergeCell ref="D40:G40"/>
+    <mergeCell ref="H17:O17"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="P51:AT51"/>
+    <mergeCell ref="H47:AT47"/>
+    <mergeCell ref="D51:O51"/>
+    <mergeCell ref="H19:O19"/>
+    <mergeCell ref="D37:T37"/>
+    <mergeCell ref="D41:G41"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="P27:AT27"/>
+    <mergeCell ref="AF1:AT2"/>
+    <mergeCell ref="D52:O52"/>
+    <mergeCell ref="H30:O30"/>
+    <mergeCell ref="H41:AT41"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AN69"/>
@@ -4114,60 +6228,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="43" t="inlineStr">
+      <c r="A1" s="54" t="inlineStr">
         <is>
           <t>tipos</t>
         </is>
       </c>
-      <c r="B1" s="43" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>trilhas</t>
         </is>
       </c>
-      <c r="C1" s="43" t="inlineStr">
+      <c r="C1" s="54" t="inlineStr">
         <is>
           <t>atributos</t>
         </is>
       </c>
-      <c r="D1" s="43" t="inlineStr">
+      <c r="D1" s="54" t="inlineStr">
         <is>
           <t>trs</t>
         </is>
       </c>
-      <c r="E1" s="43" t="inlineStr">
+      <c r="E1" s="54" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="F1" s="43" t="inlineStr">
+      <c r="F1" s="54" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="G1" s="43" t="inlineStr">
+      <c r="G1" s="54" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="H1" s="43" t="inlineStr">
+      <c r="H1" s="54" t="inlineStr">
         <is>
           <t>traco</t>
         </is>
       </c>
-      <c r="I1" s="43" t="inlineStr">
+      <c r="I1" s="54" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
       <c r="J1" s="5" t="n"/>
-      <c r="K1" s="43" t="inlineStr">
+      <c r="K1" s="54" t="inlineStr">
         <is>
           <t>tab_tipos</t>
         </is>
       </c>
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
-      <c r="N1" s="43" t="inlineStr">
+      <c r="N1" s="54" t="inlineStr">
         <is>
           <t>tab_trilhas</t>
         </is>
@@ -4177,21 +6291,21 @@
       <c r="Q1" s="5" t="n"/>
       <c r="R1" s="5" t="n"/>
       <c r="S1" s="5" t="n"/>
-      <c r="T1" s="43" t="inlineStr">
+      <c r="T1" s="54" t="inlineStr">
         <is>
           <t>tab_traco</t>
         </is>
       </c>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
-      <c r="W1" s="43" t="inlineStr">
+      <c r="W1" s="54" t="inlineStr">
         <is>
           <t>tab_comando</t>
         </is>
       </c>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
-      <c r="Z1" s="43" t="inlineStr">
+      <c r="Z1" s="54" t="inlineStr">
         <is>
           <t>tab_investir</t>
         </is>
@@ -4199,7 +6313,7 @@
       <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="5" t="n"/>
       <c r="AC1" s="5" t="n"/>
-      <c r="AD1" s="43" t="inlineStr">
+      <c r="AD1" s="54" t="inlineStr">
         <is>
           <t>tab_trs</t>
         </is>
@@ -4374,7 +6488,7 @@
           <t>campo</t>
         </is>
       </c>
-      <c r="AN2" s="45" t="inlineStr">
+      <c r="AN2" s="59" t="inlineStr">
         <is>
           <t>célula</t>
         </is>
@@ -4519,7 +6633,7 @@
           <t>nivel</t>
         </is>
       </c>
-      <c r="AN3" s="46" t="inlineStr">
+      <c r="AN3" s="60" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
@@ -4656,7 +6770,7 @@
           <t>ess_dono</t>
         </is>
       </c>
-      <c r="AN4" s="46" t="inlineStr">
+      <c r="AN4" s="60" t="inlineStr">
         <is>
           <t>K7</t>
         </is>
@@ -4789,7 +6903,7 @@
           <t>int_dono</t>
         </is>
       </c>
-      <c r="AN5" s="46" t="inlineStr">
+      <c r="AN5" s="60" t="inlineStr">
         <is>
           <t>R7</t>
         </is>
@@ -4894,7 +7008,7 @@
           <t>maestria</t>
         </is>
       </c>
-      <c r="AN6" s="46" t="inlineStr">
+      <c r="AN6" s="60" t="inlineStr">
         <is>
           <t>Y7</t>
         </is>
@@ -4981,7 +7095,7 @@
           <t>marcos</t>
         </is>
       </c>
-      <c r="AN7" s="46" t="inlineStr">
+      <c r="AN7" s="60" t="inlineStr">
         <is>
           <t>AF7</t>
         </is>
@@ -5065,7 +7179,7 @@
           <t>classe</t>
         </is>
       </c>
-      <c r="AN8" s="46" t="inlineStr">
+      <c r="AN8" s="60" t="inlineStr">
         <is>
           <t>AM7</t>
         </is>
@@ -5149,7 +7263,7 @@
           <t>nome</t>
         </is>
       </c>
-      <c r="AN9" s="46" t="inlineStr">
+      <c r="AN9" s="60" t="inlineStr">
         <is>
           <t>D14</t>
         </is>
@@ -5215,7 +7329,7 @@
           <t>tipo</t>
         </is>
       </c>
-      <c r="AN10" s="46" t="inlineStr">
+      <c r="AN10" s="60" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
@@ -5275,7 +7389,7 @@
           <t>trilha</t>
         </is>
       </c>
-      <c r="AN11" s="46" t="inlineStr">
+      <c r="AN11" s="60" t="inlineStr">
         <is>
           <t>AA14</t>
         </is>
@@ -5335,7 +7449,7 @@
           <t>sintonia</t>
         </is>
       </c>
-      <c r="AN12" s="46" t="inlineStr">
+      <c r="AN12" s="60" t="inlineStr">
         <is>
           <t>AI14</t>
         </is>
@@ -5395,7 +7509,7 @@
           <t>pontos_atributo</t>
         </is>
       </c>
-      <c r="AN13" s="46" t="inlineStr">
+      <c r="AN13" s="60" t="inlineStr">
         <is>
           <t>D26</t>
         </is>
@@ -5455,7 +7569,7 @@
           <t>pontos_disp</t>
         </is>
       </c>
-      <c r="AN14" s="46" t="inlineStr">
+      <c r="AN14" s="60" t="inlineStr">
         <is>
           <t>N26</t>
         </is>
@@ -5515,7 +7629,7 @@
           <t>aviso_atributo</t>
         </is>
       </c>
-      <c r="AN15" s="46" t="inlineStr">
+      <c r="AN15" s="60" t="inlineStr">
         <is>
           <t>X26</t>
         </is>
@@ -5571,7 +7685,7 @@
           <t>atr_acerto</t>
         </is>
       </c>
-      <c r="AN16" s="46" t="inlineStr">
+      <c r="AN16" s="60" t="inlineStr">
         <is>
           <t>D33</t>
         </is>
@@ -5621,7 +7735,7 @@
           <t>acerto</t>
         </is>
       </c>
-      <c r="AN17" s="46" t="inlineStr">
+      <c r="AN17" s="60" t="inlineStr">
         <is>
           <t>N33</t>
         </is>
@@ -5671,7 +7785,7 @@
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="AN18" s="46" t="inlineStr">
+      <c r="AN18" s="60" t="inlineStr">
         <is>
           <t>U33</t>
         </is>
@@ -5721,7 +7835,7 @@
           <t>defesa</t>
         </is>
       </c>
-      <c r="AN19" s="46" t="inlineStr">
+      <c r="AN19" s="60" t="inlineStr">
         <is>
           <t>AF33</t>
         </is>
@@ -5771,7 +7885,7 @@
           <t>critico</t>
         </is>
       </c>
-      <c r="AN20" s="46" t="inlineStr">
+      <c r="AN20" s="60" t="inlineStr">
         <is>
           <t>AM33</t>
         </is>
@@ -5821,7 +7935,7 @@
           <t>tr_treinado</t>
         </is>
       </c>
-      <c r="AN21" s="46" t="inlineStr">
+      <c r="AN21" s="60" t="inlineStr">
         <is>
           <t>D37</t>
         </is>
@@ -5871,7 +7985,7 @@
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="AN22" s="46" t="inlineStr">
+      <c r="AN22" s="60" t="inlineStr">
         <is>
           <t>N37</t>
         </is>
@@ -5921,7 +8035,7 @@
           <t>vida_max</t>
         </is>
       </c>
-      <c r="AN23" s="46" t="inlineStr">
+      <c r="AN23" s="60" t="inlineStr">
         <is>
           <t>D48</t>
         </is>
@@ -5971,7 +8085,7 @@
           <t>vida</t>
         </is>
       </c>
-      <c r="AN24" s="46" t="inlineStr">
+      <c r="AN24" s="60" t="inlineStr">
         <is>
           <t>L48</t>
         </is>
@@ -6021,7 +8135,7 @@
           <t>corpos</t>
         </is>
       </c>
-      <c r="AN25" s="46" t="inlineStr">
+      <c r="AN25" s="60" t="inlineStr">
         <is>
           <t>AG48</t>
         </is>
@@ -6071,7 +8185,7 @@
           <t>area</t>
         </is>
       </c>
-      <c r="AN26" s="46" t="inlineStr">
+      <c r="AN26" s="60" t="inlineStr">
         <is>
           <t>AN48</t>
         </is>
@@ -6121,7 +8235,7 @@
           <t>regua</t>
         </is>
       </c>
-      <c r="AN27" s="46" t="inlineStr">
+      <c r="AN27" s="60" t="inlineStr">
         <is>
           <t>D52</t>
         </is>
@@ -6171,7 +8285,7 @@
           <t>meia_regua</t>
         </is>
       </c>
-      <c r="AN28" s="46" t="inlineStr">
+      <c r="AN28" s="60" t="inlineStr">
         <is>
           <t>M52</t>
         </is>
@@ -6221,7 +8335,7 @@
           <t>volta_com</t>
         </is>
       </c>
-      <c r="AN29" s="46" t="inlineStr">
+      <c r="AN29" s="60" t="inlineStr">
         <is>
           <t>V52</t>
         </is>
@@ -6271,475 +8385,475 @@
           <t>orcamento</t>
         </is>
       </c>
-      <c r="AN30" s="46" t="inlineStr">
+      <c r="AN30" s="60" t="inlineStr">
         <is>
           <t>D61</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="AM31" s="46" t="inlineStr">
+      <c r="AM31" s="60" t="inlineStr">
         <is>
           <t>gasto</t>
         </is>
       </c>
-      <c r="AN31" s="46" t="inlineStr">
+      <c r="AN31" s="60" t="inlineStr">
         <is>
           <t>D76</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="AM32" s="46" t="inlineStr">
+      <c r="AM32" s="60" t="inlineStr">
         <is>
           <t>sobra</t>
         </is>
       </c>
-      <c r="AN32" s="46" t="inlineStr">
+      <c r="AN32" s="60" t="inlineStr">
         <is>
           <t>L76</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="AM33" s="46" t="inlineStr">
+      <c r="AM33" s="60" t="inlineStr">
         <is>
           <t>investir</t>
         </is>
       </c>
-      <c r="AN33" s="46" t="inlineStr">
+      <c r="AN33" s="60" t="inlineStr">
         <is>
           <t>D84</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="AM34" s="46" t="inlineStr">
+      <c r="AM34" s="60" t="inlineStr">
         <is>
           <t>cd_pendente</t>
         </is>
       </c>
-      <c r="AN34" s="46" t="inlineStr">
+      <c r="AN34" s="60" t="inlineStr">
         <is>
           <t>D99</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="AM35" s="46" t="inlineStr">
+      <c r="AM35" s="60" t="inlineStr">
         <is>
           <t>atr_Força</t>
         </is>
       </c>
-      <c r="AN35" s="46" t="inlineStr">
+      <c r="AN35" s="60" t="inlineStr">
         <is>
           <t>D22</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="AM36" s="46" t="inlineStr">
+      <c r="AM36" s="60" t="inlineStr">
         <is>
           <t>atr_Destreza</t>
         </is>
       </c>
-      <c r="AN36" s="46" t="inlineStr">
+      <c r="AN36" s="60" t="inlineStr">
         <is>
           <t>K22</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="AM37" s="46" t="inlineStr">
+      <c r="AM37" s="60" t="inlineStr">
         <is>
           <t>atr_Constituição</t>
         </is>
       </c>
-      <c r="AN37" s="46" t="inlineStr">
+      <c r="AN37" s="60" t="inlineStr">
         <is>
           <t>R22</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="AM38" s="46" t="inlineStr">
+      <c r="AM38" s="60" t="inlineStr">
         <is>
           <t>atr_Inteligência</t>
         </is>
       </c>
-      <c r="AN38" s="46" t="inlineStr">
+      <c r="AN38" s="60" t="inlineStr">
         <is>
           <t>Y22</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="AM39" s="46" t="inlineStr">
+      <c r="AM39" s="60" t="inlineStr">
         <is>
           <t>atr_Essência</t>
         </is>
       </c>
-      <c r="AN39" s="46" t="inlineStr">
+      <c r="AN39" s="60" t="inlineStr">
         <is>
           <t>AF22</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="AM40" s="46" t="inlineStr">
+      <c r="AM40" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_1</t>
         </is>
       </c>
-      <c r="AN40" s="46" t="inlineStr">
+      <c r="AN40" s="60" t="inlineStr">
         <is>
           <t>Q65</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="AM41" s="46" t="inlineStr">
+      <c r="AM41" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_2</t>
         </is>
       </c>
-      <c r="AN41" s="46" t="inlineStr">
+      <c r="AN41" s="60" t="inlineStr">
         <is>
           <t>Q66</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="AM42" s="46" t="inlineStr">
+      <c r="AM42" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_3</t>
         </is>
       </c>
-      <c r="AN42" s="46" t="inlineStr">
+      <c r="AN42" s="60" t="inlineStr">
         <is>
           <t>Q67</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="AM43" s="46" t="inlineStr">
+      <c r="AM43" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_4</t>
         </is>
       </c>
-      <c r="AN43" s="46" t="inlineStr">
+      <c r="AN43" s="60" t="inlineStr">
         <is>
           <t>Q68</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="AM44" s="46" t="inlineStr">
+      <c r="AM44" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_5</t>
         </is>
       </c>
-      <c r="AN44" s="46" t="inlineStr">
+      <c r="AN44" s="60" t="inlineStr">
         <is>
           <t>Q69</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="AM45" s="46" t="inlineStr">
+      <c r="AM45" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_6</t>
         </is>
       </c>
-      <c r="AN45" s="46" t="inlineStr">
+      <c r="AN45" s="60" t="inlineStr">
         <is>
           <t>Q70</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="AM46" s="46" t="inlineStr">
+      <c r="AM46" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_7</t>
         </is>
       </c>
-      <c r="AN46" s="46" t="inlineStr">
+      <c r="AN46" s="60" t="inlineStr">
         <is>
           <t>Q71</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="AM47" s="46" t="inlineStr">
+      <c r="AM47" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_8</t>
         </is>
       </c>
-      <c r="AN47" s="46" t="inlineStr">
+      <c r="AN47" s="60" t="inlineStr">
         <is>
           <t>Q72</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="AM48" s="46" t="inlineStr">
+      <c r="AM48" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_9</t>
         </is>
       </c>
-      <c r="AN48" s="46" t="inlineStr">
+      <c r="AN48" s="60" t="inlineStr">
         <is>
           <t>Q73</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="AM49" s="46" t="inlineStr">
+      <c r="AM49" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_10</t>
         </is>
       </c>
-      <c r="AN49" s="46" t="inlineStr">
+      <c r="AN49" s="60" t="inlineStr">
         <is>
           <t>AM65</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="AM50" s="46" t="inlineStr">
+      <c r="AM50" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_11</t>
         </is>
       </c>
-      <c r="AN50" s="46" t="inlineStr">
+      <c r="AN50" s="60" t="inlineStr">
         <is>
           <t>AM66</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="AM51" s="46" t="inlineStr">
+      <c r="AM51" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_12</t>
         </is>
       </c>
-      <c r="AN51" s="46" t="inlineStr">
+      <c r="AN51" s="60" t="inlineStr">
         <is>
           <t>AM67</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="AM52" s="46" t="inlineStr">
+      <c r="AM52" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_13</t>
         </is>
       </c>
-      <c r="AN52" s="46" t="inlineStr">
+      <c r="AN52" s="60" t="inlineStr">
         <is>
           <t>AM68</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="AM53" s="46" t="inlineStr">
+      <c r="AM53" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_14</t>
         </is>
       </c>
-      <c r="AN53" s="46" t="inlineStr">
+      <c r="AN53" s="60" t="inlineStr">
         <is>
           <t>AM69</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="AM54" s="46" t="inlineStr">
+      <c r="AM54" s="60" t="inlineStr">
         <is>
           <t>slot_pontos_15</t>
         </is>
       </c>
-      <c r="AN54" s="46" t="inlineStr">
+      <c r="AN54" s="60" t="inlineStr">
         <is>
           <t>AM70</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="AM55" s="46" t="inlineStr">
+      <c r="AM55" s="60" t="inlineStr">
         <is>
           <t>traco_1</t>
         </is>
       </c>
-      <c r="AN55" s="46" t="inlineStr">
+      <c r="AN55" s="60" t="inlineStr">
         <is>
           <t>D65</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="AM56" s="46" t="inlineStr">
+      <c r="AM56" s="60" t="inlineStr">
         <is>
           <t>traco_2</t>
         </is>
       </c>
-      <c r="AN56" s="46" t="inlineStr">
+      <c r="AN56" s="60" t="inlineStr">
         <is>
           <t>D66</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="AM57" s="46" t="inlineStr">
+      <c r="AM57" s="60" t="inlineStr">
         <is>
           <t>traco_3</t>
         </is>
       </c>
-      <c r="AN57" s="46" t="inlineStr">
+      <c r="AN57" s="60" t="inlineStr">
         <is>
           <t>D67</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="AM58" s="46" t="inlineStr">
+      <c r="AM58" s="60" t="inlineStr">
         <is>
           <t>traco_4</t>
         </is>
       </c>
-      <c r="AN58" s="46" t="inlineStr">
+      <c r="AN58" s="60" t="inlineStr">
         <is>
           <t>D68</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="AM59" s="46" t="inlineStr">
+      <c r="AM59" s="60" t="inlineStr">
         <is>
           <t>traco_5</t>
         </is>
       </c>
-      <c r="AN59" s="46" t="inlineStr">
+      <c r="AN59" s="60" t="inlineStr">
         <is>
           <t>D69</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="AM60" s="46" t="inlineStr">
+      <c r="AM60" s="60" t="inlineStr">
         <is>
           <t>traco_6</t>
         </is>
       </c>
-      <c r="AN60" s="46" t="inlineStr">
+      <c r="AN60" s="60" t="inlineStr">
         <is>
           <t>D70</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="AM61" s="46" t="inlineStr">
+      <c r="AM61" s="60" t="inlineStr">
         <is>
           <t>traco_7</t>
         </is>
       </c>
-      <c r="AN61" s="46" t="inlineStr">
+      <c r="AN61" s="60" t="inlineStr">
         <is>
           <t>D71</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="AM62" s="46" t="inlineStr">
+      <c r="AM62" s="60" t="inlineStr">
         <is>
           <t>traco_8</t>
         </is>
       </c>
-      <c r="AN62" s="46" t="inlineStr">
+      <c r="AN62" s="60" t="inlineStr">
         <is>
           <t>D72</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="AM63" s="46" t="inlineStr">
+      <c r="AM63" s="60" t="inlineStr">
         <is>
           <t>traco_9</t>
         </is>
       </c>
-      <c r="AN63" s="46" t="inlineStr">
+      <c r="AN63" s="60" t="inlineStr">
         <is>
           <t>D73</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="AM64" s="46" t="inlineStr">
+      <c r="AM64" s="60" t="inlineStr">
         <is>
           <t>comando_1</t>
         </is>
       </c>
-      <c r="AN64" s="46" t="inlineStr">
+      <c r="AN64" s="60" t="inlineStr">
         <is>
           <t>Z65</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="AM65" s="46" t="inlineStr">
+      <c r="AM65" s="60" t="inlineStr">
         <is>
           <t>comando_2</t>
         </is>
       </c>
-      <c r="AN65" s="46" t="inlineStr">
+      <c r="AN65" s="60" t="inlineStr">
         <is>
           <t>Z66</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="AM66" s="46" t="inlineStr">
+      <c r="AM66" s="60" t="inlineStr">
         <is>
           <t>comando_3</t>
         </is>
       </c>
-      <c r="AN66" s="46" t="inlineStr">
+      <c r="AN66" s="60" t="inlineStr">
         <is>
           <t>Z67</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="AM67" s="46" t="inlineStr">
+      <c r="AM67" s="60" t="inlineStr">
         <is>
           <t>comando_4</t>
         </is>
       </c>
-      <c r="AN67" s="46" t="inlineStr">
+      <c r="AN67" s="60" t="inlineStr">
         <is>
           <t>Z68</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="AM68" s="46" t="inlineStr">
+      <c r="AM68" s="60" t="inlineStr">
         <is>
           <t>comando_5</t>
         </is>
       </c>
-      <c r="AN68" s="46" t="inlineStr">
+      <c r="AN68" s="60" t="inlineStr">
         <is>
           <t>Z69</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="AM69" s="46" t="inlineStr">
+      <c r="AM69" s="60" t="inlineStr">
         <is>
           <t>comando_6</t>
         </is>
       </c>
-      <c r="AN69" s="46" t="inlineStr">
+      <c r="AN69" s="60" t="inlineStr">
         <is>
           <t>Z70</t>
         </is>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -57,7 +57,7 @@
     </font>
     <font>
       <name val="Oswald"/>
-      <color rgb="0030294D"/>
+      <color rgb="003D2E78"/>
       <sz val="22"/>
     </font>
     <font>
@@ -212,14 +212,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0030294D"/>
-        <bgColor rgb="0030294D"/>
+        <fgColor rgb="003D2E78"/>
+        <bgColor rgb="003D2E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00211C35"/>
-        <bgColor rgb="00211C35"/>
+        <fgColor rgb="001E1733"/>
+        <bgColor rgb="001E1733"/>
       </patternFill>
     </fill>
   </fills>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Roboto"/>
       <color rgb="00F4F1F7"/>
@@ -118,17 +118,22 @@
     <font>
       <name val="Castoro"/>
       <color rgb="00E8DCD4"/>
+      <sz val="6"/>
+    </font>
+    <font>
+      <name val="Castoro"/>
+      <color rgb="00E8DCD4"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Oswald"/>
+      <color rgb="00E8DCD4"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Oswald"/>
       <color rgb="00998BA9"/>
       <sz val="8"/>
-    </font>
-    <font>
-      <name val="Oswald"/>
-      <color rgb="00E8DCD4"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Oswald"/>
@@ -206,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -268,19 +273,31 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -289,34 +306,34 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -328,10 +345,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2082,7 +2099,7 @@
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="C48" s="5" t="n"/>
-      <c r="D48" s="22" t="inlineStr">
+      <c r="D48" s="15" t="inlineStr">
         <is>
           <t>OS QUATRO TESTES DE RESISTÊNCIA · ela treina UM, e a sua maestria entra só nele</t>
         </is>
@@ -2092,82 +2109,88 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="1" t="n"/>
       <c r="C49" s="5" t="n"/>
-      <c r="D49" s="23" t="inlineStr">
-        <is>
-          <t>Físico</t>
-        </is>
-      </c>
-      <c r="P49" s="24" t="inlineStr">
-        <is>
-          <t>For ou Des</t>
-        </is>
-      </c>
-      <c r="R49" s="25">
-        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH($Z$46,DADOS!$C$2:$C$6,0))+IF($O$46="Físico",$AK$7,0),"")</f>
-        <v/>
-      </c>
-      <c r="U49" s="5" t="n"/>
-      <c r="V49" s="5" t="n"/>
-      <c r="W49" s="5" t="n"/>
-      <c r="X49" s="5" t="n"/>
-      <c r="Y49" s="23" t="inlineStr">
-        <is>
-          <t>Vigor</t>
-        </is>
-      </c>
-      <c r="AK49" s="24" t="inlineStr">
-        <is>
-          <t>Con</t>
-        </is>
-      </c>
-      <c r="AM49" s="25">
-        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Constituição",DADOS!$C$2:$C$6,0))+IF($O$46="Vigor",$AK$7,0),"")</f>
-        <v/>
-      </c>
-      <c r="AP49" s="5" t="n"/>
-      <c r="AQ49" s="5" t="n"/>
-      <c r="AR49" s="5" t="n"/>
-      <c r="AS49" s="5" t="n"/>
-      <c r="AT49" s="5" t="n"/>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="K49" s="23" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="24" t="inlineStr">
+        <is>
+          <t>d20 +</t>
+        </is>
+      </c>
+      <c r="Y49" s="5" t="n"/>
+      <c r="Z49" s="22" t="inlineStr">
+        <is>
+          <t>TESTE</t>
+        </is>
+      </c>
+      <c r="AG49" s="23" t="inlineStr">
+        <is>
+          <t>Extra</t>
+        </is>
+      </c>
+      <c r="AH49" s="8" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="AM49" s="2" t="n"/>
+      <c r="AN49" s="24" t="inlineStr">
+        <is>
+          <t>d20 +</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="1" t="n"/>
       <c r="C50" s="5" t="n"/>
-      <c r="D50" s="26" t="inlineStr">
-        <is>
-          <t>Intelecto</t>
-        </is>
-      </c>
-      <c r="P50" s="27" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="R50" s="28">
-        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Inteligência",DADOS!$C$2:$C$6,0))+IF($O$46="Intelecto",$AK$7,0),"")</f>
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>Físico</t>
+        </is>
+      </c>
+      <c r="K50" s="26" t="n"/>
+      <c r="L50" s="27" t="inlineStr">
+        <is>
+          <t>For ou Des</t>
+        </is>
+      </c>
+      <c r="Q50" s="28">
+        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH($Z$46,DADOS!$C$2:$C$6,0))+IF($O$46="Físico",$AK$7,0)+N($K$50),"")</f>
         <v/>
       </c>
-      <c r="U50" s="5" t="n"/>
       <c r="V50" s="5" t="n"/>
       <c r="W50" s="5" t="n"/>
       <c r="X50" s="5" t="n"/>
-      <c r="Y50" s="26" t="inlineStr">
-        <is>
-          <t>Espírito</t>
-        </is>
-      </c>
-      <c r="AK50" s="27" t="inlineStr">
-        <is>
-          <t>Ess</t>
+      <c r="Y50" s="5" t="n"/>
+      <c r="Z50" s="25" t="inlineStr">
+        <is>
+          <t>Vigor</t>
+        </is>
+      </c>
+      <c r="AG50" s="26" t="n"/>
+      <c r="AH50" s="27" t="inlineStr">
+        <is>
+          <t>Con</t>
         </is>
       </c>
       <c r="AM50" s="28">
-        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Essência",DADOS!$C$2:$C$6,0))+IF($O$46="Espírito",$AK$7,0),"")</f>
+        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Constituição",DADOS!$C$2:$C$6,0))+IF($O$46="Vigor",$AK$7,0)+N($AG$50),"")</f>
         <v/>
       </c>
-      <c r="AP50" s="5" t="n"/>
-      <c r="AQ50" s="5" t="n"/>
       <c r="AR50" s="5" t="n"/>
       <c r="AS50" s="5" t="n"/>
       <c r="AT50" s="5" t="n"/>
@@ -2176,46 +2199,40 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="1" t="n"/>
       <c r="C51" s="5" t="n"/>
-      <c r="D51" s="5" t="n"/>
-      <c r="E51" s="5" t="n"/>
-      <c r="F51" s="5" t="n"/>
-      <c r="G51" s="5" t="n"/>
-      <c r="H51" s="5" t="n"/>
-      <c r="I51" s="5" t="n"/>
-      <c r="J51" s="5" t="n"/>
-      <c r="K51" s="5" t="n"/>
-      <c r="L51" s="5" t="n"/>
-      <c r="M51" s="5" t="n"/>
-      <c r="N51" s="5" t="n"/>
-      <c r="O51" s="5" t="n"/>
-      <c r="P51" s="5" t="n"/>
-      <c r="Q51" s="5" t="n"/>
-      <c r="R51" s="5" t="n"/>
-      <c r="S51" s="5" t="n"/>
-      <c r="T51" s="5" t="n"/>
-      <c r="U51" s="5" t="n"/>
+      <c r="D51" s="29" t="inlineStr">
+        <is>
+          <t>Intelecto</t>
+        </is>
+      </c>
+      <c r="K51" s="30" t="n"/>
+      <c r="L51" s="31" t="inlineStr">
+        <is>
+          <t>Int</t>
+        </is>
+      </c>
+      <c r="Q51" s="32">
+        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Inteligência",DADOS!$C$2:$C$6,0))+IF($O$46="Intelecto",$AK$7,0)+N($K$51),"")</f>
+        <v/>
+      </c>
       <c r="V51" s="5" t="n"/>
       <c r="W51" s="5" t="n"/>
       <c r="X51" s="5" t="n"/>
       <c r="Y51" s="5" t="n"/>
-      <c r="Z51" s="5" t="n"/>
-      <c r="AA51" s="5" t="n"/>
-      <c r="AB51" s="5" t="n"/>
-      <c r="AC51" s="5" t="n"/>
-      <c r="AD51" s="5" t="n"/>
-      <c r="AE51" s="5" t="n"/>
-      <c r="AF51" s="5" t="n"/>
-      <c r="AG51" s="5" t="n"/>
-      <c r="AH51" s="5" t="n"/>
-      <c r="AI51" s="5" t="n"/>
-      <c r="AJ51" s="5" t="n"/>
-      <c r="AK51" s="5" t="n"/>
-      <c r="AL51" s="5" t="n"/>
-      <c r="AM51" s="5" t="n"/>
-      <c r="AN51" s="5" t="n"/>
-      <c r="AO51" s="5" t="n"/>
-      <c r="AP51" s="5" t="n"/>
-      <c r="AQ51" s="5" t="n"/>
+      <c r="Z51" s="29" t="inlineStr">
+        <is>
+          <t>Espírito</t>
+        </is>
+      </c>
+      <c r="AG51" s="30" t="n"/>
+      <c r="AH51" s="31" t="inlineStr">
+        <is>
+          <t>Ess</t>
+        </is>
+      </c>
+      <c r="AM51" s="32">
+        <f>IFERROR(INDEX(DADOS!$AK$3:$AK$7,MATCH("Essência",DADOS!$C$2:$C$6,0))+IF($O$46="Espírito",$AK$7,0)+N($AG$51),"")</f>
+        <v/>
+      </c>
       <c r="AR51" s="5" t="n"/>
       <c r="AS51" s="5" t="n"/>
       <c r="AT51" s="5" t="n"/>
@@ -2224,79 +2241,86 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="1" t="n"/>
       <c r="C52" s="5" t="n"/>
-      <c r="D52" s="12" t="inlineStr">
-        <is>
-          <t>Acerto e Teste de Resistência rolam d20 + isto. A Defesa é passiva, e a maestria não entra nela.</t>
-        </is>
-      </c>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="n"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="n"/>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
+      <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="5" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="5" t="n"/>
+      <c r="U52" s="5" t="n"/>
+      <c r="V52" s="5" t="n"/>
+      <c r="W52" s="5" t="n"/>
+      <c r="X52" s="5" t="n"/>
+      <c r="Y52" s="5" t="n"/>
+      <c r="Z52" s="5" t="n"/>
+      <c r="AA52" s="5" t="n"/>
+      <c r="AB52" s="5" t="n"/>
+      <c r="AC52" s="5" t="n"/>
+      <c r="AD52" s="5" t="n"/>
+      <c r="AE52" s="5" t="n"/>
+      <c r="AF52" s="5" t="n"/>
+      <c r="AG52" s="5" t="n"/>
+      <c r="AH52" s="5" t="n"/>
+      <c r="AI52" s="5" t="n"/>
+      <c r="AJ52" s="5" t="n"/>
+      <c r="AK52" s="5" t="n"/>
+      <c r="AL52" s="5" t="n"/>
+      <c r="AM52" s="5" t="n"/>
+      <c r="AN52" s="5" t="n"/>
+      <c r="AO52" s="5" t="n"/>
+      <c r="AP52" s="5" t="n"/>
+      <c r="AQ52" s="5" t="n"/>
+      <c r="AR52" s="5" t="n"/>
+      <c r="AS52" s="5" t="n"/>
+      <c r="AT52" s="5" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="1" t="n"/>
       <c r="B53" s="1" t="n"/>
       <c r="C53" s="5" t="n"/>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Acerto e Teste de Resistência rolam d20 + isto, e o Extra entra na conta — é onde entra o que a ficha não sabe. A Defesa é passiva, e a maestria não entra nela.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="1" t="n"/>
       <c r="B54" s="1" t="n"/>
       <c r="C54" s="5" t="n"/>
-      <c r="D54" s="5" t="n"/>
-      <c r="E54" s="5" t="n"/>
-      <c r="F54" s="5" t="n"/>
-      <c r="G54" s="5" t="n"/>
-      <c r="H54" s="5" t="n"/>
-      <c r="I54" s="5" t="n"/>
-      <c r="J54" s="5" t="n"/>
-      <c r="K54" s="5" t="n"/>
-      <c r="L54" s="5" t="n"/>
-      <c r="M54" s="5" t="n"/>
-      <c r="N54" s="5" t="n"/>
-      <c r="O54" s="5" t="n"/>
-      <c r="P54" s="5" t="n"/>
-      <c r="Q54" s="5" t="n"/>
-      <c r="R54" s="5" t="n"/>
-      <c r="S54" s="5" t="n"/>
-      <c r="T54" s="5" t="n"/>
-      <c r="U54" s="5" t="n"/>
-      <c r="V54" s="5" t="n"/>
-      <c r="W54" s="5" t="n"/>
-      <c r="X54" s="5" t="n"/>
-      <c r="Y54" s="5" t="n"/>
-      <c r="Z54" s="5" t="n"/>
-      <c r="AA54" s="5" t="n"/>
-      <c r="AB54" s="5" t="n"/>
-      <c r="AC54" s="5" t="n"/>
-      <c r="AD54" s="5" t="n"/>
-      <c r="AE54" s="5" t="n"/>
-      <c r="AF54" s="5" t="n"/>
-      <c r="AG54" s="5" t="n"/>
-      <c r="AH54" s="5" t="n"/>
-      <c r="AI54" s="5" t="n"/>
-      <c r="AJ54" s="5" t="n"/>
-      <c r="AK54" s="5" t="n"/>
-      <c r="AL54" s="5" t="n"/>
-      <c r="AM54" s="5" t="n"/>
-      <c r="AN54" s="5" t="n"/>
-      <c r="AO54" s="5" t="n"/>
-      <c r="AP54" s="5" t="n"/>
-      <c r="AQ54" s="5" t="n"/>
-      <c r="AR54" s="5" t="n"/>
-      <c r="AS54" s="5" t="n"/>
-      <c r="AT54" s="5" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="1" t="n"/>
       <c r="B55" s="1" t="n"/>
       <c r="C55" s="5" t="n"/>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>VIDA E MORTE</t>
-        </is>
-      </c>
+      <c r="D55" s="5" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="5" t="n"/>
+      <c r="H55" s="5" t="n"/>
+      <c r="I55" s="5" t="n"/>
+      <c r="J55" s="5" t="n"/>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
+      <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="5" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="5" t="n"/>
       <c r="U55" s="5" t="n"/>
       <c r="V55" s="5" t="n"/>
       <c r="W55" s="5" t="n"/>
@@ -2328,20 +2352,16 @@
       <c r="A56" s="1" t="n"/>
       <c r="B56" s="1" t="n"/>
       <c r="C56" s="5" t="n"/>
-      <c r="G56" s="5" t="n"/>
-      <c r="H56" s="5" t="n"/>
-      <c r="I56" s="5" t="n"/>
-      <c r="J56" s="5" t="n"/>
-      <c r="K56" s="5" t="n"/>
-      <c r="L56" s="5" t="n"/>
-      <c r="M56" s="5" t="n"/>
-      <c r="N56" s="5" t="n"/>
-      <c r="O56" s="5" t="n"/>
-      <c r="P56" s="5" t="n"/>
-      <c r="Q56" s="5" t="n"/>
-      <c r="R56" s="5" t="n"/>
-      <c r="S56" s="5" t="n"/>
-      <c r="T56" s="5" t="n"/>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>VIDA E MORTE</t>
+        </is>
+      </c>
       <c r="U56" s="5" t="n"/>
       <c r="V56" s="5" t="n"/>
       <c r="W56" s="5" t="n"/>
@@ -2373,190 +2393,202 @@
       <c r="A57" s="1" t="n"/>
       <c r="B57" s="1" t="n"/>
       <c r="C57" s="5" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>VIDA MÁXIMA</t>
-        </is>
-      </c>
+      <c r="G57" s="5" t="n"/>
+      <c r="H57" s="5" t="n"/>
+      <c r="I57" s="5" t="n"/>
+      <c r="J57" s="5" t="n"/>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
       <c r="N57" s="5" t="n"/>
-      <c r="O57" s="8" t="inlineStr">
-        <is>
-          <t>VIDA AGORA</t>
-        </is>
-      </c>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="5" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="5" t="n"/>
+      <c r="U57" s="5" t="n"/>
+      <c r="V57" s="5" t="n"/>
+      <c r="W57" s="5" t="n"/>
+      <c r="X57" s="5" t="n"/>
       <c r="Y57" s="5" t="n"/>
-      <c r="Z57" s="8" t="inlineStr">
-        <is>
-          <t>CORPOS EM CAMPO</t>
-        </is>
-      </c>
+      <c r="Z57" s="5" t="n"/>
+      <c r="AA57" s="5" t="n"/>
+      <c r="AB57" s="5" t="n"/>
+      <c r="AC57" s="5" t="n"/>
+      <c r="AD57" s="5" t="n"/>
+      <c r="AE57" s="5" t="n"/>
+      <c r="AF57" s="5" t="n"/>
+      <c r="AG57" s="5" t="n"/>
+      <c r="AH57" s="5" t="n"/>
+      <c r="AI57" s="5" t="n"/>
       <c r="AJ57" s="5" t="n"/>
-      <c r="AK57" s="8" t="inlineStr">
-        <is>
-          <t>ÁREA BATE ×</t>
-        </is>
-      </c>
+      <c r="AK57" s="5" t="n"/>
+      <c r="AL57" s="5" t="n"/>
+      <c r="AM57" s="5" t="n"/>
+      <c r="AN57" s="5" t="n"/>
+      <c r="AO57" s="5" t="n"/>
+      <c r="AP57" s="5" t="n"/>
+      <c r="AQ57" s="5" t="n"/>
+      <c r="AR57" s="5" t="n"/>
+      <c r="AS57" s="5" t="n"/>
+      <c r="AT57" s="5" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="1" t="n"/>
       <c r="B58" s="1" t="n"/>
       <c r="C58" s="5" t="n"/>
-      <c r="D58" s="9">
-        <f>IF($Z$19="","",IF(IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,4,FALSE),"cru")="forte",FLOOR(2.5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+2*$D$7)+$T$30*$D$7,1),(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))+IF($D$22="Parrudo",5*$AK$7,0))</f>
-        <v/>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>VIDA MÁXIMA</t>
+        </is>
       </c>
       <c r="N58" s="5" t="n"/>
-      <c r="O58" s="9" t="n"/>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>VIDA AGORA</t>
+        </is>
+      </c>
       <c r="Y58" s="5" t="n"/>
-      <c r="Z58" s="10">
-        <f>IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,2,FALSE),"")</f>
-        <v/>
+      <c r="Z58" s="8" t="inlineStr">
+        <is>
+          <t>CORPOS EM CAMPO</t>
+        </is>
       </c>
       <c r="AJ58" s="5" t="n"/>
-      <c r="AK58" s="10">
-        <f>IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,5,FALSE),"")</f>
-        <v/>
+      <c r="AK58" s="8" t="inlineStr">
+        <is>
+          <t>ÁREA BATE ×</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="1" t="n"/>
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="5" t="n"/>
+      <c r="D59" s="9">
+        <f>IF($Z$19="","",IF(IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,4,FALSE),"cru")="forte",FLOOR(2.5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+2*$D$7)+$T$30*$D$7,1),(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))+IF($D$22="Parrudo",5*$AK$7,0))</f>
+        <v/>
+      </c>
       <c r="N59" s="5" t="n"/>
+      <c r="O59" s="9" t="n"/>
       <c r="Y59" s="5" t="n"/>
+      <c r="Z59" s="10">
+        <f>IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,2,FALSE),"")</f>
+        <v/>
+      </c>
       <c r="AJ59" s="5" t="n"/>
+      <c r="AK59" s="10">
+        <f>IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,5,FALSE),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="1" t="n"/>
       <c r="B60" s="1" t="n"/>
       <c r="C60" s="5" t="n"/>
-      <c r="D60" s="5" t="n"/>
-      <c r="E60" s="5" t="n"/>
-      <c r="F60" s="5" t="n"/>
-      <c r="G60" s="5" t="n"/>
-      <c r="H60" s="5" t="n"/>
-      <c r="I60" s="5" t="n"/>
-      <c r="J60" s="5" t="n"/>
-      <c r="K60" s="5" t="n"/>
-      <c r="L60" s="5" t="n"/>
-      <c r="M60" s="5" t="n"/>
       <c r="N60" s="5" t="n"/>
-      <c r="O60" s="5" t="n"/>
-      <c r="P60" s="5" t="n"/>
-      <c r="Q60" s="5" t="n"/>
-      <c r="R60" s="5" t="n"/>
-      <c r="S60" s="5" t="n"/>
-      <c r="T60" s="5" t="n"/>
-      <c r="U60" s="5" t="n"/>
-      <c r="V60" s="5" t="n"/>
-      <c r="W60" s="5" t="n"/>
-      <c r="X60" s="5" t="n"/>
       <c r="Y60" s="5" t="n"/>
-      <c r="Z60" s="5" t="n"/>
-      <c r="AA60" s="5" t="n"/>
-      <c r="AB60" s="5" t="n"/>
-      <c r="AC60" s="5" t="n"/>
-      <c r="AD60" s="5" t="n"/>
-      <c r="AE60" s="5" t="n"/>
-      <c r="AF60" s="5" t="n"/>
-      <c r="AG60" s="5" t="n"/>
-      <c r="AH60" s="5" t="n"/>
-      <c r="AI60" s="5" t="n"/>
       <c r="AJ60" s="5" t="n"/>
-      <c r="AK60" s="5" t="n"/>
-      <c r="AL60" s="5" t="n"/>
-      <c r="AM60" s="5" t="n"/>
-      <c r="AN60" s="5" t="n"/>
-      <c r="AO60" s="5" t="n"/>
-      <c r="AP60" s="5" t="n"/>
-      <c r="AQ60" s="5" t="n"/>
-      <c r="AR60" s="5" t="n"/>
-      <c r="AS60" s="5" t="n"/>
-      <c r="AT60" s="5" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="1" t="n"/>
       <c r="B61" s="1" t="n"/>
       <c r="C61" s="5" t="n"/>
-      <c r="D61" s="22" t="inlineStr">
-        <is>
-          <t>A BARRA</t>
-        </is>
-      </c>
-      <c r="O61" s="29">
-        <f>IFERROR(SPARKLINE($O$58,{"charttype","bar";"max",$D$58;"color1",IF(N($D$58)=0,"#E8DCD4",IF($O$58/$D$58&lt;=0.25,"#C2334D",IF($O$58/$D$58&lt;=0.5,"#D89B3A","#E8DCD4")))}),"")</f>
-        <v/>
-      </c>
+      <c r="D61" s="5" t="n"/>
+      <c r="E61" s="5" t="n"/>
+      <c r="F61" s="5" t="n"/>
+      <c r="G61" s="5" t="n"/>
+      <c r="H61" s="5" t="n"/>
+      <c r="I61" s="5" t="n"/>
+      <c r="J61" s="5" t="n"/>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="5" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="5" t="n"/>
+      <c r="U61" s="5" t="n"/>
+      <c r="V61" s="5" t="n"/>
+      <c r="W61" s="5" t="n"/>
+      <c r="X61" s="5" t="n"/>
+      <c r="Y61" s="5" t="n"/>
+      <c r="Z61" s="5" t="n"/>
+      <c r="AA61" s="5" t="n"/>
+      <c r="AB61" s="5" t="n"/>
+      <c r="AC61" s="5" t="n"/>
+      <c r="AD61" s="5" t="n"/>
+      <c r="AE61" s="5" t="n"/>
+      <c r="AF61" s="5" t="n"/>
+      <c r="AG61" s="5" t="n"/>
+      <c r="AH61" s="5" t="n"/>
+      <c r="AI61" s="5" t="n"/>
+      <c r="AJ61" s="5" t="n"/>
+      <c r="AK61" s="5" t="n"/>
+      <c r="AL61" s="5" t="n"/>
+      <c r="AM61" s="5" t="n"/>
+      <c r="AN61" s="5" t="n"/>
+      <c r="AO61" s="5" t="n"/>
+      <c r="AP61" s="5" t="n"/>
+      <c r="AQ61" s="5" t="n"/>
+      <c r="AR61" s="5" t="n"/>
+      <c r="AS61" s="5" t="n"/>
+      <c r="AT61" s="5" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="1" t="n"/>
       <c r="B62" s="1" t="n"/>
       <c r="C62" s="5" t="n"/>
-      <c r="D62" s="5" t="n"/>
-      <c r="E62" s="5" t="n"/>
-      <c r="F62" s="5" t="n"/>
-      <c r="G62" s="5" t="n"/>
-      <c r="H62" s="5" t="n"/>
-      <c r="I62" s="5" t="n"/>
-      <c r="J62" s="5" t="n"/>
-      <c r="K62" s="5" t="n"/>
-      <c r="L62" s="5" t="n"/>
-      <c r="M62" s="5" t="n"/>
-      <c r="N62" s="5" t="n"/>
-      <c r="O62" s="5" t="n"/>
-      <c r="P62" s="5" t="n"/>
-      <c r="Q62" s="5" t="n"/>
-      <c r="R62" s="5" t="n"/>
-      <c r="S62" s="5" t="n"/>
-      <c r="T62" s="5" t="n"/>
-      <c r="U62" s="5" t="n"/>
-      <c r="V62" s="5" t="n"/>
-      <c r="W62" s="5" t="n"/>
-      <c r="X62" s="5" t="n"/>
-      <c r="Y62" s="5" t="n"/>
-      <c r="Z62" s="5" t="n"/>
-      <c r="AA62" s="5" t="n"/>
-      <c r="AB62" s="5" t="n"/>
-      <c r="AC62" s="5" t="n"/>
-      <c r="AD62" s="5" t="n"/>
-      <c r="AE62" s="5" t="n"/>
-      <c r="AF62" s="5" t="n"/>
-      <c r="AG62" s="5" t="n"/>
-      <c r="AH62" s="5" t="n"/>
-      <c r="AI62" s="5" t="n"/>
-      <c r="AJ62" s="5" t="n"/>
-      <c r="AK62" s="5" t="n"/>
-      <c r="AL62" s="5" t="n"/>
-      <c r="AM62" s="5" t="n"/>
-      <c r="AN62" s="5" t="n"/>
-      <c r="AO62" s="5" t="n"/>
-      <c r="AP62" s="5" t="n"/>
-      <c r="AQ62" s="5" t="n"/>
-      <c r="AR62" s="5" t="n"/>
-      <c r="AS62" s="5" t="n"/>
-      <c r="AT62" s="5" t="n"/>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>A BARRA</t>
+        </is>
+      </c>
+      <c r="O62" s="33">
+        <f>IFERROR(SPARKLINE($O$59,{"charttype","bar";"max",$D$59;"color1",IF(N($D$59)=0,"#E8DCD4",IF($O$59/$D$59&lt;=0.25,"#C2334D",IF($O$59/$D$59&lt;=0.5,"#D89B3A","#E8DCD4")))}),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="1" t="n"/>
       <c r="B63" s="1" t="n"/>
       <c r="C63" s="5" t="n"/>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>RÉGUA DA MORTE</t>
-        </is>
-      </c>
+      <c r="D63" s="5" t="n"/>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="n"/>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="n"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="n"/>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
       <c r="N63" s="5" t="n"/>
-      <c r="O63" s="8" t="inlineStr">
-        <is>
-          <t>METADE DELA</t>
-        </is>
-      </c>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="5" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="5" t="n"/>
+      <c r="U63" s="5" t="n"/>
+      <c r="V63" s="5" t="n"/>
+      <c r="W63" s="5" t="n"/>
+      <c r="X63" s="5" t="n"/>
       <c r="Y63" s="5" t="n"/>
-      <c r="Z63" s="8" t="inlineStr">
-        <is>
-          <t>VOLTA COM</t>
-        </is>
-      </c>
+      <c r="Z63" s="5" t="n"/>
+      <c r="AA63" s="5" t="n"/>
+      <c r="AB63" s="5" t="n"/>
+      <c r="AC63" s="5" t="n"/>
+      <c r="AD63" s="5" t="n"/>
+      <c r="AE63" s="5" t="n"/>
+      <c r="AF63" s="5" t="n"/>
+      <c r="AG63" s="5" t="n"/>
+      <c r="AH63" s="5" t="n"/>
+      <c r="AI63" s="5" t="n"/>
       <c r="AJ63" s="5" t="n"/>
       <c r="AK63" s="5" t="n"/>
       <c r="AL63" s="5" t="n"/>
@@ -2573,19 +2605,22 @@
       <c r="A64" s="1" t="n"/>
       <c r="B64" s="1" t="n"/>
       <c r="C64" s="5" t="n"/>
-      <c r="D64" s="10">
-        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))</f>
-        <v/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>RÉGUA DA MORTE</t>
+        </is>
       </c>
       <c r="N64" s="5" t="n"/>
-      <c r="O64" s="10">
-        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7)/2)</f>
-        <v/>
+      <c r="O64" s="8" t="inlineStr">
+        <is>
+          <t>METADE DELA</t>
+        </is>
       </c>
       <c r="Y64" s="5" t="n"/>
-      <c r="Z64" s="10">
-        <f>IF($Z$19="","",FLOOR($D$58/2,1))</f>
-        <v/>
+      <c r="Z64" s="8" t="inlineStr">
+        <is>
+          <t>VOLTA COM</t>
+        </is>
       </c>
       <c r="AJ64" s="5" t="n"/>
       <c r="AK64" s="5" t="n"/>
@@ -2603,38 +2638,20 @@
       <c r="A65" s="1" t="n"/>
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="5" t="n"/>
-      <c r="D65" s="5" t="n"/>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
+      <c r="D65" s="10">
+        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))</f>
+        <v/>
+      </c>
       <c r="N65" s="5" t="n"/>
-      <c r="O65" s="5" t="n"/>
-      <c r="P65" s="5" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
-      <c r="S65" s="5" t="n"/>
-      <c r="T65" s="5" t="n"/>
-      <c r="U65" s="5" t="n"/>
-      <c r="V65" s="5" t="n"/>
-      <c r="W65" s="5" t="n"/>
-      <c r="X65" s="5" t="n"/>
+      <c r="O65" s="10">
+        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7)/2)</f>
+        <v/>
+      </c>
       <c r="Y65" s="5" t="n"/>
-      <c r="Z65" s="5" t="n"/>
-      <c r="AA65" s="5" t="n"/>
-      <c r="AB65" s="5" t="n"/>
-      <c r="AC65" s="5" t="n"/>
-      <c r="AD65" s="5" t="n"/>
-      <c r="AE65" s="5" t="n"/>
-      <c r="AF65" s="5" t="n"/>
-      <c r="AG65" s="5" t="n"/>
-      <c r="AH65" s="5" t="n"/>
-      <c r="AI65" s="5" t="n"/>
+      <c r="Z65" s="10">
+        <f>IF($Z$19="","",FLOOR($D$59/2,1))</f>
+        <v/>
+      </c>
       <c r="AJ65" s="5" t="n"/>
       <c r="AK65" s="5" t="n"/>
       <c r="AL65" s="5" t="n"/>
@@ -2651,19 +2668,57 @@
       <c r="A66" s="1" t="n"/>
       <c r="B66" s="1" t="n"/>
       <c r="C66" s="5" t="n"/>
-      <c r="D66" s="30" t="inlineStr">
-        <is>
-          <t>MORRE DE VEZ SE</t>
-        </is>
-      </c>
+      <c r="D66" s="5" t="n"/>
+      <c r="E66" s="5" t="n"/>
+      <c r="F66" s="5" t="n"/>
+      <c r="G66" s="5" t="n"/>
+      <c r="H66" s="5" t="n"/>
+      <c r="I66" s="5" t="n"/>
+      <c r="J66" s="5" t="n"/>
+      <c r="K66" s="5" t="n"/>
+      <c r="L66" s="5" t="n"/>
+      <c r="M66" s="5" t="n"/>
+      <c r="N66" s="5" t="n"/>
+      <c r="O66" s="5" t="n"/>
+      <c r="P66" s="5" t="n"/>
+      <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="5" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="5" t="n"/>
+      <c r="U66" s="5" t="n"/>
+      <c r="V66" s="5" t="n"/>
+      <c r="W66" s="5" t="n"/>
+      <c r="X66" s="5" t="n"/>
+      <c r="Y66" s="5" t="n"/>
+      <c r="Z66" s="5" t="n"/>
+      <c r="AA66" s="5" t="n"/>
+      <c r="AB66" s="5" t="n"/>
+      <c r="AC66" s="5" t="n"/>
+      <c r="AD66" s="5" t="n"/>
+      <c r="AE66" s="5" t="n"/>
+      <c r="AF66" s="5" t="n"/>
+      <c r="AG66" s="5" t="n"/>
+      <c r="AH66" s="5" t="n"/>
+      <c r="AI66" s="5" t="n"/>
+      <c r="AJ66" s="5" t="n"/>
+      <c r="AK66" s="5" t="n"/>
+      <c r="AL66" s="5" t="n"/>
+      <c r="AM66" s="5" t="n"/>
+      <c r="AN66" s="5" t="n"/>
+      <c r="AO66" s="5" t="n"/>
+      <c r="AP66" s="5" t="n"/>
+      <c r="AQ66" s="5" t="n"/>
+      <c r="AR66" s="5" t="n"/>
+      <c r="AS66" s="5" t="n"/>
+      <c r="AT66" s="5" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="1" t="n"/>
       <c r="B67" s="1" t="n"/>
       <c r="C67" s="5" t="n"/>
-      <c r="D67" s="31" t="inlineStr">
-        <is>
-          <t>o excedente passar da metade da régua, ou um golpe só causar a régua inteira. A régua sai da vida CRUA do tipo, nunca da do corpo forte — é a mesma para um corpo, cinco, ou o corpo grande.</t>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t>MORRE DE VEZ SE</t>
         </is>
       </c>
     </row>
@@ -2671,84 +2726,65 @@
       <c r="A68" s="1" t="n"/>
       <c r="B68" s="1" t="n"/>
       <c r="C68" s="5" t="n"/>
+      <c r="D68" s="35" t="inlineStr">
+        <is>
+          <t>o excedente passar da metade da régua, ou um golpe só causar a régua inteira. A régua sai da vida CRUA do tipo, nunca da do corpo forte — é a mesma para um corpo, cinco, ou o corpo grande.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="1" t="n"/>
       <c r="B69" s="1" t="n"/>
       <c r="C69" s="5" t="n"/>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>Ela some no zero: sem Inconsciente, sem Sequela e sem Cicatriz. A vida cheia volta no descanso longo.</t>
-        </is>
-      </c>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="1" t="n"/>
       <c r="B70" s="1" t="n"/>
       <c r="C70" s="5" t="n"/>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Ela some no zero: sem Inconsciente, sem Sequela e sem Cicatriz. A vida cheia volta no descanso longo.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="1" t="n"/>
       <c r="B71" s="1" t="n"/>
       <c r="C71" s="5" t="n"/>
-      <c r="D71" s="5" t="n"/>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="n"/>
-      <c r="I71" s="5" t="n"/>
-      <c r="J71" s="5" t="n"/>
-      <c r="K71" s="5" t="n"/>
-      <c r="L71" s="5" t="n"/>
-      <c r="M71" s="5" t="n"/>
-      <c r="N71" s="5" t="n"/>
-      <c r="O71" s="5" t="n"/>
-      <c r="P71" s="5" t="n"/>
-      <c r="Q71" s="5" t="n"/>
-      <c r="R71" s="5" t="n"/>
-      <c r="S71" s="5" t="n"/>
-      <c r="T71" s="5" t="n"/>
-      <c r="U71" s="5" t="n"/>
-      <c r="V71" s="5" t="n"/>
-      <c r="W71" s="5" t="n"/>
-      <c r="X71" s="5" t="n"/>
-      <c r="Y71" s="5" t="n"/>
-      <c r="Z71" s="5" t="n"/>
-      <c r="AA71" s="5" t="n"/>
-      <c r="AB71" s="5" t="n"/>
-      <c r="AC71" s="5" t="n"/>
-      <c r="AD71" s="5" t="n"/>
-      <c r="AE71" s="5" t="n"/>
-      <c r="AF71" s="5" t="n"/>
-      <c r="AG71" s="5" t="n"/>
-      <c r="AH71" s="5" t="n"/>
-      <c r="AI71" s="5" t="n"/>
-      <c r="AJ71" s="5" t="n"/>
-      <c r="AK71" s="5" t="n"/>
-      <c r="AL71" s="5" t="n"/>
-      <c r="AM71" s="5" t="n"/>
-      <c r="AN71" s="5" t="n"/>
-      <c r="AO71" s="5" t="n"/>
-      <c r="AP71" s="5" t="n"/>
-      <c r="AQ71" s="5" t="n"/>
-      <c r="AR71" s="5" t="n"/>
-      <c r="AS71" s="5" t="n"/>
-      <c r="AT71" s="5" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="1" t="n"/>
       <c r="B72" s="1" t="n"/>
       <c r="C72" s="5" t="n"/>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>O ORÇAMENTO — compra o que ela FAZ, nunca número</t>
-        </is>
-      </c>
+      <c r="D72" s="5" t="n"/>
+      <c r="E72" s="5" t="n"/>
+      <c r="F72" s="5" t="n"/>
+      <c r="G72" s="5" t="n"/>
+      <c r="H72" s="5" t="n"/>
+      <c r="I72" s="5" t="n"/>
+      <c r="J72" s="5" t="n"/>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
+      <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="5" t="n"/>
+      <c r="S72" s="5" t="n"/>
+      <c r="T72" s="5" t="n"/>
+      <c r="U72" s="5" t="n"/>
+      <c r="V72" s="5" t="n"/>
+      <c r="W72" s="5" t="n"/>
+      <c r="X72" s="5" t="n"/>
+      <c r="Y72" s="5" t="n"/>
+      <c r="Z72" s="5" t="n"/>
+      <c r="AA72" s="5" t="n"/>
+      <c r="AB72" s="5" t="n"/>
+      <c r="AC72" s="5" t="n"/>
+      <c r="AD72" s="5" t="n"/>
+      <c r="AE72" s="5" t="n"/>
+      <c r="AF72" s="5" t="n"/>
       <c r="AG72" s="5" t="n"/>
       <c r="AH72" s="5" t="n"/>
       <c r="AI72" s="5" t="n"/>
@@ -2768,32 +2804,16 @@
       <c r="A73" s="1" t="n"/>
       <c r="B73" s="1" t="n"/>
       <c r="C73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="n"/>
-      <c r="I73" s="5" t="n"/>
-      <c r="J73" s="5" t="n"/>
-      <c r="K73" s="5" t="n"/>
-      <c r="L73" s="5" t="n"/>
-      <c r="M73" s="5" t="n"/>
-      <c r="N73" s="5" t="n"/>
-      <c r="O73" s="5" t="n"/>
-      <c r="P73" s="5" t="n"/>
-      <c r="Q73" s="5" t="n"/>
-      <c r="R73" s="5" t="n"/>
-      <c r="S73" s="5" t="n"/>
-      <c r="T73" s="5" t="n"/>
-      <c r="U73" s="5" t="n"/>
-      <c r="V73" s="5" t="n"/>
-      <c r="W73" s="5" t="n"/>
-      <c r="X73" s="5" t="n"/>
-      <c r="Y73" s="5" t="n"/>
-      <c r="Z73" s="5" t="n"/>
-      <c r="AA73" s="5" t="n"/>
-      <c r="AB73" s="5" t="n"/>
-      <c r="AC73" s="5" t="n"/>
-      <c r="AD73" s="5" t="n"/>
-      <c r="AE73" s="5" t="n"/>
-      <c r="AF73" s="5" t="n"/>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>O ORÇAMENTO — compra o que ela FAZ, nunca número</t>
+        </is>
+      </c>
       <c r="AG73" s="5" t="n"/>
       <c r="AH73" s="5" t="n"/>
       <c r="AI73" s="5" t="n"/>
@@ -2813,11 +2833,13 @@
       <c r="A74" s="1" t="n"/>
       <c r="B74" s="1" t="n"/>
       <c r="C74" s="5" t="n"/>
-      <c r="D74" s="8" t="inlineStr">
-        <is>
-          <t>ORÇAMENTO</t>
-        </is>
-      </c>
+      <c r="G74" s="5" t="n"/>
+      <c r="H74" s="5" t="n"/>
+      <c r="I74" s="5" t="n"/>
+      <c r="J74" s="5" t="n"/>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
       <c r="N74" s="5" t="n"/>
       <c r="O74" s="5" t="n"/>
       <c r="P74" s="5" t="n"/>
@@ -2856,9 +2878,10 @@
       <c r="A75" s="1" t="n"/>
       <c r="B75" s="1" t="n"/>
       <c r="C75" s="5" t="n"/>
-      <c r="D75" s="9">
-        <f>FLOOR((8+4*$D$11)*IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,3,FALSE),1),1)</f>
-        <v/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>ORÇAMENTO</t>
+        </is>
       </c>
       <c r="N75" s="5" t="n"/>
       <c r="O75" s="5" t="n"/>
@@ -2898,6 +2921,10 @@
       <c r="A76" s="1" t="n"/>
       <c r="B76" s="1" t="n"/>
       <c r="C76" s="5" t="n"/>
+      <c r="D76" s="9">
+        <f>FLOOR((8+4*$D$11)*IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,3,FALSE),1),1)</f>
+        <v/>
+      </c>
       <c r="N76" s="5" t="n"/>
       <c r="O76" s="5" t="n"/>
       <c r="P76" s="5" t="n"/>
@@ -2936,16 +2963,6 @@
       <c r="A77" s="1" t="n"/>
       <c r="B77" s="1" t="n"/>
       <c r="C77" s="5" t="n"/>
-      <c r="D77" s="5" t="n"/>
-      <c r="E77" s="5" t="n"/>
-      <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
-      <c r="H77" s="5" t="n"/>
-      <c r="I77" s="5" t="n"/>
-      <c r="J77" s="5" t="n"/>
-      <c r="K77" s="5" t="n"/>
-      <c r="L77" s="5" t="n"/>
-      <c r="M77" s="5" t="n"/>
       <c r="N77" s="5" t="n"/>
       <c r="O77" s="5" t="n"/>
       <c r="P77" s="5" t="n"/>
@@ -2984,43 +3001,65 @@
       <c r="A78" s="1" t="n"/>
       <c r="B78" s="1" t="n"/>
       <c r="C78" s="5" t="n"/>
-      <c r="D78" s="22" t="inlineStr">
-        <is>
-          <t>TRAÇO · até 9</t>
-        </is>
-      </c>
+      <c r="D78" s="5" t="n"/>
+      <c r="E78" s="5" t="n"/>
+      <c r="F78" s="5" t="n"/>
+      <c r="G78" s="5" t="n"/>
+      <c r="H78" s="5" t="n"/>
+      <c r="I78" s="5" t="n"/>
+      <c r="J78" s="5" t="n"/>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="5" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="5" t="n"/>
+      <c r="U78" s="5" t="n"/>
+      <c r="V78" s="5" t="n"/>
+      <c r="W78" s="5" t="n"/>
       <c r="X78" s="5" t="n"/>
       <c r="Y78" s="5" t="n"/>
-      <c r="Z78" s="22" t="inlineStr">
-        <is>
-          <t>COMANDO · até 6</t>
-        </is>
-      </c>
+      <c r="Z78" s="5" t="n"/>
+      <c r="AA78" s="5" t="n"/>
+      <c r="AB78" s="5" t="n"/>
+      <c r="AC78" s="5" t="n"/>
+      <c r="AD78" s="5" t="n"/>
+      <c r="AE78" s="5" t="n"/>
+      <c r="AF78" s="5" t="n"/>
+      <c r="AG78" s="5" t="n"/>
+      <c r="AH78" s="5" t="n"/>
+      <c r="AI78" s="5" t="n"/>
+      <c r="AJ78" s="5" t="n"/>
+      <c r="AK78" s="5" t="n"/>
+      <c r="AL78" s="5" t="n"/>
+      <c r="AM78" s="5" t="n"/>
+      <c r="AN78" s="5" t="n"/>
+      <c r="AO78" s="5" t="n"/>
+      <c r="AP78" s="5" t="n"/>
+      <c r="AQ78" s="5" t="n"/>
+      <c r="AR78" s="5" t="n"/>
+      <c r="AS78" s="5" t="n"/>
       <c r="AT78" s="5" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="1" t="n"/>
       <c r="B79" s="1" t="n"/>
       <c r="C79" s="5" t="n"/>
-      <c r="D79" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="S79" s="32">
-        <f>IFERROR(VLOOKUP($D$79,DADOS!$T$3:$U$16,2,FALSE),0)</f>
-        <v/>
+      <c r="D79" s="22" t="inlineStr">
+        <is>
+          <t>TRAÇO · até 9</t>
+        </is>
       </c>
       <c r="X79" s="5" t="n"/>
       <c r="Y79" s="5" t="n"/>
-      <c r="Z79" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AO79" s="32">
-        <f>IFERROR(VLOOKUP($Z$79,DADOS!$W$3:$X$10,2,FALSE),0)</f>
-        <v/>
+      <c r="Z79" s="22" t="inlineStr">
+        <is>
+          <t>COMANDO · até 6</t>
+        </is>
       </c>
       <c r="AT79" s="5" t="n"/>
     </row>
@@ -3028,23 +3067,23 @@
       <c r="A80" s="1" t="n"/>
       <c r="B80" s="1" t="n"/>
       <c r="C80" s="5" t="n"/>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="D80" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S80" s="33">
+      <c r="S80" s="36">
         <f>IFERROR(VLOOKUP($D$80,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X80" s="5" t="n"/>
       <c r="Y80" s="5" t="n"/>
-      <c r="Z80" s="26" t="inlineStr">
+      <c r="Z80" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO80" s="33">
+      <c r="AO80" s="36">
         <f>IFERROR(VLOOKUP($Z$80,DADOS!$W$3:$X$10,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3054,23 +3093,23 @@
       <c r="A81" s="1" t="n"/>
       <c r="B81" s="1" t="n"/>
       <c r="C81" s="5" t="n"/>
-      <c r="D81" s="23" t="inlineStr">
+      <c r="D81" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S81" s="32">
+      <c r="S81" s="37">
         <f>IFERROR(VLOOKUP($D$81,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X81" s="5" t="n"/>
       <c r="Y81" s="5" t="n"/>
-      <c r="Z81" s="23" t="inlineStr">
+      <c r="Z81" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO81" s="32">
+      <c r="AO81" s="37">
         <f>IFERROR(VLOOKUP($Z$81,DADOS!$W$3:$X$10,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3080,23 +3119,23 @@
       <c r="A82" s="1" t="n"/>
       <c r="B82" s="1" t="n"/>
       <c r="C82" s="5" t="n"/>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D82" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S82" s="33">
+      <c r="S82" s="36">
         <f>IFERROR(VLOOKUP($D$82,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X82" s="5" t="n"/>
       <c r="Y82" s="5" t="n"/>
-      <c r="Z82" s="26" t="inlineStr">
+      <c r="Z82" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO82" s="33">
+      <c r="AO82" s="36">
         <f>IFERROR(VLOOKUP($Z$82,DADOS!$W$3:$X$10,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3106,23 +3145,23 @@
       <c r="A83" s="1" t="n"/>
       <c r="B83" s="1" t="n"/>
       <c r="C83" s="5" t="n"/>
-      <c r="D83" s="23" t="inlineStr">
+      <c r="D83" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S83" s="32">
+      <c r="S83" s="37">
         <f>IFERROR(VLOOKUP($D$83,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X83" s="5" t="n"/>
       <c r="Y83" s="5" t="n"/>
-      <c r="Z83" s="23" t="inlineStr">
+      <c r="Z83" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO83" s="32">
+      <c r="AO83" s="37">
         <f>IFERROR(VLOOKUP($Z$83,DADOS!$W$3:$X$10,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3132,23 +3171,23 @@
       <c r="A84" s="1" t="n"/>
       <c r="B84" s="1" t="n"/>
       <c r="C84" s="5" t="n"/>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="D84" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S84" s="33">
+      <c r="S84" s="36">
         <f>IFERROR(VLOOKUP($D$84,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X84" s="5" t="n"/>
       <c r="Y84" s="5" t="n"/>
-      <c r="Z84" s="26" t="inlineStr">
+      <c r="Z84" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="AO84" s="33">
+      <c r="AO84" s="36">
         <f>IFERROR(VLOOKUP($Z$84,DADOS!$W$3:$X$10,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3158,49 +3197,38 @@
       <c r="A85" s="1" t="n"/>
       <c r="B85" s="1" t="n"/>
       <c r="C85" s="5" t="n"/>
-      <c r="D85" s="23" t="inlineStr">
+      <c r="D85" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S85" s="32">
+      <c r="S85" s="37">
         <f>IFERROR(VLOOKUP($D$85,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
       <c r="X85" s="5" t="n"/>
       <c r="Y85" s="5" t="n"/>
-      <c r="Z85" s="5" t="n"/>
-      <c r="AA85" s="5" t="n"/>
-      <c r="AB85" s="5" t="n"/>
-      <c r="AC85" s="5" t="n"/>
-      <c r="AD85" s="5" t="n"/>
-      <c r="AE85" s="5" t="n"/>
-      <c r="AF85" s="5" t="n"/>
-      <c r="AG85" s="5" t="n"/>
-      <c r="AH85" s="5" t="n"/>
-      <c r="AI85" s="5" t="n"/>
-      <c r="AJ85" s="5" t="n"/>
-      <c r="AK85" s="5" t="n"/>
-      <c r="AL85" s="5" t="n"/>
-      <c r="AM85" s="5" t="n"/>
-      <c r="AN85" s="5" t="n"/>
-      <c r="AO85" s="5" t="n"/>
-      <c r="AP85" s="5" t="n"/>
-      <c r="AQ85" s="5" t="n"/>
-      <c r="AR85" s="5" t="n"/>
-      <c r="AS85" s="5" t="n"/>
+      <c r="Z85" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO85" s="37">
+        <f>IFERROR(VLOOKUP($Z$85,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+        <v/>
+      </c>
       <c r="AT85" s="5" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="1" t="n"/>
       <c r="B86" s="1" t="n"/>
       <c r="C86" s="5" t="n"/>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="D86" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S86" s="33">
+      <c r="S86" s="36">
         <f>IFERROR(VLOOKUP($D$86,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3232,12 +3260,12 @@
       <c r="A87" s="1" t="n"/>
       <c r="B87" s="1" t="n"/>
       <c r="C87" s="5" t="n"/>
-      <c r="D87" s="23" t="inlineStr">
+      <c r="D87" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S87" s="32">
+      <c r="S87" s="37">
         <f>IFERROR(VLOOKUP($D$87,DADOS!$T$3:$U$16,2,FALSE),0)</f>
         <v/>
       </c>
@@ -3269,26 +3297,15 @@
       <c r="A88" s="1" t="n"/>
       <c r="B88" s="1" t="n"/>
       <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
-      <c r="H88" s="5" t="n"/>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="5" t="n"/>
-      <c r="K88" s="5" t="n"/>
-      <c r="L88" s="5" t="n"/>
-      <c r="M88" s="5" t="n"/>
-      <c r="N88" s="5" t="n"/>
-      <c r="O88" s="5" t="n"/>
-      <c r="P88" s="5" t="n"/>
-      <c r="Q88" s="5" t="n"/>
-      <c r="R88" s="5" t="n"/>
-      <c r="S88" s="5" t="n"/>
-      <c r="T88" s="5" t="n"/>
-      <c r="U88" s="5" t="n"/>
-      <c r="V88" s="5" t="n"/>
-      <c r="W88" s="5" t="n"/>
+      <c r="D88" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S88" s="36">
+        <f>IFERROR(VLOOKUP($D$88,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+        <v/>
+      </c>
       <c r="X88" s="5" t="n"/>
       <c r="Y88" s="5" t="n"/>
       <c r="Z88" s="5" t="n"/>
@@ -3317,17 +3334,27 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="5" t="n"/>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>GASTO</t>
-        </is>
-      </c>
+      <c r="D89" s="5" t="n"/>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="5" t="n"/>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
       <c r="N89" s="5" t="n"/>
-      <c r="O89" s="8" t="inlineStr">
-        <is>
-          <t>SOBRA</t>
-        </is>
-      </c>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
+      <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="5" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="5" t="n"/>
+      <c r="U89" s="5" t="n"/>
+      <c r="V89" s="5" t="n"/>
+      <c r="W89" s="5" t="n"/>
+      <c r="X89" s="5" t="n"/>
       <c r="Y89" s="5" t="n"/>
       <c r="Z89" s="5" t="n"/>
       <c r="AA89" s="5" t="n"/>
@@ -3355,14 +3382,16 @@
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="5" t="n"/>
-      <c r="D90" s="10">
-        <f>$S$79+$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$AO$79+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84</f>
-        <v/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>GASTO</t>
+        </is>
       </c>
       <c r="N90" s="5" t="n"/>
-      <c r="O90" s="34">
-        <f>IF($D$75-($S$79+$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$AO$79+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84)&lt;0,"estourou "&amp;(($S$79+$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$AO$79+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84)-$D$75),$D$75-($S$79+$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$AO$79+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84))</f>
-        <v/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>SOBRA</t>
+        </is>
       </c>
       <c r="Y90" s="5" t="n"/>
       <c r="Z90" s="5" t="n"/>
@@ -3391,27 +3420,15 @@
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="5" t="n"/>
-      <c r="D91" s="5" t="n"/>
-      <c r="E91" s="5" t="n"/>
-      <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="n"/>
-      <c r="H91" s="5" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="5" t="n"/>
-      <c r="K91" s="5" t="n"/>
-      <c r="L91" s="5" t="n"/>
-      <c r="M91" s="5" t="n"/>
+      <c r="D91" s="10">
+        <f>$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85</f>
+        <v/>
+      </c>
       <c r="N91" s="5" t="n"/>
-      <c r="O91" s="5" t="n"/>
-      <c r="P91" s="5" t="n"/>
-      <c r="Q91" s="5" t="n"/>
-      <c r="R91" s="5" t="n"/>
-      <c r="S91" s="5" t="n"/>
-      <c r="T91" s="5" t="n"/>
-      <c r="U91" s="5" t="n"/>
-      <c r="V91" s="5" t="n"/>
-      <c r="W91" s="5" t="n"/>
-      <c r="X91" s="5" t="n"/>
+      <c r="O91" s="38">
+        <f>IF($D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)&lt;0,"estourou "&amp;(($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)-$D$76),$D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85))</f>
+        <v/>
+      </c>
       <c r="Y91" s="5" t="n"/>
       <c r="Z91" s="5" t="n"/>
       <c r="AA91" s="5" t="n"/>
@@ -3439,79 +3456,94 @@
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="5" t="n"/>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>O Servo monta com o orçamento da ficha mais metade, porque é um corpo só e não cinco. O que ele NÃO compra a preço nenhum: dado de dano · qualquer coisa que cresça com refino · atributo · Defesa, acerto ou vida direto.</t>
-        </is>
-      </c>
+      <c r="D92" s="5" t="n"/>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="5" t="n"/>
+      <c r="K92" s="5" t="n"/>
+      <c r="L92" s="5" t="n"/>
+      <c r="M92" s="5" t="n"/>
+      <c r="N92" s="5" t="n"/>
+      <c r="O92" s="5" t="n"/>
+      <c r="P92" s="5" t="n"/>
+      <c r="Q92" s="5" t="n"/>
+      <c r="R92" s="5" t="n"/>
+      <c r="S92" s="5" t="n"/>
+      <c r="T92" s="5" t="n"/>
+      <c r="U92" s="5" t="n"/>
+      <c r="V92" s="5" t="n"/>
+      <c r="W92" s="5" t="n"/>
+      <c r="X92" s="5" t="n"/>
+      <c r="Y92" s="5" t="n"/>
+      <c r="Z92" s="5" t="n"/>
+      <c r="AA92" s="5" t="n"/>
+      <c r="AB92" s="5" t="n"/>
+      <c r="AC92" s="5" t="n"/>
+      <c r="AD92" s="5" t="n"/>
+      <c r="AE92" s="5" t="n"/>
+      <c r="AF92" s="5" t="n"/>
+      <c r="AG92" s="5" t="n"/>
+      <c r="AH92" s="5" t="n"/>
+      <c r="AI92" s="5" t="n"/>
+      <c r="AJ92" s="5" t="n"/>
+      <c r="AK92" s="5" t="n"/>
+      <c r="AL92" s="5" t="n"/>
+      <c r="AM92" s="5" t="n"/>
+      <c r="AN92" s="5" t="n"/>
+      <c r="AO92" s="5" t="n"/>
+      <c r="AP92" s="5" t="n"/>
+      <c r="AQ92" s="5" t="n"/>
+      <c r="AR92" s="5" t="n"/>
+      <c r="AS92" s="5" t="n"/>
+      <c r="AT92" s="5" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="5" t="n"/>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>O Servo monta com o orçamento da ficha mais metade, porque é um corpo só e não cinco. O que ele NÃO compra a preço nenhum: dado de dano · qualquer coisa que cresça com refino · atributo · Defesa, acerto ou vida direto.</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="5" t="n"/>
-      <c r="D94" s="5" t="n"/>
-      <c r="E94" s="5" t="n"/>
-      <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="n"/>
-      <c r="H94" s="5" t="n"/>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="5" t="n"/>
-      <c r="K94" s="5" t="n"/>
-      <c r="L94" s="5" t="n"/>
-      <c r="M94" s="5" t="n"/>
-      <c r="N94" s="5" t="n"/>
-      <c r="O94" s="5" t="n"/>
-      <c r="P94" s="5" t="n"/>
-      <c r="Q94" s="5" t="n"/>
-      <c r="R94" s="5" t="n"/>
-      <c r="S94" s="5" t="n"/>
-      <c r="T94" s="5" t="n"/>
-      <c r="U94" s="5" t="n"/>
-      <c r="V94" s="5" t="n"/>
-      <c r="W94" s="5" t="n"/>
-      <c r="X94" s="5" t="n"/>
-      <c r="Y94" s="5" t="n"/>
-      <c r="Z94" s="5" t="n"/>
-      <c r="AA94" s="5" t="n"/>
-      <c r="AB94" s="5" t="n"/>
-      <c r="AC94" s="5" t="n"/>
-      <c r="AD94" s="5" t="n"/>
-      <c r="AE94" s="5" t="n"/>
-      <c r="AF94" s="5" t="n"/>
-      <c r="AG94" s="5" t="n"/>
-      <c r="AH94" s="5" t="n"/>
-      <c r="AI94" s="5" t="n"/>
-      <c r="AJ94" s="5" t="n"/>
-      <c r="AK94" s="5" t="n"/>
-      <c r="AL94" s="5" t="n"/>
-      <c r="AM94" s="5" t="n"/>
-      <c r="AN94" s="5" t="n"/>
-      <c r="AO94" s="5" t="n"/>
-      <c r="AP94" s="5" t="n"/>
-      <c r="AQ94" s="5" t="n"/>
-      <c r="AR94" s="5" t="n"/>
-      <c r="AS94" s="5" t="n"/>
-      <c r="AT94" s="5" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="5" t="n"/>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>INVESTIR — o ataque, e toda invocação tem</t>
-        </is>
-      </c>
+      <c r="D95" s="5" t="n"/>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="n"/>
+      <c r="I95" s="5" t="n"/>
+      <c r="J95" s="5" t="n"/>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="n"/>
+      <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
+      <c r="Q95" s="5" t="n"/>
+      <c r="R95" s="5" t="n"/>
+      <c r="S95" s="5" t="n"/>
+      <c r="T95" s="5" t="n"/>
+      <c r="U95" s="5" t="n"/>
+      <c r="V95" s="5" t="n"/>
+      <c r="W95" s="5" t="n"/>
+      <c r="X95" s="5" t="n"/>
+      <c r="Y95" s="5" t="n"/>
+      <c r="Z95" s="5" t="n"/>
+      <c r="AA95" s="5" t="n"/>
+      <c r="AB95" s="5" t="n"/>
       <c r="AC95" s="5" t="n"/>
       <c r="AD95" s="5" t="n"/>
       <c r="AE95" s="5" t="n"/>
@@ -3535,28 +3567,16 @@
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="5" t="n"/>
-      <c r="G96" s="5" t="n"/>
-      <c r="H96" s="5" t="n"/>
-      <c r="I96" s="5" t="n"/>
-      <c r="J96" s="5" t="n"/>
-      <c r="K96" s="5" t="n"/>
-      <c r="L96" s="5" t="n"/>
-      <c r="M96" s="5" t="n"/>
-      <c r="N96" s="5" t="n"/>
-      <c r="O96" s="5" t="n"/>
-      <c r="P96" s="5" t="n"/>
-      <c r="Q96" s="5" t="n"/>
-      <c r="R96" s="5" t="n"/>
-      <c r="S96" s="5" t="n"/>
-      <c r="T96" s="5" t="n"/>
-      <c r="U96" s="5" t="n"/>
-      <c r="V96" s="5" t="n"/>
-      <c r="W96" s="5" t="n"/>
-      <c r="X96" s="5" t="n"/>
-      <c r="Y96" s="5" t="n"/>
-      <c r="Z96" s="5" t="n"/>
-      <c r="AA96" s="5" t="n"/>
-      <c r="AB96" s="5" t="n"/>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIR — o ataque, e toda invocação tem</t>
+        </is>
+      </c>
       <c r="AC96" s="5" t="n"/>
       <c r="AD96" s="5" t="n"/>
       <c r="AE96" s="5" t="n"/>
@@ -3580,163 +3600,171 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n"/>
       <c r="C97" s="5" t="n"/>
-      <c r="D97" s="8" t="inlineStr">
-        <is>
-          <t>DANO DO INVESTIR</t>
-        </is>
-      </c>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="n"/>
+      <c r="I97" s="5" t="n"/>
+      <c r="J97" s="5" t="n"/>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
-      <c r="O97" s="8" t="inlineStr">
-        <is>
-          <t>POR CORPO</t>
-        </is>
-      </c>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
+      <c r="Q97" s="5" t="n"/>
+      <c r="R97" s="5" t="n"/>
+      <c r="S97" s="5" t="n"/>
+      <c r="T97" s="5" t="n"/>
+      <c r="U97" s="5" t="n"/>
+      <c r="V97" s="5" t="n"/>
+      <c r="W97" s="5" t="n"/>
+      <c r="X97" s="5" t="n"/>
+      <c r="Y97" s="5" t="n"/>
+      <c r="Z97" s="5" t="n"/>
+      <c r="AA97" s="5" t="n"/>
+      <c r="AB97" s="5" t="n"/>
+      <c r="AC97" s="5" t="n"/>
+      <c r="AD97" s="5" t="n"/>
+      <c r="AE97" s="5" t="n"/>
+      <c r="AF97" s="5" t="n"/>
+      <c r="AG97" s="5" t="n"/>
+      <c r="AH97" s="5" t="n"/>
+      <c r="AI97" s="5" t="n"/>
+      <c r="AJ97" s="5" t="n"/>
+      <c r="AK97" s="5" t="n"/>
+      <c r="AL97" s="5" t="n"/>
+      <c r="AM97" s="5" t="n"/>
+      <c r="AN97" s="5" t="n"/>
+      <c r="AO97" s="5" t="n"/>
+      <c r="AP97" s="5" t="n"/>
+      <c r="AQ97" s="5" t="n"/>
+      <c r="AR97" s="5" t="n"/>
+      <c r="AS97" s="5" t="n"/>
+      <c r="AT97" s="5" t="n"/>
     </row>
     <row r="98" ht="15" customHeight="1">
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n"/>
       <c r="C98" s="5" t="n"/>
-      <c r="D98" s="9">
-        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AK$19="Matilha",3,2),TRUE))</f>
-        <v/>
+      <c r="D98" s="8" t="inlineStr">
+        <is>
+          <t>DANO DO INVESTIR</t>
+        </is>
       </c>
       <c r="N98" s="5" t="n"/>
-      <c r="O98" s="21">
-        <f>IF($AK$19="Matilha","cada um dos cinco rola isto",IF($AK$19="","","o corpo em campo rola isto"))</f>
-        <v/>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>POR CORPO</t>
+        </is>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="5" t="n"/>
+      <c r="D99" s="9">
+        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AK$19="Matilha",3,2),TRUE))</f>
+        <v/>
+      </c>
       <c r="N99" s="5" t="n"/>
+      <c r="O99" s="21">
+        <f>IF($AK$19="Matilha","cada um dos cinco rola isto",IF($AK$19="","","o corpo em campo rola isto"))</f>
+        <v/>
+      </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="5" t="n"/>
-      <c r="D100" s="5" t="n"/>
-      <c r="E100" s="5" t="n"/>
-      <c r="F100" s="5" t="n"/>
-      <c r="G100" s="5" t="n"/>
-      <c r="H100" s="5" t="n"/>
-      <c r="I100" s="5" t="n"/>
-      <c r="J100" s="5" t="n"/>
-      <c r="K100" s="5" t="n"/>
-      <c r="L100" s="5" t="n"/>
-      <c r="M100" s="5" t="n"/>
       <c r="N100" s="5" t="n"/>
-      <c r="O100" s="5" t="n"/>
-      <c r="P100" s="5" t="n"/>
-      <c r="Q100" s="5" t="n"/>
-      <c r="R100" s="5" t="n"/>
-      <c r="S100" s="5" t="n"/>
-      <c r="T100" s="5" t="n"/>
-      <c r="U100" s="5" t="n"/>
-      <c r="V100" s="5" t="n"/>
-      <c r="W100" s="5" t="n"/>
-      <c r="X100" s="5" t="n"/>
-      <c r="Y100" s="5" t="n"/>
-      <c r="Z100" s="5" t="n"/>
-      <c r="AA100" s="5" t="n"/>
-      <c r="AB100" s="5" t="n"/>
-      <c r="AC100" s="5" t="n"/>
-      <c r="AD100" s="5" t="n"/>
-      <c r="AE100" s="5" t="n"/>
-      <c r="AF100" s="5" t="n"/>
-      <c r="AG100" s="5" t="n"/>
-      <c r="AH100" s="5" t="n"/>
-      <c r="AI100" s="5" t="n"/>
-      <c r="AJ100" s="5" t="n"/>
-      <c r="AK100" s="5" t="n"/>
-      <c r="AL100" s="5" t="n"/>
-      <c r="AM100" s="5" t="n"/>
-      <c r="AN100" s="5" t="n"/>
-      <c r="AO100" s="5" t="n"/>
-      <c r="AP100" s="5" t="n"/>
-      <c r="AQ100" s="5" t="n"/>
-      <c r="AR100" s="5" t="n"/>
-      <c r="AS100" s="5" t="n"/>
-      <c r="AT100" s="5" t="n"/>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="5" t="n"/>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>Você e todas as suas invocações somados entregam uma Rotina. O número de dados sempre desce — a soma nunca passa do que você faria sozinho.</t>
-        </is>
-      </c>
+      <c r="D101" s="5" t="n"/>
+      <c r="E101" s="5" t="n"/>
+      <c r="F101" s="5" t="n"/>
+      <c r="G101" s="5" t="n"/>
+      <c r="H101" s="5" t="n"/>
+      <c r="I101" s="5" t="n"/>
+      <c r="J101" s="5" t="n"/>
+      <c r="K101" s="5" t="n"/>
+      <c r="L101" s="5" t="n"/>
+      <c r="M101" s="5" t="n"/>
+      <c r="N101" s="5" t="n"/>
+      <c r="O101" s="5" t="n"/>
+      <c r="P101" s="5" t="n"/>
+      <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="5" t="n"/>
+      <c r="S101" s="5" t="n"/>
+      <c r="T101" s="5" t="n"/>
+      <c r="U101" s="5" t="n"/>
+      <c r="V101" s="5" t="n"/>
+      <c r="W101" s="5" t="n"/>
+      <c r="X101" s="5" t="n"/>
+      <c r="Y101" s="5" t="n"/>
+      <c r="Z101" s="5" t="n"/>
+      <c r="AA101" s="5" t="n"/>
+      <c r="AB101" s="5" t="n"/>
+      <c r="AC101" s="5" t="n"/>
+      <c r="AD101" s="5" t="n"/>
+      <c r="AE101" s="5" t="n"/>
+      <c r="AF101" s="5" t="n"/>
+      <c r="AG101" s="5" t="n"/>
+      <c r="AH101" s="5" t="n"/>
+      <c r="AI101" s="5" t="n"/>
+      <c r="AJ101" s="5" t="n"/>
+      <c r="AK101" s="5" t="n"/>
+      <c r="AL101" s="5" t="n"/>
+      <c r="AM101" s="5" t="n"/>
+      <c r="AN101" s="5" t="n"/>
+      <c r="AO101" s="5" t="n"/>
+      <c r="AP101" s="5" t="n"/>
+      <c r="AQ101" s="5" t="n"/>
+      <c r="AR101" s="5" t="n"/>
+      <c r="AS101" s="5" t="n"/>
+      <c r="AT101" s="5" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="5" t="n"/>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Você e todas as suas invocações somados entregam uma Rotina. O número de dados sempre desce — a soma nunca passa do que você faria sozinho.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="5" t="n"/>
-      <c r="D103" s="5" t="n"/>
-      <c r="E103" s="5" t="n"/>
-      <c r="F103" s="5" t="n"/>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="n"/>
-      <c r="I103" s="5" t="n"/>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
-      <c r="L103" s="5" t="n"/>
-      <c r="M103" s="5" t="n"/>
-      <c r="N103" s="5" t="n"/>
-      <c r="O103" s="5" t="n"/>
-      <c r="P103" s="5" t="n"/>
-      <c r="Q103" s="5" t="n"/>
-      <c r="R103" s="5" t="n"/>
-      <c r="S103" s="5" t="n"/>
-      <c r="T103" s="5" t="n"/>
-      <c r="U103" s="5" t="n"/>
-      <c r="V103" s="5" t="n"/>
-      <c r="W103" s="5" t="n"/>
-      <c r="X103" s="5" t="n"/>
-      <c r="Y103" s="5" t="n"/>
-      <c r="Z103" s="5" t="n"/>
-      <c r="AA103" s="5" t="n"/>
-      <c r="AB103" s="5" t="n"/>
-      <c r="AC103" s="5" t="n"/>
-      <c r="AD103" s="5" t="n"/>
-      <c r="AE103" s="5" t="n"/>
-      <c r="AF103" s="5" t="n"/>
-      <c r="AG103" s="5" t="n"/>
-      <c r="AH103" s="5" t="n"/>
-      <c r="AI103" s="5" t="n"/>
-      <c r="AJ103" s="5" t="n"/>
-      <c r="AK103" s="5" t="n"/>
-      <c r="AL103" s="5" t="n"/>
-      <c r="AM103" s="5" t="n"/>
-      <c r="AN103" s="5" t="n"/>
-      <c r="AO103" s="5" t="n"/>
-      <c r="AP103" s="5" t="n"/>
-      <c r="AQ103" s="5" t="n"/>
-      <c r="AR103" s="5" t="n"/>
-      <c r="AS103" s="5" t="n"/>
-      <c r="AT103" s="5" t="n"/>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="5" t="n"/>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>8.0</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>NA MESA — o que não muda</t>
-        </is>
-      </c>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="5" t="n"/>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="n"/>
+      <c r="J104" s="5" t="n"/>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
+      <c r="Q104" s="5" t="n"/>
+      <c r="R104" s="5" t="n"/>
+      <c r="S104" s="5" t="n"/>
+      <c r="T104" s="5" t="n"/>
+      <c r="U104" s="5" t="n"/>
+      <c r="V104" s="5" t="n"/>
+      <c r="W104" s="5" t="n"/>
+      <c r="X104" s="5" t="n"/>
       <c r="Y104" s="5" t="n"/>
       <c r="Z104" s="5" t="n"/>
       <c r="AA104" s="5" t="n"/>
@@ -3764,24 +3792,16 @@
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="n"/>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
-      <c r="L105" s="5" t="n"/>
-      <c r="M105" s="5" t="n"/>
-      <c r="N105" s="5" t="n"/>
-      <c r="O105" s="5" t="n"/>
-      <c r="P105" s="5" t="n"/>
-      <c r="Q105" s="5" t="n"/>
-      <c r="R105" s="5" t="n"/>
-      <c r="S105" s="5" t="n"/>
-      <c r="T105" s="5" t="n"/>
-      <c r="U105" s="5" t="n"/>
-      <c r="V105" s="5" t="n"/>
-      <c r="W105" s="5" t="n"/>
-      <c r="X105" s="5" t="n"/>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>NA MESA — o que não muda</t>
+        </is>
+      </c>
       <c r="Y105" s="5" t="n"/>
       <c r="Z105" s="5" t="n"/>
       <c r="AA105" s="5" t="n"/>
@@ -3809,27 +3829,58 @@
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="5" t="n"/>
-      <c r="D106" s="35" t="inlineStr">
-        <is>
-          <t>INVOCAR</t>
-        </is>
-      </c>
-      <c r="O106" s="36">
-        <f>("custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
-        <v/>
-      </c>
+      <c r="G106" s="5" t="n"/>
+      <c r="H106" s="5" t="n"/>
+      <c r="I106" s="5" t="n"/>
+      <c r="J106" s="5" t="n"/>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
+      <c r="Q106" s="5" t="n"/>
+      <c r="R106" s="5" t="n"/>
+      <c r="S106" s="5" t="n"/>
+      <c r="T106" s="5" t="n"/>
+      <c r="U106" s="5" t="n"/>
+      <c r="V106" s="5" t="n"/>
+      <c r="W106" s="5" t="n"/>
+      <c r="X106" s="5" t="n"/>
+      <c r="Y106" s="5" t="n"/>
+      <c r="Z106" s="5" t="n"/>
+      <c r="AA106" s="5" t="n"/>
+      <c r="AB106" s="5" t="n"/>
+      <c r="AC106" s="5" t="n"/>
+      <c r="AD106" s="5" t="n"/>
+      <c r="AE106" s="5" t="n"/>
+      <c r="AF106" s="5" t="n"/>
+      <c r="AG106" s="5" t="n"/>
+      <c r="AH106" s="5" t="n"/>
+      <c r="AI106" s="5" t="n"/>
+      <c r="AJ106" s="5" t="n"/>
+      <c r="AK106" s="5" t="n"/>
+      <c r="AL106" s="5" t="n"/>
+      <c r="AM106" s="5" t="n"/>
+      <c r="AN106" s="5" t="n"/>
+      <c r="AO106" s="5" t="n"/>
+      <c r="AP106" s="5" t="n"/>
+      <c r="AQ106" s="5" t="n"/>
+      <c r="AR106" s="5" t="n"/>
+      <c r="AS106" s="5" t="n"/>
+      <c r="AT106" s="5" t="n"/>
     </row>
     <row r="107" ht="15" customHeight="1">
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="5" t="n"/>
-      <c r="D107" s="37" t="inlineStr">
-        <is>
-          <t>COMANDAR</t>
-        </is>
-      </c>
-      <c r="O107" s="38">
-        <f>"a Ação Padrão, toda rodada"</f>
+      <c r="D107" s="39" t="inlineStr">
+        <is>
+          <t>INVOCAR</t>
+        </is>
+      </c>
+      <c r="O107" s="40">
+        <f>("custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
         <v/>
       </c>
     </row>
@@ -3837,13 +3888,13 @@
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="5" t="n"/>
-      <c r="D108" s="35" t="inlineStr">
-        <is>
-          <t>INICIATIVA</t>
-        </is>
-      </c>
-      <c r="O108" s="36">
-        <f>"a sua, e ela age logo depois de você"</f>
+      <c r="D108" s="41" t="inlineStr">
+        <is>
+          <t>COMANDAR</t>
+        </is>
+      </c>
+      <c r="O108" s="42">
+        <f>"a Ação Padrão, toda rodada"</f>
         <v/>
       </c>
     </row>
@@ -3851,13 +3902,13 @@
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="5" t="n"/>
-      <c r="D109" s="37" t="inlineStr">
-        <is>
-          <t>DESLOCAMENTO</t>
-        </is>
-      </c>
-      <c r="O109" s="38">
-        <f>(9&amp;" metros")</f>
+      <c r="D109" s="39" t="inlineStr">
+        <is>
+          <t>INICIATIVA</t>
+        </is>
+      </c>
+      <c r="O109" s="40">
+        <f>"a sua, e ela age logo depois de você"</f>
         <v/>
       </c>
     </row>
@@ -3865,13 +3916,13 @@
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="5" t="n"/>
-      <c r="D110" s="35" t="inlineStr">
-        <is>
-          <t>AMARRA</t>
-        </is>
-      </c>
-      <c r="O110" s="36">
-        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
+      <c r="D110" s="41" t="inlineStr">
+        <is>
+          <t>DESLOCAMENTO</t>
+        </is>
+      </c>
+      <c r="O110" s="42">
+        <f>(9&amp;" metros")</f>
         <v/>
       </c>
     </row>
@@ -3879,64 +3930,49 @@
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
-      <c r="E111" s="5" t="n"/>
-      <c r="F111" s="5" t="n"/>
-      <c r="G111" s="5" t="n"/>
-      <c r="H111" s="5" t="n"/>
-      <c r="I111" s="5" t="n"/>
-      <c r="J111" s="5" t="n"/>
-      <c r="K111" s="5" t="n"/>
-      <c r="L111" s="5" t="n"/>
-      <c r="M111" s="5" t="n"/>
-      <c r="N111" s="5" t="n"/>
-      <c r="O111" s="5" t="n"/>
-      <c r="P111" s="5" t="n"/>
-      <c r="Q111" s="5" t="n"/>
-      <c r="R111" s="5" t="n"/>
-      <c r="S111" s="5" t="n"/>
-      <c r="T111" s="5" t="n"/>
-      <c r="U111" s="5" t="n"/>
-      <c r="V111" s="5" t="n"/>
-      <c r="W111" s="5" t="n"/>
-      <c r="X111" s="5" t="n"/>
-      <c r="Y111" s="5" t="n"/>
-      <c r="Z111" s="5" t="n"/>
-      <c r="AA111" s="5" t="n"/>
-      <c r="AB111" s="5" t="n"/>
-      <c r="AC111" s="5" t="n"/>
-      <c r="AD111" s="5" t="n"/>
-      <c r="AE111" s="5" t="n"/>
-      <c r="AF111" s="5" t="n"/>
-      <c r="AG111" s="5" t="n"/>
-      <c r="AH111" s="5" t="n"/>
-      <c r="AI111" s="5" t="n"/>
-      <c r="AJ111" s="5" t="n"/>
-      <c r="AK111" s="5" t="n"/>
-      <c r="AL111" s="5" t="n"/>
-      <c r="AM111" s="5" t="n"/>
-      <c r="AN111" s="5" t="n"/>
-      <c r="AO111" s="5" t="n"/>
-      <c r="AP111" s="5" t="n"/>
-      <c r="AQ111" s="5" t="n"/>
-      <c r="AR111" s="5" t="n"/>
-      <c r="AS111" s="5" t="n"/>
-      <c r="AT111" s="5" t="n"/>
+      <c r="D111" s="39" t="inlineStr">
+        <is>
+          <t>AMARRA</t>
+        </is>
+      </c>
+      <c r="O111" s="40">
+        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
+        <v/>
+      </c>
     </row>
     <row r="112" ht="15" customHeight="1">
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n"/>
       <c r="C112" s="5" t="n"/>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>O QUE ESTA FICHA NÃO CALCULA, E POR QUÊ</t>
-        </is>
-      </c>
+      <c r="D112" s="5" t="n"/>
+      <c r="E112" s="5" t="n"/>
+      <c r="F112" s="5" t="n"/>
+      <c r="G112" s="5" t="n"/>
+      <c r="H112" s="5" t="n"/>
+      <c r="I112" s="5" t="n"/>
+      <c r="J112" s="5" t="n"/>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="5" t="n"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
+      <c r="Q112" s="5" t="n"/>
+      <c r="R112" s="5" t="n"/>
+      <c r="S112" s="5" t="n"/>
+      <c r="T112" s="5" t="n"/>
+      <c r="U112" s="5" t="n"/>
+      <c r="V112" s="5" t="n"/>
+      <c r="W112" s="5" t="n"/>
+      <c r="X112" s="5" t="n"/>
+      <c r="Y112" s="5" t="n"/>
+      <c r="Z112" s="5" t="n"/>
+      <c r="AA112" s="5" t="n"/>
+      <c r="AB112" s="5" t="n"/>
+      <c r="AC112" s="5" t="n"/>
+      <c r="AD112" s="5" t="n"/>
+      <c r="AE112" s="5" t="n"/>
+      <c r="AF112" s="5" t="n"/>
       <c r="AG112" s="5" t="n"/>
       <c r="AH112" s="5" t="n"/>
       <c r="AI112" s="5" t="n"/>
@@ -3956,32 +3992,16 @@
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n"/>
       <c r="C113" s="5" t="n"/>
-      <c r="G113" s="5" t="n"/>
-      <c r="H113" s="5" t="n"/>
-      <c r="I113" s="5" t="n"/>
-      <c r="J113" s="5" t="n"/>
-      <c r="K113" s="5" t="n"/>
-      <c r="L113" s="5" t="n"/>
-      <c r="M113" s="5" t="n"/>
-      <c r="N113" s="5" t="n"/>
-      <c r="O113" s="5" t="n"/>
-      <c r="P113" s="5" t="n"/>
-      <c r="Q113" s="5" t="n"/>
-      <c r="R113" s="5" t="n"/>
-      <c r="S113" s="5" t="n"/>
-      <c r="T113" s="5" t="n"/>
-      <c r="U113" s="5" t="n"/>
-      <c r="V113" s="5" t="n"/>
-      <c r="W113" s="5" t="n"/>
-      <c r="X113" s="5" t="n"/>
-      <c r="Y113" s="5" t="n"/>
-      <c r="Z113" s="5" t="n"/>
-      <c r="AA113" s="5" t="n"/>
-      <c r="AB113" s="5" t="n"/>
-      <c r="AC113" s="5" t="n"/>
-      <c r="AD113" s="5" t="n"/>
-      <c r="AE113" s="5" t="n"/>
-      <c r="AF113" s="5" t="n"/>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>O QUE ESTA FICHA NÃO CALCULA, E POR QUÊ</t>
+        </is>
+      </c>
       <c r="AG113" s="5" t="n"/>
       <c r="AH113" s="5" t="n"/>
       <c r="AI113" s="5" t="n"/>
@@ -4001,83 +4021,80 @@
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="5" t="n"/>
-      <c r="D114" s="30" t="inlineStr">
-        <is>
-          <t>A CD DOS EFEITOS DELA</t>
-        </is>
-      </c>
+      <c r="G114" s="5" t="n"/>
+      <c r="H114" s="5" t="n"/>
+      <c r="I114" s="5" t="n"/>
+      <c r="J114" s="5" t="n"/>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
+      <c r="Q114" s="5" t="n"/>
+      <c r="R114" s="5" t="n"/>
+      <c r="S114" s="5" t="n"/>
+      <c r="T114" s="5" t="n"/>
+      <c r="U114" s="5" t="n"/>
+      <c r="V114" s="5" t="n"/>
+      <c r="W114" s="5" t="n"/>
+      <c r="X114" s="5" t="n"/>
+      <c r="Y114" s="5" t="n"/>
+      <c r="Z114" s="5" t="n"/>
+      <c r="AA114" s="5" t="n"/>
+      <c r="AB114" s="5" t="n"/>
+      <c r="AC114" s="5" t="n"/>
+      <c r="AD114" s="5" t="n"/>
+      <c r="AE114" s="5" t="n"/>
+      <c r="AF114" s="5" t="n"/>
+      <c r="AG114" s="5" t="n"/>
+      <c r="AH114" s="5" t="n"/>
+      <c r="AI114" s="5" t="n"/>
+      <c r="AJ114" s="5" t="n"/>
+      <c r="AK114" s="5" t="n"/>
+      <c r="AL114" s="5" t="n"/>
+      <c r="AM114" s="5" t="n"/>
+      <c r="AN114" s="5" t="n"/>
+      <c r="AO114" s="5" t="n"/>
+      <c r="AP114" s="5" t="n"/>
+      <c r="AQ114" s="5" t="n"/>
+      <c r="AR114" s="5" t="n"/>
+      <c r="AS114" s="5" t="n"/>
+      <c r="AT114" s="5" t="n"/>
     </row>
     <row r="115" ht="15" customHeight="1">
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="5" t="n"/>
-      <c r="D115" s="31">
-        <f>IF($D$22="Voz","a Voz manda subir a CD dela, e a invocação não tem fórmula de CD em documento nenhum — combine com o mestre","")</f>
-        <v/>
+      <c r="D115" s="34" t="inlineStr">
+        <is>
+          <t>A CD DOS EFEITOS DELA</t>
+        </is>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="5" t="n"/>
-      <c r="D116" s="39" t="inlineStr">
-        <is>
-          <t>A invocação não tem fórmula de CD em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Esta rota soma num número que o sistema ainda não produz, então combine com o mestre em vez de chutar.</t>
-        </is>
+      <c r="D116" s="35">
+        <f>IF($D$22="Voz","a Voz manda subir a CD dela, e a invocação não tem fórmula de CD em documento nenhum — combine com o mestre","")</f>
+        <v/>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="5" t="n"/>
+      <c r="D117" s="43" t="inlineStr">
+        <is>
+          <t>A invocação não tem fórmula de CD em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Esta rota soma num número que o sistema ainda não produz, então combine com o mestre em vez de chutar.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="5" t="n"/>
-      <c r="D118" s="5" t="n"/>
-      <c r="E118" s="5" t="n"/>
-      <c r="F118" s="5" t="n"/>
-      <c r="G118" s="5" t="n"/>
-      <c r="H118" s="5" t="n"/>
-      <c r="I118" s="5" t="n"/>
-      <c r="J118" s="5" t="n"/>
-      <c r="K118" s="5" t="n"/>
-      <c r="L118" s="5" t="n"/>
-      <c r="M118" s="5" t="n"/>
-      <c r="N118" s="5" t="n"/>
-      <c r="O118" s="5" t="n"/>
-      <c r="P118" s="5" t="n"/>
-      <c r="Q118" s="5" t="n"/>
-      <c r="R118" s="5" t="n"/>
-      <c r="S118" s="5" t="n"/>
-      <c r="T118" s="5" t="n"/>
-      <c r="U118" s="5" t="n"/>
-      <c r="V118" s="5" t="n"/>
-      <c r="W118" s="5" t="n"/>
-      <c r="X118" s="5" t="n"/>
-      <c r="Y118" s="5" t="n"/>
-      <c r="Z118" s="5" t="n"/>
-      <c r="AA118" s="5" t="n"/>
-      <c r="AB118" s="5" t="n"/>
-      <c r="AC118" s="5" t="n"/>
-      <c r="AD118" s="5" t="n"/>
-      <c r="AE118" s="5" t="n"/>
-      <c r="AF118" s="5" t="n"/>
-      <c r="AG118" s="5" t="n"/>
-      <c r="AH118" s="5" t="n"/>
-      <c r="AI118" s="5" t="n"/>
-      <c r="AJ118" s="5" t="n"/>
-      <c r="AK118" s="5" t="n"/>
-      <c r="AL118" s="5" t="n"/>
-      <c r="AM118" s="5" t="n"/>
-      <c r="AN118" s="5" t="n"/>
-      <c r="AO118" s="5" t="n"/>
-      <c r="AP118" s="5" t="n"/>
-      <c r="AQ118" s="5" t="n"/>
-      <c r="AR118" s="5" t="n"/>
-      <c r="AS118" s="5" t="n"/>
-      <c r="AT118" s="5" t="n"/>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="1" t="n"/>
@@ -4176,73 +4193,78 @@
       <c r="AT120" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="172">
+  <mergeCells count="178">
+    <mergeCell ref="D59:M60"/>
     <mergeCell ref="AB30:AH31"/>
     <mergeCell ref="T30:Z31"/>
     <mergeCell ref="Z81:AN81"/>
     <mergeCell ref="D109:N109"/>
+    <mergeCell ref="O111:AT111"/>
     <mergeCell ref="G4:AB4"/>
+    <mergeCell ref="O91:X91"/>
+    <mergeCell ref="D51:J51"/>
     <mergeCell ref="AO80:AS80"/>
     <mergeCell ref="AJ32:AP32"/>
-    <mergeCell ref="AK58:AT59"/>
+    <mergeCell ref="D111:N111"/>
     <mergeCell ref="D108:N108"/>
     <mergeCell ref="Z45:AI45"/>
     <mergeCell ref="D1:AD2"/>
-    <mergeCell ref="O97:AT97"/>
     <mergeCell ref="Z6:AI6"/>
     <mergeCell ref="D7:M8"/>
     <mergeCell ref="O108:AT108"/>
     <mergeCell ref="O10:X10"/>
+    <mergeCell ref="G96:AB96"/>
+    <mergeCell ref="AH50:AL50"/>
     <mergeCell ref="A8:B26"/>
+    <mergeCell ref="Z49:AF49"/>
     <mergeCell ref="D83:R83"/>
     <mergeCell ref="AK19:AT19"/>
     <mergeCell ref="S87:W87"/>
     <mergeCell ref="D115:AT115"/>
-    <mergeCell ref="D78:W78"/>
+    <mergeCell ref="AH49:AL49"/>
     <mergeCell ref="S80:W80"/>
-    <mergeCell ref="D57:M57"/>
     <mergeCell ref="D85:R85"/>
-    <mergeCell ref="AO79:AS79"/>
-    <mergeCell ref="O58:X59"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="D68:AT69"/>
     <mergeCell ref="D16:F17"/>
-    <mergeCell ref="D92:AT93"/>
+    <mergeCell ref="O62:AT62"/>
+    <mergeCell ref="Z79:AS79"/>
     <mergeCell ref="D84:R84"/>
     <mergeCell ref="Z18:AI18"/>
-    <mergeCell ref="D98:M99"/>
+    <mergeCell ref="Z58:AI58"/>
+    <mergeCell ref="Z85:AN85"/>
+    <mergeCell ref="G73:AF73"/>
+    <mergeCell ref="D91:M91"/>
+    <mergeCell ref="D93:AT94"/>
+    <mergeCell ref="D102:AT103"/>
     <mergeCell ref="O110:AT110"/>
     <mergeCell ref="D43:M43"/>
-    <mergeCell ref="R49:T49"/>
     <mergeCell ref="Z64:AI64"/>
-    <mergeCell ref="D112:F113"/>
     <mergeCell ref="Z42:AI42"/>
     <mergeCell ref="AK7:AT8"/>
     <mergeCell ref="O46:X46"/>
+    <mergeCell ref="D73:F74"/>
+    <mergeCell ref="D48:AT48"/>
     <mergeCell ref="D86:R86"/>
-    <mergeCell ref="D48:AT48"/>
-    <mergeCell ref="O89:X89"/>
-    <mergeCell ref="D49:O49"/>
+    <mergeCell ref="AM51:AQ51"/>
     <mergeCell ref="O64:X64"/>
-    <mergeCell ref="AM49:AO49"/>
-    <mergeCell ref="D74:M74"/>
-    <mergeCell ref="P50:Q50"/>
     <mergeCell ref="AO82:AS82"/>
+    <mergeCell ref="D99:M100"/>
     <mergeCell ref="AJ29:AP29"/>
     <mergeCell ref="Z19:AI19"/>
     <mergeCell ref="D29:J29"/>
+    <mergeCell ref="D113:F114"/>
     <mergeCell ref="G27:AF27"/>
+    <mergeCell ref="O99:AT100"/>
     <mergeCell ref="O90:X90"/>
     <mergeCell ref="D87:R87"/>
     <mergeCell ref="S86:W86"/>
-    <mergeCell ref="D114:AT114"/>
-    <mergeCell ref="G104:X104"/>
+    <mergeCell ref="D70:AT71"/>
     <mergeCell ref="D27:F28"/>
     <mergeCell ref="L30:R31"/>
     <mergeCell ref="L32:R32"/>
     <mergeCell ref="T29:Z29"/>
-    <mergeCell ref="Z79:AN79"/>
-    <mergeCell ref="D61:N61"/>
     <mergeCell ref="AO83:AS83"/>
-    <mergeCell ref="AK57:AT57"/>
     <mergeCell ref="D46:M46"/>
     <mergeCell ref="G16:X16"/>
     <mergeCell ref="AB32:AH32"/>
@@ -4250,104 +4272,105 @@
     <mergeCell ref="Z34:AT34"/>
     <mergeCell ref="AJ30:AP31"/>
     <mergeCell ref="AK18:AT18"/>
+    <mergeCell ref="R49:X49"/>
     <mergeCell ref="D21:M21"/>
-    <mergeCell ref="AK50:AL50"/>
-    <mergeCell ref="O63:X63"/>
+    <mergeCell ref="L50:P50"/>
+    <mergeCell ref="D49:J49"/>
     <mergeCell ref="AO84:AS84"/>
     <mergeCell ref="O21:AT21"/>
-    <mergeCell ref="D72:F73"/>
     <mergeCell ref="O35:X35"/>
+    <mergeCell ref="AK58:AT58"/>
     <mergeCell ref="O109:AT109"/>
-    <mergeCell ref="D97:M97"/>
-    <mergeCell ref="O98:AT99"/>
-    <mergeCell ref="AK49:AL49"/>
-    <mergeCell ref="O61:AT61"/>
-    <mergeCell ref="Z78:AS78"/>
-    <mergeCell ref="S79:W79"/>
+    <mergeCell ref="L49:P49"/>
     <mergeCell ref="O43:X43"/>
-    <mergeCell ref="D67:AT68"/>
-    <mergeCell ref="D55:F56"/>
-    <mergeCell ref="D66:AT66"/>
+    <mergeCell ref="S88:W88"/>
+    <mergeCell ref="D116:AT116"/>
+    <mergeCell ref="Z51:AF51"/>
+    <mergeCell ref="D79:W79"/>
+    <mergeCell ref="G56:T56"/>
     <mergeCell ref="O42:X42"/>
     <mergeCell ref="S81:W81"/>
-    <mergeCell ref="D69:AT70"/>
-    <mergeCell ref="G72:AF72"/>
+    <mergeCell ref="D58:M58"/>
     <mergeCell ref="AK6:AT6"/>
     <mergeCell ref="D42:M42"/>
-    <mergeCell ref="Z63:AI63"/>
     <mergeCell ref="Z83:AN83"/>
+    <mergeCell ref="D76:M77"/>
     <mergeCell ref="D35:M35"/>
-    <mergeCell ref="R50:T50"/>
-    <mergeCell ref="D52:AT53"/>
+    <mergeCell ref="Z65:AI65"/>
     <mergeCell ref="S82:W82"/>
     <mergeCell ref="D40:F41"/>
-    <mergeCell ref="D75:M76"/>
-    <mergeCell ref="P49:Q49"/>
     <mergeCell ref="G40:AH40"/>
     <mergeCell ref="D34:M34"/>
     <mergeCell ref="D107:N107"/>
     <mergeCell ref="AK42:AT42"/>
     <mergeCell ref="D18:X18"/>
+    <mergeCell ref="Q50:U50"/>
     <mergeCell ref="T32:Z32"/>
     <mergeCell ref="AB29:AH29"/>
     <mergeCell ref="O6:X6"/>
-    <mergeCell ref="AM50:AO50"/>
-    <mergeCell ref="Z58:AI59"/>
     <mergeCell ref="Z35:AT35"/>
     <mergeCell ref="D22:M22"/>
     <mergeCell ref="D13:AT14"/>
-    <mergeCell ref="Z57:AI57"/>
+    <mergeCell ref="L51:P51"/>
+    <mergeCell ref="D105:F106"/>
     <mergeCell ref="D45:M45"/>
-    <mergeCell ref="D106:N106"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="AK43:AT43"/>
-    <mergeCell ref="D50:O50"/>
-    <mergeCell ref="D79:R79"/>
+    <mergeCell ref="AH51:AL51"/>
     <mergeCell ref="S84:W84"/>
     <mergeCell ref="Z80:AN80"/>
+    <mergeCell ref="D88:R88"/>
     <mergeCell ref="O7:X8"/>
+    <mergeCell ref="G105:X105"/>
     <mergeCell ref="D24:AT25"/>
     <mergeCell ref="D32:J32"/>
-    <mergeCell ref="G55:T55"/>
+    <mergeCell ref="Z59:AI60"/>
     <mergeCell ref="D81:R81"/>
+    <mergeCell ref="AM50:AQ50"/>
+    <mergeCell ref="G113:AF113"/>
     <mergeCell ref="A30:B48"/>
-    <mergeCell ref="G95:AB95"/>
-    <mergeCell ref="O106:AT106"/>
-    <mergeCell ref="Y50:AJ50"/>
+    <mergeCell ref="O58:X58"/>
     <mergeCell ref="O11:X11"/>
     <mergeCell ref="Z7:AI8"/>
     <mergeCell ref="D64:M64"/>
     <mergeCell ref="AO81:AS81"/>
-    <mergeCell ref="D89:M89"/>
-    <mergeCell ref="O57:X57"/>
+    <mergeCell ref="D98:M98"/>
     <mergeCell ref="Z46:AI46"/>
     <mergeCell ref="O22:AT23"/>
+    <mergeCell ref="D50:J50"/>
+    <mergeCell ref="O98:AT98"/>
     <mergeCell ref="Z82:AN82"/>
     <mergeCell ref="O107:AT107"/>
-    <mergeCell ref="Y49:AJ49"/>
+    <mergeCell ref="Q51:U51"/>
     <mergeCell ref="O34:X34"/>
-    <mergeCell ref="D63:M63"/>
+    <mergeCell ref="D67:AT67"/>
+    <mergeCell ref="D96:F97"/>
     <mergeCell ref="D10:M10"/>
+    <mergeCell ref="O59:X60"/>
     <mergeCell ref="D90:M90"/>
-    <mergeCell ref="G112:AF112"/>
-    <mergeCell ref="D101:AT102"/>
+    <mergeCell ref="AN49:AT49"/>
+    <mergeCell ref="AK59:AT60"/>
+    <mergeCell ref="D65:M65"/>
     <mergeCell ref="O45:X45"/>
-    <mergeCell ref="D116:AT117"/>
-    <mergeCell ref="D95:F96"/>
     <mergeCell ref="Z84:AN84"/>
-    <mergeCell ref="D104:F105"/>
     <mergeCell ref="D4:F5"/>
+    <mergeCell ref="Z50:AF50"/>
+    <mergeCell ref="D56:F57"/>
     <mergeCell ref="Z43:AI43"/>
+    <mergeCell ref="D53:AT54"/>
     <mergeCell ref="D11:M11"/>
-    <mergeCell ref="D58:M59"/>
+    <mergeCell ref="O65:X65"/>
     <mergeCell ref="S83:W83"/>
     <mergeCell ref="D30:J31"/>
     <mergeCell ref="D19:X19"/>
     <mergeCell ref="D37:AT38"/>
+    <mergeCell ref="D117:AT118"/>
+    <mergeCell ref="D75:M75"/>
     <mergeCell ref="D80:R80"/>
     <mergeCell ref="L29:R29"/>
     <mergeCell ref="S85:W85"/>
     <mergeCell ref="AF1:AT2"/>
+    <mergeCell ref="AO85:AS85"/>
     <mergeCell ref="D110:N110"/>
   </mergeCells>
   <dataValidations count="22">
@@ -4371,9 +4394,6 @@
     </dataValidation>
     <dataValidation sqref="Z46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$G$2:$G$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="D79:R79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
     <dataValidation sqref="D80:R80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
@@ -4399,8 +4419,8 @@
     <dataValidation sqref="D87:R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="Z79:AN79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>DADOS!$I$2:$I$9</formula1>
+    <dataValidation sqref="D88:R88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
     <dataValidation sqref="Z80:AN80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
@@ -4415,6 +4435,9 @@
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
     <dataValidation sqref="Z84:AN84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>DADOS!$I$2:$I$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z85:AN85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
   </dataValidations>
@@ -4484,7 +4507,7 @@
       <c r="A1" s="5" t="n"/>
       <c r="B1" s="5" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="40" t="inlineStr">
+      <c r="D1" s="44" t="inlineStr">
         <is>
           <t>O CATÁLOGO — o que dá para comprar</t>
         </is>
@@ -4554,12 +4577,12 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="D4" s="45" t="inlineStr">
         <is>
           <t>TRAÇO</t>
         </is>
       </c>
-      <c r="U4" s="42" t="inlineStr">
+      <c r="U4" s="46" t="inlineStr">
         <is>
           <t>o que ela É. Sempre ligado, sem gastar ação.</t>
         </is>
@@ -4589,15 +4612,15 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="25" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="P6" s="31" t="inlineStr">
+      <c r="P6" s="35" t="inlineStr">
         <is>
           <t>sobe parede e teto sem teste</t>
         </is>
@@ -4607,15 +4630,15 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="48" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="26" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="P7" s="45" t="inlineStr">
+      <c r="P7" s="49" t="inlineStr">
         <is>
           <t>move na água sem penalidade. Rio, cisterna, tanque alagado de estação</t>
         </is>
@@ -4625,15 +4648,15 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="P8" s="31" t="inlineStr">
+      <c r="P8" s="35" t="inlineStr">
         <is>
           <t>ela fala, e dá para conversar com ela</t>
         </is>
@@ -4643,15 +4666,15 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="26" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="P9" s="45" t="inlineStr">
+      <c r="P9" s="49" t="inlineStr">
         <is>
           <t>rastreia por cheiro e por energia. Pega rastro velho de horas</t>
         </is>
@@ -4661,15 +4684,15 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="25" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="P10" s="31" t="inlineStr">
+      <c r="P10" s="35" t="inlineStr">
         <is>
           <t>o que ela vê e ouve, você vê e ouve também</t>
         </is>
@@ -4679,15 +4702,15 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="H11" s="26" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="P11" s="45" t="inlineStr">
+      <c r="P11" s="49" t="inlineStr">
         <is>
           <t>ocupa espaço menor e passa por vão. Duto, grade de bueiro, folga embaixo da porta</t>
         </is>
@@ -4697,15 +4720,15 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="P12" s="31" t="inlineStr">
+      <c r="P12" s="35" t="inlineStr">
         <is>
           <t>o deslocamento dela passa a ser de voo também</t>
         </is>
@@ -4715,15 +4738,15 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="26" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
       </c>
-      <c r="P13" s="45" t="inlineStr">
+      <c r="P13" s="49" t="inlineStr">
         <is>
           <t>carrega uma pessoa ou mais, dependendo do tamanho</t>
         </is>
@@ -4733,15 +4756,15 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
       </c>
-      <c r="P14" s="31" t="inlineStr">
+      <c r="P14" s="35" t="inlineStr">
         <is>
           <t>prende à distância. Ela alcança, engancha, e quem ia fugir para de conseguir</t>
         </is>
@@ -4751,15 +4774,15 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="44" t="n">
+      <c r="D15" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="P15" s="45" t="inlineStr">
+      <c r="P15" s="49" t="inlineStr">
         <is>
           <t>surge do chão, fora do alcance de visão</t>
         </is>
@@ -4769,15 +4792,15 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="25" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
       </c>
-      <c r="P16" s="31" t="inlineStr">
+      <c r="P16" s="35" t="inlineStr">
         <is>
           <t>ataca em linha ou em área</t>
         </is>
@@ -4787,15 +4810,15 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="44" t="n">
+      <c r="D17" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="H17" s="26" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="P17" s="45" t="inlineStr">
+      <c r="P17" s="49" t="inlineStr">
         <is>
           <t>ocupa espaço maior e barra passagem</t>
         </is>
@@ -4805,15 +4828,15 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H18" s="23" t="inlineStr">
+      <c r="H18" s="25" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
       </c>
-      <c r="P18" s="31" t="inlineStr">
+      <c r="P18" s="35" t="inlineStr">
         <is>
           <t>funciona além dos 18 metros da amarra. Dentro da cena, para qualquer um; fora da cena, com requisito</t>
         </is>
@@ -4919,12 +4942,12 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="41" t="inlineStr">
+      <c r="D21" s="45" t="inlineStr">
         <is>
           <t>COMANDO</t>
         </is>
       </c>
-      <c r="U21" s="42" t="inlineStr">
+      <c r="U21" s="46" t="inlineStr">
         <is>
           <t>o que ela FAZ quando o dono gasta a Ação Padrão nela.</t>
         </is>
@@ -4954,15 +4977,15 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="23" t="inlineStr">
+      <c r="H23" s="25" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="P23" s="31" t="inlineStr">
+      <c r="P23" s="35" t="inlineStr">
         <is>
           <t>o ataque. Toda invocação tem</t>
         </is>
@@ -4972,15 +4995,15 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="26" t="inlineStr">
+      <c r="H24" s="29" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="P24" s="45" t="inlineStr">
+      <c r="P24" s="49" t="inlineStr">
         <is>
           <t>prende o alvo</t>
         </is>
@@ -4990,15 +5013,15 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="43" t="n">
+      <c r="D25" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="H25" s="23" t="inlineStr">
+      <c r="H25" s="25" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
-      <c r="P25" s="31" t="inlineStr">
+      <c r="P25" s="35" t="inlineStr">
         <is>
           <t>move o alvo, ou se move levando ele. Tira alguém de cima de uma beirada, ou põe</t>
         </is>
@@ -5008,15 +5031,15 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="44" t="n">
+      <c r="D26" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="H26" s="26" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
-      <c r="P26" s="45" t="inlineStr">
+      <c r="P26" s="49" t="inlineStr">
         <is>
           <t>pega um objeto, ou rastreia de forma ativa</t>
         </is>
@@ -5026,15 +5049,15 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="43" t="n">
+      <c r="D27" s="47" t="n">
         <v>4</v>
       </c>
-      <c r="H27" s="23" t="inlineStr">
+      <c r="H27" s="25" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
       </c>
-      <c r="P27" s="31" t="inlineStr">
+      <c r="P27" s="35" t="inlineStr">
         <is>
           <t>abre buraco, desenterra, revira o terreno. Faz rota onde não havia rota</t>
         </is>
@@ -5044,15 +5067,15 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="44" t="n">
+      <c r="D28" s="48" t="n">
         <v>8</v>
       </c>
-      <c r="H28" s="26" t="inlineStr">
+      <c r="H28" s="29" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
       </c>
-      <c r="P28" s="45" t="inlineStr">
+      <c r="P28" s="49" t="inlineStr">
         <is>
           <t>se põe entre você e o golpe. O corpo dela recebe o que ia em você</t>
         </is>
@@ -5062,15 +5085,15 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="43" t="n">
+      <c r="D29" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H29" s="23" t="inlineStr">
+      <c r="H29" s="25" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
       </c>
-      <c r="P29" s="31" t="inlineStr">
+      <c r="P29" s="35" t="inlineStr">
         <is>
           <t>o alvo tem de vir para cima dela. Você escolhe em quem a coisa está prestando atenção</t>
         </is>
@@ -5176,12 +5199,12 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="41" t="inlineStr">
+      <c r="D32" s="45" t="inlineStr">
         <is>
           <t>INVENTAR O SEU</t>
         </is>
       </c>
-      <c r="U32" s="42" t="inlineStr">
+      <c r="U32" s="46" t="inlineStr">
         <is>
           <t>escreva o efeito, ache na régua o degrau em que ele cai, e leve para o mestre</t>
         </is>
@@ -5201,10 +5224,10 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
-      <c r="D34" s="43" t="n">
+      <c r="D34" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="H34" s="31" t="inlineStr">
+      <c r="H34" s="35" t="inlineStr">
         <is>
           <t>muda como ela anda, e só ela</t>
         </is>
@@ -5214,10 +5237,10 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
-      <c r="D35" s="44" t="n">
+      <c r="D35" s="48" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="45" t="inlineStr">
+      <c r="H35" s="49" t="inlineStr">
         <is>
           <t>muda o que ela comunica</t>
         </is>
@@ -5227,10 +5250,10 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="43" t="n">
+      <c r="D36" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="H36" s="31" t="inlineStr">
+      <c r="H36" s="35" t="inlineStr">
         <is>
           <t>muda o que ela percebe</t>
         </is>
@@ -5240,10 +5263,10 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
-      <c r="D37" s="44" t="n">
+      <c r="D37" s="48" t="n">
         <v>7</v>
       </c>
-      <c r="H37" s="45" t="inlineStr">
+      <c r="H37" s="49" t="inlineStr">
         <is>
           <t>muda que espaço ela ocupa, a um passo de mexer no tabuleiro</t>
         </is>
@@ -5253,10 +5276,10 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
-      <c r="D38" s="43" t="n">
+      <c r="D38" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H38" s="31" t="inlineStr">
+      <c r="H38" s="35" t="inlineStr">
         <is>
           <t>encosta em outra criatura ou no ambiente: carrega, prende, empurra, barra, alcança além do alcance, aparece onde não dava</t>
         </is>
@@ -5324,10 +5347,10 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="43" t="n">
+      <c r="D41" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="31" t="inlineStr">
+      <c r="H41" s="35" t="inlineStr">
         <is>
           <t>é o ataque</t>
         </is>
@@ -5337,10 +5360,10 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
-      <c r="D42" s="44" t="n">
+      <c r="D42" s="48" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="45" t="inlineStr">
+      <c r="H42" s="49" t="inlineStr">
         <is>
           <t>faz uma coisa com um alvo ou um objeto</t>
         </is>
@@ -5350,10 +5373,10 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
-      <c r="D43" s="43" t="n">
+      <c r="D43" s="47" t="n">
         <v>8</v>
       </c>
-      <c r="H43" s="31" t="inlineStr">
+      <c r="H43" s="35" t="inlineStr">
         <is>
           <t>protege você, ou nega a ação de outro</t>
         </is>
@@ -5411,7 +5434,7 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="5" t="n"/>
-      <c r="D45" s="30" t="inlineStr">
+      <c r="D45" s="34" t="inlineStr">
         <is>
           <t>E O QUE NÃO SE COMPRA A PREÇO NENHUM</t>
         </is>
@@ -5421,12 +5444,12 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="5" t="n"/>
-      <c r="D46" s="23" t="inlineStr">
+      <c r="D46" s="25" t="inlineStr">
         <is>
           <t>dado de dano</t>
         </is>
       </c>
-      <c r="R46" s="46" t="inlineStr">
+      <c r="R46" s="50" t="inlineStr">
         <is>
           <t>o teto de uma Rotina já governa a saída. Um Traço que dê +1d6 não existe</t>
         </is>
@@ -5436,12 +5459,12 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="5" t="n"/>
-      <c r="D47" s="26" t="inlineStr">
+      <c r="D47" s="29" t="inlineStr">
         <is>
           <t>qualquer coisa que cresça com refino</t>
         </is>
       </c>
-      <c r="R47" s="47" t="inlineStr">
+      <c r="R47" s="51" t="inlineStr">
         <is>
           <t>refino cresce muito mais rápido que a ficha dela, e ela passaria de você</t>
         </is>
@@ -5451,12 +5474,12 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="5" t="n"/>
-      <c r="D48" s="23" t="inlineStr">
+      <c r="D48" s="25" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="R48" s="46" t="inlineStr">
+      <c r="R48" s="50" t="inlineStr">
         <is>
           <t>os cinco já saem do arranjo dela, e comprar de novo é pagar duas vezes</t>
         </is>
@@ -5466,12 +5489,12 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="5" t="n"/>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D49" s="29" t="inlineStr">
         <is>
           <t>Defesa, acerto ou vida direto</t>
         </is>
       </c>
-      <c r="R49" s="47" t="inlineStr">
+      <c r="R49" s="51" t="inlineStr">
         <is>
           <t>os três saem dos atributos dela</t>
         </is>
@@ -6312,7 +6335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AN77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6349,60 +6372,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="48" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>tipos</t>
         </is>
       </c>
-      <c r="B1" s="48" t="inlineStr">
+      <c r="B1" s="52" t="inlineStr">
         <is>
           <t>trilhas</t>
         </is>
       </c>
-      <c r="C1" s="48" t="inlineStr">
+      <c r="C1" s="52" t="inlineStr">
         <is>
           <t>atributos</t>
         </is>
       </c>
-      <c r="D1" s="48" t="inlineStr">
+      <c r="D1" s="52" t="inlineStr">
         <is>
           <t>trs</t>
         </is>
       </c>
-      <c r="E1" s="48" t="inlineStr">
+      <c r="E1" s="52" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="F1" s="48" t="inlineStr">
+      <c r="F1" s="52" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="G1" s="48" t="inlineStr">
+      <c r="G1" s="52" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="H1" s="48" t="inlineStr">
+      <c r="H1" s="52" t="inlineStr">
         <is>
           <t>traco</t>
         </is>
       </c>
-      <c r="I1" s="48" t="inlineStr">
+      <c r="I1" s="52" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
       <c r="J1" s="5" t="n"/>
-      <c r="K1" s="48" t="inlineStr">
+      <c r="K1" s="52" t="inlineStr">
         <is>
           <t>tab_tipos</t>
         </is>
       </c>
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
-      <c r="N1" s="48" t="inlineStr">
+      <c r="N1" s="52" t="inlineStr">
         <is>
           <t>tab_trilhas</t>
         </is>
@@ -6412,21 +6435,21 @@
       <c r="Q1" s="5" t="n"/>
       <c r="R1" s="5" t="n"/>
       <c r="S1" s="5" t="n"/>
-      <c r="T1" s="48" t="inlineStr">
+      <c r="T1" s="52" t="inlineStr">
         <is>
           <t>tab_traco</t>
         </is>
       </c>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
-      <c r="W1" s="48" t="inlineStr">
+      <c r="W1" s="52" t="inlineStr">
         <is>
           <t>tab_comando</t>
         </is>
       </c>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
-      <c r="Z1" s="48" t="inlineStr">
+      <c r="Z1" s="52" t="inlineStr">
         <is>
           <t>tab_investir</t>
         </is>
@@ -6434,7 +6457,7 @@
       <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="5" t="n"/>
       <c r="AC1" s="5" t="n"/>
-      <c r="AD1" s="48" t="inlineStr">
+      <c r="AD1" s="52" t="inlineStr">
         <is>
           <t>tab_trs</t>
         </is>
@@ -6450,47 +6473,47 @@
       <c r="AM1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="B2" s="49" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="C2" s="49" t="inlineStr">
+      <c r="C2" s="53" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="D2" s="49" t="inlineStr">
+      <c r="D2" s="53" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="E2" s="49" t="inlineStr">
+      <c r="E2" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F2" s="49" t="inlineStr">
+      <c r="F2" s="53" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
-      <c r="G2" s="49" t="inlineStr">
+      <c r="G2" s="53" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="H2" s="49" t="inlineStr">
+      <c r="H2" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="49" t="inlineStr">
+      <c r="I2" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6609,422 +6632,422 @@
           <t>campo</t>
         </is>
       </c>
-      <c r="AN2" s="50" t="inlineStr">
+      <c r="AN2" s="54" t="inlineStr">
         <is>
           <t>célula</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="B3" s="49" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="C3" s="49" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="D3" s="49" t="inlineStr">
+      <c r="D3" s="53" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="E3" s="49" t="inlineStr">
+      <c r="E3" s="53" t="inlineStr">
         <is>
           <t>Presa</t>
         </is>
       </c>
-      <c r="F3" s="49" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="G3" s="49" t="inlineStr">
+      <c r="G3" s="53" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="H3" s="49" t="inlineStr">
+      <c r="H3" s="53" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="I3" s="49" t="inlineStr">
+      <c r="I3" s="53" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="49" t="inlineStr">
+      <c r="K3" s="53" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="L3" s="49" t="n">
+      <c r="L3" s="53" t="n">
         <v>1</v>
       </c>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="49" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="O3" s="49" t="n">
+      <c r="O3" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="49" t="n">
+      <c r="P3" s="53" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q3" s="49" t="inlineStr">
+      <c r="Q3" s="53" t="inlineStr">
         <is>
           <t>forte</t>
         </is>
       </c>
-      <c r="R3" s="49" t="n">
+      <c r="R3" s="53" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="5" t="n"/>
-      <c r="T3" s="49" t="inlineStr">
+      <c r="T3" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U3" s="49" t="n">
+      <c r="U3" s="53" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="5" t="n"/>
-      <c r="W3" s="49" t="inlineStr">
+      <c r="W3" s="53" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="X3" s="49" t="n">
+      <c r="X3" s="53" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n"/>
-      <c r="Z3" s="49" t="n">
+      <c r="Z3" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" s="49" t="inlineStr">
+      <c r="AA3" s="53" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
-      <c r="AB3" s="49" t="inlineStr">
+      <c r="AB3" s="53" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="AC3" s="5" t="n"/>
-      <c r="AD3" s="49" t="inlineStr">
+      <c r="AD3" s="53" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="AE3" s="49" t="inlineStr">
+      <c r="AE3" s="53" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
       <c r="AF3" s="5" t="n"/>
-      <c r="AG3" s="49" t="n">
+      <c r="AG3" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="AH3" s="49" t="n">
+      <c r="AH3" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="AI3" s="49" t="n">
+      <c r="AI3" s="53" t="n">
         <v>1</v>
       </c>
       <c r="AJ3" s="5" t="n"/>
-      <c r="AK3" s="49">
+      <c r="AK3" s="53">
         <f>INVOCAÇÃO!$D$30</f>
         <v/>
       </c>
       <c r="AL3" s="5" t="n"/>
-      <c r="AM3" s="49" t="inlineStr">
+      <c r="AM3" s="53" t="inlineStr">
         <is>
           <t>nivel</t>
         </is>
       </c>
-      <c r="AN3" s="51" t="inlineStr">
+      <c r="AN3" s="55" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="53" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="53" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="53" t="inlineStr">
         <is>
           <t>Parrudo</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="53" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="53" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="53" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="L4" s="49" t="n">
+      <c r="L4" s="53" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="53" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="O4" s="49" t="n">
+      <c r="O4" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="49" t="n">
+      <c r="P4" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="53" t="inlineStr">
         <is>
           <t>forte</t>
         </is>
       </c>
-      <c r="R4" s="49" t="n">
+      <c r="R4" s="53" t="n">
         <v>1.5</v>
       </c>
       <c r="S4" s="5" t="n"/>
-      <c r="T4" s="49" t="inlineStr">
+      <c r="T4" s="53" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="U4" s="49" t="n">
+      <c r="U4" s="53" t="n">
         <v>2</v>
       </c>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="49" t="inlineStr">
+      <c r="W4" s="53" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="X4" s="49" t="n">
+      <c r="X4" s="53" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="49" t="n">
+      <c r="Z4" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" s="49" t="inlineStr">
+      <c r="AA4" s="53" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
       </c>
-      <c r="AB4" s="49" t="inlineStr">
+      <c r="AB4" s="53" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
       <c r="AC4" s="5" t="n"/>
-      <c r="AD4" s="49" t="inlineStr">
+      <c r="AD4" s="53" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="AE4" s="49" t="inlineStr">
+      <c r="AE4" s="53" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
       <c r="AF4" s="5" t="n"/>
-      <c r="AG4" s="49" t="n">
+      <c r="AG4" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="AH4" s="49" t="n">
+      <c r="AH4" s="53" t="n">
         <v>18</v>
       </c>
-      <c r="AI4" s="49" t="n">
+      <c r="AI4" s="53" t="n">
         <v>5</v>
       </c>
       <c r="AJ4" s="5" t="n"/>
-      <c r="AK4" s="49">
+      <c r="AK4" s="53">
         <f>INVOCAÇÃO!$L$30</f>
         <v/>
       </c>
       <c r="AL4" s="5" t="n"/>
-      <c r="AM4" s="49" t="inlineStr">
+      <c r="AM4" s="53" t="inlineStr">
         <is>
           <t>ess_dono</t>
         </is>
       </c>
-      <c r="AN4" s="51" t="inlineStr">
+      <c r="AN4" s="55" t="inlineStr">
         <is>
           <t>O7</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="49" t="inlineStr">
+      <c r="C5" s="53" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="D5" s="49" t="inlineStr">
+      <c r="D5" s="53" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="E5" s="49" t="inlineStr">
+      <c r="E5" s="53" t="inlineStr">
         <is>
           <t>Voz</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="49" t="inlineStr">
+      <c r="H5" s="53" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="I5" s="49" t="inlineStr">
+      <c r="I5" s="53" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="49" t="inlineStr">
+      <c r="K5" s="53" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="L5" s="49" t="n">
+      <c r="L5" s="53" t="n">
         <v>2</v>
       </c>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="49" t="inlineStr">
+      <c r="N5" s="53" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="O5" s="49" t="n">
+      <c r="O5" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="49" t="n">
+      <c r="P5" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="49" t="inlineStr">
+      <c r="Q5" s="53" t="inlineStr">
         <is>
           <t>cru</t>
         </is>
       </c>
-      <c r="R5" s="49" t="n">
+      <c r="R5" s="53" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="5" t="n"/>
-      <c r="T5" s="49" t="inlineStr">
+      <c r="T5" s="53" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="U5" s="49" t="n">
+      <c r="U5" s="53" t="n">
         <v>2</v>
       </c>
       <c r="V5" s="5" t="n"/>
-      <c r="W5" s="49" t="inlineStr">
+      <c r="W5" s="53" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="X5" s="49" t="n">
+      <c r="X5" s="53" t="n">
         <v>4</v>
       </c>
       <c r="Y5" s="5" t="n"/>
-      <c r="Z5" s="49" t="n">
+      <c r="Z5" s="53" t="n">
         <v>9</v>
       </c>
-      <c r="AA5" s="49" t="inlineStr">
+      <c r="AA5" s="53" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
       </c>
-      <c r="AB5" s="49" t="inlineStr">
+      <c r="AB5" s="53" t="inlineStr">
         <is>
           <t>2d6</t>
         </is>
       </c>
       <c r="AC5" s="5" t="n"/>
-      <c r="AD5" s="49" t="inlineStr">
+      <c r="AD5" s="53" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="AE5" s="49" t="inlineStr">
+      <c r="AE5" s="53" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
       <c r="AF5" s="5" t="n"/>
-      <c r="AG5" s="49" t="n">
+      <c r="AG5" s="53" t="n">
         <v>14</v>
       </c>
-      <c r="AH5" s="49" t="n">
+      <c r="AH5" s="53" t="n">
         <v>26</v>
       </c>
-      <c r="AI5" s="49" t="n">
+      <c r="AI5" s="53" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" s="5" t="n"/>
-      <c r="AK5" s="49">
+      <c r="AK5" s="53">
         <f>INVOCAÇÃO!$T$30</f>
         <v/>
       </c>
       <c r="AL5" s="5" t="n"/>
-      <c r="AM5" s="49" t="inlineStr">
+      <c r="AM5" s="53" t="inlineStr">
         <is>
           <t>int_dono</t>
         </is>
       </c>
-      <c r="AN5" s="51" t="inlineStr">
+      <c r="AN5" s="55" t="inlineStr">
         <is>
           <t>Z7</t>
         </is>
@@ -7033,7 +7056,7 @@
     <row r="6">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="53" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -7042,23 +7065,23 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="49" t="inlineStr">
+      <c r="H6" s="53" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="I6" s="49" t="inlineStr">
+      <c r="I6" s="53" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="49" t="inlineStr">
+      <c r="K6" s="53" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
-      <c r="L6" s="49" t="n">
+      <c r="L6" s="53" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -7068,68 +7091,68 @@
       <c r="Q6" s="5" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="S6" s="5" t="n"/>
-      <c r="T6" s="49" t="inlineStr">
+      <c r="T6" s="53" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="U6" s="49" t="n">
+      <c r="U6" s="53" t="n">
         <v>3</v>
       </c>
       <c r="V6" s="5" t="n"/>
-      <c r="W6" s="49" t="inlineStr">
+      <c r="W6" s="53" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
-      <c r="X6" s="49" t="n">
+      <c r="X6" s="53" t="n">
         <v>4</v>
       </c>
       <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="49" t="n">
+      <c r="Z6" s="53" t="n">
         <v>13</v>
       </c>
-      <c r="AA6" s="49" t="inlineStr">
+      <c r="AA6" s="53" t="inlineStr">
         <is>
           <t>8d6</t>
         </is>
       </c>
-      <c r="AB6" s="49" t="inlineStr">
+      <c r="AB6" s="53" t="inlineStr">
         <is>
           <t>3d6</t>
         </is>
       </c>
       <c r="AC6" s="5" t="n"/>
-      <c r="AD6" s="49" t="inlineStr">
+      <c r="AD6" s="53" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="AE6" s="49" t="inlineStr">
+      <c r="AE6" s="53" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
       <c r="AF6" s="5" t="n"/>
-      <c r="AG6" s="49" t="n">
+      <c r="AG6" s="53" t="n">
         <v>18</v>
       </c>
       <c r="AH6" s="5" t="n"/>
-      <c r="AI6" s="49" t="n">
+      <c r="AI6" s="53" t="n">
         <v>13</v>
       </c>
       <c r="AJ6" s="5" t="n"/>
-      <c r="AK6" s="49">
+      <c r="AK6" s="53">
         <f>INVOCAÇÃO!$AB$30</f>
         <v/>
       </c>
       <c r="AL6" s="5" t="n"/>
-      <c r="AM6" s="49" t="inlineStr">
+      <c r="AM6" s="53" t="inlineStr">
         <is>
           <t>maestria</t>
         </is>
       </c>
-      <c r="AN6" s="51" t="inlineStr">
+      <c r="AN6" s="55" t="inlineStr">
         <is>
           <t>AK7</t>
         </is>
@@ -7143,12 +7166,12 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="49" t="inlineStr">
+      <c r="H7" s="53" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="I7" s="49" t="inlineStr">
+      <c r="I7" s="53" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
@@ -7163,33 +7186,33 @@
       <c r="Q7" s="5" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="S7" s="5" t="n"/>
-      <c r="T7" s="49" t="inlineStr">
+      <c r="T7" s="53" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="U7" s="49" t="n">
+      <c r="U7" s="53" t="n">
         <v>5</v>
       </c>
       <c r="V7" s="5" t="n"/>
-      <c r="W7" s="49" t="inlineStr">
+      <c r="W7" s="53" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
-      <c r="X7" s="49" t="n">
+      <c r="X7" s="53" t="n">
         <v>4</v>
       </c>
       <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="49" t="n">
+      <c r="Z7" s="53" t="n">
         <v>17</v>
       </c>
-      <c r="AA7" s="49" t="inlineStr">
+      <c r="AA7" s="53" t="inlineStr">
         <is>
           <t>10d6</t>
         </is>
       </c>
-      <c r="AB7" s="49" t="inlineStr">
+      <c r="AB7" s="53" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
@@ -7198,25 +7221,25 @@
       <c r="AD7" s="5" t="n"/>
       <c r="AE7" s="5" t="n"/>
       <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="49" t="n">
+      <c r="AG7" s="53" t="n">
         <v>22</v>
       </c>
       <c r="AH7" s="5" t="n"/>
-      <c r="AI7" s="49" t="n">
+      <c r="AI7" s="53" t="n">
         <v>17</v>
       </c>
       <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="49">
+      <c r="AK7" s="53">
         <f>INVOCAÇÃO!$AJ$30</f>
         <v/>
       </c>
       <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="49" t="inlineStr">
+      <c r="AM7" s="53" t="inlineStr">
         <is>
           <t>marcos</t>
         </is>
       </c>
-      <c r="AN7" s="51" t="inlineStr">
+      <c r="AN7" s="55" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
@@ -7230,12 +7253,12 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="49" t="inlineStr">
+      <c r="H8" s="53" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="I8" s="49" t="inlineStr">
+      <c r="I8" s="53" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
@@ -7250,33 +7273,33 @@
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="S8" s="5" t="n"/>
-      <c r="T8" s="49" t="inlineStr">
+      <c r="T8" s="53" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="U8" s="49" t="n">
+      <c r="U8" s="53" t="n">
         <v>5</v>
       </c>
       <c r="V8" s="5" t="n"/>
-      <c r="W8" s="49" t="inlineStr">
+      <c r="W8" s="53" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
       </c>
-      <c r="X8" s="49" t="n">
+      <c r="X8" s="53" t="n">
         <v>4</v>
       </c>
       <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="49" t="n">
+      <c r="Z8" s="53" t="n">
         <v>21</v>
       </c>
-      <c r="AA8" s="49" t="inlineStr">
+      <c r="AA8" s="53" t="inlineStr">
         <is>
           <t>13d6</t>
         </is>
       </c>
-      <c r="AB8" s="49" t="inlineStr">
+      <c r="AB8" s="53" t="inlineStr">
         <is>
           <t>5d6</t>
         </is>
@@ -7285,22 +7308,22 @@
       <c r="AD8" s="5" t="n"/>
       <c r="AE8" s="5" t="n"/>
       <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="49" t="n">
+      <c r="AG8" s="53" t="n">
         <v>26</v>
       </c>
       <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="49" t="n">
+      <c r="AI8" s="53" t="n">
         <v>21</v>
       </c>
       <c r="AJ8" s="5" t="n"/>
       <c r="AK8" s="5" t="n"/>
       <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="49" t="inlineStr">
+      <c r="AM8" s="53" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="AN8" s="51" t="inlineStr">
+      <c r="AN8" s="55" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
@@ -7314,12 +7337,12 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="49" t="inlineStr">
+      <c r="H9" s="53" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="I9" s="49" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
@@ -7334,33 +7357,33 @@
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="S9" s="5" t="n"/>
-      <c r="T9" s="49" t="inlineStr">
+      <c r="T9" s="53" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="U9" s="49" t="n">
+      <c r="U9" s="53" t="n">
         <v>7</v>
       </c>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="49" t="inlineStr">
+      <c r="W9" s="53" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
       </c>
-      <c r="X9" s="49" t="n">
+      <c r="X9" s="53" t="n">
         <v>8</v>
       </c>
       <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="49" t="n">
+      <c r="Z9" s="53" t="n">
         <v>26</v>
       </c>
-      <c r="AA9" s="49" t="inlineStr">
+      <c r="AA9" s="53" t="inlineStr">
         <is>
           <t>15d6</t>
         </is>
       </c>
-      <c r="AB9" s="49" t="inlineStr">
+      <c r="AB9" s="53" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
@@ -7369,22 +7392,22 @@
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
-      <c r="AG9" s="49" t="n">
+      <c r="AG9" s="53" t="n">
         <v>30</v>
       </c>
       <c r="AH9" s="5" t="n"/>
-      <c r="AI9" s="49" t="n">
+      <c r="AI9" s="53" t="n">
         <v>26</v>
       </c>
       <c r="AJ9" s="5" t="n"/>
       <c r="AK9" s="5" t="n"/>
       <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="49" t="inlineStr">
+      <c r="AM9" s="53" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="AN9" s="51" t="inlineStr">
+      <c r="AN9" s="55" t="inlineStr">
         <is>
           <t>D19</t>
         </is>
@@ -7398,7 +7421,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="49" t="inlineStr">
+      <c r="H10" s="53" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
@@ -7414,21 +7437,21 @@
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
-      <c r="T10" s="49" t="inlineStr">
+      <c r="T10" s="53" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="U10" s="49" t="n">
+      <c r="U10" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V10" s="5" t="n"/>
-      <c r="W10" s="49" t="inlineStr">
+      <c r="W10" s="53" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
       </c>
-      <c r="X10" s="49" t="n">
+      <c r="X10" s="53" t="n">
         <v>8</v>
       </c>
       <c r="Y10" s="5" t="n"/>
@@ -7445,12 +7468,12 @@
       <c r="AJ10" s="5" t="n"/>
       <c r="AK10" s="5" t="n"/>
       <c r="AL10" s="5" t="n"/>
-      <c r="AM10" s="49" t="inlineStr">
+      <c r="AM10" s="53" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="AN10" s="51" t="inlineStr">
+      <c r="AN10" s="55" t="inlineStr">
         <is>
           <t>Z19</t>
         </is>
@@ -7464,7 +7487,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="49" t="inlineStr">
+      <c r="H11" s="53" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
@@ -7480,12 +7503,12 @@
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="49" t="inlineStr">
+      <c r="T11" s="53" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
       </c>
-      <c r="U11" s="49" t="n">
+      <c r="U11" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V11" s="5" t="n"/>
@@ -7505,12 +7528,12 @@
       <c r="AJ11" s="5" t="n"/>
       <c r="AK11" s="5" t="n"/>
       <c r="AL11" s="5" t="n"/>
-      <c r="AM11" s="49" t="inlineStr">
+      <c r="AM11" s="53" t="inlineStr">
         <is>
           <t>trilha</t>
         </is>
       </c>
-      <c r="AN11" s="51" t="inlineStr">
+      <c r="AN11" s="55" t="inlineStr">
         <is>
           <t>AK19</t>
         </is>
@@ -7524,7 +7547,7 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="49" t="inlineStr">
+      <c r="H12" s="53" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
@@ -7540,12 +7563,12 @@
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="49" t="inlineStr">
+      <c r="T12" s="53" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
       </c>
-      <c r="U12" s="49" t="n">
+      <c r="U12" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V12" s="5" t="n"/>
@@ -7565,12 +7588,12 @@
       <c r="AJ12" s="5" t="n"/>
       <c r="AK12" s="5" t="n"/>
       <c r="AL12" s="5" t="n"/>
-      <c r="AM12" s="49" t="inlineStr">
+      <c r="AM12" s="53" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="AN12" s="51" t="inlineStr">
+      <c r="AN12" s="55" t="inlineStr">
         <is>
           <t>D22</t>
         </is>
@@ -7584,7 +7607,7 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="49" t="inlineStr">
+      <c r="H13" s="53" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
@@ -7600,12 +7623,12 @@
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="49" t="inlineStr">
+      <c r="T13" s="53" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="U13" s="49" t="n">
+      <c r="U13" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V13" s="5" t="n"/>
@@ -7625,12 +7648,12 @@
       <c r="AJ13" s="5" t="n"/>
       <c r="AK13" s="5" t="n"/>
       <c r="AL13" s="5" t="n"/>
-      <c r="AM13" s="49" t="inlineStr">
+      <c r="AM13" s="53" t="inlineStr">
         <is>
           <t>pontos_atributo</t>
         </is>
       </c>
-      <c r="AN13" s="51" t="inlineStr">
+      <c r="AN13" s="55" t="inlineStr">
         <is>
           <t>D35</t>
         </is>
@@ -7644,7 +7667,7 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="49" t="inlineStr">
+      <c r="H14" s="53" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
@@ -7660,12 +7683,12 @@
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="49" t="inlineStr">
+      <c r="T14" s="53" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
       </c>
-      <c r="U14" s="49" t="n">
+      <c r="U14" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V14" s="5" t="n"/>
@@ -7685,12 +7708,12 @@
       <c r="AJ14" s="5" t="n"/>
       <c r="AK14" s="5" t="n"/>
       <c r="AL14" s="5" t="n"/>
-      <c r="AM14" s="49" t="inlineStr">
+      <c r="AM14" s="53" t="inlineStr">
         <is>
           <t>pontos_disp</t>
         </is>
       </c>
-      <c r="AN14" s="51" t="inlineStr">
+      <c r="AN14" s="55" t="inlineStr">
         <is>
           <t>O35</t>
         </is>
@@ -7704,7 +7727,7 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="49" t="inlineStr">
+      <c r="H15" s="53" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
@@ -7720,12 +7743,12 @@
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="49" t="inlineStr">
+      <c r="T15" s="53" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="U15" s="49" t="n">
+      <c r="U15" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V15" s="5" t="n"/>
@@ -7745,12 +7768,12 @@
       <c r="AJ15" s="5" t="n"/>
       <c r="AK15" s="5" t="n"/>
       <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="49" t="inlineStr">
+      <c r="AM15" s="53" t="inlineStr">
         <is>
           <t>aviso_atributo</t>
         </is>
       </c>
-      <c r="AN15" s="51" t="inlineStr">
+      <c r="AN15" s="55" t="inlineStr">
         <is>
           <t>Z35</t>
         </is>
@@ -7776,12 +7799,12 @@
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="49" t="inlineStr">
+      <c r="T16" s="53" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
       </c>
-      <c r="U16" s="49" t="n">
+      <c r="U16" s="53" t="n">
         <v>8</v>
       </c>
       <c r="V16" s="5" t="n"/>
@@ -7801,12 +7824,12 @@
       <c r="AJ16" s="5" t="n"/>
       <c r="AK16" s="5" t="n"/>
       <c r="AL16" s="5" t="n"/>
-      <c r="AM16" s="49" t="inlineStr">
+      <c r="AM16" s="53" t="inlineStr">
         <is>
           <t>atr_acerto</t>
         </is>
       </c>
-      <c r="AN16" s="51" t="inlineStr">
+      <c r="AN16" s="55" t="inlineStr">
         <is>
           <t>D43</t>
         </is>
@@ -7851,12 +7874,12 @@
       <c r="AJ17" s="5" t="n"/>
       <c r="AK17" s="5" t="n"/>
       <c r="AL17" s="5" t="n"/>
-      <c r="AM17" s="49" t="inlineStr">
+      <c r="AM17" s="53" t="inlineStr">
         <is>
           <t>acerto</t>
         </is>
       </c>
-      <c r="AN17" s="51" t="inlineStr">
+      <c r="AN17" s="55" t="inlineStr">
         <is>
           <t>O43</t>
         </is>
@@ -7901,12 +7924,12 @@
       <c r="AJ18" s="5" t="n"/>
       <c r="AK18" s="5" t="n"/>
       <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="49" t="inlineStr">
+      <c r="AM18" s="53" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="AN18" s="51" t="inlineStr">
+      <c r="AN18" s="55" t="inlineStr">
         <is>
           <t>Z43</t>
         </is>
@@ -7951,12 +7974,12 @@
       <c r="AJ19" s="5" t="n"/>
       <c r="AK19" s="5" t="n"/>
       <c r="AL19" s="5" t="n"/>
-      <c r="AM19" s="49" t="inlineStr">
+      <c r="AM19" s="53" t="inlineStr">
         <is>
           <t>defesa</t>
         </is>
       </c>
-      <c r="AN19" s="51" t="inlineStr">
+      <c r="AN19" s="55" t="inlineStr">
         <is>
           <t>AK43</t>
         </is>
@@ -8001,12 +8024,12 @@
       <c r="AJ20" s="5" t="n"/>
       <c r="AK20" s="5" t="n"/>
       <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="49" t="inlineStr">
+      <c r="AM20" s="53" t="inlineStr">
         <is>
           <t>critico</t>
         </is>
       </c>
-      <c r="AN20" s="51" t="inlineStr">
+      <c r="AN20" s="55" t="inlineStr">
         <is>
           <t>D46</t>
         </is>
@@ -8051,12 +8074,12 @@
       <c r="AJ21" s="5" t="n"/>
       <c r="AK21" s="5" t="n"/>
       <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="49" t="inlineStr">
+      <c r="AM21" s="53" t="inlineStr">
         <is>
           <t>tr_treinado</t>
         </is>
       </c>
-      <c r="AN21" s="51" t="inlineStr">
+      <c r="AN21" s="55" t="inlineStr">
         <is>
           <t>O46</t>
         </is>
@@ -8101,12 +8124,12 @@
       <c r="AJ22" s="5" t="n"/>
       <c r="AK22" s="5" t="n"/>
       <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="49" t="inlineStr">
+      <c r="AM22" s="53" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="AN22" s="51" t="inlineStr">
+      <c r="AN22" s="55" t="inlineStr">
         <is>
           <t>Z46</t>
         </is>
@@ -8151,14 +8174,14 @@
       <c r="AJ23" s="5" t="n"/>
       <c r="AK23" s="5" t="n"/>
       <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="49" t="inlineStr">
-        <is>
-          <t>vida_max</t>
-        </is>
-      </c>
-      <c r="AN23" s="51" t="inlineStr">
-        <is>
-          <t>D58</t>
+      <c r="AM23" s="53" t="inlineStr">
+        <is>
+          <t>tr_Físico</t>
+        </is>
+      </c>
+      <c r="AN23" s="55" t="inlineStr">
+        <is>
+          <t>Q50</t>
         </is>
       </c>
     </row>
@@ -8201,14 +8224,14 @@
       <c r="AJ24" s="5" t="n"/>
       <c r="AK24" s="5" t="n"/>
       <c r="AL24" s="5" t="n"/>
-      <c r="AM24" s="49" t="inlineStr">
-        <is>
-          <t>vida</t>
-        </is>
-      </c>
-      <c r="AN24" s="51" t="inlineStr">
-        <is>
-          <t>O58</t>
+      <c r="AM24" s="53" t="inlineStr">
+        <is>
+          <t>tr_extra_Físico</t>
+        </is>
+      </c>
+      <c r="AN24" s="55" t="inlineStr">
+        <is>
+          <t>K50</t>
         </is>
       </c>
     </row>
@@ -8251,14 +8274,14 @@
       <c r="AJ25" s="5" t="n"/>
       <c r="AK25" s="5" t="n"/>
       <c r="AL25" s="5" t="n"/>
-      <c r="AM25" s="49" t="inlineStr">
-        <is>
-          <t>corpos</t>
-        </is>
-      </c>
-      <c r="AN25" s="51" t="inlineStr">
-        <is>
-          <t>Z58</t>
+      <c r="AM25" s="53" t="inlineStr">
+        <is>
+          <t>tr_Vigor</t>
+        </is>
+      </c>
+      <c r="AN25" s="55" t="inlineStr">
+        <is>
+          <t>AM50</t>
         </is>
       </c>
     </row>
@@ -8301,14 +8324,14 @@
       <c r="AJ26" s="5" t="n"/>
       <c r="AK26" s="5" t="n"/>
       <c r="AL26" s="5" t="n"/>
-      <c r="AM26" s="49" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AN26" s="51" t="inlineStr">
-        <is>
-          <t>AK58</t>
+      <c r="AM26" s="53" t="inlineStr">
+        <is>
+          <t>tr_extra_Vigor</t>
+        </is>
+      </c>
+      <c r="AN26" s="55" t="inlineStr">
+        <is>
+          <t>AG50</t>
         </is>
       </c>
     </row>
@@ -8351,14 +8374,14 @@
       <c r="AJ27" s="5" t="n"/>
       <c r="AK27" s="5" t="n"/>
       <c r="AL27" s="5" t="n"/>
-      <c r="AM27" s="49" t="inlineStr">
-        <is>
-          <t>regua</t>
-        </is>
-      </c>
-      <c r="AN27" s="51" t="inlineStr">
-        <is>
-          <t>D64</t>
+      <c r="AM27" s="53" t="inlineStr">
+        <is>
+          <t>tr_Intelecto</t>
+        </is>
+      </c>
+      <c r="AN27" s="55" t="inlineStr">
+        <is>
+          <t>Q51</t>
         </is>
       </c>
     </row>
@@ -8401,14 +8424,14 @@
       <c r="AJ28" s="5" t="n"/>
       <c r="AK28" s="5" t="n"/>
       <c r="AL28" s="5" t="n"/>
-      <c r="AM28" s="49" t="inlineStr">
-        <is>
-          <t>meia_regua</t>
-        </is>
-      </c>
-      <c r="AN28" s="51" t="inlineStr">
-        <is>
-          <t>O64</t>
+      <c r="AM28" s="53" t="inlineStr">
+        <is>
+          <t>tr_extra_Intelecto</t>
+        </is>
+      </c>
+      <c r="AN28" s="55" t="inlineStr">
+        <is>
+          <t>K51</t>
         </is>
       </c>
     </row>
@@ -8451,14 +8474,14 @@
       <c r="AJ29" s="5" t="n"/>
       <c r="AK29" s="5" t="n"/>
       <c r="AL29" s="5" t="n"/>
-      <c r="AM29" s="49" t="inlineStr">
-        <is>
-          <t>volta_com</t>
-        </is>
-      </c>
-      <c r="AN29" s="51" t="inlineStr">
-        <is>
-          <t>Z64</t>
+      <c r="AM29" s="53" t="inlineStr">
+        <is>
+          <t>tr_Espírito</t>
+        </is>
+      </c>
+      <c r="AN29" s="55" t="inlineStr">
+        <is>
+          <t>AM51</t>
         </is>
       </c>
     </row>
@@ -8501,482 +8524,578 @@
       <c r="AJ30" s="5" t="n"/>
       <c r="AK30" s="5" t="n"/>
       <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="49" t="inlineStr">
+      <c r="AM30" s="53" t="inlineStr">
+        <is>
+          <t>tr_extra_Espírito</t>
+        </is>
+      </c>
+      <c r="AN30" s="55" t="inlineStr">
+        <is>
+          <t>AG51</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AM31" s="55" t="inlineStr">
+        <is>
+          <t>vida_max</t>
+        </is>
+      </c>
+      <c r="AN31" s="55" t="inlineStr">
+        <is>
+          <t>D59</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AM32" s="55" t="inlineStr">
+        <is>
+          <t>vida</t>
+        </is>
+      </c>
+      <c r="AN32" s="55" t="inlineStr">
+        <is>
+          <t>O59</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="AM33" s="55" t="inlineStr">
+        <is>
+          <t>corpos</t>
+        </is>
+      </c>
+      <c r="AN33" s="55" t="inlineStr">
+        <is>
+          <t>Z59</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="AM34" s="55" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AN34" s="55" t="inlineStr">
+        <is>
+          <t>AK59</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="AM35" s="55" t="inlineStr">
+        <is>
+          <t>regua</t>
+        </is>
+      </c>
+      <c r="AN35" s="55" t="inlineStr">
+        <is>
+          <t>D65</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="AM36" s="55" t="inlineStr">
+        <is>
+          <t>meia_regua</t>
+        </is>
+      </c>
+      <c r="AN36" s="55" t="inlineStr">
+        <is>
+          <t>O65</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="AM37" s="55" t="inlineStr">
+        <is>
+          <t>volta_com</t>
+        </is>
+      </c>
+      <c r="AN37" s="55" t="inlineStr">
+        <is>
+          <t>Z65</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="AM38" s="55" t="inlineStr">
         <is>
           <t>orcamento</t>
         </is>
       </c>
-      <c r="AN30" s="51" t="inlineStr">
-        <is>
-          <t>D75</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="AM31" s="51" t="inlineStr">
+      <c r="AN38" s="55" t="inlineStr">
+        <is>
+          <t>D76</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="AM39" s="55" t="inlineStr">
         <is>
           <t>gasto</t>
         </is>
       </c>
-      <c r="AN31" s="51" t="inlineStr">
-        <is>
-          <t>D90</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="AM32" s="51" t="inlineStr">
+      <c r="AN39" s="55" t="inlineStr">
+        <is>
+          <t>D91</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="AM40" s="55" t="inlineStr">
         <is>
           <t>sobra</t>
         </is>
       </c>
-      <c r="AN32" s="51" t="inlineStr">
-        <is>
-          <t>O90</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="AM33" s="51" t="inlineStr">
+      <c r="AN40" s="55" t="inlineStr">
+        <is>
+          <t>O91</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="AM41" s="55" t="inlineStr">
         <is>
           <t>investir</t>
         </is>
       </c>
-      <c r="AN33" s="51" t="inlineStr">
-        <is>
-          <t>D98</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="AM34" s="51" t="inlineStr">
+      <c r="AN41" s="55" t="inlineStr">
+        <is>
+          <t>D99</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="AM42" s="55" t="inlineStr">
         <is>
           <t>cd_pendente</t>
         </is>
       </c>
-      <c r="AN34" s="51" t="inlineStr">
-        <is>
-          <t>D115</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="AM35" s="51" t="inlineStr">
+      <c r="AN42" s="55" t="inlineStr">
+        <is>
+          <t>D116</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="AM43" s="55" t="inlineStr">
         <is>
           <t>atr_Força</t>
         </is>
       </c>
-      <c r="AN35" s="51" t="inlineStr">
+      <c r="AN43" s="55" t="inlineStr">
         <is>
           <t>D30</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="AM36" s="51" t="inlineStr">
+    <row r="44">
+      <c r="AM44" s="55" t="inlineStr">
         <is>
           <t>atr_Destreza</t>
         </is>
       </c>
-      <c r="AN36" s="51" t="inlineStr">
+      <c r="AN44" s="55" t="inlineStr">
         <is>
           <t>L30</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="AM37" s="51" t="inlineStr">
+    <row r="45">
+      <c r="AM45" s="55" t="inlineStr">
         <is>
           <t>atr_Constituição</t>
         </is>
       </c>
-      <c r="AN37" s="51" t="inlineStr">
+      <c r="AN45" s="55" t="inlineStr">
         <is>
           <t>T30</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="AM38" s="51" t="inlineStr">
+    <row r="46">
+      <c r="AM46" s="55" t="inlineStr">
         <is>
           <t>atr_Inteligência</t>
         </is>
       </c>
-      <c r="AN38" s="51" t="inlineStr">
+      <c r="AN46" s="55" t="inlineStr">
         <is>
           <t>AB30</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="AM39" s="51" t="inlineStr">
+    <row r="47">
+      <c r="AM47" s="55" t="inlineStr">
         <is>
           <t>atr_Essência</t>
         </is>
       </c>
-      <c r="AN39" s="51" t="inlineStr">
+      <c r="AN47" s="55" t="inlineStr">
         <is>
           <t>AJ30</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="AM40" s="51" t="inlineStr">
+    <row r="48">
+      <c r="AM48" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_1</t>
         </is>
       </c>
-      <c r="AN40" s="51" t="inlineStr">
-        <is>
-          <t>S79</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="AM41" s="51" t="inlineStr">
+      <c r="AN48" s="55" t="inlineStr">
+        <is>
+          <t>S80</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="AM49" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_2</t>
         </is>
       </c>
-      <c r="AN41" s="51" t="inlineStr">
-        <is>
-          <t>S80</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="AM42" s="51" t="inlineStr">
+      <c r="AN49" s="55" t="inlineStr">
+        <is>
+          <t>S81</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="AM50" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_3</t>
         </is>
       </c>
-      <c r="AN42" s="51" t="inlineStr">
-        <is>
-          <t>S81</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="AM43" s="51" t="inlineStr">
+      <c r="AN50" s="55" t="inlineStr">
+        <is>
+          <t>S82</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="AM51" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_4</t>
         </is>
       </c>
-      <c r="AN43" s="51" t="inlineStr">
-        <is>
-          <t>S82</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="AM44" s="51" t="inlineStr">
+      <c r="AN51" s="55" t="inlineStr">
+        <is>
+          <t>S83</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="AM52" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_5</t>
         </is>
       </c>
-      <c r="AN44" s="51" t="inlineStr">
-        <is>
-          <t>S83</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="AM45" s="51" t="inlineStr">
+      <c r="AN52" s="55" t="inlineStr">
+        <is>
+          <t>S84</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="AM53" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_6</t>
         </is>
       </c>
-      <c r="AN45" s="51" t="inlineStr">
-        <is>
-          <t>S84</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="AM46" s="51" t="inlineStr">
+      <c r="AN53" s="55" t="inlineStr">
+        <is>
+          <t>S85</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="AM54" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_7</t>
         </is>
       </c>
-      <c r="AN46" s="51" t="inlineStr">
-        <is>
-          <t>S85</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="AM47" s="51" t="inlineStr">
+      <c r="AN54" s="55" t="inlineStr">
+        <is>
+          <t>S86</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="AM55" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_8</t>
         </is>
       </c>
-      <c r="AN47" s="51" t="inlineStr">
-        <is>
-          <t>S86</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="AM48" s="51" t="inlineStr">
+      <c r="AN55" s="55" t="inlineStr">
+        <is>
+          <t>S87</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="AM56" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_9</t>
         </is>
       </c>
-      <c r="AN48" s="51" t="inlineStr">
-        <is>
-          <t>S87</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="AM49" s="51" t="inlineStr">
+      <c r="AN56" s="55" t="inlineStr">
+        <is>
+          <t>S88</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="AM57" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_10</t>
         </is>
       </c>
-      <c r="AN49" s="51" t="inlineStr">
-        <is>
-          <t>AO79</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="AM50" s="51" t="inlineStr">
+      <c r="AN57" s="55" t="inlineStr">
+        <is>
+          <t>AO80</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="AM58" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_11</t>
         </is>
       </c>
-      <c r="AN50" s="51" t="inlineStr">
-        <is>
-          <t>AO80</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="AM51" s="51" t="inlineStr">
+      <c r="AN58" s="55" t="inlineStr">
+        <is>
+          <t>AO81</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="AM59" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_12</t>
         </is>
       </c>
-      <c r="AN51" s="51" t="inlineStr">
-        <is>
-          <t>AO81</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="AM52" s="51" t="inlineStr">
+      <c r="AN59" s="55" t="inlineStr">
+        <is>
+          <t>AO82</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="AM60" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_13</t>
         </is>
       </c>
-      <c r="AN52" s="51" t="inlineStr">
-        <is>
-          <t>AO82</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="AM53" s="51" t="inlineStr">
+      <c r="AN60" s="55" t="inlineStr">
+        <is>
+          <t>AO83</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="AM61" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_14</t>
         </is>
       </c>
-      <c r="AN53" s="51" t="inlineStr">
-        <is>
-          <t>AO83</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="AM54" s="51" t="inlineStr">
+      <c r="AN61" s="55" t="inlineStr">
+        <is>
+          <t>AO84</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="AM62" s="55" t="inlineStr">
         <is>
           <t>slot_pontos_15</t>
         </is>
       </c>
-      <c r="AN54" s="51" t="inlineStr">
-        <is>
-          <t>AO84</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="AM55" s="51" t="inlineStr">
+      <c r="AN62" s="55" t="inlineStr">
+        <is>
+          <t>AO85</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="AM63" s="55" t="inlineStr">
         <is>
           <t>traco_1</t>
         </is>
       </c>
-      <c r="AN55" s="51" t="inlineStr">
-        <is>
-          <t>D79</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="AM56" s="51" t="inlineStr">
+      <c r="AN63" s="55" t="inlineStr">
+        <is>
+          <t>D80</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="AM64" s="55" t="inlineStr">
         <is>
           <t>traco_2</t>
         </is>
       </c>
-      <c r="AN56" s="51" t="inlineStr">
-        <is>
-          <t>D80</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="AM57" s="51" t="inlineStr">
+      <c r="AN64" s="55" t="inlineStr">
+        <is>
+          <t>D81</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="AM65" s="55" t="inlineStr">
         <is>
           <t>traco_3</t>
         </is>
       </c>
-      <c r="AN57" s="51" t="inlineStr">
-        <is>
-          <t>D81</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="AM58" s="51" t="inlineStr">
+      <c r="AN65" s="55" t="inlineStr">
+        <is>
+          <t>D82</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="AM66" s="55" t="inlineStr">
         <is>
           <t>traco_4</t>
         </is>
       </c>
-      <c r="AN58" s="51" t="inlineStr">
-        <is>
-          <t>D82</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="AM59" s="51" t="inlineStr">
+      <c r="AN66" s="55" t="inlineStr">
+        <is>
+          <t>D83</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="AM67" s="55" t="inlineStr">
         <is>
           <t>traco_5</t>
         </is>
       </c>
-      <c r="AN59" s="51" t="inlineStr">
-        <is>
-          <t>D83</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="AM60" s="51" t="inlineStr">
+      <c r="AN67" s="55" t="inlineStr">
+        <is>
+          <t>D84</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="AM68" s="55" t="inlineStr">
         <is>
           <t>traco_6</t>
         </is>
       </c>
-      <c r="AN60" s="51" t="inlineStr">
-        <is>
-          <t>D84</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="AM61" s="51" t="inlineStr">
+      <c r="AN68" s="55" t="inlineStr">
+        <is>
+          <t>D85</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="AM69" s="55" t="inlineStr">
         <is>
           <t>traco_7</t>
         </is>
       </c>
-      <c r="AN61" s="51" t="inlineStr">
-        <is>
-          <t>D85</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="AM62" s="51" t="inlineStr">
+      <c r="AN69" s="55" t="inlineStr">
+        <is>
+          <t>D86</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="AM70" s="55" t="inlineStr">
         <is>
           <t>traco_8</t>
         </is>
       </c>
-      <c r="AN62" s="51" t="inlineStr">
-        <is>
-          <t>D86</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="AM63" s="51" t="inlineStr">
+      <c r="AN70" s="55" t="inlineStr">
+        <is>
+          <t>D87</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="AM71" s="55" t="inlineStr">
         <is>
           <t>traco_9</t>
         </is>
       </c>
-      <c r="AN63" s="51" t="inlineStr">
-        <is>
-          <t>D87</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="AM64" s="51" t="inlineStr">
+      <c r="AN71" s="55" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="AM72" s="55" t="inlineStr">
         <is>
           <t>comando_1</t>
         </is>
       </c>
-      <c r="AN64" s="51" t="inlineStr">
-        <is>
-          <t>Z79</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="AM65" s="51" t="inlineStr">
+      <c r="AN72" s="55" t="inlineStr">
+        <is>
+          <t>Z80</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="AM73" s="55" t="inlineStr">
         <is>
           <t>comando_2</t>
         </is>
       </c>
-      <c r="AN65" s="51" t="inlineStr">
-        <is>
-          <t>Z80</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="AM66" s="51" t="inlineStr">
+      <c r="AN73" s="55" t="inlineStr">
+        <is>
+          <t>Z81</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="AM74" s="55" t="inlineStr">
         <is>
           <t>comando_3</t>
         </is>
       </c>
-      <c r="AN66" s="51" t="inlineStr">
-        <is>
-          <t>Z81</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="AM67" s="51" t="inlineStr">
+      <c r="AN74" s="55" t="inlineStr">
+        <is>
+          <t>Z82</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="AM75" s="55" t="inlineStr">
         <is>
           <t>comando_4</t>
         </is>
       </c>
-      <c r="AN67" s="51" t="inlineStr">
-        <is>
-          <t>Z82</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="AM68" s="51" t="inlineStr">
+      <c r="AN75" s="55" t="inlineStr">
+        <is>
+          <t>Z83</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="AM76" s="55" t="inlineStr">
         <is>
           <t>comando_5</t>
         </is>
       </c>
-      <c r="AN68" s="51" t="inlineStr">
-        <is>
-          <t>Z83</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="AM69" s="51" t="inlineStr">
+      <c r="AN76" s="55" t="inlineStr">
+        <is>
+          <t>Z84</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="AM77" s="55" t="inlineStr">
         <is>
           <t>comando_6</t>
         </is>
       </c>
-      <c r="AN69" s="51" t="inlineStr">
-        <is>
-          <t>Z84</t>
+      <c r="AN77" s="55" t="inlineStr">
+        <is>
+          <t>Z85</t>
         </is>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -800,7 +800,7 @@
       <c r="AE1" s="2" t="n"/>
       <c r="AF1" s="4" t="inlineStr">
         <is>
-          <t>capítulo 16 · sistema v0.200</t>
+          <t>capítulo 16 · Projeto - M</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       <c r="C4" s="5" t="n"/>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>O DONO — o que a ficha dele decide</t>
+          <t>O DONO</t>
         </is>
       </c>
       <c r="AC4" s="5" t="n"/>
@@ -948,13 +948,13 @@
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="8" t="inlineStr">
         <is>
-          <t>ESSÊNCIA DELE</t>
+          <t>ESSÊNCIA DO DONO</t>
         </is>
       </c>
       <c r="Y6" s="5" t="n"/>
       <c r="Z6" s="8" t="inlineStr">
         <is>
-          <t>INTELIGÊNCIA DELE</t>
+          <t>INTELIGÊNCIA DO DONO</t>
         </is>
       </c>
       <c r="AJ6" s="5" t="n"/>
@@ -1052,7 +1052,7 @@
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="8" t="inlineStr">
         <is>
-          <t>MAIOR CLASSE · PE DE INVOCAR</t>
+          <t>MAIOR CLASSE</t>
         </is>
       </c>
       <c r="Y10" s="5" t="n"/>
@@ -1162,7 +1162,7 @@
       <c r="C13" s="5" t="n"/>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>As três da esquerda você digita. No dia em que isto virar aba da ficha grande, elas puxam da FICHA por fórmula e nada mais muda.</t>
+          <t>Copie estes três da sua ficha. O resto desta seção a planilha calcula.</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       <c r="C16" s="5" t="n"/>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1377,7 +1377,7 @@
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="15" t="inlineStr">
         <is>
-          <t>A TRILHA É O EIXO</t>
+          <t>O QUE A TRILHA DECIDE</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>ela decide quantos corpos vão a campo, qual fórmula de vida vale, e o multiplicador do orçamento</t>
+          <t>quantos corpos você põe em campo, quanta vida cada um tem, e o tamanho do orçamento</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       <c r="C24" s="5" t="n"/>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>A Sintonia é o degrau de nível 2 do Evocador: Presa — as suas invocacoes acertam critico com 19 ou 20 · Parrudo — as suas invocacoes tem mais vida, equivalente a 5 x a sua maestria · Voz — a CD dos efeitos das suas invocacoes sobe em 1, e vira metade da sua maestria a partir do nivel 7</t>
+          <t>A Sintonia é a escolha de nível 2 do Evocador. Presa: crítico com 19 ou 20. Parrudo: mais vida, 5 × a sua maestria. Voz: sobe a CD dos efeitos dela — veja a seção 9.</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       <c r="C27" s="5" t="n"/>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>OS ATRIBUTOS DELA — são dela, e ela não copia os seus</t>
+          <t>OS ATRIBUTOS DELA</t>
         </is>
       </c>
       <c r="AG27" s="5" t="n"/>
@@ -1789,7 +1789,7 @@
       <c r="C37" s="5" t="n"/>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>9 pontos na criação com teto 3, mais 1 por marco, teto 6. Mesma regra da sua ficha.</t>
+          <t>Distribua 9 pontos, nenhum acima de 3. A cada marco ela ganha 1 ponto, até o teto de 6. É a mesma regra da sua ficha.</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       <c r="C40" s="5" t="n"/>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>O QUE ENCARA O DADO — o número é dela, o ritmo é seu</t>
+          <t>ACERTO, DEFESA E TESTES DE RESISTÊNCIA</t>
         </is>
       </c>
       <c r="AI40" s="5" t="n"/>
@@ -1926,7 +1926,7 @@
       <c r="Y42" s="5" t="n"/>
       <c r="Z42" s="8" t="inlineStr">
         <is>
-          <t>DEFESA USA, DELE</t>
+          <t>DEFESA USA, DO DONO</t>
         </is>
       </c>
       <c r="AJ42" s="5" t="n"/>
@@ -2101,7 +2101,7 @@
       <c r="C48" s="5" t="n"/>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>OS QUATRO TESTES DE RESISTÊNCIA · ela treina UM, e a sua maestria entra só nele</t>
+          <t>TESTES DE RESISTÊNCIA · ela treina um, e você escolhe qual no campo acima</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
       <c r="C53" s="5" t="n"/>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Acerto e Teste de Resistência rolam d20 + isto, e o Extra entra na conta — é onde entra o que a ficha não sabe. A Defesa é passiva, e a maestria não entra nela.</t>
+          <t>Role d20 e some o número da coluna. O Extra é para bônus que a planilha não conhece; deixe vazio se não houver. A Defesa não se rola: o inimigo rola contra ela.</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       <c r="C56" s="5" t="n"/>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
@@ -2718,7 +2718,7 @@
       <c r="C67" s="5" t="n"/>
       <c r="D67" s="34" t="inlineStr">
         <is>
-          <t>MORRE DE VEZ SE</t>
+          <t>MORRE DE VEZ</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>o excedente passar da metade da régua, ou um golpe só causar a régua inteira. A régua sai da vida CRUA do tipo, nunca da do corpo forte — é a mesma para um corpo, cinco, ou o corpo grande.</t>
+          <t>quando o dano que passar de zero for maior que a metade da régua, ou quando um golpe só causar a régua inteira. Fora desses dois casos ela só cai, e você reinvoca.</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       <c r="C70" s="5" t="n"/>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Ela some no zero: sem Inconsciente, sem Sequela e sem Cicatriz. A vida cheia volta no descanso longo.</t>
+          <t>No zero ela sai do campo. Ela não fica Inconsciente e não ganha Sequela nem Cicatriz. Reinvocar custa os PE de novo, e ela volta com metade da vida; a vida cheia volta no descanso longo.</t>
         </is>
       </c>
     </row>
@@ -2806,12 +2806,12 @@
       <c r="C73" s="5" t="n"/>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>O ORÇAMENTO — compra o que ela FAZ, nunca número</t>
+          <t>O ORÇAMENTO</t>
         </is>
       </c>
       <c r="AG73" s="5" t="n"/>
@@ -3506,7 +3506,7 @@
       <c r="C93" s="5" t="n"/>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>O Servo monta com o orçamento da ficha mais metade, porque é um corpo só e não cinco. O que ele NÃO compra a preço nenhum: dado de dano · qualquer coisa que cresça com refino · atributo · Defesa, acerto ou vida direto.</t>
+          <t>Escolha Traço e Comando até o orçamento acabar. O Servo tem metade a mais que as outras duas Trilhas. Nada aqui compra dano, Defesa, acerto ou vida — esses saem dos atributos dela.</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       <c r="C96" s="5" t="n"/>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>INVESTIR — o ataque, e toda invocação tem</t>
+          <t>INVESTIR</t>
         </is>
       </c>
       <c r="AC96" s="5" t="n"/>
@@ -3731,7 +3731,7 @@
       <c r="C102" s="5" t="n"/>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Você e todas as suas invocações somados entregam uma Rotina. O número de dados sempre desce — a soma nunca passa do que você faria sozinho.</t>
+          <t>É o dano dela quando você gasta a Ação Padrão comandando. Você e as suas invocações somados causam o dano de uma rodada sua sozinho.</t>
         </is>
       </c>
     </row>
@@ -3794,12 +3794,12 @@
       <c r="C105" s="5" t="n"/>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>NA MESA — o que não muda</t>
+          <t>NA MESA</t>
         </is>
       </c>
       <c r="Y105" s="5" t="n"/>
@@ -3994,12 +3994,12 @@
       <c r="C113" s="5" t="n"/>
       <c r="D113" s="6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>O QUE ESTA FICHA NÃO CALCULA, E POR QUÊ</t>
+          <t>O QUE A FICHA NÃO CALCULA</t>
         </is>
       </c>
       <c r="AG113" s="5" t="n"/>
@@ -4077,7 +4077,7 @@
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="5" t="n"/>
       <c r="D116" s="35">
-        <f>IF($D$22="Voz","a Voz manda subir a CD dela, e a invocação não tem fórmula de CD em documento nenhum — combine com o mestre","")</f>
+        <f>IF($D$22="Voz","A Voz sobe a CD dos efeitos dela, e o sistema ainda não diz qual é essa CD. Combine com o mestre.","")</f>
         <v/>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       <c r="C117" s="5" t="n"/>
       <c r="D117" s="43" t="inlineStr">
         <is>
-          <t>A invocação não tem fórmula de CD em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Esta rota soma num número que o sistema ainda não produz, então combine com o mestre em vez de chutar.</t>
+          <t>A CD dos efeitos dela não tem fórmula em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Enquanto não existir, combine o número com o mestre.</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="U4" s="46" t="inlineStr">
         <is>
-          <t>o que ela É. Sempre ligado, sem gastar ação.</t>
+          <t>o corpo dela. Vale sempre, sem gastar ação.</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="U21" s="46" t="inlineStr">
         <is>
-          <t>o que ela FAZ quando o dono gasta a Ação Padrão nela.</t>
+          <t>o que ela faz quando você gasta a Ação Padrão comandando.</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5206,7 @@
       </c>
       <c r="U32" s="46" t="inlineStr">
         <is>
-          <t>escreva o efeito, ache na régua o degrau em que ele cai, e leve para o mestre</t>
+          <t>escreva o efeito, ache na régua o preço, e leve para o mestre aprovar</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       <c r="C45" s="5" t="n"/>
       <c r="D45" s="34" t="inlineStr">
         <is>
-          <t>E O QUE NÃO SE COMPRA A PREÇO NENHUM</t>
+          <t>O QUE O ORÇAMENTO NÃO COMPRA</t>
         </is>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="O62" s="33">
-        <f>IFERROR(SPARKLINE($O$59,{"charttype","bar";"max",$D$59;"color1",IF(N($D$59)=0,"#E8DCD4",IF($O$59/$D$59&lt;=0.25,"#C2334D",IF($O$59/$D$59&lt;=0.5,"#D89B3A","#E8DCD4")))}),"")</f>
+        <f>IFERROR(SPARKLINE({MAX(0,MIN(N($O$59),N($D$59))),MAX(0,N($D$59)-MAX(0,N($O$59)))},{"charttype","bar";"color1",IF(IFERROR(N($O$59)/N($D$59),0)&lt;=0.25,"#C2334D",IF(IFERROR(N($O$59)/N($D$59),0)&lt;=0.5,"#D89B3A","#E8DCD4"));"color2","#3D2E78"}),"")</f>
         <v/>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="O62" s="33">
-        <f>IFERROR(SPARKLINE({MAX(0,MIN(N($O$59),N($D$59))),MAX(0,N($D$59)-MAX(0,N($O$59)))},{"charttype","bar";"color1",IF(IFERROR(N($O$59)/N($D$59),0)&lt;=0.25,"#C2334D",IF(IFERROR(N($O$59)/N($D$59),0)&lt;=0.5,"#D89B3A","#E8DCD4"));"color2","#3D2E78"}),"")</f>
+        <f>IFERROR(SPARKLINE($O$59,{"charttype","bar";"max",$D$59;"color1",IF(N($D$59)=0,"#E8DCD4",IF($O$59/$D$59&lt;=0.25,"#C2334D",IF($O$59/$D$59&lt;=0.5,"#D89B3A","#E8DCD4")))}),"")</f>
         <v/>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Roboto"/>
       <color rgb="00F4F1F7"/>
@@ -142,6 +142,11 @@
     </font>
     <font>
       <name val="Oswald"/>
+      <color rgb="00998BA9"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Oswald"/>
       <color rgb="00E8DCD4"/>
       <sz val="11"/>
     </font>
@@ -211,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -312,28 +317,37 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -345,10 +359,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -364,9 +378,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3054,11 +3065,31 @@
           <t>TRAÇO · até 9</t>
         </is>
       </c>
+      <c r="O79" s="36" t="inlineStr">
+        <is>
+          <t>DEGRAU</t>
+        </is>
+      </c>
+      <c r="S79" s="37" t="inlineStr">
+        <is>
+          <t>PONTOS</t>
+        </is>
+      </c>
       <c r="X79" s="5" t="n"/>
       <c r="Y79" s="5" t="n"/>
       <c r="Z79" s="22" t="inlineStr">
         <is>
           <t>COMANDO · até 6</t>
+        </is>
+      </c>
+      <c r="AK79" s="36" t="inlineStr">
+        <is>
+          <t>DEGRAU</t>
+        </is>
+      </c>
+      <c r="AO79" s="37" t="inlineStr">
+        <is>
+          <t>PONTOS</t>
         </is>
       </c>
       <c r="AT79" s="5" t="n"/>
@@ -3072,8 +3103,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S80" s="36">
-        <f>IFERROR(VLOOKUP($D$80,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S80" s="39">
+        <f>IFERROR(VLOOKUP($D$80,DADOS!$T$3:$U$16,2,FALSE),N($O$80))</f>
         <v/>
       </c>
       <c r="X80" s="5" t="n"/>
@@ -3083,8 +3119,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO80" s="36">
-        <f>IFERROR(VLOOKUP($Z$80,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK80" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO80" s="39">
+        <f>IFERROR(VLOOKUP($Z$80,DADOS!$W$3:$X$10,2,FALSE),N($AK$80))</f>
         <v/>
       </c>
       <c r="AT80" s="5" t="n"/>
@@ -3098,8 +3139,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S81" s="37">
-        <f>IFERROR(VLOOKUP($D$81,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O81" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S81" s="41">
+        <f>IFERROR(VLOOKUP($D$81,DADOS!$T$3:$U$16,2,FALSE),N($O$81))</f>
         <v/>
       </c>
       <c r="X81" s="5" t="n"/>
@@ -3109,8 +3155,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO81" s="37">
-        <f>IFERROR(VLOOKUP($Z$81,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK81" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO81" s="41">
+        <f>IFERROR(VLOOKUP($Z$81,DADOS!$W$3:$X$10,2,FALSE),N($AK$81))</f>
         <v/>
       </c>
       <c r="AT81" s="5" t="n"/>
@@ -3124,8 +3175,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S82" s="36">
-        <f>IFERROR(VLOOKUP($D$82,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S82" s="39">
+        <f>IFERROR(VLOOKUP($D$82,DADOS!$T$3:$U$16,2,FALSE),N($O$82))</f>
         <v/>
       </c>
       <c r="X82" s="5" t="n"/>
@@ -3135,8 +3191,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO82" s="36">
-        <f>IFERROR(VLOOKUP($Z$82,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK82" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO82" s="39">
+        <f>IFERROR(VLOOKUP($Z$82,DADOS!$W$3:$X$10,2,FALSE),N($AK$82))</f>
         <v/>
       </c>
       <c r="AT82" s="5" t="n"/>
@@ -3150,8 +3211,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S83" s="37">
-        <f>IFERROR(VLOOKUP($D$83,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O83" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S83" s="41">
+        <f>IFERROR(VLOOKUP($D$83,DADOS!$T$3:$U$16,2,FALSE),N($O$83))</f>
         <v/>
       </c>
       <c r="X83" s="5" t="n"/>
@@ -3161,8 +3227,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO83" s="37">
-        <f>IFERROR(VLOOKUP($Z$83,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK83" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO83" s="41">
+        <f>IFERROR(VLOOKUP($Z$83,DADOS!$W$3:$X$10,2,FALSE),N($AK$83))</f>
         <v/>
       </c>
       <c r="AT83" s="5" t="n"/>
@@ -3176,8 +3247,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S84" s="36">
-        <f>IFERROR(VLOOKUP($D$84,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S84" s="39">
+        <f>IFERROR(VLOOKUP($D$84,DADOS!$T$3:$U$16,2,FALSE),N($O$84))</f>
         <v/>
       </c>
       <c r="X84" s="5" t="n"/>
@@ -3187,8 +3263,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO84" s="36">
-        <f>IFERROR(VLOOKUP($Z$84,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK84" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO84" s="39">
+        <f>IFERROR(VLOOKUP($Z$84,DADOS!$W$3:$X$10,2,FALSE),N($AK$84))</f>
         <v/>
       </c>
       <c r="AT84" s="5" t="n"/>
@@ -3202,8 +3283,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S85" s="37">
-        <f>IFERROR(VLOOKUP($D$85,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O85" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S85" s="41">
+        <f>IFERROR(VLOOKUP($D$85,DADOS!$T$3:$U$16,2,FALSE),N($O$85))</f>
         <v/>
       </c>
       <c r="X85" s="5" t="n"/>
@@ -3213,8 +3299,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AO85" s="37">
-        <f>IFERROR(VLOOKUP($Z$85,DADOS!$W$3:$X$10,2,FALSE),0)</f>
+      <c r="AK85" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AO85" s="41">
+        <f>IFERROR(VLOOKUP($Z$85,DADOS!$W$3:$X$10,2,FALSE),N($AK$85))</f>
         <v/>
       </c>
       <c r="AT85" s="5" t="n"/>
@@ -3228,8 +3319,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S86" s="36">
-        <f>IFERROR(VLOOKUP($D$86,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O86" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S86" s="39">
+        <f>IFERROR(VLOOKUP($D$86,DADOS!$T$3:$U$16,2,FALSE),N($O$86))</f>
         <v/>
       </c>
       <c r="X86" s="5" t="n"/>
@@ -3265,8 +3361,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S87" s="37">
-        <f>IFERROR(VLOOKUP($D$87,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O87" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S87" s="41">
+        <f>IFERROR(VLOOKUP($D$87,DADOS!$T$3:$U$16,2,FALSE),N($O$87))</f>
         <v/>
       </c>
       <c r="X87" s="5" t="n"/>
@@ -3302,8 +3403,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="S88" s="36">
-        <f>IFERROR(VLOOKUP($D$88,DADOS!$T$3:$U$16,2,FALSE),0)</f>
+      <c r="O88" s="38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S88" s="39">
+        <f>IFERROR(VLOOKUP($D$88,DADOS!$T$3:$U$16,2,FALSE),N($O$88))</f>
         <v/>
       </c>
       <c r="X88" s="5" t="n"/>
@@ -3334,100 +3440,31 @@
       <c r="A89" s="1" t="n"/>
       <c r="B89" s="1" t="n"/>
       <c r="C89" s="5" t="n"/>
-      <c r="D89" s="5" t="n"/>
-      <c r="E89" s="5" t="n"/>
-      <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="n"/>
-      <c r="H89" s="5" t="n"/>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="5" t="n"/>
-      <c r="K89" s="5" t="n"/>
-      <c r="L89" s="5" t="n"/>
-      <c r="M89" s="5" t="n"/>
-      <c r="N89" s="5" t="n"/>
-      <c r="O89" s="5" t="n"/>
-      <c r="P89" s="5" t="n"/>
-      <c r="Q89" s="5" t="n"/>
-      <c r="R89" s="5" t="n"/>
-      <c r="S89" s="5" t="n"/>
-      <c r="T89" s="5" t="n"/>
-      <c r="U89" s="5" t="n"/>
-      <c r="V89" s="5" t="n"/>
-      <c r="W89" s="5" t="n"/>
-      <c r="X89" s="5" t="n"/>
-      <c r="Y89" s="5" t="n"/>
-      <c r="Z89" s="5" t="n"/>
-      <c r="AA89" s="5" t="n"/>
-      <c r="AB89" s="5" t="n"/>
-      <c r="AC89" s="5" t="n"/>
-      <c r="AD89" s="5" t="n"/>
-      <c r="AE89" s="5" t="n"/>
-      <c r="AF89" s="5" t="n"/>
-      <c r="AG89" s="5" t="n"/>
-      <c r="AH89" s="5" t="n"/>
-      <c r="AI89" s="5" t="n"/>
-      <c r="AJ89" s="5" t="n"/>
-      <c r="AK89" s="5" t="n"/>
-      <c r="AL89" s="5" t="n"/>
-      <c r="AM89" s="5" t="n"/>
-      <c r="AN89" s="5" t="n"/>
-      <c r="AO89" s="5" t="n"/>
-      <c r="AP89" s="5" t="n"/>
-      <c r="AQ89" s="5" t="n"/>
-      <c r="AR89" s="5" t="n"/>
-      <c r="AS89" s="5" t="n"/>
-      <c r="AT89" s="5" t="n"/>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Para escrever um Traço ou Comando seu: digite o nome por cima do menu e escolha o DEGRAU em que o efeito cai. As duas réguas estão no CATÁLOGO, e a palavra final é do mestre.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="1" t="n"/>
       <c r="B90" s="1" t="n"/>
       <c r="C90" s="5" t="n"/>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>GASTO</t>
-        </is>
-      </c>
-      <c r="N90" s="5" t="n"/>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>SOBRA</t>
-        </is>
-      </c>
-      <c r="Y90" s="5" t="n"/>
-      <c r="Z90" s="5" t="n"/>
-      <c r="AA90" s="5" t="n"/>
-      <c r="AB90" s="5" t="n"/>
-      <c r="AC90" s="5" t="n"/>
-      <c r="AD90" s="5" t="n"/>
-      <c r="AE90" s="5" t="n"/>
-      <c r="AF90" s="5" t="n"/>
-      <c r="AG90" s="5" t="n"/>
-      <c r="AH90" s="5" t="n"/>
-      <c r="AI90" s="5" t="n"/>
-      <c r="AJ90" s="5" t="n"/>
-      <c r="AK90" s="5" t="n"/>
-      <c r="AL90" s="5" t="n"/>
-      <c r="AM90" s="5" t="n"/>
-      <c r="AN90" s="5" t="n"/>
-      <c r="AO90" s="5" t="n"/>
-      <c r="AP90" s="5" t="n"/>
-      <c r="AQ90" s="5" t="n"/>
-      <c r="AR90" s="5" t="n"/>
-      <c r="AS90" s="5" t="n"/>
-      <c r="AT90" s="5" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="1" t="n"/>
       <c r="B91" s="1" t="n"/>
       <c r="C91" s="5" t="n"/>
-      <c r="D91" s="10">
-        <f>$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85</f>
-        <v/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>GASTO</t>
+        </is>
       </c>
       <c r="N91" s="5" t="n"/>
-      <c r="O91" s="38">
-        <f>IF($D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)&lt;0,"estourou "&amp;(($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)-$D$76),$D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85))</f>
-        <v/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>SOBRA</t>
+        </is>
       </c>
       <c r="Y91" s="5" t="n"/>
       <c r="Z91" s="5" t="n"/>
@@ -3456,27 +3493,15 @@
       <c r="A92" s="1" t="n"/>
       <c r="B92" s="1" t="n"/>
       <c r="C92" s="5" t="n"/>
-      <c r="D92" s="5" t="n"/>
-      <c r="E92" s="5" t="n"/>
-      <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
-      <c r="H92" s="5" t="n"/>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="5" t="n"/>
-      <c r="K92" s="5" t="n"/>
-      <c r="L92" s="5" t="n"/>
-      <c r="M92" s="5" t="n"/>
+      <c r="D92" s="10">
+        <f>$S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85</f>
+        <v/>
+      </c>
       <c r="N92" s="5" t="n"/>
-      <c r="O92" s="5" t="n"/>
-      <c r="P92" s="5" t="n"/>
-      <c r="Q92" s="5" t="n"/>
-      <c r="R92" s="5" t="n"/>
-      <c r="S92" s="5" t="n"/>
-      <c r="T92" s="5" t="n"/>
-      <c r="U92" s="5" t="n"/>
-      <c r="V92" s="5" t="n"/>
-      <c r="W92" s="5" t="n"/>
-      <c r="X92" s="5" t="n"/>
+      <c r="O92" s="42">
+        <f>IF($D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)&lt;0,"estourou "&amp;(($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85)-$D$76),$D$76-($S$80+$S$81+$S$82+$S$83+$S$84+$S$85+$S$86+$S$87+$S$88+$AO$80+$AO$81+$AO$82+$AO$83+$AO$84+$AO$85))</f>
+        <v/>
+      </c>
       <c r="Y92" s="5" t="n"/>
       <c r="Z92" s="5" t="n"/>
       <c r="AA92" s="5" t="n"/>
@@ -3504,79 +3529,94 @@
       <c r="A93" s="1" t="n"/>
       <c r="B93" s="1" t="n"/>
       <c r="C93" s="5" t="n"/>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>Escolha Traço e Comando até o orçamento acabar. O Servo tem metade a mais que as outras duas Trilhas. Nada aqui compra dano, Defesa, acerto ou vida — esses saem dos atributos dela.</t>
-        </is>
-      </c>
+      <c r="D93" s="5" t="n"/>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="5" t="n"/>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
+      <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="5" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="5" t="n"/>
+      <c r="U93" s="5" t="n"/>
+      <c r="V93" s="5" t="n"/>
+      <c r="W93" s="5" t="n"/>
+      <c r="X93" s="5" t="n"/>
+      <c r="Y93" s="5" t="n"/>
+      <c r="Z93" s="5" t="n"/>
+      <c r="AA93" s="5" t="n"/>
+      <c r="AB93" s="5" t="n"/>
+      <c r="AC93" s="5" t="n"/>
+      <c r="AD93" s="5" t="n"/>
+      <c r="AE93" s="5" t="n"/>
+      <c r="AF93" s="5" t="n"/>
+      <c r="AG93" s="5" t="n"/>
+      <c r="AH93" s="5" t="n"/>
+      <c r="AI93" s="5" t="n"/>
+      <c r="AJ93" s="5" t="n"/>
+      <c r="AK93" s="5" t="n"/>
+      <c r="AL93" s="5" t="n"/>
+      <c r="AM93" s="5" t="n"/>
+      <c r="AN93" s="5" t="n"/>
+      <c r="AO93" s="5" t="n"/>
+      <c r="AP93" s="5" t="n"/>
+      <c r="AQ93" s="5" t="n"/>
+      <c r="AR93" s="5" t="n"/>
+      <c r="AS93" s="5" t="n"/>
+      <c r="AT93" s="5" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="1" t="n"/>
       <c r="B94" s="1" t="n"/>
       <c r="C94" s="5" t="n"/>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Escolha Traço e Comando até o orçamento acabar. O Servo tem metade a mais que as outras duas Trilhas. Nada aqui compra dano, Defesa, acerto ou vida — esses saem dos atributos dela.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="1" t="n"/>
       <c r="B95" s="1" t="n"/>
       <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
-      <c r="E95" s="5" t="n"/>
-      <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
-      <c r="H95" s="5" t="n"/>
-      <c r="I95" s="5" t="n"/>
-      <c r="J95" s="5" t="n"/>
-      <c r="K95" s="5" t="n"/>
-      <c r="L95" s="5" t="n"/>
-      <c r="M95" s="5" t="n"/>
-      <c r="N95" s="5" t="n"/>
-      <c r="O95" s="5" t="n"/>
-      <c r="P95" s="5" t="n"/>
-      <c r="Q95" s="5" t="n"/>
-      <c r="R95" s="5" t="n"/>
-      <c r="S95" s="5" t="n"/>
-      <c r="T95" s="5" t="n"/>
-      <c r="U95" s="5" t="n"/>
-      <c r="V95" s="5" t="n"/>
-      <c r="W95" s="5" t="n"/>
-      <c r="X95" s="5" t="n"/>
-      <c r="Y95" s="5" t="n"/>
-      <c r="Z95" s="5" t="n"/>
-      <c r="AA95" s="5" t="n"/>
-      <c r="AB95" s="5" t="n"/>
-      <c r="AC95" s="5" t="n"/>
-      <c r="AD95" s="5" t="n"/>
-      <c r="AE95" s="5" t="n"/>
-      <c r="AF95" s="5" t="n"/>
-      <c r="AG95" s="5" t="n"/>
-      <c r="AH95" s="5" t="n"/>
-      <c r="AI95" s="5" t="n"/>
-      <c r="AJ95" s="5" t="n"/>
-      <c r="AK95" s="5" t="n"/>
-      <c r="AL95" s="5" t="n"/>
-      <c r="AM95" s="5" t="n"/>
-      <c r="AN95" s="5" t="n"/>
-      <c r="AO95" s="5" t="n"/>
-      <c r="AP95" s="5" t="n"/>
-      <c r="AQ95" s="5" t="n"/>
-      <c r="AR95" s="5" t="n"/>
-      <c r="AS95" s="5" t="n"/>
-      <c r="AT95" s="5" t="n"/>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" s="1" t="n"/>
       <c r="B96" s="1" t="n"/>
       <c r="C96" s="5" t="n"/>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>INVESTIR</t>
-        </is>
-      </c>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="n"/>
+      <c r="I96" s="5" t="n"/>
+      <c r="J96" s="5" t="n"/>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
+      <c r="Q96" s="5" t="n"/>
+      <c r="R96" s="5" t="n"/>
+      <c r="S96" s="5" t="n"/>
+      <c r="T96" s="5" t="n"/>
+      <c r="U96" s="5" t="n"/>
+      <c r="V96" s="5" t="n"/>
+      <c r="W96" s="5" t="n"/>
+      <c r="X96" s="5" t="n"/>
+      <c r="Y96" s="5" t="n"/>
+      <c r="Z96" s="5" t="n"/>
+      <c r="AA96" s="5" t="n"/>
+      <c r="AB96" s="5" t="n"/>
       <c r="AC96" s="5" t="n"/>
       <c r="AD96" s="5" t="n"/>
       <c r="AE96" s="5" t="n"/>
@@ -3600,28 +3640,16 @@
       <c r="A97" s="1" t="n"/>
       <c r="B97" s="1" t="n"/>
       <c r="C97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
-      <c r="H97" s="5" t="n"/>
-      <c r="I97" s="5" t="n"/>
-      <c r="J97" s="5" t="n"/>
-      <c r="K97" s="5" t="n"/>
-      <c r="L97" s="5" t="n"/>
-      <c r="M97" s="5" t="n"/>
-      <c r="N97" s="5" t="n"/>
-      <c r="O97" s="5" t="n"/>
-      <c r="P97" s="5" t="n"/>
-      <c r="Q97" s="5" t="n"/>
-      <c r="R97" s="5" t="n"/>
-      <c r="S97" s="5" t="n"/>
-      <c r="T97" s="5" t="n"/>
-      <c r="U97" s="5" t="n"/>
-      <c r="V97" s="5" t="n"/>
-      <c r="W97" s="5" t="n"/>
-      <c r="X97" s="5" t="n"/>
-      <c r="Y97" s="5" t="n"/>
-      <c r="Z97" s="5" t="n"/>
-      <c r="AA97" s="5" t="n"/>
-      <c r="AB97" s="5" t="n"/>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>INVESTIR</t>
+        </is>
+      </c>
       <c r="AC97" s="5" t="n"/>
       <c r="AD97" s="5" t="n"/>
       <c r="AE97" s="5" t="n"/>
@@ -3645,163 +3673,171 @@
       <c r="A98" s="1" t="n"/>
       <c r="B98" s="1" t="n"/>
       <c r="C98" s="5" t="n"/>
-      <c r="D98" s="8" t="inlineStr">
-        <is>
-          <t>DANO DO INVESTIR</t>
-        </is>
-      </c>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="n"/>
+      <c r="I98" s="5" t="n"/>
+      <c r="J98" s="5" t="n"/>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
       <c r="N98" s="5" t="n"/>
-      <c r="O98" s="8" t="inlineStr">
-        <is>
-          <t>POR CORPO</t>
-        </is>
-      </c>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
+      <c r="Q98" s="5" t="n"/>
+      <c r="R98" s="5" t="n"/>
+      <c r="S98" s="5" t="n"/>
+      <c r="T98" s="5" t="n"/>
+      <c r="U98" s="5" t="n"/>
+      <c r="V98" s="5" t="n"/>
+      <c r="W98" s="5" t="n"/>
+      <c r="X98" s="5" t="n"/>
+      <c r="Y98" s="5" t="n"/>
+      <c r="Z98" s="5" t="n"/>
+      <c r="AA98" s="5" t="n"/>
+      <c r="AB98" s="5" t="n"/>
+      <c r="AC98" s="5" t="n"/>
+      <c r="AD98" s="5" t="n"/>
+      <c r="AE98" s="5" t="n"/>
+      <c r="AF98" s="5" t="n"/>
+      <c r="AG98" s="5" t="n"/>
+      <c r="AH98" s="5" t="n"/>
+      <c r="AI98" s="5" t="n"/>
+      <c r="AJ98" s="5" t="n"/>
+      <c r="AK98" s="5" t="n"/>
+      <c r="AL98" s="5" t="n"/>
+      <c r="AM98" s="5" t="n"/>
+      <c r="AN98" s="5" t="n"/>
+      <c r="AO98" s="5" t="n"/>
+      <c r="AP98" s="5" t="n"/>
+      <c r="AQ98" s="5" t="n"/>
+      <c r="AR98" s="5" t="n"/>
+      <c r="AS98" s="5" t="n"/>
+      <c r="AT98" s="5" t="n"/>
     </row>
     <row r="99" ht="15" customHeight="1">
       <c r="A99" s="1" t="n"/>
       <c r="B99" s="1" t="n"/>
       <c r="C99" s="5" t="n"/>
-      <c r="D99" s="9">
-        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AK$19="Matilha",3,2),TRUE))</f>
-        <v/>
+      <c r="D99" s="8" t="inlineStr">
+        <is>
+          <t>DANO DO INVESTIR</t>
+        </is>
       </c>
       <c r="N99" s="5" t="n"/>
-      <c r="O99" s="21">
-        <f>IF($AK$19="Matilha","cada um dos cinco rola isto",IF($AK$19="","","o corpo em campo rola isto"))</f>
-        <v/>
+      <c r="O99" s="8" t="inlineStr">
+        <is>
+          <t>POR CORPO</t>
+        </is>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
       <c r="A100" s="1" t="n"/>
       <c r="B100" s="1" t="n"/>
       <c r="C100" s="5" t="n"/>
+      <c r="D100" s="9">
+        <f>IF($D$7="","",VLOOKUP($D$7,DADOS!$Z$3:$AB$9,IF($AK$19="Matilha",3,2),TRUE))</f>
+        <v/>
+      </c>
       <c r="N100" s="5" t="n"/>
+      <c r="O100" s="21">
+        <f>IF($AK$19="Matilha","cada um dos cinco rola isto",IF($AK$19="","","o corpo em campo rola isto"))</f>
+        <v/>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" s="1" t="n"/>
       <c r="B101" s="1" t="n"/>
       <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
-      <c r="E101" s="5" t="n"/>
-      <c r="F101" s="5" t="n"/>
-      <c r="G101" s="5" t="n"/>
-      <c r="H101" s="5" t="n"/>
-      <c r="I101" s="5" t="n"/>
-      <c r="J101" s="5" t="n"/>
-      <c r="K101" s="5" t="n"/>
-      <c r="L101" s="5" t="n"/>
-      <c r="M101" s="5" t="n"/>
       <c r="N101" s="5" t="n"/>
-      <c r="O101" s="5" t="n"/>
-      <c r="P101" s="5" t="n"/>
-      <c r="Q101" s="5" t="n"/>
-      <c r="R101" s="5" t="n"/>
-      <c r="S101" s="5" t="n"/>
-      <c r="T101" s="5" t="n"/>
-      <c r="U101" s="5" t="n"/>
-      <c r="V101" s="5" t="n"/>
-      <c r="W101" s="5" t="n"/>
-      <c r="X101" s="5" t="n"/>
-      <c r="Y101" s="5" t="n"/>
-      <c r="Z101" s="5" t="n"/>
-      <c r="AA101" s="5" t="n"/>
-      <c r="AB101" s="5" t="n"/>
-      <c r="AC101" s="5" t="n"/>
-      <c r="AD101" s="5" t="n"/>
-      <c r="AE101" s="5" t="n"/>
-      <c r="AF101" s="5" t="n"/>
-      <c r="AG101" s="5" t="n"/>
-      <c r="AH101" s="5" t="n"/>
-      <c r="AI101" s="5" t="n"/>
-      <c r="AJ101" s="5" t="n"/>
-      <c r="AK101" s="5" t="n"/>
-      <c r="AL101" s="5" t="n"/>
-      <c r="AM101" s="5" t="n"/>
-      <c r="AN101" s="5" t="n"/>
-      <c r="AO101" s="5" t="n"/>
-      <c r="AP101" s="5" t="n"/>
-      <c r="AQ101" s="5" t="n"/>
-      <c r="AR101" s="5" t="n"/>
-      <c r="AS101" s="5" t="n"/>
-      <c r="AT101" s="5" t="n"/>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" s="1" t="n"/>
       <c r="B102" s="1" t="n"/>
       <c r="C102" s="5" t="n"/>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>É o dano dela quando você gasta a Ação Padrão comandando. Você e as suas invocações somados causam o dano de uma rodada sua sozinho.</t>
-        </is>
-      </c>
+      <c r="D102" s="5" t="n"/>
+      <c r="E102" s="5" t="n"/>
+      <c r="F102" s="5" t="n"/>
+      <c r="G102" s="5" t="n"/>
+      <c r="H102" s="5" t="n"/>
+      <c r="I102" s="5" t="n"/>
+      <c r="J102" s="5" t="n"/>
+      <c r="K102" s="5" t="n"/>
+      <c r="L102" s="5" t="n"/>
+      <c r="M102" s="5" t="n"/>
+      <c r="N102" s="5" t="n"/>
+      <c r="O102" s="5" t="n"/>
+      <c r="P102" s="5" t="n"/>
+      <c r="Q102" s="5" t="n"/>
+      <c r="R102" s="5" t="n"/>
+      <c r="S102" s="5" t="n"/>
+      <c r="T102" s="5" t="n"/>
+      <c r="U102" s="5" t="n"/>
+      <c r="V102" s="5" t="n"/>
+      <c r="W102" s="5" t="n"/>
+      <c r="X102" s="5" t="n"/>
+      <c r="Y102" s="5" t="n"/>
+      <c r="Z102" s="5" t="n"/>
+      <c r="AA102" s="5" t="n"/>
+      <c r="AB102" s="5" t="n"/>
+      <c r="AC102" s="5" t="n"/>
+      <c r="AD102" s="5" t="n"/>
+      <c r="AE102" s="5" t="n"/>
+      <c r="AF102" s="5" t="n"/>
+      <c r="AG102" s="5" t="n"/>
+      <c r="AH102" s="5" t="n"/>
+      <c r="AI102" s="5" t="n"/>
+      <c r="AJ102" s="5" t="n"/>
+      <c r="AK102" s="5" t="n"/>
+      <c r="AL102" s="5" t="n"/>
+      <c r="AM102" s="5" t="n"/>
+      <c r="AN102" s="5" t="n"/>
+      <c r="AO102" s="5" t="n"/>
+      <c r="AP102" s="5" t="n"/>
+      <c r="AQ102" s="5" t="n"/>
+      <c r="AR102" s="5" t="n"/>
+      <c r="AS102" s="5" t="n"/>
+      <c r="AT102" s="5" t="n"/>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" s="1" t="n"/>
       <c r="B103" s="1" t="n"/>
       <c r="C103" s="5" t="n"/>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>É o dano dela quando você gasta a Ação Padrão comandando. Você e as suas invocações somados causam o dano de uma rodada sua sozinho.</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="15" customHeight="1">
       <c r="A104" s="1" t="n"/>
       <c r="B104" s="1" t="n"/>
       <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
-      <c r="E104" s="5" t="n"/>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="n"/>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
-      <c r="L104" s="5" t="n"/>
-      <c r="M104" s="5" t="n"/>
-      <c r="N104" s="5" t="n"/>
-      <c r="O104" s="5" t="n"/>
-      <c r="P104" s="5" t="n"/>
-      <c r="Q104" s="5" t="n"/>
-      <c r="R104" s="5" t="n"/>
-      <c r="S104" s="5" t="n"/>
-      <c r="T104" s="5" t="n"/>
-      <c r="U104" s="5" t="n"/>
-      <c r="V104" s="5" t="n"/>
-      <c r="W104" s="5" t="n"/>
-      <c r="X104" s="5" t="n"/>
-      <c r="Y104" s="5" t="n"/>
-      <c r="Z104" s="5" t="n"/>
-      <c r="AA104" s="5" t="n"/>
-      <c r="AB104" s="5" t="n"/>
-      <c r="AC104" s="5" t="n"/>
-      <c r="AD104" s="5" t="n"/>
-      <c r="AE104" s="5" t="n"/>
-      <c r="AF104" s="5" t="n"/>
-      <c r="AG104" s="5" t="n"/>
-      <c r="AH104" s="5" t="n"/>
-      <c r="AI104" s="5" t="n"/>
-      <c r="AJ104" s="5" t="n"/>
-      <c r="AK104" s="5" t="n"/>
-      <c r="AL104" s="5" t="n"/>
-      <c r="AM104" s="5" t="n"/>
-      <c r="AN104" s="5" t="n"/>
-      <c r="AO104" s="5" t="n"/>
-      <c r="AP104" s="5" t="n"/>
-      <c r="AQ104" s="5" t="n"/>
-      <c r="AR104" s="5" t="n"/>
-      <c r="AS104" s="5" t="n"/>
-      <c r="AT104" s="5" t="n"/>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c r="A105" s="1" t="n"/>
       <c r="B105" s="1" t="n"/>
       <c r="C105" s="5" t="n"/>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>NA MESA</t>
-        </is>
-      </c>
+      <c r="D105" s="5" t="n"/>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
+      <c r="Q105" s="5" t="n"/>
+      <c r="R105" s="5" t="n"/>
+      <c r="S105" s="5" t="n"/>
+      <c r="T105" s="5" t="n"/>
+      <c r="U105" s="5" t="n"/>
+      <c r="V105" s="5" t="n"/>
+      <c r="W105" s="5" t="n"/>
+      <c r="X105" s="5" t="n"/>
       <c r="Y105" s="5" t="n"/>
       <c r="Z105" s="5" t="n"/>
       <c r="AA105" s="5" t="n"/>
@@ -3829,24 +3865,16 @@
       <c r="A106" s="1" t="n"/>
       <c r="B106" s="1" t="n"/>
       <c r="C106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="5" t="n"/>
-      <c r="K106" s="5" t="n"/>
-      <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n"/>
-      <c r="N106" s="5" t="n"/>
-      <c r="O106" s="5" t="n"/>
-      <c r="P106" s="5" t="n"/>
-      <c r="Q106" s="5" t="n"/>
-      <c r="R106" s="5" t="n"/>
-      <c r="S106" s="5" t="n"/>
-      <c r="T106" s="5" t="n"/>
-      <c r="U106" s="5" t="n"/>
-      <c r="V106" s="5" t="n"/>
-      <c r="W106" s="5" t="n"/>
-      <c r="X106" s="5" t="n"/>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>NA MESA</t>
+        </is>
+      </c>
       <c r="Y106" s="5" t="n"/>
       <c r="Z106" s="5" t="n"/>
       <c r="AA106" s="5" t="n"/>
@@ -3874,27 +3902,58 @@
       <c r="A107" s="1" t="n"/>
       <c r="B107" s="1" t="n"/>
       <c r="C107" s="5" t="n"/>
-      <c r="D107" s="39" t="inlineStr">
-        <is>
-          <t>INVOCAR</t>
-        </is>
-      </c>
-      <c r="O107" s="40">
-        <f>("custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
-        <v/>
-      </c>
+      <c r="G107" s="5" t="n"/>
+      <c r="H107" s="5" t="n"/>
+      <c r="I107" s="5" t="n"/>
+      <c r="J107" s="5" t="n"/>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
+      <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="5" t="n"/>
+      <c r="S107" s="5" t="n"/>
+      <c r="T107" s="5" t="n"/>
+      <c r="U107" s="5" t="n"/>
+      <c r="V107" s="5" t="n"/>
+      <c r="W107" s="5" t="n"/>
+      <c r="X107" s="5" t="n"/>
+      <c r="Y107" s="5" t="n"/>
+      <c r="Z107" s="5" t="n"/>
+      <c r="AA107" s="5" t="n"/>
+      <c r="AB107" s="5" t="n"/>
+      <c r="AC107" s="5" t="n"/>
+      <c r="AD107" s="5" t="n"/>
+      <c r="AE107" s="5" t="n"/>
+      <c r="AF107" s="5" t="n"/>
+      <c r="AG107" s="5" t="n"/>
+      <c r="AH107" s="5" t="n"/>
+      <c r="AI107" s="5" t="n"/>
+      <c r="AJ107" s="5" t="n"/>
+      <c r="AK107" s="5" t="n"/>
+      <c r="AL107" s="5" t="n"/>
+      <c r="AM107" s="5" t="n"/>
+      <c r="AN107" s="5" t="n"/>
+      <c r="AO107" s="5" t="n"/>
+      <c r="AP107" s="5" t="n"/>
+      <c r="AQ107" s="5" t="n"/>
+      <c r="AR107" s="5" t="n"/>
+      <c r="AS107" s="5" t="n"/>
+      <c r="AT107" s="5" t="n"/>
     </row>
     <row r="108" ht="15" customHeight="1">
       <c r="A108" s="1" t="n"/>
       <c r="B108" s="1" t="n"/>
       <c r="C108" s="5" t="n"/>
-      <c r="D108" s="41" t="inlineStr">
-        <is>
-          <t>COMANDAR</t>
-        </is>
-      </c>
-      <c r="O108" s="42">
-        <f>"a Ação Padrão, toda rodada"</f>
+      <c r="D108" s="43" t="inlineStr">
+        <is>
+          <t>INVOCAR</t>
+        </is>
+      </c>
+      <c r="O108" s="44">
+        <f>("custa "&amp;$O$11&amp;" PE e a Ação Padrão")</f>
         <v/>
       </c>
     </row>
@@ -3902,13 +3961,13 @@
       <c r="A109" s="1" t="n"/>
       <c r="B109" s="1" t="n"/>
       <c r="C109" s="5" t="n"/>
-      <c r="D109" s="39" t="inlineStr">
-        <is>
-          <t>INICIATIVA</t>
-        </is>
-      </c>
-      <c r="O109" s="40">
-        <f>"a sua, e ela age logo depois de você"</f>
+      <c r="D109" s="36" t="inlineStr">
+        <is>
+          <t>COMANDAR</t>
+        </is>
+      </c>
+      <c r="O109" s="45">
+        <f>"a Ação Padrão, toda rodada"</f>
         <v/>
       </c>
     </row>
@@ -3916,13 +3975,13 @@
       <c r="A110" s="1" t="n"/>
       <c r="B110" s="1" t="n"/>
       <c r="C110" s="5" t="n"/>
-      <c r="D110" s="41" t="inlineStr">
-        <is>
-          <t>DESLOCAMENTO</t>
-        </is>
-      </c>
-      <c r="O110" s="42">
-        <f>(9&amp;" metros")</f>
+      <c r="D110" s="43" t="inlineStr">
+        <is>
+          <t>INICIATIVA</t>
+        </is>
+      </c>
+      <c r="O110" s="44">
+        <f>"a sua, e ela age logo depois de você"</f>
         <v/>
       </c>
     </row>
@@ -3930,13 +3989,13 @@
       <c r="A111" s="1" t="n"/>
       <c r="B111" s="1" t="n"/>
       <c r="C111" s="5" t="n"/>
-      <c r="D111" s="39" t="inlineStr">
-        <is>
-          <t>AMARRA</t>
-        </is>
-      </c>
-      <c r="O111" s="40">
-        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
+      <c r="D111" s="36" t="inlineStr">
+        <is>
+          <t>DESLOCAMENTO</t>
+        </is>
+      </c>
+      <c r="O111" s="45">
+        <f>(9&amp;" metros")</f>
         <v/>
       </c>
     </row>
@@ -3944,64 +4003,49 @@
       <c r="A112" s="1" t="n"/>
       <c r="B112" s="1" t="n"/>
       <c r="C112" s="5" t="n"/>
-      <c r="D112" s="5" t="n"/>
-      <c r="E112" s="5" t="n"/>
-      <c r="F112" s="5" t="n"/>
-      <c r="G112" s="5" t="n"/>
-      <c r="H112" s="5" t="n"/>
-      <c r="I112" s="5" t="n"/>
-      <c r="J112" s="5" t="n"/>
-      <c r="K112" s="5" t="n"/>
-      <c r="L112" s="5" t="n"/>
-      <c r="M112" s="5" t="n"/>
-      <c r="N112" s="5" t="n"/>
-      <c r="O112" s="5" t="n"/>
-      <c r="P112" s="5" t="n"/>
-      <c r="Q112" s="5" t="n"/>
-      <c r="R112" s="5" t="n"/>
-      <c r="S112" s="5" t="n"/>
-      <c r="T112" s="5" t="n"/>
-      <c r="U112" s="5" t="n"/>
-      <c r="V112" s="5" t="n"/>
-      <c r="W112" s="5" t="n"/>
-      <c r="X112" s="5" t="n"/>
-      <c r="Y112" s="5" t="n"/>
-      <c r="Z112" s="5" t="n"/>
-      <c r="AA112" s="5" t="n"/>
-      <c r="AB112" s="5" t="n"/>
-      <c r="AC112" s="5" t="n"/>
-      <c r="AD112" s="5" t="n"/>
-      <c r="AE112" s="5" t="n"/>
-      <c r="AF112" s="5" t="n"/>
-      <c r="AG112" s="5" t="n"/>
-      <c r="AH112" s="5" t="n"/>
-      <c r="AI112" s="5" t="n"/>
-      <c r="AJ112" s="5" t="n"/>
-      <c r="AK112" s="5" t="n"/>
-      <c r="AL112" s="5" t="n"/>
-      <c r="AM112" s="5" t="n"/>
-      <c r="AN112" s="5" t="n"/>
-      <c r="AO112" s="5" t="n"/>
-      <c r="AP112" s="5" t="n"/>
-      <c r="AQ112" s="5" t="n"/>
-      <c r="AR112" s="5" t="n"/>
-      <c r="AS112" s="5" t="n"/>
-      <c r="AT112" s="5" t="n"/>
+      <c r="D112" s="43" t="inlineStr">
+        <is>
+          <t>AMARRA</t>
+        </is>
+      </c>
+      <c r="O112" s="44">
+        <f>(18&amp;" metros — além disso não pode ser comandada, e não some")</f>
+        <v/>
+      </c>
     </row>
     <row r="113" ht="15" customHeight="1">
       <c r="A113" s="1" t="n"/>
       <c r="B113" s="1" t="n"/>
       <c r="C113" s="5" t="n"/>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>O QUE A FICHA NÃO CALCULA</t>
-        </is>
-      </c>
+      <c r="D113" s="5" t="n"/>
+      <c r="E113" s="5" t="n"/>
+      <c r="F113" s="5" t="n"/>
+      <c r="G113" s="5" t="n"/>
+      <c r="H113" s="5" t="n"/>
+      <c r="I113" s="5" t="n"/>
+      <c r="J113" s="5" t="n"/>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
+      <c r="Q113" s="5" t="n"/>
+      <c r="R113" s="5" t="n"/>
+      <c r="S113" s="5" t="n"/>
+      <c r="T113" s="5" t="n"/>
+      <c r="U113" s="5" t="n"/>
+      <c r="V113" s="5" t="n"/>
+      <c r="W113" s="5" t="n"/>
+      <c r="X113" s="5" t="n"/>
+      <c r="Y113" s="5" t="n"/>
+      <c r="Z113" s="5" t="n"/>
+      <c r="AA113" s="5" t="n"/>
+      <c r="AB113" s="5" t="n"/>
+      <c r="AC113" s="5" t="n"/>
+      <c r="AD113" s="5" t="n"/>
+      <c r="AE113" s="5" t="n"/>
+      <c r="AF113" s="5" t="n"/>
       <c r="AG113" s="5" t="n"/>
       <c r="AH113" s="5" t="n"/>
       <c r="AI113" s="5" t="n"/>
@@ -4021,32 +4065,16 @@
       <c r="A114" s="1" t="n"/>
       <c r="B114" s="1" t="n"/>
       <c r="C114" s="5" t="n"/>
-      <c r="G114" s="5" t="n"/>
-      <c r="H114" s="5" t="n"/>
-      <c r="I114" s="5" t="n"/>
-      <c r="J114" s="5" t="n"/>
-      <c r="K114" s="5" t="n"/>
-      <c r="L114" s="5" t="n"/>
-      <c r="M114" s="5" t="n"/>
-      <c r="N114" s="5" t="n"/>
-      <c r="O114" s="5" t="n"/>
-      <c r="P114" s="5" t="n"/>
-      <c r="Q114" s="5" t="n"/>
-      <c r="R114" s="5" t="n"/>
-      <c r="S114" s="5" t="n"/>
-      <c r="T114" s="5" t="n"/>
-      <c r="U114" s="5" t="n"/>
-      <c r="V114" s="5" t="n"/>
-      <c r="W114" s="5" t="n"/>
-      <c r="X114" s="5" t="n"/>
-      <c r="Y114" s="5" t="n"/>
-      <c r="Z114" s="5" t="n"/>
-      <c r="AA114" s="5" t="n"/>
-      <c r="AB114" s="5" t="n"/>
-      <c r="AC114" s="5" t="n"/>
-      <c r="AD114" s="5" t="n"/>
-      <c r="AE114" s="5" t="n"/>
-      <c r="AF114" s="5" t="n"/>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>O QUE A FICHA NÃO CALCULA</t>
+        </is>
+      </c>
       <c r="AG114" s="5" t="n"/>
       <c r="AH114" s="5" t="n"/>
       <c r="AI114" s="5" t="n"/>
@@ -4066,83 +4094,80 @@
       <c r="A115" s="1" t="n"/>
       <c r="B115" s="1" t="n"/>
       <c r="C115" s="5" t="n"/>
-      <c r="D115" s="34" t="inlineStr">
-        <is>
-          <t>A CD DOS EFEITOS DELA</t>
-        </is>
-      </c>
+      <c r="G115" s="5" t="n"/>
+      <c r="H115" s="5" t="n"/>
+      <c r="I115" s="5" t="n"/>
+      <c r="J115" s="5" t="n"/>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="5" t="n"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
+      <c r="Q115" s="5" t="n"/>
+      <c r="R115" s="5" t="n"/>
+      <c r="S115" s="5" t="n"/>
+      <c r="T115" s="5" t="n"/>
+      <c r="U115" s="5" t="n"/>
+      <c r="V115" s="5" t="n"/>
+      <c r="W115" s="5" t="n"/>
+      <c r="X115" s="5" t="n"/>
+      <c r="Y115" s="5" t="n"/>
+      <c r="Z115" s="5" t="n"/>
+      <c r="AA115" s="5" t="n"/>
+      <c r="AB115" s="5" t="n"/>
+      <c r="AC115" s="5" t="n"/>
+      <c r="AD115" s="5" t="n"/>
+      <c r="AE115" s="5" t="n"/>
+      <c r="AF115" s="5" t="n"/>
+      <c r="AG115" s="5" t="n"/>
+      <c r="AH115" s="5" t="n"/>
+      <c r="AI115" s="5" t="n"/>
+      <c r="AJ115" s="5" t="n"/>
+      <c r="AK115" s="5" t="n"/>
+      <c r="AL115" s="5" t="n"/>
+      <c r="AM115" s="5" t="n"/>
+      <c r="AN115" s="5" t="n"/>
+      <c r="AO115" s="5" t="n"/>
+      <c r="AP115" s="5" t="n"/>
+      <c r="AQ115" s="5" t="n"/>
+      <c r="AR115" s="5" t="n"/>
+      <c r="AS115" s="5" t="n"/>
+      <c r="AT115" s="5" t="n"/>
     </row>
     <row r="116" ht="15" customHeight="1">
       <c r="A116" s="1" t="n"/>
       <c r="B116" s="1" t="n"/>
       <c r="C116" s="5" t="n"/>
-      <c r="D116" s="35">
-        <f>IF($D$22="Voz","A Voz sobe a CD dos efeitos dela, e o sistema ainda não diz qual é essa CD. Combine com o mestre.","")</f>
-        <v/>
+      <c r="D116" s="34" t="inlineStr">
+        <is>
+          <t>A CD DOS EFEITOS DELA</t>
+        </is>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1">
       <c r="A117" s="1" t="n"/>
       <c r="B117" s="1" t="n"/>
       <c r="C117" s="5" t="n"/>
-      <c r="D117" s="43" t="inlineStr">
-        <is>
-          <t>A CD dos efeitos dela não tem fórmula em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Enquanto não existir, combine o número com o mestre.</t>
-        </is>
+      <c r="D117" s="35">
+        <f>IF($D$22="Voz","A Voz sobe a CD dos efeitos dela, e o sistema ainda não diz qual é essa CD. Combine com o mestre.","")</f>
+        <v/>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1">
       <c r="A118" s="1" t="n"/>
       <c r="B118" s="1" t="n"/>
       <c r="C118" s="5" t="n"/>
+      <c r="D118" s="46" t="inlineStr">
+        <is>
+          <t>A CD dos efeitos dela não tem fórmula em documento nenhum — nem o capítulo 16, nem a peça 15 escrevem uma. Enquanto não existir, combine o número com o mestre.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="1" t="n"/>
       <c r="B119" s="1" t="n"/>
       <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="5" t="n"/>
-      <c r="F119" s="5" t="n"/>
-      <c r="G119" s="5" t="n"/>
-      <c r="H119" s="5" t="n"/>
-      <c r="I119" s="5" t="n"/>
-      <c r="J119" s="5" t="n"/>
-      <c r="K119" s="5" t="n"/>
-      <c r="L119" s="5" t="n"/>
-      <c r="M119" s="5" t="n"/>
-      <c r="N119" s="5" t="n"/>
-      <c r="O119" s="5" t="n"/>
-      <c r="P119" s="5" t="n"/>
-      <c r="Q119" s="5" t="n"/>
-      <c r="R119" s="5" t="n"/>
-      <c r="S119" s="5" t="n"/>
-      <c r="T119" s="5" t="n"/>
-      <c r="U119" s="5" t="n"/>
-      <c r="V119" s="5" t="n"/>
-      <c r="W119" s="5" t="n"/>
-      <c r="X119" s="5" t="n"/>
-      <c r="Y119" s="5" t="n"/>
-      <c r="Z119" s="5" t="n"/>
-      <c r="AA119" s="5" t="n"/>
-      <c r="AB119" s="5" t="n"/>
-      <c r="AC119" s="5" t="n"/>
-      <c r="AD119" s="5" t="n"/>
-      <c r="AE119" s="5" t="n"/>
-      <c r="AF119" s="5" t="n"/>
-      <c r="AG119" s="5" t="n"/>
-      <c r="AH119" s="5" t="n"/>
-      <c r="AI119" s="5" t="n"/>
-      <c r="AJ119" s="5" t="n"/>
-      <c r="AK119" s="5" t="n"/>
-      <c r="AL119" s="5" t="n"/>
-      <c r="AM119" s="5" t="n"/>
-      <c r="AN119" s="5" t="n"/>
-      <c r="AO119" s="5" t="n"/>
-      <c r="AP119" s="5" t="n"/>
-      <c r="AQ119" s="5" t="n"/>
-      <c r="AR119" s="5" t="n"/>
-      <c r="AS119" s="5" t="n"/>
-      <c r="AT119" s="5" t="n"/>
     </row>
     <row r="120" ht="15" customHeight="1">
       <c r="A120" s="1" t="n"/>
@@ -4193,107 +4218,118 @@
       <c r="AT120" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="178">
+  <mergeCells count="198">
+    <mergeCell ref="AK84:AN84"/>
     <mergeCell ref="D59:M60"/>
     <mergeCell ref="AB30:AH31"/>
     <mergeCell ref="T30:Z31"/>
-    <mergeCell ref="Z81:AN81"/>
+    <mergeCell ref="O79:R79"/>
+    <mergeCell ref="D92:M92"/>
     <mergeCell ref="D109:N109"/>
     <mergeCell ref="O111:AT111"/>
     <mergeCell ref="G4:AB4"/>
+    <mergeCell ref="D84:N84"/>
+    <mergeCell ref="Z85:AJ85"/>
     <mergeCell ref="O91:X91"/>
     <mergeCell ref="D51:J51"/>
     <mergeCell ref="AO80:AS80"/>
     <mergeCell ref="AJ32:AP32"/>
     <mergeCell ref="D111:N111"/>
     <mergeCell ref="D108:N108"/>
+    <mergeCell ref="D86:N86"/>
     <mergeCell ref="Z45:AI45"/>
     <mergeCell ref="D1:AD2"/>
     <mergeCell ref="Z6:AI6"/>
+    <mergeCell ref="O87:R87"/>
     <mergeCell ref="D7:M8"/>
     <mergeCell ref="O108:AT108"/>
     <mergeCell ref="O10:X10"/>
-    <mergeCell ref="G96:AB96"/>
     <mergeCell ref="AH50:AL50"/>
     <mergeCell ref="A8:B26"/>
     <mergeCell ref="Z49:AF49"/>
-    <mergeCell ref="D83:R83"/>
     <mergeCell ref="AK19:AT19"/>
     <mergeCell ref="S87:W87"/>
-    <mergeCell ref="D115:AT115"/>
+    <mergeCell ref="D112:N112"/>
+    <mergeCell ref="D87:N87"/>
     <mergeCell ref="AH49:AL49"/>
     <mergeCell ref="S80:W80"/>
-    <mergeCell ref="D85:R85"/>
     <mergeCell ref="D62:N62"/>
     <mergeCell ref="D68:AT69"/>
+    <mergeCell ref="AO79:AS79"/>
+    <mergeCell ref="O88:R88"/>
     <mergeCell ref="D16:F17"/>
+    <mergeCell ref="Z79:AJ79"/>
     <mergeCell ref="O62:AT62"/>
-    <mergeCell ref="Z79:AS79"/>
-    <mergeCell ref="D84:R84"/>
     <mergeCell ref="Z18:AI18"/>
     <mergeCell ref="Z58:AI58"/>
-    <mergeCell ref="Z85:AN85"/>
     <mergeCell ref="G73:AF73"/>
     <mergeCell ref="D91:M91"/>
-    <mergeCell ref="D93:AT94"/>
-    <mergeCell ref="D102:AT103"/>
     <mergeCell ref="O110:AT110"/>
     <mergeCell ref="D43:M43"/>
     <mergeCell ref="Z64:AI64"/>
+    <mergeCell ref="AK85:AN85"/>
     <mergeCell ref="Z42:AI42"/>
     <mergeCell ref="AK7:AT8"/>
     <mergeCell ref="O46:X46"/>
     <mergeCell ref="D73:F74"/>
     <mergeCell ref="D48:AT48"/>
-    <mergeCell ref="D86:R86"/>
     <mergeCell ref="AM51:AQ51"/>
     <mergeCell ref="O64:X64"/>
+    <mergeCell ref="D114:F115"/>
+    <mergeCell ref="O82:R82"/>
     <mergeCell ref="AO82:AS82"/>
-    <mergeCell ref="D99:M100"/>
+    <mergeCell ref="D94:AT95"/>
     <mergeCell ref="AJ29:AP29"/>
     <mergeCell ref="Z19:AI19"/>
     <mergeCell ref="D29:J29"/>
-    <mergeCell ref="D113:F114"/>
+    <mergeCell ref="AK80:AN80"/>
     <mergeCell ref="G27:AF27"/>
-    <mergeCell ref="O99:AT100"/>
-    <mergeCell ref="O90:X90"/>
-    <mergeCell ref="D87:R87"/>
     <mergeCell ref="S86:W86"/>
     <mergeCell ref="D70:AT71"/>
     <mergeCell ref="D27:F28"/>
     <mergeCell ref="L30:R31"/>
     <mergeCell ref="L32:R32"/>
     <mergeCell ref="T29:Z29"/>
+    <mergeCell ref="D110:N110"/>
     <mergeCell ref="AO83:AS83"/>
+    <mergeCell ref="O112:AT112"/>
     <mergeCell ref="D46:M46"/>
     <mergeCell ref="G16:X16"/>
     <mergeCell ref="AB32:AH32"/>
-    <mergeCell ref="D82:R82"/>
+    <mergeCell ref="Z83:AJ83"/>
     <mergeCell ref="Z34:AT34"/>
     <mergeCell ref="AJ30:AP31"/>
     <mergeCell ref="AK18:AT18"/>
     <mergeCell ref="R49:X49"/>
     <mergeCell ref="D21:M21"/>
     <mergeCell ref="L50:P50"/>
+    <mergeCell ref="G97:AB97"/>
     <mergeCell ref="D49:J49"/>
     <mergeCell ref="AO84:AS84"/>
     <mergeCell ref="O21:AT21"/>
     <mergeCell ref="O35:X35"/>
     <mergeCell ref="AK58:AT58"/>
+    <mergeCell ref="AK79:AN79"/>
     <mergeCell ref="O109:AT109"/>
     <mergeCell ref="L49:P49"/>
+    <mergeCell ref="S79:W79"/>
     <mergeCell ref="O43:X43"/>
+    <mergeCell ref="D89:AT90"/>
     <mergeCell ref="S88:W88"/>
     <mergeCell ref="D116:AT116"/>
     <mergeCell ref="Z51:AF51"/>
-    <mergeCell ref="D79:W79"/>
+    <mergeCell ref="AK81:AN81"/>
+    <mergeCell ref="D79:N79"/>
+    <mergeCell ref="Z80:AJ80"/>
+    <mergeCell ref="D88:N88"/>
     <mergeCell ref="G56:T56"/>
     <mergeCell ref="O42:X42"/>
     <mergeCell ref="S81:W81"/>
     <mergeCell ref="D58:M58"/>
+    <mergeCell ref="D81:N81"/>
+    <mergeCell ref="O85:R85"/>
     <mergeCell ref="AK6:AT6"/>
     <mergeCell ref="D42:M42"/>
-    <mergeCell ref="Z83:AN83"/>
     <mergeCell ref="D76:M77"/>
     <mergeCell ref="D35:M35"/>
     <mergeCell ref="Z65:AI65"/>
@@ -4301,79 +4337,88 @@
     <mergeCell ref="D40:F41"/>
     <mergeCell ref="G40:AH40"/>
     <mergeCell ref="D34:M34"/>
-    <mergeCell ref="D107:N107"/>
+    <mergeCell ref="O86:R86"/>
     <mergeCell ref="AK42:AT42"/>
     <mergeCell ref="D18:X18"/>
     <mergeCell ref="Q50:U50"/>
+    <mergeCell ref="D99:M99"/>
     <mergeCell ref="T32:Z32"/>
     <mergeCell ref="AB29:AH29"/>
     <mergeCell ref="O6:X6"/>
     <mergeCell ref="Z35:AT35"/>
+    <mergeCell ref="O83:R83"/>
     <mergeCell ref="D22:M22"/>
     <mergeCell ref="D13:AT14"/>
     <mergeCell ref="L51:P51"/>
-    <mergeCell ref="D105:F106"/>
     <mergeCell ref="D45:M45"/>
+    <mergeCell ref="Z82:AJ82"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="AK43:AT43"/>
     <mergeCell ref="AH51:AL51"/>
     <mergeCell ref="S84:W84"/>
-    <mergeCell ref="Z80:AN80"/>
-    <mergeCell ref="D88:R88"/>
     <mergeCell ref="O7:X8"/>
-    <mergeCell ref="G105:X105"/>
     <mergeCell ref="D24:AT25"/>
     <mergeCell ref="D32:J32"/>
+    <mergeCell ref="G114:AF114"/>
+    <mergeCell ref="D83:N83"/>
     <mergeCell ref="Z59:AI60"/>
-    <mergeCell ref="D81:R81"/>
     <mergeCell ref="AM50:AQ50"/>
-    <mergeCell ref="G113:AF113"/>
     <mergeCell ref="A30:B48"/>
+    <mergeCell ref="D85:N85"/>
+    <mergeCell ref="Z84:AJ84"/>
     <mergeCell ref="O58:X58"/>
     <mergeCell ref="O11:X11"/>
     <mergeCell ref="Z7:AI8"/>
     <mergeCell ref="D64:M64"/>
+    <mergeCell ref="O81:R81"/>
+    <mergeCell ref="D80:N80"/>
     <mergeCell ref="AO81:AS81"/>
-    <mergeCell ref="D98:M98"/>
     <mergeCell ref="Z46:AI46"/>
     <mergeCell ref="O22:AT23"/>
     <mergeCell ref="D50:J50"/>
-    <mergeCell ref="O98:AT98"/>
-    <mergeCell ref="Z82:AN82"/>
-    <mergeCell ref="O107:AT107"/>
+    <mergeCell ref="D117:AT117"/>
     <mergeCell ref="Q51:U51"/>
+    <mergeCell ref="Z81:AJ81"/>
     <mergeCell ref="O34:X34"/>
     <mergeCell ref="D67:AT67"/>
-    <mergeCell ref="D96:F97"/>
+    <mergeCell ref="AK82:AN82"/>
     <mergeCell ref="D10:M10"/>
     <mergeCell ref="O59:X60"/>
-    <mergeCell ref="D90:M90"/>
+    <mergeCell ref="O100:AT101"/>
     <mergeCell ref="AN49:AT49"/>
     <mergeCell ref="AK59:AT60"/>
     <mergeCell ref="D65:M65"/>
+    <mergeCell ref="O92:X92"/>
+    <mergeCell ref="O99:AT99"/>
     <mergeCell ref="O45:X45"/>
-    <mergeCell ref="Z84:AN84"/>
+    <mergeCell ref="AK83:AN83"/>
     <mergeCell ref="D4:F5"/>
     <mergeCell ref="Z50:AF50"/>
     <mergeCell ref="D56:F57"/>
+    <mergeCell ref="G106:X106"/>
     <mergeCell ref="Z43:AI43"/>
     <mergeCell ref="D53:AT54"/>
     <mergeCell ref="D11:M11"/>
     <mergeCell ref="O65:X65"/>
     <mergeCell ref="S83:W83"/>
+    <mergeCell ref="D118:AT119"/>
+    <mergeCell ref="D97:F98"/>
+    <mergeCell ref="O84:R84"/>
     <mergeCell ref="D30:J31"/>
+    <mergeCell ref="D106:F107"/>
+    <mergeCell ref="D103:AT104"/>
     <mergeCell ref="D19:X19"/>
     <mergeCell ref="D37:AT38"/>
-    <mergeCell ref="D117:AT118"/>
+    <mergeCell ref="D82:N82"/>
     <mergeCell ref="D75:M75"/>
-    <mergeCell ref="D80:R80"/>
     <mergeCell ref="L29:R29"/>
     <mergeCell ref="S85:W85"/>
+    <mergeCell ref="D100:M101"/>
     <mergeCell ref="AF1:AT2"/>
     <mergeCell ref="AO85:AS85"/>
-    <mergeCell ref="D110:N110"/>
+    <mergeCell ref="O80:R80"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="37">
     <dataValidation sqref="Z19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$A$2:$A$5</formula1>
     </dataValidation>
@@ -4395,50 +4440,95 @@
     <dataValidation sqref="Z46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$G$2:$G$3</formula1>
     </dataValidation>
-    <dataValidation sqref="D80:R80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D80:N80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D81:R81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O80:R80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D81:N81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D82:R82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O81:R81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D82:N82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D83:R83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O82:R82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D83:N83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D84:R84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O83:R83" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D84:N84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D85:R85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O84:R84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D85:N85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D86:R86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O85:R85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D86:N86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D87:R87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O86:R86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D87:N87" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="D88:R88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O87:R87" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="D88:N88" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$H$2:$H$15</formula1>
     </dataValidation>
-    <dataValidation sqref="Z80:AN80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O88:R88" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AP$2:$AP$7</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z80:AJ80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation sqref="Z81:AN81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK80:AN80" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z81:AJ81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation sqref="Z82:AN82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK81:AN81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z82:AJ82" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation sqref="Z83:AN83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK82:AN82" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z83:AJ83" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation sqref="Z84:AN84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK83:AN83" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z84:AJ84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
     </dataValidation>
-    <dataValidation sqref="Z85:AN85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK84:AN84" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="Z85:AJ85" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>DADOS!$I$2:$I$9</formula1>
+    </dataValidation>
+    <dataValidation sqref="AK85:AN85" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="O degrau sai da régua do capítulo 16." type="list" errorStyle="stop">
+      <formula1>DADOS!$AQ$2:$AQ$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4507,7 +4597,7 @@
       <c r="A1" s="5" t="n"/>
       <c r="B1" s="5" t="n"/>
       <c r="C1" s="2" t="n"/>
-      <c r="D1" s="44" t="inlineStr">
+      <c r="D1" s="47" t="inlineStr">
         <is>
           <t>O CATÁLOGO — o que dá para comprar</t>
         </is>
@@ -4577,12 +4667,12 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="5" t="n"/>
-      <c r="D4" s="45" t="inlineStr">
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>TRAÇO</t>
         </is>
       </c>
-      <c r="U4" s="46" t="inlineStr">
+      <c r="U4" s="49" t="inlineStr">
         <is>
           <t>o corpo dela. Vale sempre, sem gastar ação.</t>
         </is>
@@ -4612,7 +4702,7 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="5" t="n"/>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="50" t="n">
         <v>2</v>
       </c>
       <c r="H6" s="25" t="inlineStr">
@@ -4630,7 +4720,7 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="5" t="n"/>
-      <c r="D7" s="48" t="n">
+      <c r="D7" s="51" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="29" t="inlineStr">
@@ -4638,7 +4728,7 @@
           <t>Nado</t>
         </is>
       </c>
-      <c r="P7" s="49" t="inlineStr">
+      <c r="P7" s="52" t="inlineStr">
         <is>
           <t>move na água sem penalidade. Rio, cisterna, tanque alagado de estação</t>
         </is>
@@ -4648,7 +4738,7 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="5" t="n"/>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="50" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="25" t="inlineStr">
@@ -4666,7 +4756,7 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
-      <c r="D9" s="48" t="n">
+      <c r="D9" s="51" t="n">
         <v>5</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
@@ -4674,7 +4764,7 @@
           <t>Faro</t>
         </is>
       </c>
-      <c r="P9" s="49" t="inlineStr">
+      <c r="P9" s="52" t="inlineStr">
         <is>
           <t>rastreia por cheiro e por energia. Pega rastro velho de horas</t>
         </is>
@@ -4684,7 +4774,7 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="5" t="n"/>
-      <c r="D10" s="47" t="n">
+      <c r="D10" s="50" t="n">
         <v>5</v>
       </c>
       <c r="H10" s="25" t="inlineStr">
@@ -4702,7 +4792,7 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
-      <c r="D11" s="48" t="n">
+      <c r="D11" s="51" t="n">
         <v>7</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
@@ -4710,7 +4800,7 @@
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="P11" s="49" t="inlineStr">
+      <c r="P11" s="52" t="inlineStr">
         <is>
           <t>ocupa espaço menor e passa por vão. Duto, grade de bueiro, folga embaixo da porta</t>
         </is>
@@ -4720,7 +4810,7 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="47" t="n">
+      <c r="D12" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H12" s="25" t="inlineStr">
@@ -4738,7 +4828,7 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="5" t="n"/>
-      <c r="D13" s="48" t="n">
+      <c r="D13" s="51" t="n">
         <v>8</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
@@ -4746,7 +4836,7 @@
           <t>Montaria</t>
         </is>
       </c>
-      <c r="P13" s="49" t="inlineStr">
+      <c r="P13" s="52" t="inlineStr">
         <is>
           <t>carrega uma pessoa ou mais, dependendo do tamanho</t>
         </is>
@@ -4756,7 +4846,7 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="47" t="n">
+      <c r="D14" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H14" s="25" t="inlineStr">
@@ -4774,7 +4864,7 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="n"/>
-      <c r="D15" s="48" t="n">
+      <c r="D15" s="51" t="n">
         <v>8</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
@@ -4782,7 +4872,7 @@
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="P15" s="49" t="inlineStr">
+      <c r="P15" s="52" t="inlineStr">
         <is>
           <t>surge do chão, fora do alcance de visão</t>
         </is>
@@ -4792,7 +4882,7 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="5" t="n"/>
-      <c r="D16" s="47" t="n">
+      <c r="D16" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H16" s="25" t="inlineStr">
@@ -4810,7 +4900,7 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="5" t="n"/>
-      <c r="D17" s="48" t="n">
+      <c r="D17" s="51" t="n">
         <v>8</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
@@ -4818,7 +4908,7 @@
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="P17" s="49" t="inlineStr">
+      <c r="P17" s="52" t="inlineStr">
         <is>
           <t>ocupa espaço maior e barra passagem</t>
         </is>
@@ -4828,7 +4918,7 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="47" t="n">
+      <c r="D18" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H18" s="25" t="inlineStr">
@@ -4942,12 +5032,12 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="45" t="inlineStr">
+      <c r="D21" s="48" t="inlineStr">
         <is>
           <t>COMANDO</t>
         </is>
       </c>
-      <c r="U21" s="46" t="inlineStr">
+      <c r="U21" s="49" t="inlineStr">
         <is>
           <t>o que ela faz quando você gasta a Ação Padrão comandando.</t>
         </is>
@@ -4977,7 +5067,7 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="5" t="n"/>
-      <c r="D23" s="47" t="n">
+      <c r="D23" s="50" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="25" t="inlineStr">
@@ -4995,7 +5085,7 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="5" t="n"/>
-      <c r="D24" s="48" t="n">
+      <c r="D24" s="51" t="n">
         <v>4</v>
       </c>
       <c r="H24" s="29" t="inlineStr">
@@ -5003,7 +5093,7 @@
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="P24" s="49" t="inlineStr">
+      <c r="P24" s="52" t="inlineStr">
         <is>
           <t>prende o alvo</t>
         </is>
@@ -5013,7 +5103,7 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="5" t="n"/>
-      <c r="D25" s="47" t="n">
+      <c r="D25" s="50" t="n">
         <v>4</v>
       </c>
       <c r="H25" s="25" t="inlineStr">
@@ -5031,7 +5121,7 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
-      <c r="D26" s="48" t="n">
+      <c r="D26" s="51" t="n">
         <v>4</v>
       </c>
       <c r="H26" s="29" t="inlineStr">
@@ -5039,7 +5129,7 @@
           <t>Buscar</t>
         </is>
       </c>
-      <c r="P26" s="49" t="inlineStr">
+      <c r="P26" s="52" t="inlineStr">
         <is>
           <t>pega um objeto, ou rastreia de forma ativa</t>
         </is>
@@ -5049,7 +5139,7 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="5" t="n"/>
-      <c r="D27" s="47" t="n">
+      <c r="D27" s="50" t="n">
         <v>4</v>
       </c>
       <c r="H27" s="25" t="inlineStr">
@@ -5067,7 +5157,7 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="5" t="n"/>
-      <c r="D28" s="48" t="n">
+      <c r="D28" s="51" t="n">
         <v>8</v>
       </c>
       <c r="H28" s="29" t="inlineStr">
@@ -5075,7 +5165,7 @@
           <t>Interpor</t>
         </is>
       </c>
-      <c r="P28" s="49" t="inlineStr">
+      <c r="P28" s="52" t="inlineStr">
         <is>
           <t>se põe entre você e o golpe. O corpo dela recebe o que ia em você</t>
         </is>
@@ -5085,7 +5175,7 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="5" t="n"/>
-      <c r="D29" s="47" t="n">
+      <c r="D29" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H29" s="25" t="inlineStr">
@@ -5199,12 +5289,12 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="5" t="n"/>
-      <c r="D32" s="45" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>INVENTAR O SEU</t>
         </is>
       </c>
-      <c r="U32" s="46" t="inlineStr">
+      <c r="U32" s="49" t="inlineStr">
         <is>
           <t>escreva o efeito, ache na régua o preço, e leve para o mestre aprovar</t>
         </is>
@@ -5224,7 +5314,7 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="5" t="n"/>
-      <c r="D34" s="47" t="n">
+      <c r="D34" s="50" t="n">
         <v>2</v>
       </c>
       <c r="H34" s="35" t="inlineStr">
@@ -5237,10 +5327,10 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="5" t="n"/>
-      <c r="D35" s="48" t="n">
+      <c r="D35" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="H35" s="49" t="inlineStr">
+      <c r="H35" s="52" t="inlineStr">
         <is>
           <t>muda o que ela comunica</t>
         </is>
@@ -5250,7 +5340,7 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="5" t="n"/>
-      <c r="D36" s="47" t="n">
+      <c r="D36" s="50" t="n">
         <v>5</v>
       </c>
       <c r="H36" s="35" t="inlineStr">
@@ -5263,10 +5353,10 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="5" t="n"/>
-      <c r="D37" s="48" t="n">
+      <c r="D37" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="H37" s="49" t="inlineStr">
+      <c r="H37" s="52" t="inlineStr">
         <is>
           <t>muda que espaço ela ocupa, a um passo de mexer no tabuleiro</t>
         </is>
@@ -5276,7 +5366,7 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="5" t="n"/>
-      <c r="D38" s="47" t="n">
+      <c r="D38" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H38" s="35" t="inlineStr">
@@ -5347,7 +5437,7 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="5" t="n"/>
-      <c r="D41" s="47" t="n">
+      <c r="D41" s="50" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="35" t="inlineStr">
@@ -5360,10 +5450,10 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="5" t="n"/>
-      <c r="D42" s="48" t="n">
+      <c r="D42" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="H42" s="49" t="inlineStr">
+      <c r="H42" s="52" t="inlineStr">
         <is>
           <t>faz uma coisa com um alvo ou um objeto</t>
         </is>
@@ -5373,7 +5463,7 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="5" t="n"/>
-      <c r="D43" s="47" t="n">
+      <c r="D43" s="50" t="n">
         <v>8</v>
       </c>
       <c r="H43" s="35" t="inlineStr">
@@ -5449,7 +5539,7 @@
           <t>dado de dano</t>
         </is>
       </c>
-      <c r="R46" s="50" t="inlineStr">
+      <c r="R46" s="53" t="inlineStr">
         <is>
           <t>o teto de uma Rotina já governa a saída. Um Traço que dê +1d6 não existe</t>
         </is>
@@ -5464,7 +5554,7 @@
           <t>qualquer coisa que cresça com refino</t>
         </is>
       </c>
-      <c r="R47" s="51" t="inlineStr">
+      <c r="R47" s="54" t="inlineStr">
         <is>
           <t>refino cresce muito mais rápido que a ficha dela, e ela passaria de você</t>
         </is>
@@ -5479,7 +5569,7 @@
           <t>atributo</t>
         </is>
       </c>
-      <c r="R48" s="50" t="inlineStr">
+      <c r="R48" s="53" t="inlineStr">
         <is>
           <t>os cinco já saem do arranjo dela, e comprar de novo é pagar duas vezes</t>
         </is>
@@ -5494,7 +5584,7 @@
           <t>Defesa, acerto ou vida direto</t>
         </is>
       </c>
-      <c r="R49" s="51" t="inlineStr">
+      <c r="R49" s="54" t="inlineStr">
         <is>
           <t>os três saem dos atributos dela</t>
         </is>
@@ -6335,7 +6425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN77"/>
+  <dimension ref="A1:AR92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6369,63 +6459,65 @@
     <col width="10" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="39" max="39"/>
     <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="52" t="inlineStr">
+      <c r="A1" s="55" t="inlineStr">
         <is>
           <t>tipos</t>
         </is>
       </c>
-      <c r="B1" s="52" t="inlineStr">
+      <c r="B1" s="55" t="inlineStr">
         <is>
           <t>trilhas</t>
         </is>
       </c>
-      <c r="C1" s="52" t="inlineStr">
+      <c r="C1" s="55" t="inlineStr">
         <is>
           <t>atributos</t>
         </is>
       </c>
-      <c r="D1" s="52" t="inlineStr">
+      <c r="D1" s="55" t="inlineStr">
         <is>
           <t>trs</t>
         </is>
       </c>
-      <c r="E1" s="52" t="inlineStr">
+      <c r="E1" s="55" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="F1" s="52" t="inlineStr">
+      <c r="F1" s="55" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="G1" s="52" t="inlineStr">
+      <c r="G1" s="55" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="H1" s="52" t="inlineStr">
+      <c r="H1" s="55" t="inlineStr">
         <is>
           <t>traco</t>
         </is>
       </c>
-      <c r="I1" s="52" t="inlineStr">
+      <c r="I1" s="55" t="inlineStr">
         <is>
           <t>comando</t>
         </is>
       </c>
       <c r="J1" s="5" t="n"/>
-      <c r="K1" s="52" t="inlineStr">
+      <c r="K1" s="55" t="inlineStr">
         <is>
           <t>tab_tipos</t>
         </is>
       </c>
       <c r="L1" s="5" t="n"/>
       <c r="M1" s="5" t="n"/>
-      <c r="N1" s="52" t="inlineStr">
+      <c r="N1" s="55" t="inlineStr">
         <is>
           <t>tab_trilhas</t>
         </is>
@@ -6435,21 +6527,21 @@
       <c r="Q1" s="5" t="n"/>
       <c r="R1" s="5" t="n"/>
       <c r="S1" s="5" t="n"/>
-      <c r="T1" s="52" t="inlineStr">
+      <c r="T1" s="55" t="inlineStr">
         <is>
           <t>tab_traco</t>
         </is>
       </c>
       <c r="U1" s="5" t="n"/>
       <c r="V1" s="5" t="n"/>
-      <c r="W1" s="52" t="inlineStr">
+      <c r="W1" s="55" t="inlineStr">
         <is>
           <t>tab_comando</t>
         </is>
       </c>
       <c r="X1" s="5" t="n"/>
       <c r="Y1" s="5" t="n"/>
-      <c r="Z1" s="52" t="inlineStr">
+      <c r="Z1" s="55" t="inlineStr">
         <is>
           <t>tab_investir</t>
         </is>
@@ -6457,7 +6549,7 @@
       <c r="AA1" s="5" t="n"/>
       <c r="AB1" s="5" t="n"/>
       <c r="AC1" s="5" t="n"/>
-      <c r="AD1" s="52" t="inlineStr">
+      <c r="AD1" s="55" t="inlineStr">
         <is>
           <t>tab_trs</t>
         </is>
@@ -6471,49 +6563,62 @@
       <c r="AK1" s="5" t="n"/>
       <c r="AL1" s="5" t="n"/>
       <c r="AM1" s="5" t="n"/>
+      <c r="AN1" s="5" t="n"/>
+      <c r="AO1" s="5" t="n"/>
+      <c r="AP1" s="55" t="inlineStr">
+        <is>
+          <t>degrau_traco</t>
+        </is>
+      </c>
+      <c r="AQ1" s="55" t="inlineStr">
+        <is>
+          <t>degrau_comando</t>
+        </is>
+      </c>
+      <c r="AR1" s="5" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="53" t="inlineStr">
+      <c r="A2" s="56" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="B2" s="53" t="inlineStr">
+      <c r="B2" s="56" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="C2" s="53" t="inlineStr">
+      <c r="C2" s="56" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="D2" s="53" t="inlineStr">
+      <c r="D2" s="56" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="E2" s="53" t="inlineStr">
+      <c r="E2" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F2" s="53" t="inlineStr">
+      <c r="F2" s="56" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
-      <c r="G2" s="53" t="inlineStr">
+      <c r="G2" s="56" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
-      <c r="H2" s="53" t="inlineStr">
+      <c r="H2" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I2" s="53" t="inlineStr">
+      <c r="I2" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6632,431 +6737,467 @@
           <t>campo</t>
         </is>
       </c>
-      <c r="AN2" s="54" t="inlineStr">
+      <c r="AN2" s="12" t="inlineStr">
         <is>
           <t>célula</t>
         </is>
       </c>
+      <c r="AO2" s="5" t="n"/>
+      <c r="AP2" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AQ2" s="56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AR2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="56" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="B3" s="53" t="inlineStr">
+      <c r="B3" s="56" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="56" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="D3" s="53" t="inlineStr">
+      <c r="D3" s="56" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="E3" s="53" t="inlineStr">
+      <c r="E3" s="56" t="inlineStr">
         <is>
           <t>Presa</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="56" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="G3" s="53" t="inlineStr">
+      <c r="G3" s="56" t="inlineStr">
         <is>
           <t>Destreza</t>
         </is>
       </c>
-      <c r="H3" s="53" t="inlineStr">
+      <c r="H3" s="56" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="I3" s="53" t="inlineStr">
+      <c r="I3" s="56" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
       <c r="J3" s="5" t="n"/>
-      <c r="K3" s="53" t="inlineStr">
+      <c r="K3" s="56" t="inlineStr">
         <is>
           <t>talismã</t>
         </is>
       </c>
-      <c r="L3" s="53" t="n">
+      <c r="L3" s="56" t="n">
         <v>1</v>
       </c>
       <c r="M3" s="5" t="n"/>
-      <c r="N3" s="53" t="inlineStr">
+      <c r="N3" s="56" t="inlineStr">
         <is>
           <t>Servo</t>
         </is>
       </c>
-      <c r="O3" s="53" t="n">
+      <c r="O3" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="53" t="n">
+      <c r="P3" s="56" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q3" s="53" t="inlineStr">
+      <c r="Q3" s="56" t="inlineStr">
         <is>
           <t>forte</t>
         </is>
       </c>
-      <c r="R3" s="53" t="n">
+      <c r="R3" s="56" t="n">
         <v>1</v>
       </c>
       <c r="S3" s="5" t="n"/>
-      <c r="T3" s="53" t="inlineStr">
+      <c r="T3" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U3" s="53" t="n">
+      <c r="U3" s="56" t="n">
         <v>0</v>
       </c>
       <c r="V3" s="5" t="n"/>
-      <c r="W3" s="53" t="inlineStr">
+      <c r="W3" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="X3" s="53" t="n">
+      <c r="X3" s="56" t="n">
         <v>0</v>
       </c>
       <c r="Y3" s="5" t="n"/>
-      <c r="Z3" s="53" t="n">
+      <c r="Z3" s="56" t="n">
         <v>2</v>
       </c>
-      <c r="AA3" s="53" t="inlineStr">
+      <c r="AA3" s="56" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
-      <c r="AB3" s="53" t="inlineStr">
+      <c r="AB3" s="56" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
       <c r="AC3" s="5" t="n"/>
-      <c r="AD3" s="53" t="inlineStr">
+      <c r="AD3" s="56" t="inlineStr">
         <is>
           <t>Físico</t>
         </is>
       </c>
-      <c r="AE3" s="53" t="inlineStr">
+      <c r="AE3" s="56" t="inlineStr">
         <is>
           <t>Força</t>
         </is>
       </c>
       <c r="AF3" s="5" t="n"/>
-      <c r="AG3" s="53" t="n">
+      <c r="AG3" s="56" t="n">
         <v>6</v>
       </c>
-      <c r="AH3" s="53" t="n">
+      <c r="AH3" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="AI3" s="53" t="n">
+      <c r="AI3" s="56" t="n">
         <v>1</v>
       </c>
       <c r="AJ3" s="5" t="n"/>
-      <c r="AK3" s="53">
+      <c r="AK3" s="56">
         <f>INVOCAÇÃO!$D$30</f>
         <v/>
       </c>
       <c r="AL3" s="5" t="n"/>
-      <c r="AM3" s="53" t="inlineStr">
+      <c r="AM3" s="56" t="inlineStr">
         <is>
           <t>nivel</t>
         </is>
       </c>
-      <c r="AN3" s="55" t="inlineStr">
+      <c r="AN3" s="56" t="inlineStr">
         <is>
           <t>D7</t>
         </is>
       </c>
+      <c r="AO3" s="5" t="n"/>
+      <c r="AP3" s="56" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ3" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="56" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="B4" s="53" t="inlineStr">
+      <c r="B4" s="56" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="56" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
-      <c r="D4" s="53" t="inlineStr">
+      <c r="D4" s="56" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="E4" s="53" t="inlineStr">
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>Parrudo</t>
         </is>
       </c>
       <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
-      <c r="H4" s="53" t="inlineStr">
+      <c r="H4" s="56" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="I4" s="53" t="inlineStr">
+      <c r="I4" s="56" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
       <c r="J4" s="5" t="n"/>
-      <c r="K4" s="53" t="inlineStr">
+      <c r="K4" s="56" t="inlineStr">
         <is>
           <t>corpo amaldiçoado</t>
         </is>
       </c>
-      <c r="L4" s="53" t="n">
+      <c r="L4" s="56" t="n">
         <v>1</v>
       </c>
       <c r="M4" s="5" t="n"/>
-      <c r="N4" s="53" t="inlineStr">
+      <c r="N4" s="56" t="inlineStr">
         <is>
           <t>Matilha</t>
         </is>
       </c>
-      <c r="O4" s="53" t="n">
+      <c r="O4" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="P4" s="53" t="n">
+      <c r="P4" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="53" t="inlineStr">
+      <c r="Q4" s="56" t="inlineStr">
         <is>
           <t>forte</t>
         </is>
       </c>
-      <c r="R4" s="53" t="n">
+      <c r="R4" s="56" t="n">
         <v>1.5</v>
       </c>
       <c r="S4" s="5" t="n"/>
-      <c r="T4" s="53" t="inlineStr">
+      <c r="T4" s="56" t="inlineStr">
         <is>
           <t>Escalada</t>
         </is>
       </c>
-      <c r="U4" s="53" t="n">
+      <c r="U4" s="56" t="n">
         <v>2</v>
       </c>
       <c r="V4" s="5" t="n"/>
-      <c r="W4" s="53" t="inlineStr">
+      <c r="W4" s="56" t="inlineStr">
         <is>
           <t>Investir</t>
         </is>
       </c>
-      <c r="X4" s="53" t="n">
+      <c r="X4" s="56" t="n">
         <v>0</v>
       </c>
       <c r="Y4" s="5" t="n"/>
-      <c r="Z4" s="53" t="n">
+      <c r="Z4" s="56" t="n">
         <v>5</v>
       </c>
-      <c r="AA4" s="53" t="inlineStr">
+      <c r="AA4" s="56" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
       </c>
-      <c r="AB4" s="53" t="inlineStr">
+      <c r="AB4" s="56" t="inlineStr">
         <is>
           <t>1d6</t>
         </is>
       </c>
       <c r="AC4" s="5" t="n"/>
-      <c r="AD4" s="53" t="inlineStr">
+      <c r="AD4" s="56" t="inlineStr">
         <is>
           <t>Vigor</t>
         </is>
       </c>
-      <c r="AE4" s="53" t="inlineStr">
+      <c r="AE4" s="56" t="inlineStr">
         <is>
           <t>Constituição</t>
         </is>
       </c>
       <c r="AF4" s="5" t="n"/>
-      <c r="AG4" s="53" t="n">
+      <c r="AG4" s="56" t="n">
         <v>10</v>
       </c>
-      <c r="AH4" s="53" t="n">
+      <c r="AH4" s="56" t="n">
         <v>18</v>
       </c>
-      <c r="AI4" s="53" t="n">
+      <c r="AI4" s="56" t="n">
         <v>5</v>
       </c>
       <c r="AJ4" s="5" t="n"/>
-      <c r="AK4" s="53">
+      <c r="AK4" s="56">
         <f>INVOCAÇÃO!$L$30</f>
         <v/>
       </c>
       <c r="AL4" s="5" t="n"/>
-      <c r="AM4" s="53" t="inlineStr">
+      <c r="AM4" s="56" t="inlineStr">
         <is>
           <t>ess_dono</t>
         </is>
       </c>
-      <c r="AN4" s="55" t="inlineStr">
+      <c r="AN4" s="56" t="inlineStr">
         <is>
           <t>O7</t>
         </is>
       </c>
+      <c r="AO4" s="5" t="n"/>
+      <c r="AP4" s="56" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" s="56" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="56" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="56" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="56" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="56" t="inlineStr">
         <is>
           <t>Voz</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
       <c r="G5" s="5" t="n"/>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="56" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="I5" s="56" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
       <c r="J5" s="5" t="n"/>
-      <c r="K5" s="53" t="inlineStr">
+      <c r="K5" s="56" t="inlineStr">
         <is>
           <t>técnica</t>
         </is>
       </c>
-      <c r="L5" s="53" t="n">
+      <c r="L5" s="56" t="n">
         <v>2</v>
       </c>
       <c r="M5" s="5" t="n"/>
-      <c r="N5" s="53" t="inlineStr">
+      <c r="N5" s="56" t="inlineStr">
         <is>
           <t>Coro</t>
         </is>
       </c>
-      <c r="O5" s="53" t="n">
+      <c r="O5" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="53" t="n">
+      <c r="P5" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="53" t="inlineStr">
+      <c r="Q5" s="56" t="inlineStr">
         <is>
           <t>cru</t>
         </is>
       </c>
-      <c r="R5" s="53" t="n">
+      <c r="R5" s="56" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="5" t="n"/>
-      <c r="T5" s="53" t="inlineStr">
+      <c r="T5" s="56" t="inlineStr">
         <is>
           <t>Nado</t>
         </is>
       </c>
-      <c r="U5" s="53" t="n">
+      <c r="U5" s="56" t="n">
         <v>2</v>
       </c>
       <c r="V5" s="5" t="n"/>
-      <c r="W5" s="53" t="inlineStr">
+      <c r="W5" s="56" t="inlineStr">
         <is>
           <t>Agarrar</t>
         </is>
       </c>
-      <c r="X5" s="53" t="n">
+      <c r="X5" s="56" t="n">
         <v>4</v>
       </c>
       <c r="Y5" s="5" t="n"/>
-      <c r="Z5" s="53" t="n">
+      <c r="Z5" s="56" t="n">
         <v>9</v>
       </c>
-      <c r="AA5" s="53" t="inlineStr">
+      <c r="AA5" s="56" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
       </c>
-      <c r="AB5" s="53" t="inlineStr">
+      <c r="AB5" s="56" t="inlineStr">
         <is>
           <t>2d6</t>
         </is>
       </c>
       <c r="AC5" s="5" t="n"/>
-      <c r="AD5" s="53" t="inlineStr">
+      <c r="AD5" s="56" t="inlineStr">
         <is>
           <t>Intelecto</t>
         </is>
       </c>
-      <c r="AE5" s="53" t="inlineStr">
+      <c r="AE5" s="56" t="inlineStr">
         <is>
           <t>Inteligência</t>
         </is>
       </c>
       <c r="AF5" s="5" t="n"/>
-      <c r="AG5" s="53" t="n">
+      <c r="AG5" s="56" t="n">
         <v>14</v>
       </c>
-      <c r="AH5" s="53" t="n">
+      <c r="AH5" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="AI5" s="53" t="n">
+      <c r="AI5" s="56" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" s="5" t="n"/>
-      <c r="AK5" s="53">
+      <c r="AK5" s="56">
         <f>INVOCAÇÃO!$T$30</f>
         <v/>
       </c>
       <c r="AL5" s="5" t="n"/>
-      <c r="AM5" s="53" t="inlineStr">
+      <c r="AM5" s="56" t="inlineStr">
         <is>
           <t>int_dono</t>
         </is>
       </c>
-      <c r="AN5" s="55" t="inlineStr">
+      <c r="AN5" s="56" t="inlineStr">
         <is>
           <t>Z7</t>
         </is>
       </c>
+      <c r="AO5" s="5" t="n"/>
+      <c r="AP5" s="56" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ5" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
@@ -7065,23 +7206,23 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
       <c r="G6" s="5" t="n"/>
-      <c r="H6" s="53" t="inlineStr">
+      <c r="H6" s="56" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="I6" s="53" t="inlineStr">
+      <c r="I6" s="56" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
       <c r="J6" s="5" t="n"/>
-      <c r="K6" s="53" t="inlineStr">
+      <c r="K6" s="56" t="inlineStr">
         <is>
           <t>maldição domada</t>
         </is>
       </c>
-      <c r="L6" s="53" t="n">
+      <c r="L6" s="56" t="n">
         <v>3</v>
       </c>
       <c r="M6" s="5" t="n"/>
@@ -7091,72 +7232,78 @@
       <c r="Q6" s="5" t="n"/>
       <c r="R6" s="5" t="n"/>
       <c r="S6" s="5" t="n"/>
-      <c r="T6" s="53" t="inlineStr">
+      <c r="T6" s="56" t="inlineStr">
         <is>
           <t>Fala</t>
         </is>
       </c>
-      <c r="U6" s="53" t="n">
+      <c r="U6" s="56" t="n">
         <v>3</v>
       </c>
       <c r="V6" s="5" t="n"/>
-      <c r="W6" s="53" t="inlineStr">
+      <c r="W6" s="56" t="inlineStr">
         <is>
           <t>Arrastar</t>
         </is>
       </c>
-      <c r="X6" s="53" t="n">
+      <c r="X6" s="56" t="n">
         <v>4</v>
       </c>
       <c r="Y6" s="5" t="n"/>
-      <c r="Z6" s="53" t="n">
+      <c r="Z6" s="56" t="n">
         <v>13</v>
       </c>
-      <c r="AA6" s="53" t="inlineStr">
+      <c r="AA6" s="56" t="inlineStr">
         <is>
           <t>8d6</t>
         </is>
       </c>
-      <c r="AB6" s="53" t="inlineStr">
+      <c r="AB6" s="56" t="inlineStr">
         <is>
           <t>3d6</t>
         </is>
       </c>
       <c r="AC6" s="5" t="n"/>
-      <c r="AD6" s="53" t="inlineStr">
+      <c r="AD6" s="56" t="inlineStr">
         <is>
           <t>Espírito</t>
         </is>
       </c>
-      <c r="AE6" s="53" t="inlineStr">
+      <c r="AE6" s="56" t="inlineStr">
         <is>
           <t>Essência</t>
         </is>
       </c>
       <c r="AF6" s="5" t="n"/>
-      <c r="AG6" s="53" t="n">
+      <c r="AG6" s="56" t="n">
         <v>18</v>
       </c>
       <c r="AH6" s="5" t="n"/>
-      <c r="AI6" s="53" t="n">
+      <c r="AI6" s="56" t="n">
         <v>13</v>
       </c>
       <c r="AJ6" s="5" t="n"/>
-      <c r="AK6" s="53">
+      <c r="AK6" s="56">
         <f>INVOCAÇÃO!$AB$30</f>
         <v/>
       </c>
       <c r="AL6" s="5" t="n"/>
-      <c r="AM6" s="53" t="inlineStr">
+      <c r="AM6" s="56" t="inlineStr">
         <is>
           <t>maestria</t>
         </is>
       </c>
-      <c r="AN6" s="55" t="inlineStr">
+      <c r="AN6" s="56" t="inlineStr">
         <is>
           <t>AK7</t>
         </is>
       </c>
+      <c r="AO6" s="5" t="n"/>
+      <c r="AP6" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ6" s="5" t="n"/>
+      <c r="AR6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -7166,12 +7313,12 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n"/>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="H7" s="56" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="I7" s="53" t="inlineStr">
+      <c r="I7" s="56" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
@@ -7186,33 +7333,33 @@
       <c r="Q7" s="5" t="n"/>
       <c r="R7" s="5" t="n"/>
       <c r="S7" s="5" t="n"/>
-      <c r="T7" s="53" t="inlineStr">
+      <c r="T7" s="56" t="inlineStr">
         <is>
           <t>Faro</t>
         </is>
       </c>
-      <c r="U7" s="53" t="n">
+      <c r="U7" s="56" t="n">
         <v>5</v>
       </c>
       <c r="V7" s="5" t="n"/>
-      <c r="W7" s="53" t="inlineStr">
+      <c r="W7" s="56" t="inlineStr">
         <is>
           <t>Buscar</t>
         </is>
       </c>
-      <c r="X7" s="53" t="n">
+      <c r="X7" s="56" t="n">
         <v>4</v>
       </c>
       <c r="Y7" s="5" t="n"/>
-      <c r="Z7" s="53" t="n">
+      <c r="Z7" s="56" t="n">
         <v>17</v>
       </c>
-      <c r="AA7" s="53" t="inlineStr">
+      <c r="AA7" s="56" t="inlineStr">
         <is>
           <t>10d6</t>
         </is>
       </c>
-      <c r="AB7" s="53" t="inlineStr">
+      <c r="AB7" s="56" t="inlineStr">
         <is>
           <t>4d6</t>
         </is>
@@ -7221,29 +7368,35 @@
       <c r="AD7" s="5" t="n"/>
       <c r="AE7" s="5" t="n"/>
       <c r="AF7" s="5" t="n"/>
-      <c r="AG7" s="53" t="n">
+      <c r="AG7" s="56" t="n">
         <v>22</v>
       </c>
       <c r="AH7" s="5" t="n"/>
-      <c r="AI7" s="53" t="n">
+      <c r="AI7" s="56" t="n">
         <v>17</v>
       </c>
       <c r="AJ7" s="5" t="n"/>
-      <c r="AK7" s="53">
+      <c r="AK7" s="56">
         <f>INVOCAÇÃO!$AJ$30</f>
         <v/>
       </c>
       <c r="AL7" s="5" t="n"/>
-      <c r="AM7" s="53" t="inlineStr">
+      <c r="AM7" s="56" t="inlineStr">
         <is>
           <t>marcos</t>
         </is>
       </c>
-      <c r="AN7" s="55" t="inlineStr">
+      <c r="AN7" s="56" t="inlineStr">
         <is>
           <t>D11</t>
         </is>
       </c>
+      <c r="AO7" s="5" t="n"/>
+      <c r="AP7" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" s="5" t="n"/>
+      <c r="AR7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -7253,12 +7406,12 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
       <c r="G8" s="5" t="n"/>
-      <c r="H8" s="53" t="inlineStr">
+      <c r="H8" s="56" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="I8" s="56" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
@@ -7273,33 +7426,33 @@
       <c r="Q8" s="5" t="n"/>
       <c r="R8" s="5" t="n"/>
       <c r="S8" s="5" t="n"/>
-      <c r="T8" s="53" t="inlineStr">
+      <c r="T8" s="56" t="inlineStr">
         <is>
           <t>Vigia</t>
         </is>
       </c>
-      <c r="U8" s="53" t="n">
+      <c r="U8" s="56" t="n">
         <v>5</v>
       </c>
       <c r="V8" s="5" t="n"/>
-      <c r="W8" s="53" t="inlineStr">
+      <c r="W8" s="56" t="inlineStr">
         <is>
           <t>Cavar</t>
         </is>
       </c>
-      <c r="X8" s="53" t="n">
+      <c r="X8" s="56" t="n">
         <v>4</v>
       </c>
       <c r="Y8" s="5" t="n"/>
-      <c r="Z8" s="53" t="n">
+      <c r="Z8" s="56" t="n">
         <v>21</v>
       </c>
-      <c r="AA8" s="53" t="inlineStr">
+      <c r="AA8" s="56" t="inlineStr">
         <is>
           <t>13d6</t>
         </is>
       </c>
-      <c r="AB8" s="53" t="inlineStr">
+      <c r="AB8" s="56" t="inlineStr">
         <is>
           <t>5d6</t>
         </is>
@@ -7308,26 +7461,30 @@
       <c r="AD8" s="5" t="n"/>
       <c r="AE8" s="5" t="n"/>
       <c r="AF8" s="5" t="n"/>
-      <c r="AG8" s="53" t="n">
+      <c r="AG8" s="56" t="n">
         <v>26</v>
       </c>
       <c r="AH8" s="5" t="n"/>
-      <c r="AI8" s="53" t="n">
+      <c r="AI8" s="56" t="n">
         <v>21</v>
       </c>
       <c r="AJ8" s="5" t="n"/>
       <c r="AK8" s="5" t="n"/>
       <c r="AL8" s="5" t="n"/>
-      <c r="AM8" s="53" t="inlineStr">
+      <c r="AM8" s="56" t="inlineStr">
         <is>
           <t>classe</t>
         </is>
       </c>
-      <c r="AN8" s="55" t="inlineStr">
+      <c r="AN8" s="56" t="inlineStr">
         <is>
           <t>O11</t>
         </is>
       </c>
+      <c r="AO8" s="5" t="n"/>
+      <c r="AP8" s="5" t="n"/>
+      <c r="AQ8" s="5" t="n"/>
+      <c r="AR8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -7337,12 +7494,12 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="56" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="I9" s="53" t="inlineStr">
+      <c r="I9" s="56" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
@@ -7357,33 +7514,33 @@
       <c r="Q9" s="5" t="n"/>
       <c r="R9" s="5" t="n"/>
       <c r="S9" s="5" t="n"/>
-      <c r="T9" s="53" t="inlineStr">
+      <c r="T9" s="56" t="inlineStr">
         <is>
           <t>Miúdo</t>
         </is>
       </c>
-      <c r="U9" s="53" t="n">
+      <c r="U9" s="56" t="n">
         <v>7</v>
       </c>
       <c r="V9" s="5" t="n"/>
-      <c r="W9" s="53" t="inlineStr">
+      <c r="W9" s="56" t="inlineStr">
         <is>
           <t>Interpor</t>
         </is>
       </c>
-      <c r="X9" s="53" t="n">
+      <c r="X9" s="56" t="n">
         <v>8</v>
       </c>
       <c r="Y9" s="5" t="n"/>
-      <c r="Z9" s="53" t="n">
+      <c r="Z9" s="56" t="n">
         <v>26</v>
       </c>
-      <c r="AA9" s="53" t="inlineStr">
+      <c r="AA9" s="56" t="inlineStr">
         <is>
           <t>15d6</t>
         </is>
       </c>
-      <c r="AB9" s="53" t="inlineStr">
+      <c r="AB9" s="56" t="inlineStr">
         <is>
           <t>6d6</t>
         </is>
@@ -7392,26 +7549,30 @@
       <c r="AD9" s="5" t="n"/>
       <c r="AE9" s="5" t="n"/>
       <c r="AF9" s="5" t="n"/>
-      <c r="AG9" s="53" t="n">
+      <c r="AG9" s="56" t="n">
         <v>30</v>
       </c>
       <c r="AH9" s="5" t="n"/>
-      <c r="AI9" s="53" t="n">
+      <c r="AI9" s="56" t="n">
         <v>26</v>
       </c>
       <c r="AJ9" s="5" t="n"/>
       <c r="AK9" s="5" t="n"/>
       <c r="AL9" s="5" t="n"/>
-      <c r="AM9" s="53" t="inlineStr">
+      <c r="AM9" s="56" t="inlineStr">
         <is>
           <t>nome</t>
         </is>
       </c>
-      <c r="AN9" s="55" t="inlineStr">
+      <c r="AN9" s="56" t="inlineStr">
         <is>
           <t>D19</t>
         </is>
       </c>
+      <c r="AO9" s="5" t="n"/>
+      <c r="AP9" s="5" t="n"/>
+      <c r="AQ9" s="5" t="n"/>
+      <c r="AR9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -7421,7 +7582,7 @@
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
       <c r="G10" s="5" t="n"/>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="56" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
@@ -7437,21 +7598,21 @@
       <c r="Q10" s="5" t="n"/>
       <c r="R10" s="5" t="n"/>
       <c r="S10" s="5" t="n"/>
-      <c r="T10" s="53" t="inlineStr">
+      <c r="T10" s="56" t="inlineStr">
         <is>
           <t>Voo</t>
         </is>
       </c>
-      <c r="U10" s="53" t="n">
+      <c r="U10" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V10" s="5" t="n"/>
-      <c r="W10" s="53" t="inlineStr">
+      <c r="W10" s="56" t="inlineStr">
         <is>
           <t>Chamariz</t>
         </is>
       </c>
-      <c r="X10" s="53" t="n">
+      <c r="X10" s="56" t="n">
         <v>8</v>
       </c>
       <c r="Y10" s="5" t="n"/>
@@ -7468,16 +7629,20 @@
       <c r="AJ10" s="5" t="n"/>
       <c r="AK10" s="5" t="n"/>
       <c r="AL10" s="5" t="n"/>
-      <c r="AM10" s="53" t="inlineStr">
+      <c r="AM10" s="56" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="AN10" s="55" t="inlineStr">
+      <c r="AN10" s="56" t="inlineStr">
         <is>
           <t>Z19</t>
         </is>
       </c>
+      <c r="AO10" s="5" t="n"/>
+      <c r="AP10" s="5" t="n"/>
+      <c r="AQ10" s="5" t="n"/>
+      <c r="AR10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -7487,7 +7652,7 @@
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="5" t="n"/>
-      <c r="H11" s="53" t="inlineStr">
+      <c r="H11" s="56" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
@@ -7503,12 +7668,12 @@
       <c r="Q11" s="5" t="n"/>
       <c r="R11" s="5" t="n"/>
       <c r="S11" s="5" t="n"/>
-      <c r="T11" s="53" t="inlineStr">
+      <c r="T11" s="56" t="inlineStr">
         <is>
           <t>Montaria</t>
         </is>
       </c>
-      <c r="U11" s="53" t="n">
+      <c r="U11" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V11" s="5" t="n"/>
@@ -7528,16 +7693,20 @@
       <c r="AJ11" s="5" t="n"/>
       <c r="AK11" s="5" t="n"/>
       <c r="AL11" s="5" t="n"/>
-      <c r="AM11" s="53" t="inlineStr">
+      <c r="AM11" s="56" t="inlineStr">
         <is>
           <t>trilha</t>
         </is>
       </c>
-      <c r="AN11" s="55" t="inlineStr">
+      <c r="AN11" s="56" t="inlineStr">
         <is>
           <t>AK19</t>
         </is>
       </c>
+      <c r="AO11" s="5" t="n"/>
+      <c r="AP11" s="5" t="n"/>
+      <c r="AQ11" s="5" t="n"/>
+      <c r="AR11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -7547,7 +7716,7 @@
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="53" t="inlineStr">
+      <c r="H12" s="56" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
@@ -7563,12 +7732,12 @@
       <c r="Q12" s="5" t="n"/>
       <c r="R12" s="5" t="n"/>
       <c r="S12" s="5" t="n"/>
-      <c r="T12" s="53" t="inlineStr">
+      <c r="T12" s="56" t="inlineStr">
         <is>
           <t>Fisgada</t>
         </is>
       </c>
-      <c r="U12" s="53" t="n">
+      <c r="U12" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V12" s="5" t="n"/>
@@ -7588,16 +7757,20 @@
       <c r="AJ12" s="5" t="n"/>
       <c r="AK12" s="5" t="n"/>
       <c r="AL12" s="5" t="n"/>
-      <c r="AM12" s="53" t="inlineStr">
+      <c r="AM12" s="56" t="inlineStr">
         <is>
           <t>sintonia</t>
         </is>
       </c>
-      <c r="AN12" s="55" t="inlineStr">
+      <c r="AN12" s="56" t="inlineStr">
         <is>
           <t>D22</t>
         </is>
       </c>
+      <c r="AO12" s="5" t="n"/>
+      <c r="AP12" s="5" t="n"/>
+      <c r="AQ12" s="5" t="n"/>
+      <c r="AR12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -7607,7 +7780,7 @@
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
       <c r="G13" s="5" t="n"/>
-      <c r="H13" s="53" t="inlineStr">
+      <c r="H13" s="56" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
@@ -7623,12 +7796,12 @@
       <c r="Q13" s="5" t="n"/>
       <c r="R13" s="5" t="n"/>
       <c r="S13" s="5" t="n"/>
-      <c r="T13" s="53" t="inlineStr">
+      <c r="T13" s="56" t="inlineStr">
         <is>
           <t>Emboscada</t>
         </is>
       </c>
-      <c r="U13" s="53" t="n">
+      <c r="U13" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V13" s="5" t="n"/>
@@ -7648,16 +7821,20 @@
       <c r="AJ13" s="5" t="n"/>
       <c r="AK13" s="5" t="n"/>
       <c r="AL13" s="5" t="n"/>
-      <c r="AM13" s="53" t="inlineStr">
+      <c r="AM13" s="56" t="inlineStr">
         <is>
           <t>pontos_atributo</t>
         </is>
       </c>
-      <c r="AN13" s="55" t="inlineStr">
+      <c r="AN13" s="56" t="inlineStr">
         <is>
           <t>D35</t>
         </is>
       </c>
+      <c r="AO13" s="5" t="n"/>
+      <c r="AP13" s="5" t="n"/>
+      <c r="AQ13" s="5" t="n"/>
+      <c r="AR13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -7667,7 +7844,7 @@
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
       <c r="G14" s="5" t="n"/>
-      <c r="H14" s="53" t="inlineStr">
+      <c r="H14" s="56" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
@@ -7683,12 +7860,12 @@
       <c r="Q14" s="5" t="n"/>
       <c r="R14" s="5" t="n"/>
       <c r="S14" s="5" t="n"/>
-      <c r="T14" s="53" t="inlineStr">
+      <c r="T14" s="56" t="inlineStr">
         <is>
           <t>Jorro</t>
         </is>
       </c>
-      <c r="U14" s="53" t="n">
+      <c r="U14" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V14" s="5" t="n"/>
@@ -7708,16 +7885,20 @@
       <c r="AJ14" s="5" t="n"/>
       <c r="AK14" s="5" t="n"/>
       <c r="AL14" s="5" t="n"/>
-      <c r="AM14" s="53" t="inlineStr">
+      <c r="AM14" s="56" t="inlineStr">
         <is>
           <t>pontos_disp</t>
         </is>
       </c>
-      <c r="AN14" s="55" t="inlineStr">
+      <c r="AN14" s="56" t="inlineStr">
         <is>
           <t>O35</t>
         </is>
       </c>
+      <c r="AO14" s="5" t="n"/>
+      <c r="AP14" s="5" t="n"/>
+      <c r="AQ14" s="5" t="n"/>
+      <c r="AR14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -7727,7 +7908,7 @@
       <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
-      <c r="H15" s="53" t="inlineStr">
+      <c r="H15" s="56" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
@@ -7743,12 +7924,12 @@
       <c r="Q15" s="5" t="n"/>
       <c r="R15" s="5" t="n"/>
       <c r="S15" s="5" t="n"/>
-      <c r="T15" s="53" t="inlineStr">
+      <c r="T15" s="56" t="inlineStr">
         <is>
           <t>Graúdo</t>
         </is>
       </c>
-      <c r="U15" s="53" t="n">
+      <c r="U15" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V15" s="5" t="n"/>
@@ -7768,16 +7949,20 @@
       <c r="AJ15" s="5" t="n"/>
       <c r="AK15" s="5" t="n"/>
       <c r="AL15" s="5" t="n"/>
-      <c r="AM15" s="53" t="inlineStr">
+      <c r="AM15" s="56" t="inlineStr">
         <is>
           <t>aviso_atributo</t>
         </is>
       </c>
-      <c r="AN15" s="55" t="inlineStr">
+      <c r="AN15" s="56" t="inlineStr">
         <is>
           <t>Z35</t>
         </is>
       </c>
+      <c r="AO15" s="5" t="n"/>
+      <c r="AP15" s="5" t="n"/>
+      <c r="AQ15" s="5" t="n"/>
+      <c r="AR15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -7799,12 +7984,12 @@
       <c r="Q16" s="5" t="n"/>
       <c r="R16" s="5" t="n"/>
       <c r="S16" s="5" t="n"/>
-      <c r="T16" s="53" t="inlineStr">
+      <c r="T16" s="56" t="inlineStr">
         <is>
           <t>Remoto</t>
         </is>
       </c>
-      <c r="U16" s="53" t="n">
+      <c r="U16" s="56" t="n">
         <v>8</v>
       </c>
       <c r="V16" s="5" t="n"/>
@@ -7824,16 +8009,20 @@
       <c r="AJ16" s="5" t="n"/>
       <c r="AK16" s="5" t="n"/>
       <c r="AL16" s="5" t="n"/>
-      <c r="AM16" s="53" t="inlineStr">
+      <c r="AM16" s="56" t="inlineStr">
         <is>
           <t>atr_acerto</t>
         </is>
       </c>
-      <c r="AN16" s="55" t="inlineStr">
+      <c r="AN16" s="56" t="inlineStr">
         <is>
           <t>D43</t>
         </is>
       </c>
+      <c r="AO16" s="5" t="n"/>
+      <c r="AP16" s="5" t="n"/>
+      <c r="AQ16" s="5" t="n"/>
+      <c r="AR16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -7874,16 +8063,20 @@
       <c r="AJ17" s="5" t="n"/>
       <c r="AK17" s="5" t="n"/>
       <c r="AL17" s="5" t="n"/>
-      <c r="AM17" s="53" t="inlineStr">
+      <c r="AM17" s="56" t="inlineStr">
         <is>
           <t>acerto</t>
         </is>
       </c>
-      <c r="AN17" s="55" t="inlineStr">
+      <c r="AN17" s="56" t="inlineStr">
         <is>
           <t>O43</t>
         </is>
       </c>
+      <c r="AO17" s="5" t="n"/>
+      <c r="AP17" s="5" t="n"/>
+      <c r="AQ17" s="5" t="n"/>
+      <c r="AR17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="n"/>
@@ -7924,16 +8117,20 @@
       <c r="AJ18" s="5" t="n"/>
       <c r="AK18" s="5" t="n"/>
       <c r="AL18" s="5" t="n"/>
-      <c r="AM18" s="53" t="inlineStr">
+      <c r="AM18" s="56" t="inlineStr">
         <is>
           <t>defesa_de</t>
         </is>
       </c>
-      <c r="AN18" s="55" t="inlineStr">
+      <c r="AN18" s="56" t="inlineStr">
         <is>
           <t>Z43</t>
         </is>
       </c>
+      <c r="AO18" s="5" t="n"/>
+      <c r="AP18" s="5" t="n"/>
+      <c r="AQ18" s="5" t="n"/>
+      <c r="AR18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -7974,16 +8171,20 @@
       <c r="AJ19" s="5" t="n"/>
       <c r="AK19" s="5" t="n"/>
       <c r="AL19" s="5" t="n"/>
-      <c r="AM19" s="53" t="inlineStr">
+      <c r="AM19" s="56" t="inlineStr">
         <is>
           <t>defesa</t>
         </is>
       </c>
-      <c r="AN19" s="55" t="inlineStr">
+      <c r="AN19" s="56" t="inlineStr">
         <is>
           <t>AK43</t>
         </is>
       </c>
+      <c r="AO19" s="5" t="n"/>
+      <c r="AP19" s="5" t="n"/>
+      <c r="AQ19" s="5" t="n"/>
+      <c r="AR19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -8024,16 +8225,20 @@
       <c r="AJ20" s="5" t="n"/>
       <c r="AK20" s="5" t="n"/>
       <c r="AL20" s="5" t="n"/>
-      <c r="AM20" s="53" t="inlineStr">
+      <c r="AM20" s="56" t="inlineStr">
         <is>
           <t>critico</t>
         </is>
       </c>
-      <c r="AN20" s="55" t="inlineStr">
+      <c r="AN20" s="56" t="inlineStr">
         <is>
           <t>D46</t>
         </is>
       </c>
+      <c r="AO20" s="5" t="n"/>
+      <c r="AP20" s="5" t="n"/>
+      <c r="AQ20" s="5" t="n"/>
+      <c r="AR20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n"/>
@@ -8074,16 +8279,20 @@
       <c r="AJ21" s="5" t="n"/>
       <c r="AK21" s="5" t="n"/>
       <c r="AL21" s="5" t="n"/>
-      <c r="AM21" s="53" t="inlineStr">
+      <c r="AM21" s="56" t="inlineStr">
         <is>
           <t>tr_treinado</t>
         </is>
       </c>
-      <c r="AN21" s="55" t="inlineStr">
+      <c r="AN21" s="56" t="inlineStr">
         <is>
           <t>O46</t>
         </is>
       </c>
+      <c r="AO21" s="5" t="n"/>
+      <c r="AP21" s="5" t="n"/>
+      <c r="AQ21" s="5" t="n"/>
+      <c r="AR21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n"/>
@@ -8124,16 +8333,20 @@
       <c r="AJ22" s="5" t="n"/>
       <c r="AK22" s="5" t="n"/>
       <c r="AL22" s="5" t="n"/>
-      <c r="AM22" s="53" t="inlineStr">
+      <c r="AM22" s="56" t="inlineStr">
         <is>
           <t>fisico_de</t>
         </is>
       </c>
-      <c r="AN22" s="55" t="inlineStr">
+      <c r="AN22" s="56" t="inlineStr">
         <is>
           <t>Z46</t>
         </is>
       </c>
+      <c r="AO22" s="5" t="n"/>
+      <c r="AP22" s="5" t="n"/>
+      <c r="AQ22" s="5" t="n"/>
+      <c r="AR22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -8174,16 +8387,20 @@
       <c r="AJ23" s="5" t="n"/>
       <c r="AK23" s="5" t="n"/>
       <c r="AL23" s="5" t="n"/>
-      <c r="AM23" s="53" t="inlineStr">
+      <c r="AM23" s="56" t="inlineStr">
         <is>
           <t>tr_Físico</t>
         </is>
       </c>
-      <c r="AN23" s="55" t="inlineStr">
+      <c r="AN23" s="56" t="inlineStr">
         <is>
           <t>Q50</t>
         </is>
       </c>
+      <c r="AO23" s="5" t="n"/>
+      <c r="AP23" s="5" t="n"/>
+      <c r="AQ23" s="5" t="n"/>
+      <c r="AR23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -8224,16 +8441,20 @@
       <c r="AJ24" s="5" t="n"/>
       <c r="AK24" s="5" t="n"/>
       <c r="AL24" s="5" t="n"/>
-      <c r="AM24" s="53" t="inlineStr">
+      <c r="AM24" s="56" t="inlineStr">
         <is>
           <t>tr_extra_Físico</t>
         </is>
       </c>
-      <c r="AN24" s="55" t="inlineStr">
+      <c r="AN24" s="56" t="inlineStr">
         <is>
           <t>K50</t>
         </is>
       </c>
+      <c r="AO24" s="5" t="n"/>
+      <c r="AP24" s="5" t="n"/>
+      <c r="AQ24" s="5" t="n"/>
+      <c r="AR24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n"/>
@@ -8274,16 +8495,20 @@
       <c r="AJ25" s="5" t="n"/>
       <c r="AK25" s="5" t="n"/>
       <c r="AL25" s="5" t="n"/>
-      <c r="AM25" s="53" t="inlineStr">
+      <c r="AM25" s="56" t="inlineStr">
         <is>
           <t>tr_Vigor</t>
         </is>
       </c>
-      <c r="AN25" s="55" t="inlineStr">
+      <c r="AN25" s="56" t="inlineStr">
         <is>
           <t>AM50</t>
         </is>
       </c>
+      <c r="AO25" s="5" t="n"/>
+      <c r="AP25" s="5" t="n"/>
+      <c r="AQ25" s="5" t="n"/>
+      <c r="AR25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="n"/>
@@ -8324,16 +8549,20 @@
       <c r="AJ26" s="5" t="n"/>
       <c r="AK26" s="5" t="n"/>
       <c r="AL26" s="5" t="n"/>
-      <c r="AM26" s="53" t="inlineStr">
+      <c r="AM26" s="56" t="inlineStr">
         <is>
           <t>tr_extra_Vigor</t>
         </is>
       </c>
-      <c r="AN26" s="55" t="inlineStr">
+      <c r="AN26" s="56" t="inlineStr">
         <is>
           <t>AG50</t>
         </is>
       </c>
+      <c r="AO26" s="5" t="n"/>
+      <c r="AP26" s="5" t="n"/>
+      <c r="AQ26" s="5" t="n"/>
+      <c r="AR26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -8374,16 +8603,20 @@
       <c r="AJ27" s="5" t="n"/>
       <c r="AK27" s="5" t="n"/>
       <c r="AL27" s="5" t="n"/>
-      <c r="AM27" s="53" t="inlineStr">
+      <c r="AM27" s="56" t="inlineStr">
         <is>
           <t>tr_Intelecto</t>
         </is>
       </c>
-      <c r="AN27" s="55" t="inlineStr">
+      <c r="AN27" s="56" t="inlineStr">
         <is>
           <t>Q51</t>
         </is>
       </c>
+      <c r="AO27" s="5" t="n"/>
+      <c r="AP27" s="5" t="n"/>
+      <c r="AQ27" s="5" t="n"/>
+      <c r="AR27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -8424,16 +8657,20 @@
       <c r="AJ28" s="5" t="n"/>
       <c r="AK28" s="5" t="n"/>
       <c r="AL28" s="5" t="n"/>
-      <c r="AM28" s="53" t="inlineStr">
+      <c r="AM28" s="56" t="inlineStr">
         <is>
           <t>tr_extra_Intelecto</t>
         </is>
       </c>
-      <c r="AN28" s="55" t="inlineStr">
+      <c r="AN28" s="56" t="inlineStr">
         <is>
           <t>K51</t>
         </is>
       </c>
+      <c r="AO28" s="5" t="n"/>
+      <c r="AP28" s="5" t="n"/>
+      <c r="AQ28" s="5" t="n"/>
+      <c r="AR28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n"/>
@@ -8474,16 +8711,20 @@
       <c r="AJ29" s="5" t="n"/>
       <c r="AK29" s="5" t="n"/>
       <c r="AL29" s="5" t="n"/>
-      <c r="AM29" s="53" t="inlineStr">
+      <c r="AM29" s="56" t="inlineStr">
         <is>
           <t>tr_Espírito</t>
         </is>
       </c>
-      <c r="AN29" s="55" t="inlineStr">
+      <c r="AN29" s="56" t="inlineStr">
         <is>
           <t>AM51</t>
         </is>
       </c>
+      <c r="AO29" s="5" t="n"/>
+      <c r="AP29" s="5" t="n"/>
+      <c r="AQ29" s="5" t="n"/>
+      <c r="AR29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="n"/>
@@ -8524,578 +8765,762 @@
       <c r="AJ30" s="5" t="n"/>
       <c r="AK30" s="5" t="n"/>
       <c r="AL30" s="5" t="n"/>
-      <c r="AM30" s="53" t="inlineStr">
+      <c r="AM30" s="56" t="inlineStr">
         <is>
           <t>tr_extra_Espírito</t>
         </is>
       </c>
-      <c r="AN30" s="55" t="inlineStr">
+      <c r="AN30" s="56" t="inlineStr">
         <is>
           <t>AG51</t>
         </is>
       </c>
+      <c r="AO30" s="5" t="n"/>
+      <c r="AP30" s="5" t="n"/>
+      <c r="AQ30" s="5" t="n"/>
+      <c r="AR30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="AM31" s="55" t="inlineStr">
+      <c r="AM31" s="57" t="inlineStr">
         <is>
           <t>vida_max</t>
         </is>
       </c>
-      <c r="AN31" s="55" t="inlineStr">
+      <c r="AN31" s="57" t="inlineStr">
         <is>
           <t>D59</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="AM32" s="55" t="inlineStr">
+      <c r="AM32" s="57" t="inlineStr">
         <is>
           <t>vida</t>
         </is>
       </c>
-      <c r="AN32" s="55" t="inlineStr">
+      <c r="AN32" s="57" t="inlineStr">
         <is>
           <t>O59</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="AM33" s="55" t="inlineStr">
+      <c r="AM33" s="57" t="inlineStr">
         <is>
           <t>corpos</t>
         </is>
       </c>
-      <c r="AN33" s="55" t="inlineStr">
+      <c r="AN33" s="57" t="inlineStr">
         <is>
           <t>Z59</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="AM34" s="55" t="inlineStr">
+      <c r="AM34" s="57" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="AN34" s="55" t="inlineStr">
+      <c r="AN34" s="57" t="inlineStr">
         <is>
           <t>AK59</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="AM35" s="55" t="inlineStr">
+      <c r="AM35" s="57" t="inlineStr">
         <is>
           <t>regua</t>
         </is>
       </c>
-      <c r="AN35" s="55" t="inlineStr">
+      <c r="AN35" s="57" t="inlineStr">
         <is>
           <t>D65</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="AM36" s="55" t="inlineStr">
+      <c r="AM36" s="57" t="inlineStr">
         <is>
           <t>meia_regua</t>
         </is>
       </c>
-      <c r="AN36" s="55" t="inlineStr">
+      <c r="AN36" s="57" t="inlineStr">
         <is>
           <t>O65</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="AM37" s="55" t="inlineStr">
+      <c r="AM37" s="57" t="inlineStr">
         <is>
           <t>volta_com</t>
         </is>
       </c>
-      <c r="AN37" s="55" t="inlineStr">
+      <c r="AN37" s="57" t="inlineStr">
         <is>
           <t>Z65</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="AM38" s="55" t="inlineStr">
+      <c r="AM38" s="57" t="inlineStr">
         <is>
           <t>orcamento</t>
         </is>
       </c>
-      <c r="AN38" s="55" t="inlineStr">
+      <c r="AN38" s="57" t="inlineStr">
         <is>
           <t>D76</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="AM39" s="55" t="inlineStr">
+      <c r="AM39" s="57" t="inlineStr">
         <is>
           <t>gasto</t>
         </is>
       </c>
-      <c r="AN39" s="55" t="inlineStr">
-        <is>
-          <t>D91</t>
+      <c r="AN39" s="57" t="inlineStr">
+        <is>
+          <t>D92</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="AM40" s="55" t="inlineStr">
+      <c r="AM40" s="57" t="inlineStr">
         <is>
           <t>sobra</t>
         </is>
       </c>
-      <c r="AN40" s="55" t="inlineStr">
-        <is>
-          <t>O91</t>
+      <c r="AN40" s="57" t="inlineStr">
+        <is>
+          <t>O92</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="AM41" s="55" t="inlineStr">
+      <c r="AM41" s="57" t="inlineStr">
         <is>
           <t>investir</t>
         </is>
       </c>
-      <c r="AN41" s="55" t="inlineStr">
-        <is>
-          <t>D99</t>
+      <c r="AN41" s="57" t="inlineStr">
+        <is>
+          <t>D100</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="AM42" s="55" t="inlineStr">
+      <c r="AM42" s="57" t="inlineStr">
         <is>
           <t>cd_pendente</t>
         </is>
       </c>
-      <c r="AN42" s="55" t="inlineStr">
-        <is>
-          <t>D116</t>
+      <c r="AN42" s="57" t="inlineStr">
+        <is>
+          <t>D117</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="AM43" s="55" t="inlineStr">
+      <c r="AM43" s="57" t="inlineStr">
         <is>
           <t>atr_Força</t>
         </is>
       </c>
-      <c r="AN43" s="55" t="inlineStr">
+      <c r="AN43" s="57" t="inlineStr">
         <is>
           <t>D30</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="AM44" s="55" t="inlineStr">
+      <c r="AM44" s="57" t="inlineStr">
         <is>
           <t>atr_Destreza</t>
         </is>
       </c>
-      <c r="AN44" s="55" t="inlineStr">
+      <c r="AN44" s="57" t="inlineStr">
         <is>
           <t>L30</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="AM45" s="55" t="inlineStr">
+      <c r="AM45" s="57" t="inlineStr">
         <is>
           <t>atr_Constituição</t>
         </is>
       </c>
-      <c r="AN45" s="55" t="inlineStr">
+      <c r="AN45" s="57" t="inlineStr">
         <is>
           <t>T30</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="AM46" s="55" t="inlineStr">
+      <c r="AM46" s="57" t="inlineStr">
         <is>
           <t>atr_Inteligência</t>
         </is>
       </c>
-      <c r="AN46" s="55" t="inlineStr">
+      <c r="AN46" s="57" t="inlineStr">
         <is>
           <t>AB30</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="AM47" s="55" t="inlineStr">
+      <c r="AM47" s="57" t="inlineStr">
         <is>
           <t>atr_Essência</t>
         </is>
       </c>
-      <c r="AN47" s="55" t="inlineStr">
+      <c r="AN47" s="57" t="inlineStr">
         <is>
           <t>AJ30</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="AM48" s="55" t="inlineStr">
+      <c r="AM48" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_1</t>
         </is>
       </c>
-      <c r="AN48" s="55" t="inlineStr">
+      <c r="AN48" s="57" t="inlineStr">
         <is>
           <t>S80</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="AM49" s="55" t="inlineStr">
+      <c r="AM49" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_2</t>
         </is>
       </c>
-      <c r="AN49" s="55" t="inlineStr">
+      <c r="AN49" s="57" t="inlineStr">
         <is>
           <t>S81</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="AM50" s="55" t="inlineStr">
+      <c r="AM50" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_3</t>
         </is>
       </c>
-      <c r="AN50" s="55" t="inlineStr">
+      <c r="AN50" s="57" t="inlineStr">
         <is>
           <t>S82</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="AM51" s="55" t="inlineStr">
+      <c r="AM51" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_4</t>
         </is>
       </c>
-      <c r="AN51" s="55" t="inlineStr">
+      <c r="AN51" s="57" t="inlineStr">
         <is>
           <t>S83</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="AM52" s="55" t="inlineStr">
+      <c r="AM52" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_5</t>
         </is>
       </c>
-      <c r="AN52" s="55" t="inlineStr">
+      <c r="AN52" s="57" t="inlineStr">
         <is>
           <t>S84</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="AM53" s="55" t="inlineStr">
+      <c r="AM53" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_6</t>
         </is>
       </c>
-      <c r="AN53" s="55" t="inlineStr">
+      <c r="AN53" s="57" t="inlineStr">
         <is>
           <t>S85</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="AM54" s="55" t="inlineStr">
+      <c r="AM54" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_7</t>
         </is>
       </c>
-      <c r="AN54" s="55" t="inlineStr">
+      <c r="AN54" s="57" t="inlineStr">
         <is>
           <t>S86</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="AM55" s="55" t="inlineStr">
+      <c r="AM55" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_8</t>
         </is>
       </c>
-      <c r="AN55" s="55" t="inlineStr">
+      <c r="AN55" s="57" t="inlineStr">
         <is>
           <t>S87</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="AM56" s="55" t="inlineStr">
+      <c r="AM56" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_9</t>
         </is>
       </c>
-      <c r="AN56" s="55" t="inlineStr">
+      <c r="AN56" s="57" t="inlineStr">
         <is>
           <t>S88</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="AM57" s="55" t="inlineStr">
+      <c r="AM57" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_10</t>
         </is>
       </c>
-      <c r="AN57" s="55" t="inlineStr">
+      <c r="AN57" s="57" t="inlineStr">
         <is>
           <t>AO80</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="AM58" s="55" t="inlineStr">
+      <c r="AM58" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_11</t>
         </is>
       </c>
-      <c r="AN58" s="55" t="inlineStr">
+      <c r="AN58" s="57" t="inlineStr">
         <is>
           <t>AO81</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="AM59" s="55" t="inlineStr">
+      <c r="AM59" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_12</t>
         </is>
       </c>
-      <c r="AN59" s="55" t="inlineStr">
+      <c r="AN59" s="57" t="inlineStr">
         <is>
           <t>AO82</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="AM60" s="55" t="inlineStr">
+      <c r="AM60" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_13</t>
         </is>
       </c>
-      <c r="AN60" s="55" t="inlineStr">
+      <c r="AN60" s="57" t="inlineStr">
         <is>
           <t>AO83</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="AM61" s="55" t="inlineStr">
+      <c r="AM61" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_14</t>
         </is>
       </c>
-      <c r="AN61" s="55" t="inlineStr">
+      <c r="AN61" s="57" t="inlineStr">
         <is>
           <t>AO84</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="AM62" s="55" t="inlineStr">
+      <c r="AM62" s="57" t="inlineStr">
         <is>
           <t>slot_pontos_15</t>
         </is>
       </c>
-      <c r="AN62" s="55" t="inlineStr">
+      <c r="AN62" s="57" t="inlineStr">
         <is>
           <t>AO85</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="AM63" s="55" t="inlineStr">
+      <c r="AM63" s="57" t="inlineStr">
         <is>
           <t>traco_1</t>
         </is>
       </c>
-      <c r="AN63" s="55" t="inlineStr">
+      <c r="AN63" s="57" t="inlineStr">
         <is>
           <t>D80</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="AM64" s="55" t="inlineStr">
+      <c r="AM64" s="57" t="inlineStr">
         <is>
           <t>traco_2</t>
         </is>
       </c>
-      <c r="AN64" s="55" t="inlineStr">
+      <c r="AN64" s="57" t="inlineStr">
         <is>
           <t>D81</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="AM65" s="55" t="inlineStr">
+      <c r="AM65" s="57" t="inlineStr">
         <is>
           <t>traco_3</t>
         </is>
       </c>
-      <c r="AN65" s="55" t="inlineStr">
+      <c r="AN65" s="57" t="inlineStr">
         <is>
           <t>D82</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="AM66" s="55" t="inlineStr">
+      <c r="AM66" s="57" t="inlineStr">
         <is>
           <t>traco_4</t>
         </is>
       </c>
-      <c r="AN66" s="55" t="inlineStr">
+      <c r="AN66" s="57" t="inlineStr">
         <is>
           <t>D83</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="AM67" s="55" t="inlineStr">
+      <c r="AM67" s="57" t="inlineStr">
         <is>
           <t>traco_5</t>
         </is>
       </c>
-      <c r="AN67" s="55" t="inlineStr">
+      <c r="AN67" s="57" t="inlineStr">
         <is>
           <t>D84</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="AM68" s="55" t="inlineStr">
+      <c r="AM68" s="57" t="inlineStr">
         <is>
           <t>traco_6</t>
         </is>
       </c>
-      <c r="AN68" s="55" t="inlineStr">
+      <c r="AN68" s="57" t="inlineStr">
         <is>
           <t>D85</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="AM69" s="55" t="inlineStr">
+      <c r="AM69" s="57" t="inlineStr">
         <is>
           <t>traco_7</t>
         </is>
       </c>
-      <c r="AN69" s="55" t="inlineStr">
+      <c r="AN69" s="57" t="inlineStr">
         <is>
           <t>D86</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="AM70" s="55" t="inlineStr">
+      <c r="AM70" s="57" t="inlineStr">
         <is>
           <t>traco_8</t>
         </is>
       </c>
-      <c r="AN70" s="55" t="inlineStr">
+      <c r="AN70" s="57" t="inlineStr">
         <is>
           <t>D87</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="AM71" s="55" t="inlineStr">
+      <c r="AM71" s="57" t="inlineStr">
         <is>
           <t>traco_9</t>
         </is>
       </c>
-      <c r="AN71" s="55" t="inlineStr">
+      <c r="AN71" s="57" t="inlineStr">
         <is>
           <t>D88</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="AM72" s="55" t="inlineStr">
+      <c r="AM72" s="57" t="inlineStr">
         <is>
           <t>comando_1</t>
         </is>
       </c>
-      <c r="AN72" s="55" t="inlineStr">
+      <c r="AN72" s="57" t="inlineStr">
         <is>
           <t>Z80</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="AM73" s="55" t="inlineStr">
+      <c r="AM73" s="57" t="inlineStr">
         <is>
           <t>comando_2</t>
         </is>
       </c>
-      <c r="AN73" s="55" t="inlineStr">
+      <c r="AN73" s="57" t="inlineStr">
         <is>
           <t>Z81</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="AM74" s="55" t="inlineStr">
+      <c r="AM74" s="57" t="inlineStr">
         <is>
           <t>comando_3</t>
         </is>
       </c>
-      <c r="AN74" s="55" t="inlineStr">
+      <c r="AN74" s="57" t="inlineStr">
         <is>
           <t>Z82</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="AM75" s="55" t="inlineStr">
+      <c r="AM75" s="57" t="inlineStr">
         <is>
           <t>comando_4</t>
         </is>
       </c>
-      <c r="AN75" s="55" t="inlineStr">
+      <c r="AN75" s="57" t="inlineStr">
         <is>
           <t>Z83</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="AM76" s="55" t="inlineStr">
+      <c r="AM76" s="57" t="inlineStr">
         <is>
           <t>comando_5</t>
         </is>
       </c>
-      <c r="AN76" s="55" t="inlineStr">
+      <c r="AN76" s="57" t="inlineStr">
         <is>
           <t>Z84</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="AM77" s="55" t="inlineStr">
+      <c r="AM77" s="57" t="inlineStr">
         <is>
           <t>comando_6</t>
         </is>
       </c>
-      <c r="AN77" s="55" t="inlineStr">
+      <c r="AN77" s="57" t="inlineStr">
         <is>
           <t>Z85</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="AM78" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_1</t>
+        </is>
+      </c>
+      <c r="AN78" s="57" t="inlineStr">
+        <is>
+          <t>O80</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="AM79" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_2</t>
+        </is>
+      </c>
+      <c r="AN79" s="57" t="inlineStr">
+        <is>
+          <t>O81</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="AM80" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_3</t>
+        </is>
+      </c>
+      <c r="AN80" s="57" t="inlineStr">
+        <is>
+          <t>O82</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="AM81" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_4</t>
+        </is>
+      </c>
+      <c r="AN81" s="57" t="inlineStr">
+        <is>
+          <t>O83</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="AM82" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_5</t>
+        </is>
+      </c>
+      <c r="AN82" s="57" t="inlineStr">
+        <is>
+          <t>O84</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="AM83" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_6</t>
+        </is>
+      </c>
+      <c r="AN83" s="57" t="inlineStr">
+        <is>
+          <t>O85</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="AM84" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_7</t>
+        </is>
+      </c>
+      <c r="AN84" s="57" t="inlineStr">
+        <is>
+          <t>O86</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="AM85" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_8</t>
+        </is>
+      </c>
+      <c r="AN85" s="57" t="inlineStr">
+        <is>
+          <t>O87</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="AM86" s="57" t="inlineStr">
+        <is>
+          <t>degrau_traco_9</t>
+        </is>
+      </c>
+      <c r="AN86" s="57" t="inlineStr">
+        <is>
+          <t>O88</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="AM87" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_1</t>
+        </is>
+      </c>
+      <c r="AN87" s="57" t="inlineStr">
+        <is>
+          <t>AK80</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="AM88" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_2</t>
+        </is>
+      </c>
+      <c r="AN88" s="57" t="inlineStr">
+        <is>
+          <t>AK81</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="AM89" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_3</t>
+        </is>
+      </c>
+      <c r="AN89" s="57" t="inlineStr">
+        <is>
+          <t>AK82</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="AM90" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_4</t>
+        </is>
+      </c>
+      <c r="AN90" s="57" t="inlineStr">
+        <is>
+          <t>AK83</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="AM91" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_5</t>
+        </is>
+      </c>
+      <c r="AN91" s="57" t="inlineStr">
+        <is>
+          <t>AK84</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="AM92" s="57" t="inlineStr">
+        <is>
+          <t>degrau_comando_6</t>
+        </is>
+      </c>
+      <c r="AN92" s="57" t="inlineStr">
+        <is>
+          <t>AK85</t>
         </is>
       </c>
     </row>

--- a/ficha-invocacao/ficha-invocacao.xlsx
+++ b/ficha-invocacao/ficha-invocacao.xlsx
@@ -2478,7 +2478,7 @@
       <c r="B59" s="1" t="n"/>
       <c r="C59" s="5" t="n"/>
       <c r="D59" s="9">
-        <f>IF($Z$19="","",IF(IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,4,FALSE),"cru")="forte",FLOOR(2.5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+2*$D$7)+$T$30*$D$7,1),(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))+IF($D$22="Parrudo",5*$AK$7,0))</f>
+        <f>IF($Z$19="","",FLOOR(IFERROR(VLOOKUP($AK$19,DADOS!$N$3:$R$5,4,FALSE),1)*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+2*$D$7)+$T$30*$D$7,1)+IF($D$22="Parrudo",5*$AK$7,0))</f>
         <v/>
       </c>
       <c r="N59" s="5" t="n"/>
@@ -2650,12 +2650,12 @@
       <c r="B65" s="1" t="n"/>
       <c r="C65" s="5" t="n"/>
       <c r="D65" s="10">
-        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7))</f>
+        <f>IF($Z$19="","",$D$59)</f>
         <v/>
       </c>
       <c r="N65" s="5" t="n"/>
       <c r="O65" s="10">
-        <f>IF($Z$19="","",5*(IFERROR(VLOOKUP($Z$19,DADOS!$K$3:$L$6,2,FALSE),0)+(2+$T$30)*$D$7)/2)</f>
+        <f>IF($Z$19="","",$D$59/2)</f>
         <v/>
       </c>
       <c r="Y65" s="5" t="n"/>
@@ -2739,7 +2739,7 @@
       <c r="C68" s="5" t="n"/>
       <c r="D68" s="35" t="inlineStr">
         <is>
-          <t>quando o dano que passar de zero for maior que a metade da régua, ou quando um golpe só causar a régua inteira. Fora desses dois casos ela só cai, e você reinvoca.</t>
+          <t>quando um golpe só causar a régua inteira, ou quando o dano que passar de zero for maior que a metade da régua. A régua é a vida máxima dela. Área nunca destrói: ela derruba como qualquer dano. Fora desses dois casos ela só cai, e você reinvoca.</t>
         </is>
       </c>
     </row>
@@ -6822,10 +6822,8 @@
       <c r="P3" s="56" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q3" s="56" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
+      <c r="Q3" s="56" t="n">
+        <v>2.5</v>
       </c>
       <c r="R3" s="56" t="n">
         <v>1</v>
@@ -6967,10 +6965,8 @@
       <c r="P4" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" s="56" t="inlineStr">
-        <is>
-          <t>forte</t>
-        </is>
+      <c r="Q4" s="56" t="n">
+        <v>2.5</v>
       </c>
       <c r="R4" s="56" t="n">
         <v>1.5</v>
@@ -7108,10 +7104,8 @@
       <c r="P5" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="56" t="inlineStr">
-        <is>
-          <t>cru</t>
-        </is>
+      <c r="Q5" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="R5" s="56" t="n">
         <v>1</v>
